--- a/QUADROS ABNT.xlsx
+++ b/QUADROS ABNT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Desktop\DOCUMENTOS APROVAÇÃO EMPREEDIMENTOS\DOCUMENTOS INCIAIS\5 - QUADROS ABNT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81D461C6-3676-468C-838A-607A299BDD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6740D1-A7EA-4142-B3C7-42CC07421633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="976" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'QUADRO VII'!$A$1:$M$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2320,7 +2319,7 @@
     </xf>
     <xf numFmtId="9" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="498">
+  <cellXfs count="502">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3302,82 +3301,18 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3397,188 +3332,208 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="39" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
     <xf numFmtId="39" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="39" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="39" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3587,44 +3542,50 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3665,59 +3626,109 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="39" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4046,15 +4057,15 @@
   <sheetData>
     <row r="1" spans="1:9" ht="40.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A1" s="168"/>
-      <c r="B1" s="366" t="s">
+      <c r="B1" s="338" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="367"/>
-      <c r="D1" s="367"/>
-      <c r="E1" s="367"/>
-      <c r="F1" s="367"/>
-      <c r="G1" s="367"/>
-      <c r="H1" s="367"/>
+      <c r="C1" s="339"/>
+      <c r="D1" s="339"/>
+      <c r="E1" s="339"/>
+      <c r="F1" s="339"/>
+      <c r="G1" s="339"/>
+      <c r="H1" s="339"/>
       <c r="I1" s="169"/>
     </row>
     <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4071,15 +4082,15 @@
       <c r="B3" s="178" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="368" t="s">
+      <c r="C3" s="340" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="365"/>
-      <c r="E3" s="365"/>
-      <c r="F3" s="365"/>
-      <c r="G3" s="365"/>
-      <c r="H3" s="365"/>
-      <c r="I3" s="369"/>
+      <c r="D3" s="334"/>
+      <c r="E3" s="334"/>
+      <c r="F3" s="334"/>
+      <c r="G3" s="334"/>
+      <c r="H3" s="334"/>
+      <c r="I3" s="341"/>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="170"/>
@@ -4124,32 +4135,32 @@
     </row>
     <row r="7" spans="1:9" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="170"/>
-      <c r="B7" s="370" t="s">
+      <c r="B7" s="342" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="371"/>
-      <c r="D7" s="377" t="s">
+      <c r="C7" s="343"/>
+      <c r="D7" s="348" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="379" t="s">
+      <c r="E7" s="349" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="380" t="s">
+      <c r="F7" s="335" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="374" t="s">
+      <c r="G7" s="346" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="375"/>
+      <c r="H7" s="347"/>
       <c r="I7" s="171"/>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="170"/>
-      <c r="B8" s="372"/>
-      <c r="C8" s="373"/>
-      <c r="D8" s="378"/>
-      <c r="E8" s="378"/>
-      <c r="F8" s="378"/>
+      <c r="B8" s="344"/>
+      <c r="C8" s="345"/>
+      <c r="D8" s="336"/>
+      <c r="E8" s="336"/>
+      <c r="F8" s="336"/>
       <c r="G8" s="177" t="s">
         <v>45</v>
       </c>
@@ -4215,17 +4226,17 @@
       <c r="I10" s="171"/>
     </row>
     <row r="11" spans="1:9" ht="38.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="170"/>
-      <c r="B11" s="376" t="s">
+      <c r="A11" s="500" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="365"/>
-      <c r="D11" s="365"/>
-      <c r="E11" s="365"/>
-      <c r="F11" s="365"/>
-      <c r="G11" s="365"/>
-      <c r="H11" s="365"/>
-      <c r="I11" s="171"/>
+      <c r="B11" s="395"/>
+      <c r="C11" s="395"/>
+      <c r="D11" s="395"/>
+      <c r="E11" s="395"/>
+      <c r="F11" s="395"/>
+      <c r="G11" s="395"/>
+      <c r="H11" s="395"/>
+      <c r="I11" s="501"/>
     </row>
     <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="170"/>
@@ -4233,42 +4244,42 @@
     </row>
     <row r="13" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="170"/>
-      <c r="B13" s="376" t="s">
+      <c r="B13" s="337" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="365"/>
-      <c r="D13" s="365"/>
-      <c r="E13" s="365"/>
-      <c r="F13" s="365"/>
-      <c r="G13" s="365"/>
-      <c r="H13" s="365"/>
+      <c r="C13" s="334"/>
+      <c r="D13" s="334"/>
+      <c r="E13" s="334"/>
+      <c r="F13" s="334"/>
+      <c r="G13" s="334"/>
+      <c r="H13" s="334"/>
       <c r="I13" s="171"/>
     </row>
     <row r="14" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="170"/>
-      <c r="B14" s="364" t="s">
+      <c r="A14" s="498" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="365"/>
-      <c r="D14" s="365"/>
-      <c r="E14" s="365"/>
-      <c r="F14" s="365"/>
-      <c r="G14" s="365"/>
-      <c r="H14" s="365"/>
-      <c r="I14" s="171"/>
+      <c r="B14" s="333"/>
+      <c r="C14" s="333"/>
+      <c r="D14" s="333"/>
+      <c r="E14" s="333"/>
+      <c r="F14" s="333"/>
+      <c r="G14" s="333"/>
+      <c r="H14" s="333"/>
+      <c r="I14" s="499"/>
     </row>
     <row r="15" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="170"/>
-      <c r="B15" s="364" t="s">
+      <c r="A15" s="498" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="365"/>
-      <c r="D15" s="365"/>
-      <c r="E15" s="365"/>
-      <c r="F15" s="365"/>
-      <c r="G15" s="365"/>
-      <c r="H15" s="365"/>
-      <c r="I15" s="171"/>
+      <c r="B15" s="333"/>
+      <c r="C15" s="333"/>
+      <c r="D15" s="333"/>
+      <c r="E15" s="333"/>
+      <c r="F15" s="333"/>
+      <c r="G15" s="333"/>
+      <c r="H15" s="333"/>
+      <c r="I15" s="499"/>
     </row>
     <row r="16" spans="1:9" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="172"/>
@@ -4285,10 +4296,7 @@
     <row r="18" ht="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B15:H15"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B14:H14"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="B7:C8"/>
@@ -4296,6 +4304,9 @@
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <pageMargins left="1.181102362204725" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait"/>
@@ -4323,65 +4334,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="355"/>
-      <c r="C1" s="356"/>
-      <c r="D1" s="356"/>
-      <c r="E1" s="356"/>
-      <c r="F1" s="356"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="356"/>
-      <c r="I1" s="356"/>
-      <c r="J1" s="356"/>
-      <c r="K1" s="356"/>
-      <c r="L1" s="356"/>
+      <c r="B1" s="364"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
+      <c r="K1" s="365"/>
+      <c r="L1" s="365"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="354" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="338"/>
+      <c r="B2" s="431" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="368"/>
       <c r="M2" s="202"/>
     </row>
     <row r="3" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="346" t="s">
+      <c r="B3" s="422" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="340"/>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="340"/>
-      <c r="K3" s="340"/>
-      <c r="L3" s="341"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="359"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="370"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="360" t="s">
+      <c r="B4" s="428" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="344"/>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="344"/>
-      <c r="I4" s="334"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="351"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -4394,36 +4405,36 @@
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="353" t="s">
+      <c r="B5" s="484" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="338"/>
-      <c r="D5" s="336" t="str">
+      <c r="C5" s="368"/>
+      <c r="D5" s="470" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="338"/>
-      <c r="J5" s="362" t="s">
+      <c r="E5" s="367"/>
+      <c r="F5" s="367"/>
+      <c r="G5" s="367"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="368"/>
+      <c r="J5" s="425" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="344"/>
-      <c r="L5" s="334"/>
+      <c r="K5" s="363"/>
+      <c r="L5" s="351"/>
       <c r="M5" s="202"/>
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="339"/>
-      <c r="C6" s="341"/>
-      <c r="D6" s="339"/>
-      <c r="E6" s="340"/>
-      <c r="F6" s="340"/>
-      <c r="G6" s="340"/>
-      <c r="H6" s="340"/>
-      <c r="I6" s="341"/>
+      <c r="B6" s="369"/>
+      <c r="C6" s="370"/>
+      <c r="D6" s="369"/>
+      <c r="E6" s="359"/>
+      <c r="F6" s="359"/>
+      <c r="G6" s="359"/>
+      <c r="H6" s="359"/>
+      <c r="I6" s="370"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -4436,21 +4447,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="360" t="s">
+      <c r="B7" s="428" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="344"/>
-      <c r="D7" s="344"/>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
-      <c r="G7" s="334"/>
-      <c r="H7" s="360" t="s">
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
+      <c r="E7" s="363"/>
+      <c r="F7" s="363"/>
+      <c r="G7" s="351"/>
+      <c r="H7" s="428" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="344"/>
-      <c r="J7" s="344"/>
-      <c r="K7" s="344"/>
-      <c r="L7" s="334"/>
+      <c r="I7" s="363"/>
+      <c r="J7" s="363"/>
+      <c r="K7" s="363"/>
+      <c r="L7" s="351"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -4510,11 +4521,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="345" t="str">
+      <c r="J10" s="436" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="340"/>
+      <c r="K10" s="359"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -4529,215 +4540,246 @@
     </row>
     <row r="12" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="200"/>
-      <c r="B12" s="347" t="s">
+      <c r="B12" s="482" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="348"/>
-      <c r="D12" s="349" t="s">
+      <c r="C12" s="477"/>
+      <c r="D12" s="476" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="348"/>
-      <c r="F12" s="349" t="s">
+      <c r="E12" s="477"/>
+      <c r="F12" s="476" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="348"/>
-      <c r="H12" s="349" t="s">
+      <c r="G12" s="477"/>
+      <c r="H12" s="476" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="363"/>
-      <c r="J12" s="363"/>
-      <c r="K12" s="363"/>
-      <c r="L12" s="348"/>
+      <c r="I12" s="479"/>
+      <c r="J12" s="479"/>
+      <c r="K12" s="479"/>
+      <c r="L12" s="477"/>
       <c r="M12" s="202"/>
     </row>
     <row r="13" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="200"/>
-      <c r="B13" s="357" t="s">
+      <c r="B13" s="472" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="341"/>
-      <c r="D13" s="352" t="s">
+      <c r="C13" s="370"/>
+      <c r="D13" s="475" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="341"/>
-      <c r="F13" s="352" t="s">
+      <c r="E13" s="370"/>
+      <c r="F13" s="475" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="341"/>
-      <c r="H13" s="361" t="s">
+      <c r="G13" s="370"/>
+      <c r="H13" s="474" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="340"/>
-      <c r="J13" s="340"/>
-      <c r="K13" s="340"/>
-      <c r="L13" s="341"/>
+      <c r="I13" s="359"/>
+      <c r="J13" s="359"/>
+      <c r="K13" s="359"/>
+      <c r="L13" s="370"/>
       <c r="M13" s="202"/>
     </row>
     <row r="14" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="200"/>
-      <c r="B14" s="335" t="s">
+      <c r="B14" s="478" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="334"/>
-      <c r="D14" s="342" t="s">
+      <c r="C14" s="351"/>
+      <c r="D14" s="480" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="334"/>
-      <c r="F14" s="342" t="s">
+      <c r="E14" s="351"/>
+      <c r="F14" s="480" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="334"/>
-      <c r="H14" s="359"/>
-      <c r="I14" s="344"/>
-      <c r="J14" s="344"/>
-      <c r="K14" s="344"/>
-      <c r="L14" s="334"/>
+      <c r="G14" s="351"/>
+      <c r="H14" s="350"/>
+      <c r="I14" s="363"/>
+      <c r="J14" s="363"/>
+      <c r="K14" s="363"/>
+      <c r="L14" s="351"/>
       <c r="M14" s="202"/>
     </row>
     <row r="15" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="200"/>
-      <c r="B15" s="335" t="s">
+      <c r="B15" s="478" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="334"/>
-      <c r="D15" s="342" t="s">
+      <c r="C15" s="351"/>
+      <c r="D15" s="480" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="334"/>
-      <c r="F15" s="342" t="s">
+      <c r="E15" s="351"/>
+      <c r="F15" s="480" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="334"/>
-      <c r="H15" s="359"/>
-      <c r="I15" s="344"/>
-      <c r="J15" s="344"/>
-      <c r="K15" s="344"/>
-      <c r="L15" s="334"/>
+      <c r="G15" s="351"/>
+      <c r="H15" s="350"/>
+      <c r="I15" s="363"/>
+      <c r="J15" s="363"/>
+      <c r="K15" s="363"/>
+      <c r="L15" s="351"/>
       <c r="M15" s="202"/>
     </row>
     <row r="16" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="200"/>
-      <c r="B16" s="335" t="s">
+      <c r="B16" s="478" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="334"/>
-      <c r="D16" s="358" t="s">
+      <c r="C16" s="351"/>
+      <c r="D16" s="473" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="334"/>
-      <c r="F16" s="333" t="s">
+      <c r="E16" s="351"/>
+      <c r="F16" s="481" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="334"/>
-      <c r="H16" s="359"/>
-      <c r="I16" s="344"/>
-      <c r="J16" s="344"/>
-      <c r="K16" s="344"/>
-      <c r="L16" s="334"/>
+      <c r="G16" s="351"/>
+      <c r="H16" s="350"/>
+      <c r="I16" s="363"/>
+      <c r="J16" s="363"/>
+      <c r="K16" s="363"/>
+      <c r="L16" s="351"/>
       <c r="M16" s="202"/>
     </row>
     <row r="17" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="200"/>
-      <c r="B17" s="335" t="s">
+      <c r="B17" s="478" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="334"/>
-      <c r="D17" s="342" t="s">
+      <c r="C17" s="351"/>
+      <c r="D17" s="480" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="334"/>
-      <c r="F17" s="342" t="s">
+      <c r="E17" s="351"/>
+      <c r="F17" s="480" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="334"/>
-      <c r="H17" s="359"/>
-      <c r="I17" s="344"/>
-      <c r="J17" s="344"/>
-      <c r="K17" s="344"/>
-      <c r="L17" s="334"/>
+      <c r="G17" s="351"/>
+      <c r="H17" s="350"/>
+      <c r="I17" s="363"/>
+      <c r="J17" s="363"/>
+      <c r="K17" s="363"/>
+      <c r="L17" s="351"/>
       <c r="M17" s="202"/>
     </row>
     <row r="18" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="200"/>
-      <c r="B18" s="335" t="s">
+      <c r="B18" s="478" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="334"/>
-      <c r="D18" s="342" t="s">
+      <c r="C18" s="351"/>
+      <c r="D18" s="480" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="334"/>
-      <c r="F18" s="342" t="s">
+      <c r="E18" s="351"/>
+      <c r="F18" s="480" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="334"/>
-      <c r="H18" s="359"/>
-      <c r="I18" s="344"/>
-      <c r="J18" s="344"/>
-      <c r="K18" s="344"/>
-      <c r="L18" s="334"/>
+      <c r="G18" s="351"/>
+      <c r="H18" s="350"/>
+      <c r="I18" s="363"/>
+      <c r="J18" s="363"/>
+      <c r="K18" s="363"/>
+      <c r="L18" s="351"/>
       <c r="M18" s="202"/>
     </row>
     <row r="19" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="200"/>
-      <c r="B19" s="335" t="s">
+      <c r="B19" s="478" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="334"/>
-      <c r="D19" s="342" t="s">
+      <c r="C19" s="351"/>
+      <c r="D19" s="480" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="334"/>
-      <c r="F19" s="342" t="s">
+      <c r="E19" s="351"/>
+      <c r="F19" s="480" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="334"/>
-      <c r="H19" s="343"/>
-      <c r="I19" s="344"/>
-      <c r="J19" s="344"/>
-      <c r="K19" s="344"/>
-      <c r="L19" s="334"/>
+      <c r="G19" s="351"/>
+      <c r="H19" s="441"/>
+      <c r="I19" s="363"/>
+      <c r="J19" s="363"/>
+      <c r="K19" s="363"/>
+      <c r="L19" s="351"/>
       <c r="M19" s="202"/>
     </row>
     <row r="20" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="335" t="s">
+      <c r="B20" s="478" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="333" t="s">
+      <c r="C20" s="351"/>
+      <c r="D20" s="481" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="334"/>
-      <c r="F20" s="333" t="s">
+      <c r="E20" s="351"/>
+      <c r="F20" s="481" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="334"/>
-      <c r="H20" s="343"/>
-      <c r="I20" s="344"/>
-      <c r="J20" s="344"/>
-      <c r="K20" s="344"/>
-      <c r="L20" s="334"/>
+      <c r="G20" s="351"/>
+      <c r="H20" s="441"/>
+      <c r="I20" s="363"/>
+      <c r="J20" s="363"/>
+      <c r="K20" s="363"/>
+      <c r="L20" s="351"/>
       <c r="M20" s="202"/>
     </row>
     <row r="21" spans="1:13" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="203"/>
-      <c r="B21" s="350"/>
-      <c r="C21" s="351"/>
-      <c r="D21" s="351"/>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
-      <c r="G21" s="351"/>
-      <c r="H21" s="351"/>
-      <c r="I21" s="351"/>
-      <c r="J21" s="351"/>
-      <c r="K21" s="351"/>
-      <c r="L21" s="351"/>
+      <c r="B21" s="483"/>
+      <c r="C21" s="373"/>
+      <c r="D21" s="373"/>
+      <c r="E21" s="373"/>
+      <c r="F21" s="373"/>
+      <c r="G21" s="373"/>
+      <c r="H21" s="373"/>
+      <c r="I21" s="373"/>
+      <c r="J21" s="373"/>
+      <c r="K21" s="373"/>
+      <c r="L21" s="373"/>
       <c r="M21" s="204"/>
     </row>
     <row r="22" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D16:E16"/>
@@ -4754,37 +4796,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="H15:L15"/>
     <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="J10:K10"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -4807,65 +4818,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="355"/>
-      <c r="C1" s="356"/>
-      <c r="D1" s="356"/>
-      <c r="E1" s="356"/>
-      <c r="F1" s="356"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="356"/>
-      <c r="I1" s="356"/>
-      <c r="J1" s="356"/>
-      <c r="K1" s="356"/>
-      <c r="L1" s="356"/>
+      <c r="B1" s="364"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
+      <c r="K1" s="365"/>
+      <c r="L1" s="365"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="354" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="338"/>
+      <c r="B2" s="431" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="368"/>
       <c r="M2" s="282"/>
     </row>
     <row r="3" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="346" t="s">
+      <c r="B3" s="422" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="340"/>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="340"/>
-      <c r="K3" s="340"/>
-      <c r="L3" s="341"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="359"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="370"/>
       <c r="M3" s="282"/>
     </row>
     <row r="4" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="360" t="s">
+      <c r="B4" s="428" t="s">
         <v>351</v>
       </c>
-      <c r="C4" s="344"/>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="344"/>
-      <c r="I4" s="334"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="351"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -4878,36 +4889,36 @@
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="353" t="s">
+      <c r="B5" s="484" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="338"/>
-      <c r="D5" s="336" t="str">
+      <c r="C5" s="368"/>
+      <c r="D5" s="470" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="338"/>
-      <c r="J5" s="362" t="s">
+      <c r="E5" s="367"/>
+      <c r="F5" s="367"/>
+      <c r="G5" s="367"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="368"/>
+      <c r="J5" s="425" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="344"/>
-      <c r="L5" s="334"/>
+      <c r="K5" s="363"/>
+      <c r="L5" s="351"/>
       <c r="M5" s="213"/>
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="339"/>
-      <c r="C6" s="341"/>
-      <c r="D6" s="339"/>
-      <c r="E6" s="340"/>
-      <c r="F6" s="340"/>
-      <c r="G6" s="340"/>
-      <c r="H6" s="340"/>
-      <c r="I6" s="341"/>
+      <c r="B6" s="369"/>
+      <c r="C6" s="370"/>
+      <c r="D6" s="369"/>
+      <c r="E6" s="359"/>
+      <c r="F6" s="359"/>
+      <c r="G6" s="359"/>
+      <c r="H6" s="359"/>
+      <c r="I6" s="370"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -4920,21 +4931,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="360" t="s">
+      <c r="B7" s="428" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="344"/>
-      <c r="D7" s="344"/>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
-      <c r="G7" s="334"/>
-      <c r="H7" s="360" t="s">
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
+      <c r="E7" s="363"/>
+      <c r="F7" s="363"/>
+      <c r="G7" s="351"/>
+      <c r="H7" s="428" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="344"/>
-      <c r="J7" s="344"/>
-      <c r="K7" s="344"/>
-      <c r="L7" s="334"/>
+      <c r="I7" s="363"/>
+      <c r="J7" s="363"/>
+      <c r="K7" s="363"/>
+      <c r="L7" s="351"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -4994,11 +5005,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="345" t="str">
+      <c r="J10" s="436" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="340"/>
+      <c r="K10" s="359"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -5013,24 +5024,24 @@
     </row>
     <row r="12" spans="1:13" s="25" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="285"/>
-      <c r="B12" s="347" t="s">
+      <c r="B12" s="482" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="348"/>
-      <c r="D12" s="349" t="s">
+      <c r="C12" s="477"/>
+      <c r="D12" s="476" t="s">
         <v>353</v>
       </c>
-      <c r="E12" s="363"/>
-      <c r="F12" s="348"/>
-      <c r="G12" s="349" t="s">
+      <c r="E12" s="479"/>
+      <c r="F12" s="477"/>
+      <c r="G12" s="476" t="s">
         <v>354</v>
       </c>
-      <c r="H12" s="363"/>
-      <c r="I12" s="348"/>
-      <c r="J12" s="349" t="s">
+      <c r="H12" s="479"/>
+      <c r="I12" s="477"/>
+      <c r="J12" s="476" t="s">
         <v>355</v>
       </c>
-      <c r="K12" s="348"/>
+      <c r="K12" s="477"/>
       <c r="L12" s="291" t="s">
         <v>356</v>
       </c>
@@ -5038,155 +5049,155 @@
     </row>
     <row r="13" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="285"/>
-      <c r="B13" s="492" t="s">
+      <c r="B13" s="490" t="s">
         <v>357</v>
       </c>
-      <c r="C13" s="488"/>
-      <c r="D13" s="486" t="s">
+      <c r="C13" s="491"/>
+      <c r="D13" s="492" t="s">
         <v>358</v>
       </c>
-      <c r="E13" s="487"/>
-      <c r="F13" s="488"/>
-      <c r="G13" s="486" t="s">
+      <c r="E13" s="493"/>
+      <c r="F13" s="491"/>
+      <c r="G13" s="492" t="s">
         <v>359</v>
       </c>
-      <c r="H13" s="487"/>
-      <c r="I13" s="488"/>
-      <c r="J13" s="486" t="s">
+      <c r="H13" s="493"/>
+      <c r="I13" s="491"/>
+      <c r="J13" s="492" t="s">
         <v>360</v>
       </c>
-      <c r="K13" s="488"/>
+      <c r="K13" s="491"/>
       <c r="L13" s="279"/>
       <c r="M13" s="286"/>
     </row>
     <row r="14" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="285"/>
-      <c r="B14" s="485" t="s">
+      <c r="B14" s="486" t="s">
         <v>197</v>
       </c>
-      <c r="C14" s="409"/>
-      <c r="D14" s="489" t="s">
+      <c r="C14" s="376"/>
+      <c r="D14" s="488" t="s">
         <v>358</v>
       </c>
-      <c r="E14" s="491"/>
-      <c r="F14" s="409"/>
-      <c r="G14" s="489" t="s">
+      <c r="E14" s="489"/>
+      <c r="F14" s="376"/>
+      <c r="G14" s="488" t="s">
         <v>359</v>
       </c>
-      <c r="H14" s="491"/>
-      <c r="I14" s="409"/>
-      <c r="J14" s="489" t="s">
+      <c r="H14" s="489"/>
+      <c r="I14" s="376"/>
+      <c r="J14" s="488" t="s">
         <v>360</v>
       </c>
-      <c r="K14" s="409"/>
+      <c r="K14" s="376"/>
       <c r="L14" s="280"/>
       <c r="M14" s="286"/>
     </row>
     <row r="15" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="285"/>
-      <c r="B15" s="485" t="s">
+      <c r="B15" s="486" t="s">
         <v>361</v>
       </c>
-      <c r="C15" s="409"/>
-      <c r="D15" s="489" t="s">
+      <c r="C15" s="376"/>
+      <c r="D15" s="488" t="s">
         <v>358</v>
       </c>
-      <c r="E15" s="491"/>
-      <c r="F15" s="409"/>
-      <c r="G15" s="489" t="s">
+      <c r="E15" s="489"/>
+      <c r="F15" s="376"/>
+      <c r="G15" s="488" t="s">
         <v>362</v>
       </c>
-      <c r="H15" s="491"/>
-      <c r="I15" s="409"/>
-      <c r="J15" s="489" t="s">
+      <c r="H15" s="489"/>
+      <c r="I15" s="376"/>
+      <c r="J15" s="488" t="s">
         <v>360</v>
       </c>
-      <c r="K15" s="409"/>
+      <c r="K15" s="376"/>
       <c r="L15" s="280"/>
       <c r="M15" s="286"/>
     </row>
     <row r="16" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="285"/>
-      <c r="B16" s="485" t="s">
+      <c r="B16" s="486" t="s">
         <v>363</v>
       </c>
-      <c r="C16" s="409"/>
-      <c r="D16" s="489" t="s">
+      <c r="C16" s="376"/>
+      <c r="D16" s="488" t="s">
         <v>358</v>
       </c>
-      <c r="E16" s="491"/>
-      <c r="F16" s="409"/>
-      <c r="G16" s="489" t="s">
+      <c r="E16" s="489"/>
+      <c r="F16" s="376"/>
+      <c r="G16" s="488" t="s">
         <v>362</v>
       </c>
-      <c r="H16" s="491"/>
-      <c r="I16" s="409"/>
-      <c r="J16" s="489" t="s">
+      <c r="H16" s="489"/>
+      <c r="I16" s="376"/>
+      <c r="J16" s="488" t="s">
         <v>360</v>
       </c>
-      <c r="K16" s="409"/>
+      <c r="K16" s="376"/>
       <c r="L16" s="280"/>
       <c r="M16" s="286"/>
     </row>
     <row r="17" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="285"/>
-      <c r="B17" s="485" t="s">
+      <c r="B17" s="486" t="s">
         <v>364</v>
       </c>
-      <c r="C17" s="409"/>
-      <c r="D17" s="489" t="s">
+      <c r="C17" s="376"/>
+      <c r="D17" s="488" t="s">
         <v>358</v>
       </c>
-      <c r="E17" s="491"/>
-      <c r="F17" s="409"/>
-      <c r="G17" s="489" t="s">
+      <c r="E17" s="489"/>
+      <c r="F17" s="376"/>
+      <c r="G17" s="488" t="s">
         <v>365</v>
       </c>
-      <c r="H17" s="491"/>
-      <c r="I17" s="409"/>
-      <c r="J17" s="489" t="s">
+      <c r="H17" s="489"/>
+      <c r="I17" s="376"/>
+      <c r="J17" s="488" t="s">
         <v>360</v>
       </c>
-      <c r="K17" s="409"/>
+      <c r="K17" s="376"/>
       <c r="L17" s="280"/>
       <c r="M17" s="286"/>
     </row>
     <row r="18" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="285"/>
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="472" t="s">
         <v>366</v>
       </c>
-      <c r="C18" s="341"/>
-      <c r="D18" s="489" t="s">
+      <c r="C18" s="370"/>
+      <c r="D18" s="488" t="s">
         <v>358</v>
       </c>
-      <c r="E18" s="491"/>
-      <c r="F18" s="409"/>
-      <c r="G18" s="490" t="s">
+      <c r="E18" s="489"/>
+      <c r="F18" s="376"/>
+      <c r="G18" s="487" t="s">
         <v>362</v>
       </c>
-      <c r="H18" s="340"/>
-      <c r="I18" s="341"/>
-      <c r="J18" s="490" t="s">
+      <c r="H18" s="359"/>
+      <c r="I18" s="370"/>
+      <c r="J18" s="487" t="s">
         <v>360</v>
       </c>
-      <c r="K18" s="341"/>
+      <c r="K18" s="370"/>
       <c r="L18" s="281"/>
       <c r="M18" s="286"/>
     </row>
     <row r="19" spans="1:13" s="25" customFormat="1" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="287"/>
-      <c r="B19" s="493"/>
-      <c r="C19" s="351"/>
-      <c r="D19" s="351"/>
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
-      <c r="G19" s="351"/>
-      <c r="H19" s="351"/>
-      <c r="I19" s="351"/>
-      <c r="J19" s="351"/>
-      <c r="K19" s="351"/>
-      <c r="L19" s="351"/>
+      <c r="B19" s="485"/>
+      <c r="C19" s="373"/>
+      <c r="D19" s="373"/>
+      <c r="E19" s="373"/>
+      <c r="F19" s="373"/>
+      <c r="G19" s="373"/>
+      <c r="H19" s="373"/>
+      <c r="I19" s="373"/>
+      <c r="J19" s="373"/>
+      <c r="K19" s="373"/>
+      <c r="L19" s="373"/>
       <c r="M19" s="288"/>
     </row>
     <row r="20" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -5481,15 +5492,13 @@
     <row r="309" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B19:L19"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="G13:I13"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
@@ -5502,24 +5511,26 @@
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B3:L3"/>
-    <mergeCell ref="G18:I18"/>
     <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B18:C18"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="G15:I15"/>
+    <mergeCell ref="B19:L19"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="B5:C6"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J10:K10"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -5546,65 +5557,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="13.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="355"/>
-      <c r="C1" s="356"/>
-      <c r="D1" s="356"/>
-      <c r="E1" s="356"/>
-      <c r="F1" s="356"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="356"/>
-      <c r="I1" s="356"/>
-      <c r="J1" s="356"/>
-      <c r="K1" s="356"/>
-      <c r="L1" s="356"/>
+      <c r="B1" s="364"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
+      <c r="K1" s="365"/>
+      <c r="L1" s="365"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="354" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="338"/>
+      <c r="B2" s="431" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="368"/>
       <c r="M2" s="282"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="346" t="s">
+      <c r="B3" s="422" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="340"/>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="340"/>
-      <c r="K3" s="340"/>
-      <c r="L3" s="341"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="359"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="370"/>
       <c r="M3" s="282"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="360" t="s">
+      <c r="B4" s="428" t="s">
         <v>367</v>
       </c>
-      <c r="C4" s="344"/>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="344"/>
-      <c r="I4" s="334"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="351"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -5614,36 +5625,36 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="353" t="s">
+      <c r="B5" s="484" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="338"/>
-      <c r="D5" s="336" t="str">
+      <c r="C5" s="368"/>
+      <c r="D5" s="470" t="str">
         <f>'QUADRO I'!D5:O6</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="338"/>
-      <c r="J5" s="362" t="s">
+      <c r="E5" s="367"/>
+      <c r="F5" s="367"/>
+      <c r="G5" s="367"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="368"/>
+      <c r="J5" s="425" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="344"/>
-      <c r="L5" s="334"/>
+      <c r="K5" s="363"/>
+      <c r="L5" s="351"/>
       <c r="M5" s="213"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="339"/>
-      <c r="C6" s="341"/>
-      <c r="D6" s="339"/>
-      <c r="E6" s="340"/>
-      <c r="F6" s="340"/>
-      <c r="G6" s="340"/>
-      <c r="H6" s="340"/>
-      <c r="I6" s="341"/>
+      <c r="B6" s="369"/>
+      <c r="C6" s="370"/>
+      <c r="D6" s="369"/>
+      <c r="E6" s="359"/>
+      <c r="F6" s="359"/>
+      <c r="G6" s="359"/>
+      <c r="H6" s="359"/>
+      <c r="I6" s="370"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -5655,21 +5666,21 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="360" t="s">
+      <c r="B7" s="428" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="344"/>
-      <c r="D7" s="344"/>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
-      <c r="G7" s="334"/>
-      <c r="H7" s="360" t="s">
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
+      <c r="E7" s="363"/>
+      <c r="F7" s="363"/>
+      <c r="G7" s="351"/>
+      <c r="H7" s="428" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="344"/>
-      <c r="J7" s="344"/>
-      <c r="K7" s="344"/>
-      <c r="L7" s="334"/>
+      <c r="I7" s="363"/>
+      <c r="J7" s="363"/>
+      <c r="K7" s="363"/>
+      <c r="L7" s="351"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -5677,14 +5688,14 @@
       <c r="B8" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="497" t="str">
+      <c r="C8" s="496" t="str">
         <f>'QUADRO VII'!C8</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="D8" s="337"/>
-      <c r="E8" s="337"/>
-      <c r="F8" s="337"/>
-      <c r="G8" s="338"/>
+      <c r="D8" s="367"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
+      <c r="G8" s="368"/>
       <c r="H8" s="19" t="s">
         <v>9</v>
       </c>
@@ -5736,11 +5747,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="345" t="str">
+      <c r="J10" s="436" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="340"/>
+      <c r="K10" s="359"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -5749,24 +5760,24 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="343" t="s">
+      <c r="B11" s="441" t="s">
         <v>352</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="343" t="s">
+      <c r="C11" s="351"/>
+      <c r="D11" s="441" t="s">
         <v>353</v>
       </c>
-      <c r="E11" s="344"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="343" t="s">
+      <c r="E11" s="363"/>
+      <c r="F11" s="351"/>
+      <c r="G11" s="441" t="s">
         <v>354</v>
       </c>
-      <c r="H11" s="344"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="343" t="s">
+      <c r="H11" s="363"/>
+      <c r="I11" s="351"/>
+      <c r="J11" s="441" t="s">
         <v>355</v>
       </c>
-      <c r="K11" s="334"/>
+      <c r="K11" s="351"/>
       <c r="L11" s="306" t="s">
         <v>356</v>
       </c>
@@ -5774,24 +5785,24 @@
     </row>
     <row r="12" spans="1:13" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="285"/>
-      <c r="B12" s="450" t="s">
+      <c r="B12" s="437" t="s">
         <v>368</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="450" t="s">
+      <c r="C12" s="368"/>
+      <c r="D12" s="437" t="s">
         <v>369</v>
       </c>
-      <c r="E12" s="337"/>
-      <c r="F12" s="338"/>
-      <c r="G12" s="450" t="s">
+      <c r="E12" s="367"/>
+      <c r="F12" s="368"/>
+      <c r="G12" s="437" t="s">
         <v>370</v>
       </c>
-      <c r="H12" s="337"/>
-      <c r="I12" s="338"/>
-      <c r="J12" s="450" t="s">
+      <c r="H12" s="367"/>
+      <c r="I12" s="368"/>
+      <c r="J12" s="437" t="s">
         <v>371</v>
       </c>
-      <c r="K12" s="338"/>
+      <c r="K12" s="368"/>
       <c r="L12" s="307"/>
       <c r="M12" s="286"/>
     </row>
@@ -5800,21 +5811,21 @@
       <c r="B13" s="494" t="s">
         <v>372</v>
       </c>
-      <c r="C13" s="409"/>
+      <c r="C13" s="376"/>
       <c r="D13" s="494" t="s">
         <v>369</v>
       </c>
       <c r="E13" s="495"/>
-      <c r="F13" s="409"/>
+      <c r="F13" s="376"/>
       <c r="G13" s="494" t="s">
         <v>370</v>
       </c>
       <c r="H13" s="495"/>
-      <c r="I13" s="409"/>
+      <c r="I13" s="376"/>
       <c r="J13" s="494" t="s">
         <v>371</v>
       </c>
-      <c r="K13" s="409"/>
+      <c r="K13" s="376"/>
       <c r="L13" s="280"/>
       <c r="M13" s="286"/>
     </row>
@@ -5823,21 +5834,21 @@
       <c r="B14" s="494" t="s">
         <v>373</v>
       </c>
-      <c r="C14" s="409"/>
+      <c r="C14" s="376"/>
       <c r="D14" s="494" t="s">
         <v>369</v>
       </c>
       <c r="E14" s="495"/>
-      <c r="F14" s="409"/>
+      <c r="F14" s="376"/>
       <c r="G14" s="494" t="s">
         <v>369</v>
       </c>
       <c r="H14" s="495"/>
-      <c r="I14" s="409"/>
+      <c r="I14" s="376"/>
       <c r="J14" s="494" t="s">
         <v>371</v>
       </c>
-      <c r="K14" s="409"/>
+      <c r="K14" s="376"/>
       <c r="L14" s="280"/>
       <c r="M14" s="286"/>
     </row>
@@ -5846,21 +5857,21 @@
       <c r="B15" s="494" t="s">
         <v>374</v>
       </c>
-      <c r="C15" s="409"/>
+      <c r="C15" s="376"/>
       <c r="D15" s="494" t="s">
         <v>369</v>
       </c>
       <c r="E15" s="495"/>
-      <c r="F15" s="409"/>
+      <c r="F15" s="376"/>
       <c r="G15" s="494" t="s">
         <v>369</v>
       </c>
       <c r="H15" s="495"/>
-      <c r="I15" s="409"/>
+      <c r="I15" s="376"/>
       <c r="J15" s="494" t="s">
         <v>371</v>
       </c>
-      <c r="K15" s="409"/>
+      <c r="K15" s="376"/>
       <c r="L15" s="280"/>
       <c r="M15" s="286"/>
     </row>
@@ -5869,21 +5880,21 @@
       <c r="B16" s="494" t="s">
         <v>375</v>
       </c>
-      <c r="C16" s="409"/>
+      <c r="C16" s="376"/>
       <c r="D16" s="494" t="s">
         <v>369</v>
       </c>
       <c r="E16" s="495"/>
-      <c r="F16" s="409"/>
+      <c r="F16" s="376"/>
       <c r="G16" s="494" t="s">
         <v>370</v>
       </c>
       <c r="H16" s="495"/>
-      <c r="I16" s="409"/>
+      <c r="I16" s="376"/>
       <c r="J16" s="494" t="s">
         <v>371</v>
       </c>
-      <c r="K16" s="409"/>
+      <c r="K16" s="376"/>
       <c r="L16" s="280"/>
       <c r="M16" s="286"/>
     </row>
@@ -5892,21 +5903,21 @@
       <c r="B17" s="494" t="s">
         <v>376</v>
       </c>
-      <c r="C17" s="409"/>
+      <c r="C17" s="376"/>
       <c r="D17" s="494" t="s">
         <v>369</v>
       </c>
       <c r="E17" s="495"/>
-      <c r="F17" s="409"/>
+      <c r="F17" s="376"/>
       <c r="G17" s="494" t="s">
         <v>369</v>
       </c>
       <c r="H17" s="495"/>
-      <c r="I17" s="409"/>
+      <c r="I17" s="376"/>
       <c r="J17" s="494" t="s">
         <v>371</v>
       </c>
-      <c r="K17" s="409"/>
+      <c r="K17" s="376"/>
       <c r="L17" s="280"/>
       <c r="M17" s="286"/>
     </row>
@@ -5915,21 +5926,21 @@
       <c r="B18" s="494" t="s">
         <v>377</v>
       </c>
-      <c r="C18" s="409"/>
+      <c r="C18" s="376"/>
       <c r="D18" s="494" t="s">
         <v>378</v>
       </c>
       <c r="E18" s="495"/>
-      <c r="F18" s="409"/>
+      <c r="F18" s="376"/>
       <c r="G18" s="494" t="s">
         <v>369</v>
       </c>
       <c r="H18" s="495"/>
-      <c r="I18" s="409"/>
+      <c r="I18" s="376"/>
       <c r="J18" s="494" t="s">
         <v>371</v>
       </c>
-      <c r="K18" s="409"/>
+      <c r="K18" s="376"/>
       <c r="L18" s="280"/>
       <c r="M18" s="286"/>
     </row>
@@ -6085,22 +6096,22 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="285"/>
-      <c r="B29" s="496"/>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
-      <c r="G29" s="337"/>
-      <c r="H29" s="337"/>
-      <c r="I29" s="337"/>
-      <c r="J29" s="337"/>
-      <c r="K29" s="337"/>
-      <c r="L29" s="338"/>
+      <c r="B29" s="497"/>
+      <c r="C29" s="367"/>
+      <c r="D29" s="367"/>
+      <c r="E29" s="367"/>
+      <c r="F29" s="367"/>
+      <c r="G29" s="367"/>
+      <c r="H29" s="367"/>
+      <c r="I29" s="367"/>
+      <c r="J29" s="367"/>
+      <c r="K29" s="367"/>
+      <c r="L29" s="368"/>
       <c r="M29" s="286"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="285"/>
-      <c r="B30" s="429"/>
+      <c r="B30" s="418"/>
       <c r="C30" s="495"/>
       <c r="D30" s="495"/>
       <c r="E30" s="495"/>
@@ -6110,12 +6121,12 @@
       <c r="I30" s="495"/>
       <c r="J30" s="495"/>
       <c r="K30" s="495"/>
-      <c r="L30" s="409"/>
+      <c r="L30" s="376"/>
       <c r="M30" s="286"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="285"/>
-      <c r="B31" s="429"/>
+      <c r="B31" s="418"/>
       <c r="C31" s="495"/>
       <c r="D31" s="495"/>
       <c r="E31" s="495"/>
@@ -6125,47 +6136,55 @@
       <c r="I31" s="495"/>
       <c r="J31" s="495"/>
       <c r="K31" s="495"/>
-      <c r="L31" s="409"/>
+      <c r="L31" s="376"/>
       <c r="M31" s="286"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="285"/>
-      <c r="B32" s="339"/>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
-      <c r="G32" s="340"/>
-      <c r="H32" s="340"/>
-      <c r="I32" s="340"/>
-      <c r="J32" s="340"/>
-      <c r="K32" s="340"/>
-      <c r="L32" s="341"/>
+      <c r="B32" s="369"/>
+      <c r="C32" s="359"/>
+      <c r="D32" s="359"/>
+      <c r="E32" s="359"/>
+      <c r="F32" s="359"/>
+      <c r="G32" s="359"/>
+      <c r="H32" s="359"/>
+      <c r="I32" s="359"/>
+      <c r="J32" s="359"/>
+      <c r="K32" s="359"/>
+      <c r="L32" s="370"/>
       <c r="M32" s="286"/>
     </row>
     <row r="33" spans="1:13" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="287"/>
-      <c r="B33" s="493"/>
-      <c r="C33" s="351"/>
-      <c r="D33" s="351"/>
-      <c r="E33" s="351"/>
-      <c r="F33" s="351"/>
-      <c r="G33" s="351"/>
-      <c r="H33" s="351"/>
-      <c r="I33" s="351"/>
-      <c r="J33" s="351"/>
-      <c r="K33" s="351"/>
-      <c r="L33" s="351"/>
+      <c r="B33" s="485"/>
+      <c r="C33" s="373"/>
+      <c r="D33" s="373"/>
+      <c r="E33" s="373"/>
+      <c r="F33" s="373"/>
+      <c r="G33" s="373"/>
+      <c r="H33" s="373"/>
+      <c r="I33" s="373"/>
+      <c r="J33" s="373"/>
+      <c r="K33" s="373"/>
+      <c r="L33" s="373"/>
       <c r="M33" s="288"/>
     </row>
     <row r="34" spans="1:13" ht="13.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="B33:L33"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="G13:I13"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="G16:I16"/>
@@ -6182,6 +6201,11 @@
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="D12:F12"/>
+    <mergeCell ref="B33:L33"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="J17:K17"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="D15:F15"/>
@@ -6193,19 +6217,6 @@
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="G13:I13"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -6234,32 +6245,32 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="355"/>
-      <c r="C1" s="356"/>
-      <c r="D1" s="356"/>
-      <c r="E1" s="356"/>
-      <c r="F1" s="356"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="356"/>
-      <c r="I1" s="356"/>
-      <c r="J1" s="356"/>
-      <c r="K1" s="356"/>
-      <c r="L1" s="356"/>
+      <c r="B1" s="364"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
+      <c r="K1" s="365"/>
+      <c r="L1" s="365"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="412" t="s">
+      <c r="B2" s="366" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="338"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="368"/>
       <c r="K2" s="152" t="s">
         <v>58</v>
       </c>
@@ -6270,17 +6281,17 @@
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="339"/>
-      <c r="C3" s="340"/>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="341"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="334"/>
+      <c r="B3" s="369"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="370"/>
+      <c r="K3" s="350"/>
+      <c r="L3" s="351"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6288,18 +6299,18 @@
       <c r="B4" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="399" t="s">
+      <c r="C4" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="344"/>
-      <c r="I4" s="344"/>
-      <c r="J4" s="344"/>
-      <c r="K4" s="344"/>
-      <c r="L4" s="334"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
+      <c r="L4" s="351"/>
       <c r="M4" s="202"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6308,19 +6319,19 @@
       <c r="C5" s="140" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="403" t="s">
+      <c r="D5" s="357" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="394"/>
-      <c r="F5" s="419" t="s">
+      <c r="E5" s="353"/>
+      <c r="F5" s="352" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="394"/>
-      <c r="H5" s="394"/>
-      <c r="I5" s="394"/>
-      <c r="J5" s="394"/>
-      <c r="K5" s="394"/>
-      <c r="L5" s="395"/>
+      <c r="G5" s="353"/>
+      <c r="H5" s="353"/>
+      <c r="I5" s="353"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="353"/>
+      <c r="L5" s="354"/>
       <c r="M5" s="202"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6329,19 +6340,19 @@
       <c r="C6" s="141" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="390" t="s">
+      <c r="D6" s="355" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="383"/>
-      <c r="F6" s="413" t="s">
+      <c r="E6" s="356"/>
+      <c r="F6" s="371" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="383"/>
-      <c r="H6" s="383"/>
-      <c r="I6" s="383"/>
-      <c r="J6" s="383"/>
-      <c r="K6" s="383"/>
-      <c r="L6" s="384"/>
+      <c r="G6" s="356"/>
+      <c r="H6" s="356"/>
+      <c r="I6" s="356"/>
+      <c r="J6" s="356"/>
+      <c r="K6" s="356"/>
+      <c r="L6" s="361"/>
       <c r="M6" s="202"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6350,17 +6361,17 @@
       <c r="C7" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="417" t="s">
+      <c r="D7" s="378" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="386"/>
-      <c r="F7" s="385"/>
-      <c r="G7" s="386"/>
-      <c r="H7" s="386"/>
-      <c r="I7" s="386"/>
-      <c r="J7" s="386"/>
-      <c r="K7" s="386"/>
-      <c r="L7" s="387"/>
+      <c r="E7" s="379"/>
+      <c r="F7" s="400"/>
+      <c r="G7" s="379"/>
+      <c r="H7" s="379"/>
+      <c r="I7" s="379"/>
+      <c r="J7" s="379"/>
+      <c r="K7" s="379"/>
+      <c r="L7" s="401"/>
       <c r="M7" s="202"/>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6369,13 +6380,13 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="340"/>
-      <c r="G8" s="340"/>
-      <c r="H8" s="340"/>
-      <c r="I8" s="340"/>
-      <c r="J8" s="340"/>
-      <c r="K8" s="340"/>
-      <c r="L8" s="341"/>
+      <c r="F8" s="359"/>
+      <c r="G8" s="359"/>
+      <c r="H8" s="359"/>
+      <c r="I8" s="359"/>
+      <c r="J8" s="359"/>
+      <c r="K8" s="359"/>
+      <c r="L8" s="370"/>
       <c r="M8" s="202"/>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6383,18 +6394,18 @@
       <c r="B9" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="399" t="s">
+      <c r="C9" s="362" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="344"/>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
-      <c r="G9" s="344"/>
-      <c r="H9" s="344"/>
-      <c r="I9" s="344"/>
-      <c r="J9" s="344"/>
-      <c r="K9" s="344"/>
-      <c r="L9" s="334"/>
+      <c r="D9" s="363"/>
+      <c r="E9" s="363"/>
+      <c r="F9" s="363"/>
+      <c r="G9" s="363"/>
+      <c r="H9" s="363"/>
+      <c r="I9" s="363"/>
+      <c r="J9" s="363"/>
+      <c r="K9" s="363"/>
+      <c r="L9" s="351"/>
       <c r="M9" s="202"/>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6403,20 +6414,20 @@
       <c r="C10" s="140" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="403" t="s">
+      <c r="D10" s="357" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="394"/>
-      <c r="F10" s="394"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="G10" s="393" t="str">
-        <f>CAPA!B14</f>
+        <f>CAPA!A14</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="H10" s="394"/>
-      <c r="I10" s="394"/>
-      <c r="J10" s="394"/>
-      <c r="K10" s="394"/>
-      <c r="L10" s="395"/>
+      <c r="H10" s="353"/>
+      <c r="I10" s="353"/>
+      <c r="J10" s="353"/>
+      <c r="K10" s="353"/>
+      <c r="L10" s="354"/>
       <c r="M10" s="202"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6425,20 +6436,20 @@
       <c r="C11" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="390" t="s">
+      <c r="D11" s="355" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="383"/>
-      <c r="F11" s="383"/>
-      <c r="G11" s="405" t="str">
-        <f>CAPA!B15</f>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="G11" s="360" t="str">
+        <f>CAPA!A15</f>
         <v>{CREA}</v>
       </c>
-      <c r="H11" s="383"/>
-      <c r="I11" s="383"/>
-      <c r="J11" s="383"/>
-      <c r="K11" s="383"/>
-      <c r="L11" s="384"/>
+      <c r="H11" s="356"/>
+      <c r="I11" s="356"/>
+      <c r="J11" s="356"/>
+      <c r="K11" s="356"/>
+      <c r="L11" s="361"/>
       <c r="M11" s="202"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6447,30 +6458,30 @@
       <c r="C12" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="390" t="s">
+      <c r="D12" s="355" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="383"/>
-      <c r="F12" s="383"/>
-      <c r="G12" s="405"/>
-      <c r="H12" s="383"/>
-      <c r="I12" s="383"/>
-      <c r="J12" s="383"/>
-      <c r="K12" s="383"/>
-      <c r="L12" s="384"/>
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="G12" s="360"/>
+      <c r="H12" s="356"/>
+      <c r="I12" s="356"/>
+      <c r="J12" s="356"/>
+      <c r="K12" s="356"/>
+      <c r="L12" s="361"/>
       <c r="M12" s="202"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="200"/>
-      <c r="B13" s="406"/>
-      <c r="C13" s="416" t="s">
+      <c r="B13" s="385"/>
+      <c r="C13" s="358" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="416" t="s">
+      <c r="D13" s="358" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="386"/>
-      <c r="F13" s="386"/>
+      <c r="E13" s="379"/>
+      <c r="F13" s="379"/>
       <c r="G13" s="187"/>
       <c r="H13" s="187"/>
       <c r="I13" s="187"/>
@@ -6481,11 +6492,11 @@
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="200"/>
-      <c r="B14" s="339"/>
-      <c r="C14" s="340"/>
-      <c r="D14" s="340"/>
-      <c r="E14" s="340"/>
-      <c r="F14" s="340"/>
+      <c r="B14" s="369"/>
+      <c r="C14" s="359"/>
+      <c r="D14" s="359"/>
+      <c r="E14" s="359"/>
+      <c r="F14" s="359"/>
       <c r="G14" s="188"/>
       <c r="H14" s="188"/>
       <c r="I14" s="188"/>
@@ -6499,18 +6510,18 @@
       <c r="B15" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="399" t="s">
+      <c r="C15" s="362" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="344"/>
-      <c r="E15" s="344"/>
-      <c r="F15" s="344"/>
-      <c r="G15" s="344"/>
-      <c r="H15" s="344"/>
-      <c r="I15" s="344"/>
-      <c r="J15" s="344"/>
-      <c r="K15" s="344"/>
-      <c r="L15" s="334"/>
+      <c r="D15" s="363"/>
+      <c r="E15" s="363"/>
+      <c r="F15" s="363"/>
+      <c r="G15" s="363"/>
+      <c r="H15" s="363"/>
+      <c r="I15" s="363"/>
+      <c r="J15" s="363"/>
+      <c r="K15" s="363"/>
+      <c r="L15" s="351"/>
       <c r="M15" s="202"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6519,19 +6530,19 @@
       <c r="C16" s="140" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="403" t="s">
+      <c r="D16" s="357" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="394"/>
-      <c r="F16" s="394"/>
-      <c r="G16" s="418" t="s">
+      <c r="E16" s="353"/>
+      <c r="F16" s="353"/>
+      <c r="G16" s="380" t="s">
         <v>80</v>
       </c>
-      <c r="H16" s="337"/>
-      <c r="I16" s="337"/>
-      <c r="J16" s="337"/>
-      <c r="K16" s="337"/>
-      <c r="L16" s="338"/>
+      <c r="H16" s="367"/>
+      <c r="I16" s="367"/>
+      <c r="J16" s="367"/>
+      <c r="K16" s="367"/>
+      <c r="L16" s="368"/>
       <c r="M16" s="202"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6540,20 +6551,20 @@
       <c r="C17" s="141" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="390" t="s">
+      <c r="D17" s="355" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="383"/>
-      <c r="F17" s="383"/>
-      <c r="G17" s="408" t="str">
+      <c r="E17" s="356"/>
+      <c r="F17" s="356"/>
+      <c r="G17" s="387" t="str">
         <f>CAPA!C3</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="H17" s="392"/>
-      <c r="I17" s="392"/>
-      <c r="J17" s="392"/>
-      <c r="K17" s="392"/>
-      <c r="L17" s="409"/>
+      <c r="H17" s="375"/>
+      <c r="I17" s="375"/>
+      <c r="J17" s="375"/>
+      <c r="K17" s="375"/>
+      <c r="L17" s="376"/>
       <c r="M17" s="202"/>
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6563,12 +6574,12 @@
       <c r="D18" s="310"/>
       <c r="E18" s="310"/>
       <c r="F18" s="310"/>
-      <c r="G18" s="389"/>
-      <c r="H18" s="389"/>
-      <c r="I18" s="389"/>
-      <c r="J18" s="389"/>
-      <c r="K18" s="389"/>
-      <c r="L18" s="410"/>
+      <c r="G18" s="388"/>
+      <c r="H18" s="388"/>
+      <c r="I18" s="388"/>
+      <c r="J18" s="388"/>
+      <c r="K18" s="388"/>
+      <c r="L18" s="389"/>
       <c r="M18" s="202"/>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6577,18 +6588,18 @@
       <c r="C19" s="141" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="390" t="s">
+      <c r="D19" s="355" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="383"/>
-      <c r="F19" s="383"/>
-      <c r="G19" s="407" t="s">
+      <c r="E19" s="356"/>
+      <c r="F19" s="356"/>
+      <c r="G19" s="386" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="401"/>
-      <c r="I19" s="401"/>
-      <c r="J19" s="401"/>
-      <c r="K19" s="401"/>
+      <c r="H19" s="377"/>
+      <c r="I19" s="377"/>
+      <c r="J19" s="377"/>
+      <c r="K19" s="377"/>
       <c r="L19" s="207" t="s">
         <v>86</v>
       </c>
@@ -6596,15 +6607,15 @@
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="421"/>
-      <c r="C20" s="390" t="s">
+      <c r="B20" s="382"/>
+      <c r="C20" s="355" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="388" t="s">
+      <c r="D20" s="402" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="386"/>
-      <c r="F20" s="386"/>
+      <c r="E20" s="379"/>
+      <c r="F20" s="379"/>
       <c r="G20" s="72" t="s">
         <v>89</v>
       </c>
@@ -6623,11 +6634,11 @@
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="200"/>
-      <c r="B21" s="422"/>
-      <c r="C21" s="389"/>
-      <c r="D21" s="389"/>
-      <c r="E21" s="389"/>
-      <c r="F21" s="389"/>
+      <c r="B21" s="383"/>
+      <c r="C21" s="388"/>
+      <c r="D21" s="388"/>
+      <c r="E21" s="388"/>
+      <c r="F21" s="388"/>
       <c r="G21" s="72" t="s">
         <v>93</v>
       </c>
@@ -6648,19 +6659,19 @@
       <c r="C22" s="141" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="390" t="s">
+      <c r="D22" s="355" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="383"/>
-      <c r="F22" s="383"/>
-      <c r="G22" s="419" t="s">
+      <c r="E22" s="356"/>
+      <c r="F22" s="356"/>
+      <c r="G22" s="352" t="s">
         <v>98</v>
       </c>
-      <c r="H22" s="394"/>
-      <c r="I22" s="394"/>
-      <c r="J22" s="394"/>
-      <c r="K22" s="394"/>
-      <c r="L22" s="395"/>
+      <c r="H22" s="353"/>
+      <c r="I22" s="353"/>
+      <c r="J22" s="353"/>
+      <c r="K22" s="353"/>
+      <c r="L22" s="354"/>
       <c r="M22" s="202"/>
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6669,19 +6680,19 @@
       <c r="C23" s="141" t="s">
         <v>99</v>
       </c>
-      <c r="D23" s="390" t="s">
+      <c r="D23" s="355" t="s">
         <v>100</v>
       </c>
-      <c r="E23" s="383"/>
-      <c r="F23" s="383"/>
-      <c r="G23" s="405" t="s">
+      <c r="E23" s="356"/>
+      <c r="F23" s="356"/>
+      <c r="G23" s="360" t="s">
         <v>101</v>
       </c>
-      <c r="H23" s="383"/>
-      <c r="I23" s="383"/>
-      <c r="J23" s="383"/>
-      <c r="K23" s="383"/>
-      <c r="L23" s="384"/>
+      <c r="H23" s="356"/>
+      <c r="I23" s="356"/>
+      <c r="J23" s="356"/>
+      <c r="K23" s="356"/>
+      <c r="L23" s="361"/>
       <c r="M23" s="202"/>
     </row>
     <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6690,19 +6701,19 @@
       <c r="C24" s="141" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="390" t="s">
+      <c r="D24" s="355" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="383"/>
-      <c r="F24" s="383"/>
-      <c r="G24" s="405" t="s">
+      <c r="E24" s="356"/>
+      <c r="F24" s="356"/>
+      <c r="G24" s="360" t="s">
         <v>104</v>
       </c>
-      <c r="H24" s="383"/>
-      <c r="I24" s="383"/>
-      <c r="J24" s="383"/>
-      <c r="K24" s="383"/>
-      <c r="L24" s="384"/>
+      <c r="H24" s="356"/>
+      <c r="I24" s="356"/>
+      <c r="J24" s="356"/>
+      <c r="K24" s="356"/>
+      <c r="L24" s="361"/>
       <c r="M24" s="202"/>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6711,17 +6722,17 @@
       <c r="C25" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="D25" s="411" t="s">
+      <c r="D25" s="390" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="383"/>
-      <c r="F25" s="383"/>
-      <c r="G25" s="383"/>
-      <c r="H25" s="383"/>
-      <c r="I25" s="383"/>
-      <c r="J25" s="383"/>
-      <c r="K25" s="383"/>
-      <c r="L25" s="384"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
+      <c r="G25" s="356"/>
+      <c r="H25" s="356"/>
+      <c r="I25" s="356"/>
+      <c r="J25" s="356"/>
+      <c r="K25" s="356"/>
+      <c r="L25" s="361"/>
       <c r="M25" s="202"/>
     </row>
     <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6731,18 +6742,18 @@
       <c r="D26" s="141" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="390" t="s">
+      <c r="E26" s="355" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="383"/>
-      <c r="G26" s="383"/>
-      <c r="H26" s="383"/>
-      <c r="I26" s="405" t="s">
+      <c r="F26" s="356"/>
+      <c r="G26" s="356"/>
+      <c r="H26" s="356"/>
+      <c r="I26" s="360" t="s">
         <v>109</v>
       </c>
-      <c r="J26" s="383"/>
-      <c r="K26" s="383"/>
-      <c r="L26" s="384"/>
+      <c r="J26" s="356"/>
+      <c r="K26" s="356"/>
+      <c r="L26" s="361"/>
       <c r="M26" s="202"/>
     </row>
     <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6752,16 +6763,16 @@
       <c r="D27" s="141" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="390" t="s">
+      <c r="E27" s="355" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="383"/>
-      <c r="G27" s="383"/>
-      <c r="H27" s="383"/>
-      <c r="I27" s="382"/>
-      <c r="J27" s="383"/>
-      <c r="K27" s="383"/>
-      <c r="L27" s="384"/>
+      <c r="F27" s="356"/>
+      <c r="G27" s="356"/>
+      <c r="H27" s="356"/>
+      <c r="I27" s="391"/>
+      <c r="J27" s="356"/>
+      <c r="K27" s="356"/>
+      <c r="L27" s="361"/>
       <c r="M27" s="202"/>
     </row>
     <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6771,12 +6782,12 @@
       <c r="D28" s="141" t="s">
         <v>112</v>
       </c>
-      <c r="E28" s="390" t="s">
+      <c r="E28" s="355" t="s">
         <v>113</v>
       </c>
-      <c r="F28" s="383"/>
-      <c r="G28" s="383"/>
-      <c r="H28" s="383"/>
+      <c r="F28" s="356"/>
+      <c r="G28" s="356"/>
+      <c r="H28" s="356"/>
       <c r="I28" s="186"/>
       <c r="J28" s="141"/>
       <c r="K28" s="141"/>
@@ -6789,17 +6800,17 @@
       <c r="C29" s="141" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="390" t="s">
+      <c r="D29" s="355" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="383"/>
-      <c r="F29" s="383"/>
-      <c r="G29" s="383"/>
-      <c r="H29" s="396">
+      <c r="E29" s="356"/>
+      <c r="F29" s="356"/>
+      <c r="G29" s="356"/>
+      <c r="H29" s="394">
         <f>CAPA!D4</f>
         <v>0</v>
       </c>
-      <c r="I29" s="383"/>
+      <c r="I29" s="356"/>
       <c r="J29" s="308" t="s">
         <v>40</v>
       </c>
@@ -6813,17 +6824,17 @@
       <c r="C30" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="390" t="s">
+      <c r="D30" s="355" t="s">
         <v>117</v>
       </c>
-      <c r="E30" s="383"/>
-      <c r="F30" s="383"/>
-      <c r="G30" s="383"/>
-      <c r="H30" s="382"/>
-      <c r="I30" s="383"/>
-      <c r="J30" s="383"/>
-      <c r="K30" s="383"/>
-      <c r="L30" s="384"/>
+      <c r="E30" s="356"/>
+      <c r="F30" s="356"/>
+      <c r="G30" s="356"/>
+      <c r="H30" s="391"/>
+      <c r="I30" s="356"/>
+      <c r="J30" s="356"/>
+      <c r="K30" s="356"/>
+      <c r="L30" s="361"/>
       <c r="M30" s="202"/>
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6832,17 +6843,17 @@
       <c r="C31" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="416" t="s">
+      <c r="D31" s="358" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="401"/>
-      <c r="F31" s="401"/>
-      <c r="G31" s="401"/>
-      <c r="H31" s="400"/>
-      <c r="I31" s="401"/>
-      <c r="J31" s="401"/>
-      <c r="K31" s="401"/>
-      <c r="L31" s="402"/>
+      <c r="E31" s="377"/>
+      <c r="F31" s="377"/>
+      <c r="G31" s="377"/>
+      <c r="H31" s="397"/>
+      <c r="I31" s="377"/>
+      <c r="J31" s="377"/>
+      <c r="K31" s="377"/>
+      <c r="L31" s="398"/>
       <c r="M31" s="202"/>
     </row>
     <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6850,73 +6861,73 @@
       <c r="B32" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="C32" s="399" t="s">
+      <c r="C32" s="362" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="344"/>
-      <c r="E32" s="344"/>
-      <c r="F32" s="344"/>
-      <c r="G32" s="344"/>
-      <c r="H32" s="344"/>
-      <c r="I32" s="344"/>
-      <c r="J32" s="344"/>
-      <c r="K32" s="344"/>
-      <c r="L32" s="334"/>
+      <c r="D32" s="363"/>
+      <c r="E32" s="363"/>
+      <c r="F32" s="363"/>
+      <c r="G32" s="363"/>
+      <c r="H32" s="363"/>
+      <c r="I32" s="363"/>
+      <c r="J32" s="363"/>
+      <c r="K32" s="363"/>
+      <c r="L32" s="351"/>
       <c r="M32" s="202"/>
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
-      <c r="B33" s="398" t="s">
+      <c r="B33" s="396" t="s">
         <v>122</v>
       </c>
-      <c r="C33" s="337"/>
-      <c r="D33" s="337"/>
-      <c r="E33" s="337"/>
+      <c r="C33" s="367"/>
+      <c r="D33" s="367"/>
+      <c r="E33" s="367"/>
       <c r="F33" s="72">
         <v>10</v>
       </c>
-      <c r="G33" s="404" t="s">
+      <c r="G33" s="384" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="337"/>
-      <c r="I33" s="337"/>
-      <c r="J33" s="337"/>
-      <c r="K33" s="337"/>
-      <c r="L33" s="338"/>
+      <c r="H33" s="367"/>
+      <c r="I33" s="367"/>
+      <c r="J33" s="367"/>
+      <c r="K33" s="367"/>
+      <c r="L33" s="368"/>
       <c r="M33" s="202"/>
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="200"/>
-      <c r="B34" s="420" t="s">
+      <c r="B34" s="381" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="392"/>
-      <c r="D34" s="392"/>
-      <c r="E34" s="392"/>
-      <c r="F34" s="392"/>
-      <c r="G34" s="392"/>
-      <c r="H34" s="392"/>
-      <c r="I34" s="392"/>
-      <c r="J34" s="392"/>
-      <c r="K34" s="392"/>
-      <c r="L34" s="409"/>
+      <c r="C34" s="375"/>
+      <c r="D34" s="375"/>
+      <c r="E34" s="375"/>
+      <c r="F34" s="375"/>
+      <c r="G34" s="375"/>
+      <c r="H34" s="375"/>
+      <c r="I34" s="375"/>
+      <c r="J34" s="375"/>
+      <c r="K34" s="375"/>
+      <c r="L34" s="376"/>
       <c r="M34" s="202"/>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="200"/>
-      <c r="B35" s="381" t="s">
+      <c r="B35" s="399" t="s">
         <v>125</v>
       </c>
-      <c r="C35" s="340"/>
-      <c r="D35" s="340"/>
-      <c r="E35" s="340"/>
-      <c r="F35" s="340"/>
-      <c r="G35" s="340"/>
-      <c r="H35" s="340"/>
-      <c r="I35" s="340"/>
-      <c r="J35" s="340"/>
-      <c r="K35" s="340"/>
-      <c r="L35" s="341"/>
+      <c r="C35" s="359"/>
+      <c r="D35" s="359"/>
+      <c r="E35" s="359"/>
+      <c r="F35" s="359"/>
+      <c r="G35" s="359"/>
+      <c r="H35" s="359"/>
+      <c r="I35" s="359"/>
+      <c r="J35" s="359"/>
+      <c r="K35" s="359"/>
+      <c r="L35" s="370"/>
       <c r="M35" s="202"/>
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6924,24 +6935,24 @@
       <c r="B36" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="C36" s="399" t="s">
+      <c r="C36" s="362" t="s">
         <v>127</v>
       </c>
-      <c r="D36" s="344"/>
-      <c r="E36" s="344"/>
-      <c r="F36" s="344"/>
-      <c r="G36" s="344"/>
-      <c r="H36" s="344"/>
-      <c r="I36" s="344"/>
-      <c r="J36" s="344"/>
-      <c r="K36" s="344"/>
-      <c r="L36" s="334"/>
+      <c r="D36" s="363"/>
+      <c r="E36" s="363"/>
+      <c r="F36" s="363"/>
+      <c r="G36" s="363"/>
+      <c r="H36" s="363"/>
+      <c r="I36" s="363"/>
+      <c r="J36" s="363"/>
+      <c r="K36" s="363"/>
+      <c r="L36" s="351"/>
       <c r="M36" s="202"/>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="200"/>
       <c r="B37" s="46" t="str">
-        <f>CAPA!B11</f>
+        <f>CAPA!A11</f>
         <v>{CIDADE} , {DATA HOJE}</v>
       </c>
       <c r="C37" s="27"/>
@@ -6979,27 +6990,27 @@
       <c r="B41" s="209" t="s">
         <v>128</v>
       </c>
-      <c r="G41" s="391" t="s">
+      <c r="G41" s="392" t="s">
         <v>54</v>
       </c>
-      <c r="H41" s="392"/>
-      <c r="I41" s="392"/>
-      <c r="J41" s="392"/>
-      <c r="K41" s="392"/>
+      <c r="H41" s="375"/>
+      <c r="I41" s="375"/>
+      <c r="J41" s="375"/>
+      <c r="K41" s="375"/>
       <c r="L41" s="4"/>
       <c r="M41" s="202"/>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="200"/>
       <c r="B42" s="12"/>
-      <c r="G42" s="397" t="str">
+      <c r="G42" s="395" t="str">
         <f>F5</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="H42" s="392"/>
-      <c r="I42" s="392"/>
-      <c r="J42" s="392"/>
-      <c r="K42" s="392"/>
+      <c r="H42" s="375"/>
+      <c r="I42" s="375"/>
+      <c r="J42" s="375"/>
+      <c r="K42" s="375"/>
       <c r="L42" s="4"/>
       <c r="M42" s="202"/>
     </row>
@@ -7032,27 +7043,27 @@
       <c r="B47" s="209" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="391" t="s">
+      <c r="G47" s="392" t="s">
         <v>54</v>
       </c>
-      <c r="H47" s="392"/>
-      <c r="I47" s="392"/>
-      <c r="J47" s="392"/>
-      <c r="K47" s="392"/>
+      <c r="H47" s="375"/>
+      <c r="I47" s="375"/>
+      <c r="J47" s="375"/>
+      <c r="K47" s="375"/>
       <c r="L47" s="4"/>
       <c r="M47" s="202"/>
     </row>
     <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="200"/>
       <c r="B48" s="12"/>
-      <c r="G48" s="397" t="str">
-        <f>CAPA!B14</f>
+      <c r="G48" s="395" t="str">
+        <f>CAPA!A14</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="H48" s="392"/>
-      <c r="I48" s="392"/>
-      <c r="J48" s="392"/>
-      <c r="K48" s="392"/>
+      <c r="H48" s="375"/>
+      <c r="I48" s="375"/>
+      <c r="J48" s="375"/>
+      <c r="K48" s="375"/>
       <c r="L48" s="4"/>
       <c r="M48" s="202"/>
     </row>
@@ -7070,79 +7081,99 @@
     </row>
     <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="200"/>
-      <c r="B51" s="415" t="s">
+      <c r="B51" s="374" t="s">
         <v>130</v>
       </c>
-      <c r="C51" s="392"/>
-      <c r="D51" s="392"/>
-      <c r="E51" s="392"/>
-      <c r="F51" s="392"/>
-      <c r="G51" s="392"/>
-      <c r="H51" s="392"/>
-      <c r="I51" s="392"/>
-      <c r="J51" s="392"/>
-      <c r="K51" s="392"/>
-      <c r="L51" s="409"/>
+      <c r="C51" s="375"/>
+      <c r="D51" s="375"/>
+      <c r="E51" s="375"/>
+      <c r="F51" s="375"/>
+      <c r="G51" s="375"/>
+      <c r="H51" s="375"/>
+      <c r="I51" s="375"/>
+      <c r="J51" s="375"/>
+      <c r="K51" s="375"/>
+      <c r="L51" s="376"/>
       <c r="M51" s="202"/>
     </row>
     <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="200"/>
-      <c r="B52" s="339"/>
-      <c r="C52" s="340"/>
-      <c r="D52" s="340"/>
-      <c r="E52" s="340"/>
-      <c r="F52" s="340"/>
-      <c r="G52" s="340"/>
-      <c r="H52" s="340"/>
-      <c r="I52" s="340"/>
-      <c r="J52" s="340"/>
-      <c r="K52" s="340"/>
-      <c r="L52" s="341"/>
+      <c r="B52" s="369"/>
+      <c r="C52" s="359"/>
+      <c r="D52" s="359"/>
+      <c r="E52" s="359"/>
+      <c r="F52" s="359"/>
+      <c r="G52" s="359"/>
+      <c r="H52" s="359"/>
+      <c r="I52" s="359"/>
+      <c r="J52" s="359"/>
+      <c r="K52" s="359"/>
+      <c r="L52" s="370"/>
       <c r="M52" s="202"/>
     </row>
     <row r="53" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="203"/>
-      <c r="B53" s="414"/>
-      <c r="C53" s="351"/>
-      <c r="D53" s="351"/>
-      <c r="E53" s="351"/>
-      <c r="F53" s="351"/>
-      <c r="G53" s="351"/>
-      <c r="H53" s="351"/>
-      <c r="I53" s="351"/>
-      <c r="J53" s="351"/>
-      <c r="K53" s="351"/>
-      <c r="L53" s="351"/>
+      <c r="B53" s="372"/>
+      <c r="C53" s="373"/>
+      <c r="D53" s="373"/>
+      <c r="E53" s="373"/>
+      <c r="F53" s="373"/>
+      <c r="G53" s="373"/>
+      <c r="H53" s="373"/>
+      <c r="I53" s="373"/>
+      <c r="J53" s="373"/>
+      <c r="K53" s="373"/>
+      <c r="L53" s="373"/>
       <c r="M53" s="204"/>
     </row>
     <row r="54" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
-      <c r="B54" s="391"/>
-      <c r="C54" s="392"/>
-      <c r="D54" s="392"/>
-      <c r="E54" s="392"/>
-      <c r="F54" s="392"/>
-      <c r="G54" s="392"/>
-      <c r="H54" s="392"/>
-      <c r="I54" s="392"/>
-      <c r="J54" s="392"/>
-      <c r="K54" s="392"/>
-      <c r="L54" s="392"/>
+      <c r="B54" s="392"/>
+      <c r="C54" s="375"/>
+      <c r="D54" s="375"/>
+      <c r="E54" s="375"/>
+      <c r="F54" s="375"/>
+      <c r="G54" s="375"/>
+      <c r="H54" s="375"/>
+      <c r="I54" s="375"/>
+      <c r="J54" s="375"/>
+      <c r="K54" s="375"/>
+      <c r="L54" s="375"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="C9:L9"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="B35:L35"/>
+    <mergeCell ref="H30:L30"/>
+    <mergeCell ref="F7:L8"/>
+    <mergeCell ref="D20:F21"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="H31:L31"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="G47:K47"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="C36:L36"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="G17:L18"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="G12:L12"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="B2:J3"/>
@@ -7159,39 +7190,19 @@
     <mergeCell ref="B34:L34"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="D13:F14"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="E27:H27"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="G17:L18"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B54:L54"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="G42:K42"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="H31:L31"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G48:K48"/>
-    <mergeCell ref="G47:K47"/>
-    <mergeCell ref="G41:K41"/>
-    <mergeCell ref="C36:L36"/>
-    <mergeCell ref="B35:L35"/>
-    <mergeCell ref="H30:L30"/>
-    <mergeCell ref="F7:L8"/>
-    <mergeCell ref="D20:F21"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="E26:H26"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -7215,95 +7226,95 @@
   <sheetData>
     <row r="1" spans="1:30" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="210"/>
-      <c r="B1" s="438"/>
-      <c r="C1" s="367"/>
-      <c r="D1" s="367"/>
-      <c r="E1" s="367"/>
-      <c r="F1" s="367"/>
-      <c r="G1" s="367"/>
-      <c r="H1" s="367"/>
-      <c r="I1" s="367"/>
-      <c r="J1" s="367"/>
-      <c r="K1" s="367"/>
-      <c r="L1" s="367"/>
-      <c r="M1" s="367"/>
-      <c r="N1" s="367"/>
-      <c r="O1" s="367"/>
-      <c r="P1" s="367"/>
-      <c r="Q1" s="367"/>
-      <c r="R1" s="367"/>
-      <c r="S1" s="367"/>
-      <c r="T1" s="367"/>
+      <c r="B1" s="409"/>
+      <c r="C1" s="339"/>
+      <c r="D1" s="339"/>
+      <c r="E1" s="339"/>
+      <c r="F1" s="339"/>
+      <c r="G1" s="339"/>
+      <c r="H1" s="339"/>
+      <c r="I1" s="339"/>
+      <c r="J1" s="339"/>
+      <c r="K1" s="339"/>
+      <c r="L1" s="339"/>
+      <c r="M1" s="339"/>
+      <c r="N1" s="339"/>
+      <c r="O1" s="339"/>
+      <c r="P1" s="339"/>
+      <c r="Q1" s="339"/>
+      <c r="R1" s="339"/>
+      <c r="S1" s="339"/>
+      <c r="T1" s="339"/>
       <c r="U1" s="211"/>
     </row>
     <row r="2" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="212"/>
-      <c r="B2" s="435" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="436"/>
-      <c r="D2" s="436"/>
-      <c r="E2" s="436"/>
-      <c r="F2" s="436"/>
-      <c r="G2" s="436"/>
-      <c r="H2" s="436"/>
-      <c r="I2" s="436"/>
-      <c r="J2" s="436"/>
-      <c r="K2" s="436"/>
-      <c r="L2" s="436"/>
-      <c r="M2" s="436"/>
-      <c r="N2" s="436"/>
-      <c r="O2" s="436"/>
-      <c r="P2" s="436"/>
-      <c r="Q2" s="436"/>
-      <c r="R2" s="436"/>
-      <c r="S2" s="436"/>
-      <c r="T2" s="436"/>
+      <c r="B2" s="403" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="404"/>
+      <c r="D2" s="404"/>
+      <c r="E2" s="404"/>
+      <c r="F2" s="404"/>
+      <c r="G2" s="404"/>
+      <c r="H2" s="404"/>
+      <c r="I2" s="404"/>
+      <c r="J2" s="404"/>
+      <c r="K2" s="404"/>
+      <c r="L2" s="404"/>
+      <c r="M2" s="404"/>
+      <c r="N2" s="404"/>
+      <c r="O2" s="404"/>
+      <c r="P2" s="404"/>
+      <c r="Q2" s="404"/>
+      <c r="R2" s="404"/>
+      <c r="S2" s="404"/>
+      <c r="T2" s="404"/>
       <c r="U2" s="213"/>
     </row>
     <row r="3" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="212"/>
-      <c r="B3" s="432" t="s">
+      <c r="B3" s="413" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="340"/>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="340"/>
-      <c r="K3" s="340"/>
-      <c r="L3" s="340"/>
-      <c r="M3" s="340"/>
-      <c r="N3" s="340"/>
-      <c r="O3" s="340"/>
-      <c r="P3" s="340"/>
-      <c r="Q3" s="340"/>
-      <c r="R3" s="340"/>
-      <c r="S3" s="340"/>
-      <c r="T3" s="340"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="359"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="359"/>
+      <c r="M3" s="359"/>
+      <c r="N3" s="359"/>
+      <c r="O3" s="359"/>
+      <c r="P3" s="359"/>
+      <c r="Q3" s="359"/>
+      <c r="R3" s="359"/>
+      <c r="S3" s="359"/>
+      <c r="T3" s="359"/>
       <c r="U3" s="213"/>
     </row>
     <row r="4" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="212"/>
-      <c r="B4" s="423" t="s">
+      <c r="B4" s="414" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="344"/>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="344"/>
-      <c r="I4" s="344"/>
-      <c r="J4" s="344"/>
-      <c r="K4" s="344"/>
-      <c r="L4" s="344"/>
-      <c r="M4" s="344"/>
-      <c r="N4" s="344"/>
-      <c r="O4" s="334"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
+      <c r="L4" s="363"/>
+      <c r="M4" s="363"/>
+      <c r="N4" s="363"/>
+      <c r="O4" s="351"/>
       <c r="P4" s="259" t="s">
         <v>58</v>
       </c>
@@ -7318,50 +7329,50 @@
     </row>
     <row r="5" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="212"/>
-      <c r="B5" s="431" t="s">
+      <c r="B5" s="419" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="337"/>
-      <c r="D5" s="427" t="str">
+      <c r="C5" s="367"/>
+      <c r="D5" s="417" t="str">
         <f>CAPA!C3</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="337"/>
-      <c r="J5" s="337"/>
-      <c r="K5" s="337"/>
-      <c r="L5" s="337"/>
-      <c r="M5" s="337"/>
-      <c r="N5" s="337"/>
-      <c r="O5" s="338"/>
-      <c r="P5" s="439" t="s">
+      <c r="E5" s="367"/>
+      <c r="F5" s="367"/>
+      <c r="G5" s="367"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="367"/>
+      <c r="K5" s="367"/>
+      <c r="L5" s="367"/>
+      <c r="M5" s="367"/>
+      <c r="N5" s="367"/>
+      <c r="O5" s="368"/>
+      <c r="P5" s="411" t="s">
         <v>5</v>
       </c>
-      <c r="Q5" s="337"/>
-      <c r="R5" s="337"/>
-      <c r="S5" s="337"/>
-      <c r="T5" s="338"/>
+      <c r="Q5" s="367"/>
+      <c r="R5" s="367"/>
+      <c r="S5" s="367"/>
+      <c r="T5" s="368"/>
       <c r="U5" s="213"/>
     </row>
     <row r="6" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="212"/>
-      <c r="B6" s="339"/>
-      <c r="C6" s="340"/>
-      <c r="D6" s="340"/>
-      <c r="E6" s="340"/>
-      <c r="F6" s="340"/>
-      <c r="G6" s="340"/>
-      <c r="H6" s="340"/>
-      <c r="I6" s="340"/>
-      <c r="J6" s="340"/>
-      <c r="K6" s="340"/>
-      <c r="L6" s="340"/>
-      <c r="M6" s="340"/>
-      <c r="N6" s="340"/>
-      <c r="O6" s="341"/>
+      <c r="B6" s="369"/>
+      <c r="C6" s="359"/>
+      <c r="D6" s="359"/>
+      <c r="E6" s="359"/>
+      <c r="F6" s="359"/>
+      <c r="G6" s="359"/>
+      <c r="H6" s="359"/>
+      <c r="I6" s="359"/>
+      <c r="J6" s="359"/>
+      <c r="K6" s="359"/>
+      <c r="L6" s="359"/>
+      <c r="M6" s="359"/>
+      <c r="N6" s="359"/>
+      <c r="O6" s="370"/>
       <c r="P6" s="75" t="s">
         <v>6</v>
       </c>
@@ -7375,29 +7386,29 @@
     </row>
     <row r="7" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="212"/>
-      <c r="B7" s="437" t="s">
+      <c r="B7" s="407" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="344"/>
-      <c r="D7" s="344"/>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
-      <c r="G7" s="344"/>
-      <c r="H7" s="344"/>
-      <c r="I7" s="344"/>
-      <c r="J7" s="344"/>
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
+      <c r="E7" s="363"/>
+      <c r="F7" s="363"/>
+      <c r="G7" s="363"/>
+      <c r="H7" s="363"/>
+      <c r="I7" s="363"/>
+      <c r="J7" s="363"/>
       <c r="K7" s="267"/>
       <c r="L7" s="268"/>
-      <c r="M7" s="423" t="s">
+      <c r="M7" s="414" t="s">
         <v>8</v>
       </c>
-      <c r="N7" s="344"/>
-      <c r="O7" s="344"/>
-      <c r="P7" s="344"/>
-      <c r="Q7" s="344"/>
-      <c r="R7" s="344"/>
-      <c r="S7" s="344"/>
-      <c r="T7" s="334"/>
+      <c r="N7" s="363"/>
+      <c r="O7" s="363"/>
+      <c r="P7" s="363"/>
+      <c r="Q7" s="363"/>
+      <c r="R7" s="363"/>
+      <c r="S7" s="363"/>
+      <c r="T7" s="351"/>
       <c r="U7" s="213"/>
     </row>
     <row r="8" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7486,110 +7497,110 @@
     <row r="11" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="214"/>
       <c r="B11" s="159"/>
-      <c r="C11" s="433" t="s">
+      <c r="C11" s="412" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="344"/>
-      <c r="E11" s="344"/>
-      <c r="F11" s="344"/>
-      <c r="G11" s="344"/>
-      <c r="H11" s="344"/>
-      <c r="I11" s="344"/>
-      <c r="J11" s="344"/>
-      <c r="K11" s="344"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="430" t="s">
+      <c r="D11" s="363"/>
+      <c r="E11" s="363"/>
+      <c r="F11" s="363"/>
+      <c r="G11" s="363"/>
+      <c r="H11" s="363"/>
+      <c r="I11" s="363"/>
+      <c r="J11" s="363"/>
+      <c r="K11" s="363"/>
+      <c r="L11" s="351"/>
+      <c r="M11" s="408" t="s">
         <v>136</v>
       </c>
-      <c r="N11" s="344"/>
-      <c r="O11" s="344"/>
-      <c r="P11" s="344"/>
-      <c r="Q11" s="334"/>
-      <c r="R11" s="428" t="s">
+      <c r="N11" s="363"/>
+      <c r="O11" s="363"/>
+      <c r="P11" s="363"/>
+      <c r="Q11" s="351"/>
+      <c r="R11" s="405" t="s">
         <v>137</v>
       </c>
-      <c r="S11" s="338"/>
-      <c r="T11" s="424" t="s">
+      <c r="S11" s="368"/>
+      <c r="T11" s="416" t="s">
         <v>138</v>
       </c>
       <c r="U11" s="215"/>
     </row>
     <row r="12" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="214"/>
-      <c r="B12" s="428" t="s">
+      <c r="B12" s="405" t="s">
         <v>139</v>
       </c>
-      <c r="C12" s="433" t="s">
+      <c r="C12" s="412" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="344"/>
-      <c r="E12" s="344"/>
-      <c r="F12" s="344"/>
-      <c r="G12" s="334"/>
-      <c r="H12" s="430" t="s">
+      <c r="D12" s="363"/>
+      <c r="E12" s="363"/>
+      <c r="F12" s="363"/>
+      <c r="G12" s="351"/>
+      <c r="H12" s="408" t="s">
         <v>141</v>
       </c>
-      <c r="I12" s="344"/>
-      <c r="J12" s="344"/>
-      <c r="K12" s="344"/>
-      <c r="L12" s="334"/>
-      <c r="M12" s="430" t="s">
+      <c r="I12" s="363"/>
+      <c r="J12" s="363"/>
+      <c r="K12" s="363"/>
+      <c r="L12" s="351"/>
+      <c r="M12" s="408" t="s">
         <v>142</v>
       </c>
-      <c r="N12" s="344"/>
-      <c r="O12" s="344"/>
-      <c r="P12" s="344"/>
-      <c r="Q12" s="334"/>
-      <c r="R12" s="429"/>
-      <c r="S12" s="409"/>
-      <c r="T12" s="425"/>
+      <c r="N12" s="363"/>
+      <c r="O12" s="363"/>
+      <c r="P12" s="363"/>
+      <c r="Q12" s="351"/>
+      <c r="R12" s="418"/>
+      <c r="S12" s="376"/>
+      <c r="T12" s="415"/>
       <c r="U12" s="215"/>
     </row>
     <row r="13" spans="1:30" s="53" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="216"/>
-      <c r="B13" s="425"/>
-      <c r="C13" s="428" t="s">
+      <c r="B13" s="415"/>
+      <c r="C13" s="405" t="s">
         <v>143</v>
       </c>
-      <c r="D13" s="428" t="s">
+      <c r="D13" s="405" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="334"/>
-      <c r="F13" s="434" t="s">
+      <c r="E13" s="351"/>
+      <c r="F13" s="410" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="334"/>
-      <c r="H13" s="428" t="s">
+      <c r="G13" s="351"/>
+      <c r="H13" s="405" t="s">
         <v>143</v>
       </c>
-      <c r="I13" s="428" t="s">
+      <c r="I13" s="405" t="s">
         <v>144</v>
       </c>
-      <c r="J13" s="334"/>
-      <c r="K13" s="434" t="s">
+      <c r="J13" s="351"/>
+      <c r="K13" s="410" t="s">
         <v>145</v>
       </c>
-      <c r="L13" s="334"/>
-      <c r="M13" s="428" t="s">
+      <c r="L13" s="351"/>
+      <c r="M13" s="405" t="s">
         <v>143</v>
       </c>
-      <c r="N13" s="428" t="s">
+      <c r="N13" s="405" t="s">
         <v>144</v>
       </c>
-      <c r="O13" s="334"/>
-      <c r="P13" s="434" t="s">
+      <c r="O13" s="351"/>
+      <c r="P13" s="410" t="s">
         <v>145</v>
       </c>
-      <c r="Q13" s="334"/>
-      <c r="R13" s="339"/>
-      <c r="S13" s="341"/>
-      <c r="T13" s="425"/>
+      <c r="Q13" s="351"/>
+      <c r="R13" s="369"/>
+      <c r="S13" s="370"/>
+      <c r="T13" s="415"/>
       <c r="U13" s="217"/>
     </row>
     <row r="14" spans="1:30" s="53" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="216"/>
-      <c r="B14" s="426"/>
-      <c r="C14" s="426"/>
+      <c r="B14" s="406"/>
+      <c r="C14" s="406"/>
       <c r="D14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7602,7 +7613,7 @@
       <c r="G14" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="H14" s="426"/>
+      <c r="H14" s="406"/>
       <c r="I14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7615,7 +7626,7 @@
       <c r="L14" s="151" t="s">
         <v>151</v>
       </c>
-      <c r="M14" s="426"/>
+      <c r="M14" s="406"/>
       <c r="N14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7634,7 +7645,7 @@
       <c r="S14" s="151" t="s">
         <v>155</v>
       </c>
-      <c r="T14" s="425"/>
+      <c r="T14" s="415"/>
       <c r="U14" s="217"/>
     </row>
     <row r="15" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7693,7 +7704,7 @@
       <c r="S15" s="15">
         <v>18</v>
       </c>
-      <c r="T15" s="426"/>
+      <c r="T15" s="406"/>
       <c r="U15" s="201"/>
       <c r="V15" s="10"/>
       <c r="W15" s="10"/>
@@ -8904,6 +8915,16 @@
     <row r="42" spans="1:21" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="T11:T15"/>
+    <mergeCell ref="D5:O6"/>
+    <mergeCell ref="R11:S13"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="B5:C6"/>
     <mergeCell ref="B2:T2"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="B7:J7"/>
@@ -8920,16 +8941,6 @@
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="T11:T15"/>
-    <mergeCell ref="D5:O6"/>
-    <mergeCell ref="R11:S13"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="M11:Q11"/>
-    <mergeCell ref="B5:C6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -8970,103 +8981,103 @@
   <sheetData>
     <row r="1" spans="1:23" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="223"/>
-      <c r="B1" s="441"/>
-      <c r="C1" s="356"/>
-      <c r="D1" s="356"/>
-      <c r="E1" s="356"/>
-      <c r="F1" s="356"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="356"/>
-      <c r="I1" s="356"/>
-      <c r="J1" s="356"/>
-      <c r="K1" s="356"/>
-      <c r="L1" s="356"/>
-      <c r="M1" s="356"/>
-      <c r="N1" s="356"/>
-      <c r="O1" s="356"/>
-      <c r="P1" s="356"/>
-      <c r="Q1" s="356"/>
-      <c r="R1" s="356"/>
-      <c r="S1" s="356"/>
-      <c r="T1" s="356"/>
-      <c r="U1" s="356"/>
-      <c r="V1" s="356"/>
+      <c r="B1" s="426"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
+      <c r="K1" s="365"/>
+      <c r="L1" s="365"/>
+      <c r="M1" s="365"/>
+      <c r="N1" s="365"/>
+      <c r="O1" s="365"/>
+      <c r="P1" s="365"/>
+      <c r="Q1" s="365"/>
+      <c r="R1" s="365"/>
+      <c r="S1" s="365"/>
+      <c r="T1" s="365"/>
+      <c r="U1" s="365"/>
+      <c r="V1" s="365"/>
       <c r="W1" s="224"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="354" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="337"/>
-      <c r="M2" s="337"/>
-      <c r="N2" s="337"/>
-      <c r="O2" s="337"/>
-      <c r="P2" s="337"/>
-      <c r="Q2" s="337"/>
-      <c r="R2" s="337"/>
-      <c r="S2" s="337"/>
-      <c r="T2" s="337"/>
-      <c r="U2" s="337"/>
-      <c r="V2" s="338"/>
+      <c r="B2" s="431" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
+      <c r="M2" s="367"/>
+      <c r="N2" s="367"/>
+      <c r="O2" s="367"/>
+      <c r="P2" s="367"/>
+      <c r="Q2" s="367"/>
+      <c r="R2" s="367"/>
+      <c r="S2" s="367"/>
+      <c r="T2" s="367"/>
+      <c r="U2" s="367"/>
+      <c r="V2" s="368"/>
       <c r="W2" s="202"/>
     </row>
     <row r="3" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="346" t="s">
+      <c r="B3" s="422" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="340"/>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="340"/>
-      <c r="K3" s="340"/>
-      <c r="L3" s="340"/>
-      <c r="M3" s="340"/>
-      <c r="N3" s="340"/>
-      <c r="O3" s="340"/>
-      <c r="P3" s="340"/>
-      <c r="Q3" s="340"/>
-      <c r="R3" s="340"/>
-      <c r="S3" s="340"/>
-      <c r="T3" s="340"/>
-      <c r="U3" s="340"/>
-      <c r="V3" s="341"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="359"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="359"/>
+      <c r="M3" s="359"/>
+      <c r="N3" s="359"/>
+      <c r="O3" s="359"/>
+      <c r="P3" s="359"/>
+      <c r="Q3" s="359"/>
+      <c r="R3" s="359"/>
+      <c r="S3" s="359"/>
+      <c r="T3" s="359"/>
+      <c r="U3" s="359"/>
+      <c r="V3" s="370"/>
       <c r="W3" s="202"/>
     </row>
     <row r="4" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="360" t="s">
+      <c r="B4" s="428" t="s">
         <v>160</v>
       </c>
-      <c r="C4" s="344"/>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="344"/>
-      <c r="I4" s="344"/>
-      <c r="J4" s="344"/>
-      <c r="K4" s="344"/>
-      <c r="L4" s="344"/>
-      <c r="M4" s="344"/>
-      <c r="N4" s="344"/>
-      <c r="O4" s="344"/>
-      <c r="P4" s="344"/>
-      <c r="Q4" s="334"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
+      <c r="L4" s="363"/>
+      <c r="M4" s="363"/>
+      <c r="N4" s="363"/>
+      <c r="O4" s="363"/>
+      <c r="P4" s="363"/>
+      <c r="Q4" s="351"/>
       <c r="R4" s="259" t="s">
         <v>58</v>
       </c>
@@ -9081,54 +9092,54 @@
     </row>
     <row r="5" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="442" t="s">
+      <c r="B5" s="427" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="337"/>
-      <c r="D5" s="427" t="str">
+      <c r="C5" s="367"/>
+      <c r="D5" s="417" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="337"/>
-      <c r="J5" s="337"/>
-      <c r="K5" s="337"/>
-      <c r="L5" s="337"/>
-      <c r="M5" s="337"/>
-      <c r="N5" s="337"/>
-      <c r="O5" s="337"/>
-      <c r="P5" s="337"/>
-      <c r="Q5" s="338"/>
-      <c r="R5" s="362" t="s">
+      <c r="E5" s="367"/>
+      <c r="F5" s="367"/>
+      <c r="G5" s="367"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="367"/>
+      <c r="K5" s="367"/>
+      <c r="L5" s="367"/>
+      <c r="M5" s="367"/>
+      <c r="N5" s="367"/>
+      <c r="O5" s="367"/>
+      <c r="P5" s="367"/>
+      <c r="Q5" s="368"/>
+      <c r="R5" s="425" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="344"/>
-      <c r="T5" s="344"/>
-      <c r="U5" s="344"/>
-      <c r="V5" s="334"/>
+      <c r="S5" s="363"/>
+      <c r="T5" s="363"/>
+      <c r="U5" s="363"/>
+      <c r="V5" s="351"/>
       <c r="W5" s="202"/>
     </row>
     <row r="6" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="225"/>
-      <c r="B6" s="339"/>
-      <c r="C6" s="340"/>
-      <c r="D6" s="340"/>
-      <c r="E6" s="340"/>
-      <c r="F6" s="340"/>
-      <c r="G6" s="340"/>
-      <c r="H6" s="340"/>
-      <c r="I6" s="340"/>
-      <c r="J6" s="340"/>
-      <c r="K6" s="340"/>
-      <c r="L6" s="340"/>
-      <c r="M6" s="340"/>
-      <c r="N6" s="340"/>
-      <c r="O6" s="340"/>
-      <c r="P6" s="340"/>
-      <c r="Q6" s="341"/>
+      <c r="B6" s="369"/>
+      <c r="C6" s="359"/>
+      <c r="D6" s="359"/>
+      <c r="E6" s="359"/>
+      <c r="F6" s="359"/>
+      <c r="G6" s="359"/>
+      <c r="H6" s="359"/>
+      <c r="I6" s="359"/>
+      <c r="J6" s="359"/>
+      <c r="K6" s="359"/>
+      <c r="L6" s="359"/>
+      <c r="M6" s="359"/>
+      <c r="N6" s="359"/>
+      <c r="O6" s="359"/>
+      <c r="P6" s="359"/>
+      <c r="Q6" s="370"/>
       <c r="R6" s="49" t="s">
         <v>6</v>
       </c>
@@ -9143,31 +9154,31 @@
     </row>
     <row r="7" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="225"/>
-      <c r="B7" s="449" t="s">
+      <c r="B7" s="433" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="344"/>
-      <c r="D7" s="344"/>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
-      <c r="G7" s="344"/>
-      <c r="H7" s="344"/>
-      <c r="I7" s="344"/>
-      <c r="J7" s="344"/>
-      <c r="K7" s="344"/>
-      <c r="L7" s="344"/>
-      <c r="M7" s="334"/>
-      <c r="N7" s="449" t="s">
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
+      <c r="E7" s="363"/>
+      <c r="F7" s="363"/>
+      <c r="G7" s="363"/>
+      <c r="H7" s="363"/>
+      <c r="I7" s="363"/>
+      <c r="J7" s="363"/>
+      <c r="K7" s="363"/>
+      <c r="L7" s="363"/>
+      <c r="M7" s="351"/>
+      <c r="N7" s="433" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="344"/>
-      <c r="P7" s="344"/>
-      <c r="Q7" s="344"/>
-      <c r="R7" s="344"/>
-      <c r="S7" s="344"/>
-      <c r="T7" s="344"/>
-      <c r="U7" s="344"/>
-      <c r="V7" s="334"/>
+      <c r="O7" s="363"/>
+      <c r="P7" s="363"/>
+      <c r="Q7" s="363"/>
+      <c r="R7" s="363"/>
+      <c r="S7" s="363"/>
+      <c r="T7" s="363"/>
+      <c r="U7" s="363"/>
+      <c r="V7" s="351"/>
       <c r="W7" s="226"/>
     </row>
     <row r="8" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9261,184 +9272,184 @@
     </row>
     <row r="11" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="296"/>
-      <c r="B11" s="440" t="s">
+      <c r="B11" s="421" t="s">
         <v>161</v>
       </c>
-      <c r="C11" s="443" t="s">
+      <c r="C11" s="429" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="344"/>
-      <c r="E11" s="344"/>
-      <c r="F11" s="344"/>
-      <c r="G11" s="344"/>
-      <c r="H11" s="344"/>
-      <c r="I11" s="344"/>
-      <c r="J11" s="344"/>
-      <c r="K11" s="344"/>
-      <c r="L11" s="344"/>
-      <c r="M11" s="334"/>
-      <c r="N11" s="444" t="s">
+      <c r="D11" s="363"/>
+      <c r="E11" s="363"/>
+      <c r="F11" s="363"/>
+      <c r="G11" s="363"/>
+      <c r="H11" s="363"/>
+      <c r="I11" s="363"/>
+      <c r="J11" s="363"/>
+      <c r="K11" s="363"/>
+      <c r="L11" s="363"/>
+      <c r="M11" s="351"/>
+      <c r="N11" s="423" t="s">
         <v>162</v>
       </c>
-      <c r="O11" s="447" t="s">
+      <c r="O11" s="420" t="s">
         <v>136</v>
       </c>
-      <c r="P11" s="344"/>
-      <c r="Q11" s="344"/>
-      <c r="R11" s="344"/>
-      <c r="S11" s="334"/>
-      <c r="T11" s="448" t="s">
+      <c r="P11" s="363"/>
+      <c r="Q11" s="363"/>
+      <c r="R11" s="363"/>
+      <c r="S11" s="351"/>
+      <c r="T11" s="432" t="s">
         <v>163</v>
       </c>
-      <c r="U11" s="338"/>
-      <c r="V11" s="445" t="s">
+      <c r="U11" s="368"/>
+      <c r="V11" s="430" t="s">
         <v>164</v>
       </c>
       <c r="W11" s="227"/>
     </row>
     <row r="12" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="296"/>
-      <c r="B12" s="425"/>
-      <c r="C12" s="443" t="s">
+      <c r="B12" s="415"/>
+      <c r="C12" s="429" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="344"/>
-      <c r="E12" s="344"/>
-      <c r="F12" s="344"/>
-      <c r="G12" s="334"/>
-      <c r="H12" s="447" t="s">
+      <c r="D12" s="363"/>
+      <c r="E12" s="363"/>
+      <c r="F12" s="363"/>
+      <c r="G12" s="351"/>
+      <c r="H12" s="420" t="s">
         <v>141</v>
       </c>
-      <c r="I12" s="344"/>
-      <c r="J12" s="344"/>
-      <c r="K12" s="344"/>
-      <c r="L12" s="334"/>
-      <c r="M12" s="444" t="s">
+      <c r="I12" s="363"/>
+      <c r="J12" s="363"/>
+      <c r="K12" s="363"/>
+      <c r="L12" s="351"/>
+      <c r="M12" s="423" t="s">
         <v>165</v>
       </c>
-      <c r="N12" s="425"/>
-      <c r="O12" s="447" t="s">
+      <c r="N12" s="415"/>
+      <c r="O12" s="420" t="s">
         <v>142</v>
       </c>
-      <c r="P12" s="344"/>
-      <c r="Q12" s="344"/>
-      <c r="R12" s="344"/>
-      <c r="S12" s="334"/>
-      <c r="T12" s="429"/>
-      <c r="U12" s="409"/>
-      <c r="V12" s="425"/>
+      <c r="P12" s="363"/>
+      <c r="Q12" s="363"/>
+      <c r="R12" s="363"/>
+      <c r="S12" s="351"/>
+      <c r="T12" s="418"/>
+      <c r="U12" s="376"/>
+      <c r="V12" s="415"/>
       <c r="W12" s="227"/>
     </row>
     <row r="13" spans="1:23" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="296"/>
-      <c r="B13" s="425"/>
-      <c r="C13" s="428" t="s">
+      <c r="B13" s="415"/>
+      <c r="C13" s="405" t="s">
         <v>166</v>
       </c>
-      <c r="D13" s="428" t="s">
+      <c r="D13" s="405" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="334"/>
-      <c r="F13" s="446" t="s">
+      <c r="E13" s="351"/>
+      <c r="F13" s="424" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="338"/>
-      <c r="H13" s="428" t="s">
+      <c r="G13" s="368"/>
+      <c r="H13" s="405" t="s">
         <v>166</v>
       </c>
-      <c r="I13" s="428" t="s">
+      <c r="I13" s="405" t="s">
         <v>144</v>
       </c>
-      <c r="J13" s="334"/>
-      <c r="K13" s="446" t="s">
+      <c r="J13" s="351"/>
+      <c r="K13" s="424" t="s">
         <v>145</v>
       </c>
-      <c r="L13" s="338"/>
-      <c r="M13" s="425"/>
-      <c r="N13" s="425"/>
-      <c r="O13" s="428" t="s">
+      <c r="L13" s="368"/>
+      <c r="M13" s="415"/>
+      <c r="N13" s="415"/>
+      <c r="O13" s="405" t="s">
         <v>167</v>
       </c>
-      <c r="P13" s="428" t="s">
+      <c r="P13" s="405" t="s">
         <v>144</v>
       </c>
-      <c r="Q13" s="334"/>
-      <c r="R13" s="440" t="s">
+      <c r="Q13" s="351"/>
+      <c r="R13" s="421" t="s">
         <v>145</v>
       </c>
-      <c r="S13" s="334"/>
-      <c r="T13" s="339"/>
-      <c r="U13" s="341"/>
-      <c r="V13" s="425"/>
+      <c r="S13" s="351"/>
+      <c r="T13" s="369"/>
+      <c r="U13" s="370"/>
+      <c r="V13" s="415"/>
       <c r="W13" s="227"/>
     </row>
     <row r="14" spans="1:23" s="36" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="296"/>
-      <c r="B14" s="425"/>
-      <c r="C14" s="425"/>
-      <c r="D14" s="440" t="s">
+      <c r="B14" s="415"/>
+      <c r="C14" s="415"/>
+      <c r="D14" s="421" t="s">
         <v>146</v>
       </c>
-      <c r="E14" s="428" t="s">
+      <c r="E14" s="405" t="s">
         <v>168</v>
       </c>
-      <c r="F14" s="428" t="s">
+      <c r="F14" s="405" t="s">
         <v>169</v>
       </c>
-      <c r="G14" s="428" t="s">
+      <c r="G14" s="405" t="s">
         <v>170</v>
       </c>
-      <c r="H14" s="425"/>
-      <c r="I14" s="440" t="s">
+      <c r="H14" s="415"/>
+      <c r="I14" s="421" t="s">
         <v>146</v>
       </c>
-      <c r="J14" s="428" t="s">
+      <c r="J14" s="405" t="s">
         <v>168</v>
       </c>
-      <c r="K14" s="428" t="s">
+      <c r="K14" s="405" t="s">
         <v>171</v>
       </c>
-      <c r="L14" s="428" t="s">
+      <c r="L14" s="405" t="s">
         <v>172</v>
       </c>
-      <c r="M14" s="425"/>
-      <c r="N14" s="426"/>
-      <c r="O14" s="426"/>
+      <c r="M14" s="415"/>
+      <c r="N14" s="406"/>
+      <c r="O14" s="406"/>
       <c r="P14" s="159" t="s">
         <v>173</v>
       </c>
       <c r="Q14" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="R14" s="428" t="s">
+      <c r="R14" s="405" t="s">
         <v>174</v>
       </c>
-      <c r="S14" s="428" t="s">
+      <c r="S14" s="405" t="s">
         <v>175</v>
       </c>
-      <c r="T14" s="428" t="s">
+      <c r="T14" s="405" t="s">
         <v>176</v>
       </c>
-      <c r="U14" s="428" t="s">
+      <c r="U14" s="405" t="s">
         <v>177</v>
       </c>
-      <c r="V14" s="425"/>
+      <c r="V14" s="415"/>
       <c r="W14" s="227"/>
     </row>
     <row r="15" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="296"/>
-      <c r="B15" s="426"/>
-      <c r="C15" s="426"/>
-      <c r="D15" s="426"/>
-      <c r="E15" s="426"/>
-      <c r="F15" s="426"/>
-      <c r="G15" s="426"/>
-      <c r="H15" s="426"/>
-      <c r="I15" s="426"/>
-      <c r="J15" s="426"/>
-      <c r="K15" s="426"/>
-      <c r="L15" s="426"/>
-      <c r="M15" s="426"/>
+      <c r="B15" s="406"/>
+      <c r="C15" s="406"/>
+      <c r="D15" s="406"/>
+      <c r="E15" s="406"/>
+      <c r="F15" s="406"/>
+      <c r="G15" s="406"/>
+      <c r="H15" s="406"/>
+      <c r="I15" s="406"/>
+      <c r="J15" s="406"/>
+      <c r="K15" s="406"/>
+      <c r="L15" s="406"/>
+      <c r="M15" s="406"/>
       <c r="N15" s="150" t="s">
         <v>178</v>
       </c>
@@ -9451,11 +9462,11 @@
       <c r="Q15" s="151" t="s">
         <v>181</v>
       </c>
-      <c r="R15" s="426"/>
-      <c r="S15" s="426"/>
-      <c r="T15" s="426"/>
-      <c r="U15" s="426"/>
-      <c r="V15" s="425"/>
+      <c r="R15" s="406"/>
+      <c r="S15" s="406"/>
+      <c r="T15" s="406"/>
+      <c r="U15" s="406"/>
+      <c r="V15" s="415"/>
       <c r="W15" s="227"/>
     </row>
     <row r="16" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9520,7 +9531,7 @@
       <c r="U16" s="38">
         <v>38</v>
       </c>
-      <c r="V16" s="426"/>
+      <c r="V16" s="406"/>
       <c r="W16" s="227"/>
     </row>
     <row r="17" spans="1:98" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9849,14 +9860,22 @@
     <row r="22" spans="1:98" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="B3:V3"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="N11:N14"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="T11:U13"/>
+    <mergeCell ref="N7:V7"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="O13:O14"/>
     <mergeCell ref="B1:V1"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="L14:L15"/>
@@ -9873,22 +9892,14 @@
     <mergeCell ref="C11:M11"/>
     <mergeCell ref="V11:V16"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="O12:S12"/>
-    <mergeCell ref="T11:U13"/>
-    <mergeCell ref="N7:V7"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="B7:M7"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="B3:V3"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="N11:N14"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -9923,90 +9934,90 @@
   <sheetData>
     <row r="1" spans="1:14" ht="5.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="355"/>
-      <c r="C1" s="356"/>
-      <c r="D1" s="356"/>
-      <c r="E1" s="356"/>
-      <c r="F1" s="356"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="356"/>
-      <c r="I1" s="356"/>
-      <c r="J1" s="356"/>
-      <c r="K1" s="356"/>
-      <c r="L1" s="356"/>
-      <c r="M1" s="356"/>
+      <c r="B1" s="364"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
+      <c r="K1" s="365"/>
+      <c r="L1" s="365"/>
+      <c r="M1" s="365"/>
       <c r="N1" s="199"/>
     </row>
     <row r="2" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="249"/>
-      <c r="B2" s="354" t="s">
+      <c r="B2" s="431" t="s">
         <v>185</v>
       </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="337"/>
-      <c r="M2" s="338"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
+      <c r="M2" s="368"/>
       <c r="N2" s="201"/>
     </row>
     <row r="3" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="249"/>
-      <c r="B3" s="346" t="s">
+      <c r="B3" s="422" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="340"/>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="340"/>
-      <c r="K3" s="340"/>
-      <c r="L3" s="340"/>
-      <c r="M3" s="341"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="359"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="359"/>
+      <c r="M3" s="370"/>
       <c r="N3" s="201"/>
     </row>
     <row r="4" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="249"/>
-      <c r="B4" s="360" t="s">
+      <c r="B4" s="428" t="s">
         <v>186</v>
       </c>
-      <c r="C4" s="344"/>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="334"/>
-      <c r="I4" s="460" t="s">
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="351"/>
+      <c r="I4" s="445" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="344"/>
-      <c r="K4" s="344"/>
-      <c r="L4" s="344"/>
-      <c r="M4" s="334"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
+      <c r="L4" s="363"/>
+      <c r="M4" s="351"/>
       <c r="N4" s="201"/>
     </row>
     <row r="5" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="249"/>
-      <c r="B5" s="442" t="s">
+      <c r="B5" s="427" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="337"/>
-      <c r="D5" s="427" t="str">
+      <c r="C5" s="367"/>
+      <c r="D5" s="417" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="338"/>
+      <c r="E5" s="367"/>
+      <c r="F5" s="367"/>
+      <c r="G5" s="367"/>
+      <c r="H5" s="368"/>
       <c r="I5" s="136" t="s">
         <v>6</v>
       </c>
@@ -10021,17 +10032,17 @@
     </row>
     <row r="6" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="249"/>
-      <c r="B6" s="339"/>
-      <c r="C6" s="340"/>
-      <c r="D6" s="340"/>
-      <c r="E6" s="340"/>
-      <c r="F6" s="340"/>
-      <c r="G6" s="340"/>
-      <c r="H6" s="341"/>
-      <c r="I6" s="451" t="s">
+      <c r="B6" s="369"/>
+      <c r="C6" s="359"/>
+      <c r="D6" s="359"/>
+      <c r="E6" s="359"/>
+      <c r="F6" s="359"/>
+      <c r="G6" s="359"/>
+      <c r="H6" s="370"/>
+      <c r="I6" s="447" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="334"/>
+      <c r="J6" s="351"/>
       <c r="K6" s="156"/>
       <c r="L6" s="148">
         <f>('QUADRO II'!T4)+1</f>
@@ -10043,21 +10054,21 @@
     <row r="7" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="249"/>
       <c r="B7" s="259"/>
-      <c r="C7" s="453" t="s">
+      <c r="C7" s="448" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="344"/>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
-      <c r="G7" s="360" t="s">
+      <c r="D7" s="363"/>
+      <c r="E7" s="363"/>
+      <c r="F7" s="363"/>
+      <c r="G7" s="428" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="344"/>
-      <c r="I7" s="344"/>
-      <c r="J7" s="344"/>
-      <c r="K7" s="344"/>
-      <c r="L7" s="344"/>
-      <c r="M7" s="334"/>
+      <c r="H7" s="363"/>
+      <c r="I7" s="363"/>
+      <c r="J7" s="363"/>
+      <c r="K7" s="363"/>
+      <c r="L7" s="363"/>
+      <c r="M7" s="351"/>
       <c r="N7" s="201"/>
     </row>
     <row r="8" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10066,24 +10077,24 @@
         <v>9</v>
       </c>
       <c r="C8" s="76"/>
-      <c r="D8" s="456" t="str">
+      <c r="D8" s="443" t="str">
         <f>('QUADRO I'!$C$8)</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="E8" s="337"/>
-      <c r="F8" s="338"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="368"/>
       <c r="G8" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="458" t="str">
+      <c r="H8" s="444" t="str">
         <f>('QUADRO I'!$N$8)</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="I8" s="337"/>
-      <c r="J8" s="337"/>
-      <c r="K8" s="337"/>
-      <c r="L8" s="337"/>
-      <c r="M8" s="338"/>
+      <c r="I8" s="367"/>
+      <c r="J8" s="367"/>
+      <c r="K8" s="367"/>
+      <c r="L8" s="367"/>
+      <c r="M8" s="368"/>
       <c r="N8" s="201"/>
     </row>
     <row r="9" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10092,18 +10103,18 @@
         <v>10</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="454"/>
-      <c r="E9" s="455"/>
-      <c r="F9" s="409"/>
+      <c r="D9" s="442"/>
+      <c r="E9" s="439"/>
+      <c r="F9" s="376"/>
       <c r="G9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="462"/>
-      <c r="I9" s="455"/>
-      <c r="J9" s="455"/>
-      <c r="K9" s="455"/>
-      <c r="L9" s="455"/>
-      <c r="M9" s="409"/>
+      <c r="H9" s="446"/>
+      <c r="I9" s="439"/>
+      <c r="J9" s="439"/>
+      <c r="K9" s="439"/>
+      <c r="L9" s="439"/>
+      <c r="M9" s="376"/>
       <c r="N9" s="201"/>
     </row>
     <row r="10" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10112,12 +10123,12 @@
         <v>11</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="459" t="str">
+      <c r="D10" s="438" t="str">
         <f>('QUADRO I'!$C$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="E10" s="340"/>
-      <c r="F10" s="341"/>
+      <c r="E10" s="359"/>
+      <c r="F10" s="370"/>
       <c r="G10" s="5" t="s">
         <v>11</v>
       </c>
@@ -10125,12 +10136,12 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="I10" s="345" t="str">
+      <c r="I10" s="436" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="J10" s="340"/>
-      <c r="K10" s="340"/>
+      <c r="J10" s="359"/>
+      <c r="K10" s="359"/>
       <c r="L10" s="67" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -10140,7 +10151,7 @@
     </row>
     <row r="11" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="457" t="s">
+      <c r="B11" s="434" t="s">
         <v>188</v>
       </c>
       <c r="C11" s="163" t="s">
@@ -10160,132 +10171,132 @@
     </row>
     <row r="12" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="249"/>
-      <c r="B12" s="425"/>
-      <c r="C12" s="461" t="s">
+      <c r="B12" s="415"/>
+      <c r="C12" s="440" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="344"/>
-      <c r="E12" s="344"/>
-      <c r="F12" s="344"/>
-      <c r="G12" s="343" t="s">
+      <c r="D12" s="363"/>
+      <c r="E12" s="363"/>
+      <c r="F12" s="363"/>
+      <c r="G12" s="441" t="s">
         <v>191</v>
       </c>
-      <c r="H12" s="344"/>
-      <c r="I12" s="344"/>
-      <c r="J12" s="344"/>
-      <c r="K12" s="344"/>
-      <c r="L12" s="344"/>
-      <c r="M12" s="334"/>
+      <c r="H12" s="363"/>
+      <c r="I12" s="363"/>
+      <c r="J12" s="363"/>
+      <c r="K12" s="363"/>
+      <c r="L12" s="363"/>
+      <c r="M12" s="351"/>
       <c r="N12" s="201"/>
     </row>
     <row r="13" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="249"/>
-      <c r="B13" s="425"/>
-      <c r="C13" s="452" t="s">
+      <c r="B13" s="415"/>
+      <c r="C13" s="435" t="s">
         <v>192</v>
       </c>
-      <c r="D13" s="452" t="s">
+      <c r="D13" s="435" t="s">
         <v>193</v>
       </c>
-      <c r="E13" s="452" t="s">
+      <c r="E13" s="435" t="s">
         <v>194</v>
       </c>
-      <c r="F13" s="452" t="s">
+      <c r="F13" s="435" t="s">
         <v>195</v>
       </c>
-      <c r="G13" s="343" t="s">
+      <c r="G13" s="441" t="s">
         <v>196</v>
       </c>
-      <c r="H13" s="337"/>
-      <c r="I13" s="337"/>
-      <c r="J13" s="337"/>
-      <c r="K13" s="337"/>
-      <c r="L13" s="337"/>
-      <c r="M13" s="338"/>
+      <c r="H13" s="367"/>
+      <c r="I13" s="367"/>
+      <c r="J13" s="367"/>
+      <c r="K13" s="367"/>
+      <c r="L13" s="367"/>
+      <c r="M13" s="368"/>
       <c r="N13" s="201"/>
     </row>
     <row r="14" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="249"/>
-      <c r="B14" s="425"/>
-      <c r="C14" s="425"/>
-      <c r="D14" s="425"/>
-      <c r="E14" s="425"/>
-      <c r="F14" s="425"/>
-      <c r="G14" s="339"/>
-      <c r="H14" s="340"/>
-      <c r="I14" s="340"/>
-      <c r="J14" s="340"/>
-      <c r="K14" s="340"/>
-      <c r="L14" s="340"/>
-      <c r="M14" s="341"/>
+      <c r="B14" s="415"/>
+      <c r="C14" s="415"/>
+      <c r="D14" s="415"/>
+      <c r="E14" s="415"/>
+      <c r="F14" s="415"/>
+      <c r="G14" s="369"/>
+      <c r="H14" s="359"/>
+      <c r="I14" s="359"/>
+      <c r="J14" s="359"/>
+      <c r="K14" s="359"/>
+      <c r="L14" s="359"/>
+      <c r="M14" s="370"/>
       <c r="N14" s="201"/>
     </row>
     <row r="15" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="249"/>
-      <c r="B15" s="425"/>
-      <c r="C15" s="425"/>
-      <c r="D15" s="425"/>
-      <c r="E15" s="425"/>
-      <c r="F15" s="425"/>
-      <c r="G15" s="343" t="s">
+      <c r="B15" s="415"/>
+      <c r="C15" s="415"/>
+      <c r="D15" s="415"/>
+      <c r="E15" s="415"/>
+      <c r="F15" s="415"/>
+      <c r="G15" s="441" t="s">
         <v>197</v>
       </c>
-      <c r="H15" s="343" t="s">
+      <c r="H15" s="441" t="s">
         <v>198</v>
       </c>
-      <c r="I15" s="452" t="s">
+      <c r="I15" s="435" t="s">
         <v>199</v>
       </c>
-      <c r="J15" s="338"/>
-      <c r="K15" s="452" t="s">
+      <c r="J15" s="368"/>
+      <c r="K15" s="435" t="s">
         <v>200</v>
       </c>
-      <c r="L15" s="337"/>
-      <c r="M15" s="338"/>
+      <c r="L15" s="367"/>
+      <c r="M15" s="368"/>
       <c r="N15" s="201"/>
     </row>
     <row r="16" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="249"/>
-      <c r="B16" s="425"/>
-      <c r="C16" s="425"/>
-      <c r="D16" s="425"/>
-      <c r="E16" s="425"/>
-      <c r="F16" s="425"/>
-      <c r="G16" s="425"/>
-      <c r="H16" s="425"/>
-      <c r="I16" s="429"/>
-      <c r="J16" s="409"/>
-      <c r="K16" s="429"/>
-      <c r="L16" s="455"/>
-      <c r="M16" s="409"/>
+      <c r="B16" s="415"/>
+      <c r="C16" s="415"/>
+      <c r="D16" s="415"/>
+      <c r="E16" s="415"/>
+      <c r="F16" s="415"/>
+      <c r="G16" s="415"/>
+      <c r="H16" s="415"/>
+      <c r="I16" s="418"/>
+      <c r="J16" s="376"/>
+      <c r="K16" s="418"/>
+      <c r="L16" s="439"/>
+      <c r="M16" s="376"/>
       <c r="N16" s="201"/>
     </row>
     <row r="17" spans="1:14" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="249"/>
-      <c r="B17" s="425"/>
-      <c r="C17" s="426"/>
-      <c r="D17" s="426"/>
-      <c r="E17" s="426"/>
-      <c r="F17" s="426"/>
-      <c r="G17" s="426"/>
-      <c r="H17" s="426"/>
-      <c r="I17" s="339"/>
-      <c r="J17" s="341"/>
-      <c r="K17" s="339"/>
-      <c r="L17" s="340"/>
-      <c r="M17" s="341"/>
+      <c r="B17" s="415"/>
+      <c r="C17" s="406"/>
+      <c r="D17" s="406"/>
+      <c r="E17" s="406"/>
+      <c r="F17" s="406"/>
+      <c r="G17" s="406"/>
+      <c r="H17" s="406"/>
+      <c r="I17" s="369"/>
+      <c r="J17" s="370"/>
+      <c r="K17" s="369"/>
+      <c r="L17" s="359"/>
+      <c r="M17" s="370"/>
       <c r="N17" s="201"/>
     </row>
     <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="200"/>
-      <c r="B18" s="425"/>
-      <c r="C18" s="450" t="s">
+      <c r="B18" s="415"/>
+      <c r="C18" s="437" t="s">
         <v>201</v>
       </c>
-      <c r="D18" s="450" t="s">
+      <c r="D18" s="437" t="s">
         <v>202</v>
       </c>
-      <c r="E18" s="450">
+      <c r="E18" s="437">
         <v>1</v>
       </c>
       <c r="F18" s="234" t="str">
@@ -10298,68 +10309,68 @@
       <c r="H18" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="I18" s="452" t="s">
+      <c r="I18" s="435" t="s">
         <v>203</v>
       </c>
-      <c r="J18" s="334"/>
-      <c r="K18" s="452" t="s">
+      <c r="J18" s="351"/>
+      <c r="K18" s="435" t="s">
         <v>203</v>
       </c>
-      <c r="L18" s="344"/>
-      <c r="M18" s="334"/>
+      <c r="L18" s="363"/>
+      <c r="M18" s="351"/>
       <c r="N18" s="202"/>
     </row>
     <row r="19" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="200"/>
-      <c r="B19" s="425"/>
-      <c r="C19" s="425"/>
-      <c r="D19" s="425"/>
-      <c r="E19" s="425"/>
+      <c r="B19" s="415"/>
+      <c r="C19" s="415"/>
+      <c r="D19" s="415"/>
+      <c r="E19" s="415"/>
       <c r="F19" s="234"/>
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
-      <c r="I19" s="452"/>
-      <c r="J19" s="334"/>
-      <c r="K19" s="452"/>
-      <c r="L19" s="344"/>
-      <c r="M19" s="334"/>
+      <c r="I19" s="435"/>
+      <c r="J19" s="351"/>
+      <c r="K19" s="435"/>
+      <c r="L19" s="363"/>
+      <c r="M19" s="351"/>
       <c r="N19" s="202"/>
     </row>
     <row r="20" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="425"/>
-      <c r="C20" s="425"/>
-      <c r="D20" s="425"/>
-      <c r="E20" s="425"/>
+      <c r="B20" s="415"/>
+      <c r="C20" s="415"/>
+      <c r="D20" s="415"/>
+      <c r="E20" s="415"/>
       <c r="F20" s="234"/>
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
-      <c r="I20" s="452"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="452"/>
-      <c r="L20" s="344"/>
-      <c r="M20" s="334"/>
+      <c r="I20" s="435"/>
+      <c r="J20" s="351"/>
+      <c r="K20" s="435"/>
+      <c r="L20" s="363"/>
+      <c r="M20" s="351"/>
       <c r="N20" s="202"/>
     </row>
     <row r="21" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="200"/>
-      <c r="B21" s="425"/>
-      <c r="C21" s="425"/>
-      <c r="D21" s="425"/>
-      <c r="E21" s="425"/>
+      <c r="B21" s="415"/>
+      <c r="C21" s="415"/>
+      <c r="D21" s="415"/>
+      <c r="E21" s="415"/>
       <c r="F21" s="234"/>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="452"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="452"/>
-      <c r="L21" s="344"/>
-      <c r="M21" s="334"/>
+      <c r="I21" s="435"/>
+      <c r="J21" s="351"/>
+      <c r="K21" s="435"/>
+      <c r="L21" s="363"/>
+      <c r="M21" s="351"/>
       <c r="N21" s="202"/>
     </row>
     <row r="22" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="200"/>
-      <c r="B22" s="425"/>
+      <c r="B22" s="415"/>
       <c r="C22" s="56" t="s">
         <v>204</v>
       </c>
@@ -10379,7 +10390,7 @@
     </row>
     <row r="23" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="200"/>
-      <c r="B23" s="425"/>
+      <c r="B23" s="415"/>
       <c r="C23" s="56" t="s">
         <v>206</v>
       </c>
@@ -10405,7 +10416,7 @@
     </row>
     <row r="24" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="200"/>
-      <c r="B24" s="425"/>
+      <c r="B24" s="415"/>
       <c r="C24" s="45" t="s">
         <v>209</v>
       </c>
@@ -10423,7 +10434,7 @@
     </row>
     <row r="25" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="200"/>
-      <c r="B25" s="425"/>
+      <c r="B25" s="415"/>
       <c r="C25" s="239"/>
       <c r="D25" s="25" t="s">
         <v>210</v>
@@ -10449,7 +10460,7 @@
     </row>
     <row r="26" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="200"/>
-      <c r="B26" s="425"/>
+      <c r="B26" s="415"/>
       <c r="C26" s="239"/>
       <c r="D26" s="25" t="s">
         <v>213</v>
@@ -10475,7 +10486,7 @@
     </row>
     <row r="27" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="200"/>
-      <c r="B27" s="425"/>
+      <c r="B27" s="415"/>
       <c r="C27" s="239"/>
       <c r="D27" s="25" t="s">
         <v>214</v>
@@ -10500,7 +10511,7 @@
     </row>
     <row r="28" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="200"/>
-      <c r="B28" s="425"/>
+      <c r="B28" s="415"/>
       <c r="C28" s="239"/>
       <c r="D28" s="25" t="s">
         <v>215</v>
@@ -10526,7 +10537,7 @@
     </row>
     <row r="29" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="200"/>
-      <c r="B29" s="425"/>
+      <c r="B29" s="415"/>
       <c r="C29" s="239"/>
       <c r="D29" s="25" t="s">
         <v>216</v>
@@ -10552,7 +10563,7 @@
     </row>
     <row r="30" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="200"/>
-      <c r="B30" s="425"/>
+      <c r="B30" s="415"/>
       <c r="C30" s="239"/>
       <c r="D30" s="25" t="s">
         <v>217</v>
@@ -10577,7 +10588,7 @@
     </row>
     <row r="31" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="200"/>
-      <c r="B31" s="426"/>
+      <c r="B31" s="406"/>
       <c r="C31" s="30"/>
       <c r="D31" s="154" t="s">
         <v>218</v>
@@ -10595,7 +10606,7 @@
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="200"/>
-      <c r="B32" s="457" t="s">
+      <c r="B32" s="434" t="s">
         <v>219</v>
       </c>
       <c r="C32" s="56" t="s">
@@ -10620,7 +10631,7 @@
     </row>
     <row r="33" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
-      <c r="B33" s="425"/>
+      <c r="B33" s="415"/>
       <c r="C33" s="45"/>
       <c r="D33" s="27" t="s">
         <v>222</v>
@@ -10638,7 +10649,7 @@
     </row>
     <row r="34" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="200"/>
-      <c r="B34" s="425"/>
+      <c r="B34" s="415"/>
       <c r="C34" s="239"/>
       <c r="E34" s="1" t="s">
         <v>223</v>
@@ -10666,7 +10677,7 @@
     </row>
     <row r="35" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="200"/>
-      <c r="B35" s="425"/>
+      <c r="B35" s="415"/>
       <c r="C35" s="30"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2" t="s">
@@ -10698,7 +10709,7 @@
     </row>
     <row r="36" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="200"/>
-      <c r="B36" s="425"/>
+      <c r="B36" s="415"/>
       <c r="C36" s="56" t="s">
         <v>225</v>
       </c>
@@ -10716,7 +10727,7 @@
     </row>
     <row r="37" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="200"/>
-      <c r="B37" s="425"/>
+      <c r="B37" s="415"/>
       <c r="C37" s="45"/>
       <c r="D37" s="246" t="s">
         <v>226</v>
@@ -10736,7 +10747,7 @@
     </row>
     <row r="38" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="200"/>
-      <c r="B38" s="425"/>
+      <c r="B38" s="415"/>
       <c r="C38" s="239"/>
       <c r="D38" s="1" t="s">
         <v>227</v>
@@ -10752,7 +10763,7 @@
     </row>
     <row r="39" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="200"/>
-      <c r="B39" s="425"/>
+      <c r="B39" s="415"/>
       <c r="C39" s="239"/>
       <c r="D39" s="1" t="s">
         <v>228</v>
@@ -10766,7 +10777,7 @@
     </row>
     <row r="40" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="200"/>
-      <c r="B40" s="425"/>
+      <c r="B40" s="415"/>
       <c r="C40" s="239"/>
       <c r="E40" s="1" t="s">
         <v>229</v>
@@ -10782,7 +10793,7 @@
     </row>
     <row r="41" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="200"/>
-      <c r="B41" s="425"/>
+      <c r="B41" s="415"/>
       <c r="C41" s="239"/>
       <c r="E41" s="1" t="s">
         <v>230</v>
@@ -10798,7 +10809,7 @@
     </row>
     <row r="42" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="200"/>
-      <c r="B42" s="425"/>
+      <c r="B42" s="415"/>
       <c r="C42" s="239"/>
       <c r="E42" s="1" t="s">
         <v>231</v>
@@ -10814,7 +10825,7 @@
     </row>
     <row r="43" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="200"/>
-      <c r="B43" s="425"/>
+      <c r="B43" s="415"/>
       <c r="C43" s="239"/>
       <c r="E43" s="1" t="s">
         <v>232</v>
@@ -10830,7 +10841,7 @@
     </row>
     <row r="44" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="200"/>
-      <c r="B44" s="425"/>
+      <c r="B44" s="415"/>
       <c r="C44" s="239"/>
       <c r="E44" s="1" t="s">
         <v>233</v>
@@ -10846,7 +10857,7 @@
     </row>
     <row r="45" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="200"/>
-      <c r="B45" s="425"/>
+      <c r="B45" s="415"/>
       <c r="C45" s="239"/>
       <c r="E45" s="1" t="s">
         <v>234</v>
@@ -10862,7 +10873,7 @@
     </row>
     <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="200"/>
-      <c r="B46" s="425"/>
+      <c r="B46" s="415"/>
       <c r="C46" s="239"/>
       <c r="E46" s="1" t="s">
         <v>235</v>
@@ -10878,7 +10889,7 @@
     </row>
     <row r="47" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="200"/>
-      <c r="B47" s="425"/>
+      <c r="B47" s="415"/>
       <c r="C47" s="239"/>
       <c r="E47" s="1" t="s">
         <v>236</v>
@@ -10894,7 +10905,7 @@
     </row>
     <row r="48" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="200"/>
-      <c r="B48" s="425"/>
+      <c r="B48" s="415"/>
       <c r="C48" s="239"/>
       <c r="D48" s="1" t="s">
         <v>237</v>
@@ -10910,7 +10921,7 @@
     </row>
     <row r="49" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="200"/>
-      <c r="B49" s="425"/>
+      <c r="B49" s="415"/>
       <c r="C49" s="248"/>
       <c r="D49" s="1" t="s">
         <v>238</v>
@@ -10924,7 +10935,7 @@
     </row>
     <row r="50" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="200"/>
-      <c r="B50" s="425"/>
+      <c r="B50" s="415"/>
       <c r="C50" s="239"/>
       <c r="E50" s="1" t="s">
         <v>239</v>
@@ -10940,7 +10951,7 @@
     </row>
     <row r="51" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="200"/>
-      <c r="B51" s="425"/>
+      <c r="B51" s="415"/>
       <c r="C51" s="239"/>
       <c r="E51" s="1" t="s">
         <v>240</v>
@@ -10956,7 +10967,7 @@
     </row>
     <row r="52" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="200"/>
-      <c r="B52" s="425"/>
+      <c r="B52" s="415"/>
       <c r="C52" s="239"/>
       <c r="E52" s="1" t="s">
         <v>241</v>
@@ -10972,7 +10983,7 @@
     </row>
     <row r="53" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="200"/>
-      <c r="B53" s="425"/>
+      <c r="B53" s="415"/>
       <c r="C53" s="239"/>
       <c r="E53" s="1" t="s">
         <v>242</v>
@@ -10988,7 +10999,7 @@
     </row>
     <row r="54" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="200"/>
-      <c r="B54" s="425"/>
+      <c r="B54" s="415"/>
       <c r="C54" s="239"/>
       <c r="E54" s="1" t="s">
         <v>243</v>
@@ -11004,7 +11015,7 @@
     </row>
     <row r="55" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="200"/>
-      <c r="B55" s="425"/>
+      <c r="B55" s="415"/>
       <c r="C55" s="30"/>
       <c r="D55" s="2" t="s">
         <v>244</v>
@@ -11024,7 +11035,7 @@
     </row>
     <row r="56" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="200"/>
-      <c r="B56" s="425"/>
+      <c r="B56" s="415"/>
       <c r="C56" s="56" t="s">
         <v>245</v>
       </c>
@@ -11047,7 +11058,7 @@
     </row>
     <row r="57" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="200"/>
-      <c r="B57" s="425"/>
+      <c r="B57" s="415"/>
       <c r="C57" s="45" t="s">
         <v>246</v>
       </c>
@@ -11067,7 +11078,7 @@
     </row>
     <row r="58" spans="1:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="200"/>
-      <c r="B58" s="425"/>
+      <c r="B58" s="415"/>
       <c r="C58" s="239" t="s">
         <v>247</v>
       </c>
@@ -11080,7 +11091,7 @@
     </row>
     <row r="59" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="200"/>
-      <c r="B59" s="425"/>
+      <c r="B59" s="415"/>
       <c r="C59" s="239"/>
       <c r="E59" s="1" t="s">
         <v>248</v>
@@ -11096,7 +11107,7 @@
     </row>
     <row r="60" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="200"/>
-      <c r="B60" s="425"/>
+      <c r="B60" s="415"/>
       <c r="C60" s="239"/>
       <c r="E60" s="1" t="s">
         <v>249</v>
@@ -11112,7 +11123,7 @@
     </row>
     <row r="61" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="200"/>
-      <c r="B61" s="425"/>
+      <c r="B61" s="415"/>
       <c r="C61" s="239"/>
       <c r="E61" s="1" t="s">
         <v>250</v>
@@ -11128,7 +11139,7 @@
     </row>
     <row r="62" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="200"/>
-      <c r="B62" s="425"/>
+      <c r="B62" s="415"/>
       <c r="C62" s="239"/>
       <c r="E62" s="1" t="s">
         <v>251</v>
@@ -11144,7 +11155,7 @@
     </row>
     <row r="63" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="200"/>
-      <c r="B63" s="425"/>
+      <c r="B63" s="415"/>
       <c r="C63" s="56" t="s">
         <v>252</v>
       </c>
@@ -11167,7 +11178,7 @@
     </row>
     <row r="64" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="200"/>
-      <c r="B64" s="425"/>
+      <c r="B64" s="415"/>
       <c r="C64" s="45" t="s">
         <v>253</v>
       </c>
@@ -11191,7 +11202,7 @@
     </row>
     <row r="65" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="200"/>
-      <c r="B65" s="425"/>
+      <c r="B65" s="415"/>
       <c r="C65" s="30" t="s">
         <v>254</v>
       </c>
@@ -11215,7 +11226,7 @@
     </row>
     <row r="66" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="200"/>
-      <c r="B66" s="425"/>
+      <c r="B66" s="415"/>
       <c r="C66" s="56" t="s">
         <v>255</v>
       </c>
@@ -11238,7 +11249,7 @@
     </row>
     <row r="67" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="200"/>
-      <c r="B67" s="426"/>
+      <c r="B67" s="406"/>
       <c r="C67" s="56" t="s">
         <v>256</v>
       </c>
@@ -11280,6 +11291,30 @@
     <row r="69" spans="1:16" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="I15:J17"/>
+    <mergeCell ref="G13:M14"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="F13:F17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="G12:M12"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G7:M7"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="H9:M9"/>
     <mergeCell ref="B32:B67"/>
     <mergeCell ref="B11:B31"/>
     <mergeCell ref="I18:J18"/>
@@ -11296,30 +11331,6 @@
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="K21:M21"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="F13:F17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="G12:M12"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G7:M7"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="D13:D17"/>
-    <mergeCell ref="I15:J17"/>
-    <mergeCell ref="G13:M14"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="C18:C21"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -11347,59 +11358,59 @@
   <sheetData>
     <row r="1" spans="1:56" ht="13.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="463" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="367"/>
-      <c r="D1" s="367"/>
-      <c r="E1" s="367"/>
-      <c r="F1" s="367"/>
-      <c r="G1" s="367"/>
-      <c r="H1" s="367"/>
-      <c r="I1" s="367"/>
-      <c r="J1" s="367"/>
-      <c r="K1" s="367"/>
-      <c r="L1" s="367"/>
-      <c r="M1" s="367"/>
-      <c r="N1" s="367"/>
-      <c r="O1" s="464"/>
+      <c r="B1" s="449" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="339"/>
+      <c r="D1" s="339"/>
+      <c r="E1" s="339"/>
+      <c r="F1" s="339"/>
+      <c r="G1" s="339"/>
+      <c r="H1" s="339"/>
+      <c r="I1" s="339"/>
+      <c r="J1" s="339"/>
+      <c r="K1" s="339"/>
+      <c r="L1" s="339"/>
+      <c r="M1" s="339"/>
+      <c r="N1" s="339"/>
+      <c r="O1" s="450"/>
       <c r="P1" s="199"/>
     </row>
     <row r="2" spans="1:56" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="346" t="s">
+      <c r="B2" s="422" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="340"/>
-      <c r="D2" s="340"/>
-      <c r="E2" s="340"/>
-      <c r="F2" s="340"/>
-      <c r="G2" s="340"/>
-      <c r="H2" s="340"/>
-      <c r="I2" s="340"/>
-      <c r="J2" s="340"/>
-      <c r="K2" s="340"/>
-      <c r="L2" s="340"/>
-      <c r="M2" s="340"/>
-      <c r="N2" s="340"/>
-      <c r="O2" s="341"/>
+      <c r="C2" s="359"/>
+      <c r="D2" s="359"/>
+      <c r="E2" s="359"/>
+      <c r="F2" s="359"/>
+      <c r="G2" s="359"/>
+      <c r="H2" s="359"/>
+      <c r="I2" s="359"/>
+      <c r="J2" s="359"/>
+      <c r="K2" s="359"/>
+      <c r="L2" s="359"/>
+      <c r="M2" s="359"/>
+      <c r="N2" s="359"/>
+      <c r="O2" s="370"/>
       <c r="P2" s="202"/>
     </row>
     <row r="3" spans="1:56" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="467" t="s">
+      <c r="B3" s="453" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="337"/>
-      <c r="D3" s="337"/>
-      <c r="E3" s="337"/>
-      <c r="F3" s="337"/>
-      <c r="G3" s="337"/>
-      <c r="H3" s="337"/>
-      <c r="I3" s="337"/>
-      <c r="J3" s="337"/>
-      <c r="K3" s="337"/>
-      <c r="L3" s="338"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="368"/>
       <c r="M3" s="259" t="s">
         <v>3</v>
       </c>
@@ -11412,42 +11423,42 @@
     </row>
     <row r="4" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="469" t="s">
+      <c r="B4" s="455" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="337"/>
-      <c r="D4" s="465" t="str">
+      <c r="C4" s="367"/>
+      <c r="D4" s="451" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E4" s="337"/>
-      <c r="F4" s="337"/>
-      <c r="G4" s="337"/>
-      <c r="H4" s="337"/>
-      <c r="I4" s="337"/>
-      <c r="J4" s="337"/>
-      <c r="K4" s="337"/>
-      <c r="L4" s="338"/>
-      <c r="M4" s="439" t="s">
+      <c r="E4" s="367"/>
+      <c r="F4" s="367"/>
+      <c r="G4" s="367"/>
+      <c r="H4" s="367"/>
+      <c r="I4" s="367"/>
+      <c r="J4" s="367"/>
+      <c r="K4" s="367"/>
+      <c r="L4" s="368"/>
+      <c r="M4" s="411" t="s">
         <v>259</v>
       </c>
-      <c r="N4" s="337"/>
-      <c r="O4" s="338"/>
+      <c r="N4" s="367"/>
+      <c r="O4" s="368"/>
       <c r="P4" s="202"/>
     </row>
     <row r="5" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="339"/>
-      <c r="C5" s="340"/>
-      <c r="D5" s="340"/>
-      <c r="E5" s="340"/>
-      <c r="F5" s="340"/>
-      <c r="G5" s="340"/>
-      <c r="H5" s="340"/>
-      <c r="I5" s="340"/>
-      <c r="J5" s="340"/>
-      <c r="K5" s="340"/>
-      <c r="L5" s="341"/>
+      <c r="B5" s="369"/>
+      <c r="C5" s="359"/>
+      <c r="D5" s="359"/>
+      <c r="E5" s="359"/>
+      <c r="F5" s="359"/>
+      <c r="G5" s="359"/>
+      <c r="H5" s="359"/>
+      <c r="I5" s="359"/>
+      <c r="J5" s="359"/>
+      <c r="K5" s="359"/>
+      <c r="L5" s="370"/>
       <c r="M5" s="75" t="s">
         <v>6</v>
       </c>
@@ -11460,24 +11471,24 @@
     </row>
     <row r="6" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="428" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="344"/>
-      <c r="D6" s="344"/>
-      <c r="E6" s="344"/>
-      <c r="F6" s="344"/>
-      <c r="G6" s="334"/>
-      <c r="H6" s="360" t="s">
+      <c r="C6" s="363"/>
+      <c r="D6" s="363"/>
+      <c r="E6" s="363"/>
+      <c r="F6" s="363"/>
+      <c r="G6" s="351"/>
+      <c r="H6" s="428" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="344"/>
-      <c r="J6" s="344"/>
-      <c r="K6" s="344"/>
-      <c r="L6" s="344"/>
-      <c r="M6" s="344"/>
-      <c r="N6" s="344"/>
-      <c r="O6" s="334"/>
+      <c r="I6" s="363"/>
+      <c r="J6" s="363"/>
+      <c r="K6" s="363"/>
+      <c r="L6" s="363"/>
+      <c r="M6" s="363"/>
+      <c r="N6" s="363"/>
+      <c r="O6" s="351"/>
       <c r="P6" s="202"/>
     </row>
     <row r="7" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -11539,11 +11550,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="K9" s="468" t="str">
+      <c r="K9" s="454" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="L9" s="392"/>
+      <c r="L9" s="375"/>
       <c r="M9" s="67" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -11554,33 +11565,33 @@
     </row>
     <row r="10" spans="1:56" s="10" customFormat="1" ht="13.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="249"/>
-      <c r="B10" s="470" t="s">
+      <c r="B10" s="456" t="s">
         <v>260</v>
       </c>
-      <c r="C10" s="474" t="s">
+      <c r="C10" s="460" t="s">
         <v>261</v>
       </c>
-      <c r="D10" s="337"/>
-      <c r="E10" s="337"/>
-      <c r="F10" s="471" t="s">
+      <c r="D10" s="367"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="457" t="s">
         <v>262</v>
       </c>
-      <c r="G10" s="472"/>
-      <c r="H10" s="472"/>
-      <c r="I10" s="472"/>
-      <c r="J10" s="472"/>
-      <c r="K10" s="472"/>
-      <c r="L10" s="473"/>
-      <c r="M10" s="466" t="s">
+      <c r="G10" s="458"/>
+      <c r="H10" s="458"/>
+      <c r="I10" s="458"/>
+      <c r="J10" s="458"/>
+      <c r="K10" s="458"/>
+      <c r="L10" s="459"/>
+      <c r="M10" s="452" t="s">
         <v>263</v>
       </c>
-      <c r="N10" s="344"/>
-      <c r="O10" s="334"/>
+      <c r="N10" s="363"/>
+      <c r="O10" s="351"/>
       <c r="P10" s="201"/>
     </row>
     <row r="11" spans="1:56" s="10" customFormat="1" ht="105" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="426"/>
+      <c r="B11" s="406"/>
       <c r="C11" s="166" t="s">
         <v>264</v>
       </c>
@@ -13032,7 +13043,7 @@
       </c>
       <c r="N46" s="253"/>
       <c r="O46" s="86" t="e">
-        <f t="shared" ref="O46:O77" si="3">SUM(M46-N46)</f>
+        <f t="shared" ref="O46:O75" si="3">SUM(M46-N46)</f>
         <v>#REF!</v>
       </c>
       <c r="P46" s="202"/>
@@ -15994,58 +16005,58 @@
   <sheetData>
     <row r="1" spans="1:11" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="355"/>
-      <c r="C1" s="356"/>
-      <c r="D1" s="356"/>
-      <c r="E1" s="356"/>
-      <c r="F1" s="356"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="356"/>
-      <c r="I1" s="356"/>
-      <c r="J1" s="356"/>
+      <c r="B1" s="364"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
       <c r="K1" s="199"/>
     </row>
     <row r="2" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="354" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="338"/>
+      <c r="B2" s="431" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="368"/>
       <c r="K2" s="202"/>
     </row>
     <row r="3" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="346" t="s">
+      <c r="B3" s="422" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="340"/>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="341"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="370"/>
       <c r="K3" s="202"/>
     </row>
     <row r="4" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="475" t="s">
+      <c r="B4" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C4" s="344"/>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="334"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="351"/>
       <c r="I4" s="144" t="s">
         <v>3</v>
       </c>
@@ -16057,33 +16068,33 @@
     </row>
     <row r="5" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="469" t="s">
+      <c r="B5" s="455" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="465" t="str">
+      <c r="C5" s="451" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="D5" s="337"/>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="338"/>
-      <c r="I5" s="439" t="s">
+      <c r="D5" s="367"/>
+      <c r="E5" s="367"/>
+      <c r="F5" s="367"/>
+      <c r="G5" s="367"/>
+      <c r="H5" s="368"/>
+      <c r="I5" s="411" t="s">
         <v>259</v>
       </c>
-      <c r="J5" s="338"/>
+      <c r="J5" s="368"/>
       <c r="K5" s="202"/>
     </row>
     <row r="6" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="339"/>
-      <c r="C6" s="340"/>
-      <c r="D6" s="340"/>
-      <c r="E6" s="340"/>
-      <c r="F6" s="340"/>
-      <c r="G6" s="340"/>
-      <c r="H6" s="341"/>
+      <c r="B6" s="369"/>
+      <c r="C6" s="359"/>
+      <c r="D6" s="359"/>
+      <c r="E6" s="359"/>
+      <c r="F6" s="359"/>
+      <c r="G6" s="359"/>
+      <c r="H6" s="370"/>
       <c r="I6" s="75" t="s">
         <v>6</v>
       </c>
@@ -16095,19 +16106,19 @@
     </row>
     <row r="7" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="475" t="s">
+      <c r="B7" s="461" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="344"/>
-      <c r="D7" s="344"/>
-      <c r="E7" s="344"/>
-      <c r="F7" s="334"/>
-      <c r="G7" s="475" t="s">
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
+      <c r="E7" s="363"/>
+      <c r="F7" s="351"/>
+      <c r="G7" s="461" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="344"/>
-      <c r="I7" s="344"/>
-      <c r="J7" s="334"/>
+      <c r="H7" s="363"/>
+      <c r="I7" s="363"/>
+      <c r="J7" s="351"/>
       <c r="K7" s="202"/>
     </row>
     <row r="8" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -16177,18 +16188,18 @@
     <row r="11" spans="1:11" s="10" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
       <c r="B11" s="164"/>
-      <c r="C11" s="343" t="s">
+      <c r="C11" s="441" t="s">
         <v>295</v>
       </c>
-      <c r="D11" s="344"/>
-      <c r="E11" s="344"/>
-      <c r="F11" s="344"/>
-      <c r="G11" s="334"/>
+      <c r="D11" s="363"/>
+      <c r="E11" s="363"/>
+      <c r="F11" s="363"/>
+      <c r="G11" s="351"/>
       <c r="H11" s="164"/>
-      <c r="I11" s="476" t="s">
+      <c r="I11" s="462" t="s">
         <v>164</v>
       </c>
-      <c r="J11" s="452" t="s">
+      <c r="J11" s="435" t="s">
         <v>159</v>
       </c>
       <c r="K11" s="201"/>
@@ -16216,8 +16227,8 @@
       <c r="H12" s="164" t="s">
         <v>302</v>
       </c>
-      <c r="I12" s="425"/>
-      <c r="J12" s="426"/>
+      <c r="I12" s="415"/>
+      <c r="J12" s="406"/>
       <c r="K12" s="201"/>
     </row>
     <row r="13" spans="1:11" s="10" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -16243,7 +16254,7 @@
       <c r="H13" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="I13" s="426"/>
+      <c r="I13" s="406"/>
       <c r="J13" s="167"/>
       <c r="K13" s="201"/>
     </row>
@@ -17454,7 +17465,7 @@
         <v>#REF!</v>
       </c>
       <c r="G46" s="109" t="e">
-        <f t="shared" ref="G46:G77" si="1">SUM(E46+F46)</f>
+        <f t="shared" ref="G46:G75" si="1">SUM(E46+F46)</f>
         <v>#REF!</v>
       </c>
       <c r="H46" s="321" t="e">
@@ -18714,69 +18725,69 @@
   <sheetData>
     <row r="1" spans="1:14" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="355"/>
-      <c r="C1" s="356"/>
-      <c r="D1" s="356"/>
-      <c r="E1" s="356"/>
-      <c r="F1" s="356"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="356"/>
-      <c r="I1" s="356"/>
-      <c r="J1" s="356"/>
-      <c r="K1" s="356"/>
-      <c r="L1" s="356"/>
-      <c r="M1" s="356"/>
+      <c r="B1" s="364"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
+      <c r="K1" s="365"/>
+      <c r="L1" s="365"/>
+      <c r="M1" s="365"/>
       <c r="N1" s="199"/>
     </row>
     <row r="2" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="354" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="337"/>
-      <c r="M2" s="338"/>
+      <c r="B2" s="431" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
+      <c r="M2" s="368"/>
       <c r="N2" s="202"/>
     </row>
     <row r="3" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="346" t="s">
+      <c r="B3" s="422" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="340"/>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="340"/>
-      <c r="K3" s="340"/>
-      <c r="L3" s="340"/>
-      <c r="M3" s="341"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="359"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="359"/>
+      <c r="M3" s="370"/>
       <c r="N3" s="202"/>
     </row>
     <row r="4" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="475" t="s">
+      <c r="B4" s="461" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="344"/>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="344"/>
-      <c r="I4" s="344"/>
-      <c r="J4" s="334"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="351"/>
       <c r="K4" s="144" t="s">
         <v>3</v>
       </c>
@@ -18788,38 +18799,38 @@
     </row>
     <row r="5" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="469" t="s">
+      <c r="B5" s="455" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="337"/>
-      <c r="D5" s="427" t="str">
+      <c r="C5" s="367"/>
+      <c r="D5" s="417" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="337"/>
-      <c r="J5" s="338"/>
-      <c r="K5" s="439" t="s">
+      <c r="E5" s="367"/>
+      <c r="F5" s="367"/>
+      <c r="G5" s="367"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="368"/>
+      <c r="K5" s="411" t="s">
         <v>259</v>
       </c>
-      <c r="L5" s="337"/>
-      <c r="M5" s="338"/>
+      <c r="L5" s="367"/>
+      <c r="M5" s="368"/>
       <c r="N5" s="202"/>
     </row>
     <row r="6" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="339"/>
-      <c r="C6" s="340"/>
-      <c r="D6" s="340"/>
-      <c r="E6" s="340"/>
-      <c r="F6" s="340"/>
-      <c r="G6" s="340"/>
-      <c r="H6" s="340"/>
-      <c r="I6" s="340"/>
-      <c r="J6" s="341"/>
+      <c r="B6" s="369"/>
+      <c r="C6" s="359"/>
+      <c r="D6" s="359"/>
+      <c r="E6" s="359"/>
+      <c r="F6" s="359"/>
+      <c r="G6" s="359"/>
+      <c r="H6" s="359"/>
+      <c r="I6" s="359"/>
+      <c r="J6" s="370"/>
       <c r="K6" s="75" t="s">
         <v>6</v>
       </c>
@@ -18832,22 +18843,22 @@
     </row>
     <row r="7" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="475" t="s">
+      <c r="B7" s="461" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="344"/>
-      <c r="D7" s="344"/>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
-      <c r="G7" s="334"/>
-      <c r="H7" s="475" t="s">
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
+      <c r="E7" s="363"/>
+      <c r="F7" s="363"/>
+      <c r="G7" s="351"/>
+      <c r="H7" s="461" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="344"/>
-      <c r="J7" s="344"/>
-      <c r="K7" s="344"/>
-      <c r="L7" s="344"/>
-      <c r="M7" s="334"/>
+      <c r="I7" s="363"/>
+      <c r="J7" s="363"/>
+      <c r="K7" s="363"/>
+      <c r="L7" s="363"/>
+      <c r="M7" s="351"/>
       <c r="N7" s="202"/>
     </row>
     <row r="8" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18909,11 +18920,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="345" t="str">
+      <c r="J10" s="436" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="340"/>
+      <c r="K10" s="359"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -18923,77 +18934,77 @@
     <row r="11" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
       <c r="B11" s="167"/>
-      <c r="C11" s="343" t="s">
+      <c r="C11" s="441" t="s">
         <v>295</v>
       </c>
-      <c r="D11" s="344"/>
-      <c r="E11" s="344"/>
-      <c r="F11" s="344"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="343" t="s">
+      <c r="D11" s="363"/>
+      <c r="E11" s="363"/>
+      <c r="F11" s="363"/>
+      <c r="G11" s="351"/>
+      <c r="H11" s="441" t="s">
         <v>321</v>
       </c>
-      <c r="I11" s="344"/>
-      <c r="J11" s="334"/>
+      <c r="I11" s="363"/>
+      <c r="J11" s="351"/>
       <c r="K11" s="167"/>
-      <c r="L11" s="476" t="s">
+      <c r="L11" s="462" t="s">
         <v>164</v>
       </c>
-      <c r="M11" s="477" t="s">
+      <c r="M11" s="463" t="s">
         <v>159</v>
       </c>
       <c r="N11" s="201"/>
     </row>
     <row r="12" spans="1:14" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="249"/>
-      <c r="B12" s="452" t="s">
+      <c r="B12" s="435" t="s">
         <v>296</v>
       </c>
-      <c r="C12" s="452" t="s">
+      <c r="C12" s="435" t="s">
         <v>297</v>
       </c>
-      <c r="D12" s="452" t="s">
+      <c r="D12" s="435" t="s">
         <v>298</v>
       </c>
-      <c r="E12" s="452" t="s">
+      <c r="E12" s="435" t="s">
         <v>299</v>
       </c>
-      <c r="F12" s="452" t="s">
+      <c r="F12" s="435" t="s">
         <v>300</v>
       </c>
-      <c r="G12" s="452" t="s">
+      <c r="G12" s="435" t="s">
         <v>322</v>
       </c>
-      <c r="H12" s="452" t="s">
+      <c r="H12" s="435" t="s">
         <v>323</v>
       </c>
-      <c r="I12" s="452" t="s">
+      <c r="I12" s="435" t="s">
         <v>324</v>
       </c>
-      <c r="J12" s="452" t="s">
+      <c r="J12" s="435" t="s">
         <v>325</v>
       </c>
-      <c r="K12" s="452" t="s">
+      <c r="K12" s="435" t="s">
         <v>326</v>
       </c>
-      <c r="L12" s="425"/>
-      <c r="M12" s="425"/>
+      <c r="L12" s="415"/>
+      <c r="M12" s="415"/>
       <c r="N12" s="201"/>
     </row>
     <row r="13" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="249"/>
-      <c r="B13" s="426"/>
-      <c r="C13" s="426"/>
-      <c r="D13" s="426"/>
-      <c r="E13" s="426"/>
-      <c r="F13" s="426"/>
-      <c r="G13" s="426"/>
-      <c r="H13" s="426"/>
-      <c r="I13" s="426"/>
-      <c r="J13" s="426"/>
-      <c r="K13" s="426"/>
-      <c r="L13" s="425"/>
-      <c r="M13" s="425"/>
+      <c r="B13" s="406"/>
+      <c r="C13" s="406"/>
+      <c r="D13" s="406"/>
+      <c r="E13" s="406"/>
+      <c r="F13" s="406"/>
+      <c r="G13" s="406"/>
+      <c r="H13" s="406"/>
+      <c r="I13" s="406"/>
+      <c r="J13" s="406"/>
+      <c r="K13" s="406"/>
+      <c r="L13" s="415"/>
+      <c r="M13" s="415"/>
       <c r="N13" s="201"/>
     </row>
     <row r="14" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19028,7 +19039,7 @@
       <c r="K14" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="L14" s="426"/>
+      <c r="L14" s="406"/>
       <c r="M14" s="167"/>
       <c r="N14" s="201"/>
     </row>
@@ -20519,7 +20530,7 @@
         <v>#REF!</v>
       </c>
       <c r="E47" s="109" t="e">
-        <f t="shared" ref="E47:E78" si="4">SUM(C47+D47)</f>
+        <f t="shared" ref="E47:E76" si="4">SUM(C47+D47)</f>
         <v>#REF!</v>
       </c>
       <c r="F47" s="109" t="e">
@@ -20527,16 +20538,16 @@
         <v>#REF!</v>
       </c>
       <c r="G47" s="109" t="e">
-        <f t="shared" ref="G47:G78" si="5">SUM(E47+F47)</f>
+        <f t="shared" ref="G47:G76" si="5">SUM(E47+F47)</f>
         <v>#REF!</v>
       </c>
       <c r="H47" s="109" t="e">
-        <f t="shared" ref="H47:H78" si="6">G47</f>
+        <f t="shared" ref="H47:H76" si="6">G47</f>
         <v>#REF!</v>
       </c>
       <c r="I47" s="109"/>
       <c r="J47" s="109" t="e">
-        <f t="shared" ref="J47:J78" si="7">SUM(H47+I47)</f>
+        <f t="shared" ref="J47:J76" si="7">SUM(H47+I47)</f>
         <v>#REF!</v>
       </c>
       <c r="K47" s="321" t="e">
@@ -21989,18 +22000,6 @@
     <row r="81" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="L11:L14"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="D5:J6"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="J10:K10"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="H7:M7"/>
@@ -22013,6 +22012,18 @@
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="J12:J13"/>
     <mergeCell ref="M11:M13"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="L11:L14"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="D5:J6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -22042,87 +22053,87 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="481"/>
-      <c r="C1" s="356"/>
-      <c r="D1" s="356"/>
-      <c r="E1" s="356"/>
-      <c r="F1" s="356"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="356"/>
-      <c r="I1" s="356"/>
-      <c r="J1" s="356"/>
-      <c r="K1" s="356"/>
-      <c r="L1" s="356"/>
+      <c r="B1" s="465"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
+      <c r="K1" s="365"/>
+      <c r="L1" s="365"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="354" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="338"/>
+      <c r="B2" s="431" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="368"/>
       <c r="M2" s="202"/>
     </row>
     <row r="3" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="346" t="s">
+      <c r="B3" s="422" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="340"/>
-      <c r="D3" s="340"/>
-      <c r="E3" s="340"/>
-      <c r="F3" s="340"/>
-      <c r="G3" s="340"/>
-      <c r="H3" s="340"/>
-      <c r="I3" s="340"/>
-      <c r="J3" s="340"/>
-      <c r="K3" s="340"/>
-      <c r="L3" s="341"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="359"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="370"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="360" t="s">
+      <c r="B4" s="428" t="s">
         <v>333</v>
       </c>
-      <c r="C4" s="344"/>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="344"/>
-      <c r="I4" s="334"/>
-      <c r="J4" s="478" t="s">
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="351"/>
+      <c r="J4" s="471" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="344"/>
-      <c r="L4" s="334"/>
+      <c r="K4" s="363"/>
+      <c r="L4" s="351"/>
       <c r="M4" s="202"/>
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="451" t="s">
+      <c r="B5" s="447" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="338"/>
-      <c r="D5" s="336" t="str">
+      <c r="C5" s="368"/>
+      <c r="D5" s="470" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="338"/>
+      <c r="E5" s="367"/>
+      <c r="F5" s="367"/>
+      <c r="G5" s="367"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="368"/>
       <c r="J5" s="49" t="s">
         <v>6</v>
       </c>
@@ -22134,14 +22145,14 @@
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="339"/>
-      <c r="C6" s="341"/>
-      <c r="D6" s="339"/>
-      <c r="E6" s="340"/>
-      <c r="F6" s="340"/>
-      <c r="G6" s="340"/>
-      <c r="H6" s="340"/>
-      <c r="I6" s="341"/>
+      <c r="B6" s="369"/>
+      <c r="C6" s="370"/>
+      <c r="D6" s="369"/>
+      <c r="E6" s="359"/>
+      <c r="F6" s="359"/>
+      <c r="G6" s="359"/>
+      <c r="H6" s="359"/>
+      <c r="I6" s="370"/>
       <c r="J6" s="31" t="s">
         <v>3</v>
       </c>
@@ -22153,21 +22164,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="360" t="s">
+      <c r="B7" s="428" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="344"/>
-      <c r="D7" s="344"/>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
-      <c r="G7" s="334"/>
-      <c r="H7" s="360" t="s">
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
+      <c r="E7" s="363"/>
+      <c r="F7" s="363"/>
+      <c r="G7" s="351"/>
+      <c r="H7" s="428" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="344"/>
-      <c r="J7" s="344"/>
-      <c r="K7" s="344"/>
-      <c r="L7" s="334"/>
+      <c r="I7" s="363"/>
+      <c r="J7" s="363"/>
+      <c r="K7" s="363"/>
+      <c r="L7" s="351"/>
       <c r="M7" s="202"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -22227,11 +22238,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="345" t="str">
+      <c r="J10" s="436" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="340"/>
+      <c r="K10" s="359"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -22359,42 +22370,42 @@
     </row>
     <row r="25" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="200"/>
-      <c r="B25" s="482" t="s">
+      <c r="B25" s="467" t="s">
         <v>340</v>
       </c>
-      <c r="C25" s="455"/>
-      <c r="D25" s="392"/>
-      <c r="E25" s="392"/>
-      <c r="F25" s="392"/>
-      <c r="G25" s="392"/>
-      <c r="H25" s="392"/>
-      <c r="I25" s="392"/>
-      <c r="J25" s="392"/>
-      <c r="K25" s="392"/>
-      <c r="L25" s="409"/>
+      <c r="C25" s="439"/>
+      <c r="D25" s="375"/>
+      <c r="E25" s="375"/>
+      <c r="F25" s="375"/>
+      <c r="G25" s="375"/>
+      <c r="H25" s="375"/>
+      <c r="I25" s="375"/>
+      <c r="J25" s="375"/>
+      <c r="K25" s="375"/>
+      <c r="L25" s="376"/>
       <c r="M25" s="202"/>
     </row>
     <row r="26" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="200"/>
-      <c r="B26" s="429"/>
-      <c r="C26" s="455"/>
-      <c r="D26" s="392"/>
-      <c r="E26" s="392"/>
-      <c r="F26" s="392"/>
-      <c r="G26" s="392"/>
-      <c r="H26" s="392"/>
-      <c r="I26" s="392"/>
-      <c r="J26" s="392"/>
-      <c r="K26" s="392"/>
-      <c r="L26" s="409"/>
+      <c r="B26" s="418"/>
+      <c r="C26" s="439"/>
+      <c r="D26" s="375"/>
+      <c r="E26" s="375"/>
+      <c r="F26" s="375"/>
+      <c r="G26" s="375"/>
+      <c r="H26" s="375"/>
+      <c r="I26" s="375"/>
+      <c r="J26" s="375"/>
+      <c r="K26" s="375"/>
+      <c r="L26" s="376"/>
       <c r="M26" s="202"/>
     </row>
     <row r="27" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="200"/>
-      <c r="B27" s="479" t="s">
+      <c r="B27" s="466" t="s">
         <v>341</v>
       </c>
-      <c r="C27" s="455"/>
+      <c r="C27" s="439"/>
       <c r="D27" s="324" t="e">
         <f>'QUADRO II'!F17</f>
         <v>#VALUE!</v>
@@ -22415,10 +22426,10 @@
     </row>
     <row r="28" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="200"/>
-      <c r="B28" s="479" t="s">
+      <c r="B28" s="466" t="s">
         <v>344</v>
       </c>
-      <c r="C28" s="455"/>
+      <c r="C28" s="439"/>
       <c r="D28" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22438,10 +22449,10 @@
     </row>
     <row r="29" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="200"/>
-      <c r="B29" s="479" t="s">
+      <c r="B29" s="466" t="s">
         <v>345</v>
       </c>
-      <c r="C29" s="455"/>
+      <c r="C29" s="439"/>
       <c r="D29" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22461,10 +22472,10 @@
     </row>
     <row r="30" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="200"/>
-      <c r="B30" s="479" t="s">
+      <c r="B30" s="466" t="s">
         <v>346</v>
       </c>
-      <c r="C30" s="455"/>
+      <c r="C30" s="439"/>
       <c r="D30" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22484,10 +22495,10 @@
     </row>
     <row r="31" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="200"/>
-      <c r="B31" s="479" t="s">
+      <c r="B31" s="466" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="455"/>
+      <c r="C31" s="439"/>
       <c r="D31" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22507,10 +22518,10 @@
     </row>
     <row r="32" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="200"/>
-      <c r="B32" s="479" t="s">
+      <c r="B32" s="466" t="s">
         <v>348</v>
       </c>
-      <c r="C32" s="455"/>
+      <c r="C32" s="439"/>
       <c r="D32" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22546,70 +22557,70 @@
     <row r="35" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="200"/>
       <c r="B35" s="271"/>
-      <c r="D35" s="484"/>
-      <c r="E35" s="392"/>
+      <c r="D35" s="469"/>
+      <c r="E35" s="375"/>
       <c r="L35" s="4"/>
       <c r="M35" s="202"/>
     </row>
     <row r="36" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="200"/>
-      <c r="B36" s="480" t="s">
+      <c r="B36" s="464" t="s">
         <v>350</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="338"/>
-      <c r="G36" s="483"/>
-      <c r="H36" s="337"/>
-      <c r="I36" s="337"/>
-      <c r="J36" s="337"/>
-      <c r="K36" s="338"/>
+      <c r="C36" s="367"/>
+      <c r="D36" s="367"/>
+      <c r="E36" s="367"/>
+      <c r="F36" s="368"/>
+      <c r="G36" s="468"/>
+      <c r="H36" s="367"/>
+      <c r="I36" s="367"/>
+      <c r="J36" s="367"/>
+      <c r="K36" s="368"/>
       <c r="L36" s="4"/>
       <c r="M36" s="202"/>
     </row>
     <row r="37" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="200"/>
-      <c r="B37" s="429"/>
-      <c r="C37" s="455"/>
-      <c r="D37" s="392"/>
-      <c r="E37" s="392"/>
-      <c r="F37" s="409"/>
-      <c r="G37" s="429"/>
-      <c r="H37" s="392"/>
-      <c r="I37" s="392"/>
-      <c r="J37" s="392"/>
-      <c r="K37" s="409"/>
+      <c r="B37" s="418"/>
+      <c r="C37" s="439"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="376"/>
+      <c r="G37" s="418"/>
+      <c r="H37" s="375"/>
+      <c r="I37" s="375"/>
+      <c r="J37" s="375"/>
+      <c r="K37" s="376"/>
       <c r="L37" s="4"/>
       <c r="M37" s="202"/>
     </row>
     <row r="38" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="200"/>
-      <c r="B38" s="429"/>
-      <c r="C38" s="455"/>
-      <c r="D38" s="392"/>
-      <c r="E38" s="392"/>
-      <c r="F38" s="409"/>
-      <c r="G38" s="429"/>
-      <c r="H38" s="392"/>
-      <c r="I38" s="392"/>
-      <c r="J38" s="392"/>
-      <c r="K38" s="409"/>
+      <c r="B38" s="418"/>
+      <c r="C38" s="439"/>
+      <c r="D38" s="375"/>
+      <c r="E38" s="375"/>
+      <c r="F38" s="376"/>
+      <c r="G38" s="418"/>
+      <c r="H38" s="375"/>
+      <c r="I38" s="375"/>
+      <c r="J38" s="375"/>
+      <c r="K38" s="376"/>
       <c r="L38" s="4"/>
       <c r="M38" s="202"/>
     </row>
     <row r="39" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="200"/>
-      <c r="B39" s="339"/>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="341"/>
-      <c r="G39" s="339"/>
-      <c r="H39" s="340"/>
-      <c r="I39" s="340"/>
-      <c r="J39" s="340"/>
-      <c r="K39" s="341"/>
+      <c r="B39" s="369"/>
+      <c r="C39" s="359"/>
+      <c r="D39" s="359"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="370"/>
+      <c r="G39" s="369"/>
+      <c r="H39" s="359"/>
+      <c r="I39" s="359"/>
+      <c r="J39" s="359"/>
+      <c r="K39" s="370"/>
       <c r="L39" s="4"/>
       <c r="M39" s="202"/>
     </row>
@@ -22653,6 +22664,10 @@
     <row r="43" spans="1:13" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B5:C6"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B36:F39"/>
     <mergeCell ref="B1:L1"/>
@@ -22669,10 +22684,6 @@
     <mergeCell ref="D5:I6"/>
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="B3:L3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B5:C6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>

--- a/QUADROS ABNT.xlsx
+++ b/QUADROS ABNT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Desktop\DOCUMENTOS APROVAÇÃO EMPREEDIMENTOS\DOCUMENTOS INCIAIS\5 - QUADROS ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6740D1-A7EA-4142-B3C7-42CC07421633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="976" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA" sheetId="1" r:id="rId1"/>
@@ -3301,25 +3301,69 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3332,40 +3376,98 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3373,10 +3475,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3387,18 +3485,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3406,54 +3504,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="39" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3461,162 +3536,99 @@
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="39" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="39" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="39" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3626,15 +3638,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="39" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3647,8 +3662,30 @@
     <xf numFmtId="39" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="39" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3659,55 +3696,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3716,18 +3728,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4057,15 +4057,15 @@
   <sheetData>
     <row r="1" spans="1:9" ht="40.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A1" s="168"/>
-      <c r="B1" s="338" t="s">
+      <c r="B1" s="360" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="339"/>
-      <c r="D1" s="339"/>
-      <c r="E1" s="339"/>
-      <c r="F1" s="339"/>
-      <c r="G1" s="339"/>
-      <c r="H1" s="339"/>
+      <c r="C1" s="334"/>
+      <c r="D1" s="334"/>
+      <c r="E1" s="334"/>
+      <c r="F1" s="334"/>
+      <c r="G1" s="334"/>
+      <c r="H1" s="334"/>
       <c r="I1" s="169"/>
     </row>
     <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4082,15 +4082,15 @@
       <c r="B3" s="178" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="340" t="s">
+      <c r="C3" s="361" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="334"/>
-      <c r="E3" s="334"/>
-      <c r="F3" s="334"/>
-      <c r="G3" s="334"/>
-      <c r="H3" s="334"/>
-      <c r="I3" s="341"/>
+      <c r="D3" s="362"/>
+      <c r="E3" s="362"/>
+      <c r="F3" s="362"/>
+      <c r="G3" s="362"/>
+      <c r="H3" s="362"/>
+      <c r="I3" s="363"/>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="170"/>
@@ -4135,32 +4135,32 @@
     </row>
     <row r="7" spans="1:9" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="170"/>
-      <c r="B7" s="342" t="s">
+      <c r="B7" s="364" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="343"/>
-      <c r="D7" s="348" t="s">
+      <c r="C7" s="365"/>
+      <c r="D7" s="371" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="349" t="s">
+      <c r="E7" s="372" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="335" t="s">
+      <c r="F7" s="358" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="346" t="s">
+      <c r="G7" s="368" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="347"/>
+      <c r="H7" s="369"/>
       <c r="I7" s="171"/>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="170"/>
-      <c r="B8" s="344"/>
-      <c r="C8" s="345"/>
-      <c r="D8" s="336"/>
-      <c r="E8" s="336"/>
-      <c r="F8" s="336"/>
+      <c r="B8" s="366"/>
+      <c r="C8" s="367"/>
+      <c r="D8" s="359"/>
+      <c r="E8" s="359"/>
+      <c r="F8" s="359"/>
       <c r="G8" s="177" t="s">
         <v>45</v>
       </c>
@@ -4226,17 +4226,17 @@
       <c r="I10" s="171"/>
     </row>
     <row r="11" spans="1:9" ht="38.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="500" t="s">
+      <c r="A11" s="376" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="395"/>
-      <c r="C11" s="395"/>
-      <c r="D11" s="395"/>
-      <c r="E11" s="395"/>
-      <c r="F11" s="395"/>
-      <c r="G11" s="395"/>
-      <c r="H11" s="395"/>
-      <c r="I11" s="501"/>
+      <c r="B11" s="377"/>
+      <c r="C11" s="377"/>
+      <c r="D11" s="377"/>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
+      <c r="G11" s="377"/>
+      <c r="H11" s="377"/>
+      <c r="I11" s="378"/>
     </row>
     <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="170"/>
@@ -4244,42 +4244,42 @@
     </row>
     <row r="13" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="170"/>
-      <c r="B13" s="337" t="s">
+      <c r="B13" s="370" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="334"/>
-      <c r="D13" s="334"/>
-      <c r="E13" s="334"/>
-      <c r="F13" s="334"/>
-      <c r="G13" s="334"/>
-      <c r="H13" s="334"/>
+      <c r="C13" s="362"/>
+      <c r="D13" s="362"/>
+      <c r="E13" s="362"/>
+      <c r="F13" s="362"/>
+      <c r="G13" s="362"/>
+      <c r="H13" s="362"/>
       <c r="I13" s="171"/>
     </row>
     <row r="14" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="498" t="s">
+      <c r="A14" s="373" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="333"/>
-      <c r="C14" s="333"/>
-      <c r="D14" s="333"/>
-      <c r="E14" s="333"/>
-      <c r="F14" s="333"/>
-      <c r="G14" s="333"/>
-      <c r="H14" s="333"/>
-      <c r="I14" s="499"/>
+      <c r="B14" s="374"/>
+      <c r="C14" s="374"/>
+      <c r="D14" s="374"/>
+      <c r="E14" s="374"/>
+      <c r="F14" s="374"/>
+      <c r="G14" s="374"/>
+      <c r="H14" s="374"/>
+      <c r="I14" s="375"/>
     </row>
     <row r="15" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="498" t="s">
+      <c r="A15" s="373" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="333"/>
-      <c r="C15" s="333"/>
-      <c r="D15" s="333"/>
-      <c r="E15" s="333"/>
-      <c r="F15" s="333"/>
-      <c r="G15" s="333"/>
-      <c r="H15" s="333"/>
-      <c r="I15" s="499"/>
+      <c r="B15" s="374"/>
+      <c r="C15" s="374"/>
+      <c r="D15" s="374"/>
+      <c r="E15" s="374"/>
+      <c r="F15" s="374"/>
+      <c r="G15" s="374"/>
+      <c r="H15" s="374"/>
+      <c r="I15" s="375"/>
     </row>
     <row r="16" spans="1:9" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="172"/>
@@ -4296,17 +4296,17 @@
     <row r="18" ht="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="G7:H7"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A11:I11"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="G7:H7"/>
   </mergeCells>
   <pageMargins left="1.181102362204725" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait"/>
@@ -4334,65 +4334,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="364"/>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
-      <c r="I1" s="365"/>
-      <c r="J1" s="365"/>
-      <c r="K1" s="365"/>
-      <c r="L1" s="365"/>
+      <c r="B1" s="408"/>
+      <c r="C1" s="409"/>
+      <c r="D1" s="409"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="409"/>
+      <c r="J1" s="409"/>
+      <c r="K1" s="409"/>
+      <c r="L1" s="409"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="431" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
-      <c r="H2" s="367"/>
-      <c r="I2" s="367"/>
-      <c r="J2" s="367"/>
-      <c r="K2" s="367"/>
-      <c r="L2" s="368"/>
+      <c r="B2" s="438" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="337"/>
+      <c r="D2" s="337"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="337"/>
+      <c r="K2" s="337"/>
+      <c r="L2" s="338"/>
       <c r="M2" s="202"/>
     </row>
     <row r="3" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="344" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="370"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="339"/>
+      <c r="I3" s="339"/>
+      <c r="J3" s="339"/>
+      <c r="K3" s="339"/>
+      <c r="L3" s="340"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="428" t="s">
+      <c r="B4" s="345" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="351"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="343"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -4405,36 +4405,36 @@
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="484" t="s">
+      <c r="B5" s="476" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="368"/>
-      <c r="D5" s="470" t="str">
+      <c r="C5" s="338"/>
+      <c r="D5" s="475" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="367"/>
-      <c r="F5" s="367"/>
-      <c r="G5" s="367"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="368"/>
-      <c r="J5" s="425" t="s">
+      <c r="E5" s="337"/>
+      <c r="F5" s="337"/>
+      <c r="G5" s="337"/>
+      <c r="H5" s="337"/>
+      <c r="I5" s="338"/>
+      <c r="J5" s="449" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="363"/>
-      <c r="L5" s="351"/>
+      <c r="K5" s="342"/>
+      <c r="L5" s="343"/>
       <c r="M5" s="202"/>
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="369"/>
-      <c r="C6" s="370"/>
-      <c r="D6" s="369"/>
-      <c r="E6" s="359"/>
-      <c r="F6" s="359"/>
-      <c r="G6" s="359"/>
-      <c r="H6" s="359"/>
-      <c r="I6" s="370"/>
+      <c r="B6" s="351"/>
+      <c r="C6" s="340"/>
+      <c r="D6" s="351"/>
+      <c r="E6" s="339"/>
+      <c r="F6" s="339"/>
+      <c r="G6" s="339"/>
+      <c r="H6" s="339"/>
+      <c r="I6" s="340"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -4447,21 +4447,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="428" t="s">
+      <c r="B7" s="345" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
-      <c r="E7" s="363"/>
-      <c r="F7" s="363"/>
-      <c r="G7" s="351"/>
-      <c r="H7" s="428" t="s">
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="342"/>
+      <c r="G7" s="343"/>
+      <c r="H7" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="363"/>
-      <c r="J7" s="363"/>
-      <c r="K7" s="363"/>
-      <c r="L7" s="351"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="342"/>
+      <c r="K7" s="342"/>
+      <c r="L7" s="343"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -4521,11 +4521,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="436" t="str">
+      <c r="J10" s="462" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="359"/>
+      <c r="K10" s="339"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -4540,227 +4540,231 @@
     </row>
     <row r="12" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="200"/>
-      <c r="B12" s="482" t="s">
+      <c r="B12" s="480" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="477"/>
-      <c r="D12" s="476" t="s">
+      <c r="C12" s="481"/>
+      <c r="D12" s="482" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="477"/>
-      <c r="F12" s="476" t="s">
+      <c r="E12" s="481"/>
+      <c r="F12" s="482" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="477"/>
-      <c r="H12" s="476" t="s">
+      <c r="G12" s="481"/>
+      <c r="H12" s="482" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="479"/>
-      <c r="J12" s="479"/>
-      <c r="K12" s="479"/>
-      <c r="L12" s="477"/>
+      <c r="I12" s="488"/>
+      <c r="J12" s="488"/>
+      <c r="K12" s="488"/>
+      <c r="L12" s="481"/>
       <c r="M12" s="202"/>
     </row>
     <row r="13" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="200"/>
-      <c r="B13" s="472" t="s">
+      <c r="B13" s="485" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="370"/>
-      <c r="D13" s="475" t="s">
+      <c r="C13" s="340"/>
+      <c r="D13" s="484" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="370"/>
-      <c r="F13" s="475" t="s">
+      <c r="E13" s="340"/>
+      <c r="F13" s="484" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="370"/>
-      <c r="H13" s="474" t="s">
+      <c r="G13" s="340"/>
+      <c r="H13" s="487" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="359"/>
-      <c r="J13" s="359"/>
-      <c r="K13" s="359"/>
-      <c r="L13" s="370"/>
+      <c r="I13" s="339"/>
+      <c r="J13" s="339"/>
+      <c r="K13" s="339"/>
+      <c r="L13" s="340"/>
       <c r="M13" s="202"/>
     </row>
     <row r="14" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="200"/>
-      <c r="B14" s="478" t="s">
+      <c r="B14" s="479" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="351"/>
-      <c r="D14" s="480" t="s">
+      <c r="C14" s="343"/>
+      <c r="D14" s="477" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="351"/>
-      <c r="F14" s="480" t="s">
+      <c r="E14" s="343"/>
+      <c r="F14" s="477" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="351"/>
-      <c r="H14" s="350"/>
-      <c r="I14" s="363"/>
-      <c r="J14" s="363"/>
-      <c r="K14" s="363"/>
-      <c r="L14" s="351"/>
+      <c r="G14" s="343"/>
+      <c r="H14" s="422"/>
+      <c r="I14" s="342"/>
+      <c r="J14" s="342"/>
+      <c r="K14" s="342"/>
+      <c r="L14" s="343"/>
       <c r="M14" s="202"/>
     </row>
     <row r="15" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="200"/>
-      <c r="B15" s="478" t="s">
+      <c r="B15" s="479" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="351"/>
-      <c r="D15" s="480" t="s">
+      <c r="C15" s="343"/>
+      <c r="D15" s="477" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="351"/>
-      <c r="F15" s="480" t="s">
+      <c r="E15" s="343"/>
+      <c r="F15" s="477" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="351"/>
-      <c r="H15" s="350"/>
-      <c r="I15" s="363"/>
-      <c r="J15" s="363"/>
-      <c r="K15" s="363"/>
-      <c r="L15" s="351"/>
+      <c r="G15" s="343"/>
+      <c r="H15" s="422"/>
+      <c r="I15" s="342"/>
+      <c r="J15" s="342"/>
+      <c r="K15" s="342"/>
+      <c r="L15" s="343"/>
       <c r="M15" s="202"/>
     </row>
     <row r="16" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="200"/>
-      <c r="B16" s="478" t="s">
+      <c r="B16" s="479" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="351"/>
-      <c r="D16" s="473" t="s">
+      <c r="C16" s="343"/>
+      <c r="D16" s="486" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="351"/>
-      <c r="F16" s="481" t="s">
+      <c r="E16" s="343"/>
+      <c r="F16" s="478" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="351"/>
-      <c r="H16" s="350"/>
-      <c r="I16" s="363"/>
-      <c r="J16" s="363"/>
-      <c r="K16" s="363"/>
-      <c r="L16" s="351"/>
+      <c r="G16" s="343"/>
+      <c r="H16" s="422"/>
+      <c r="I16" s="342"/>
+      <c r="J16" s="342"/>
+      <c r="K16" s="342"/>
+      <c r="L16" s="343"/>
       <c r="M16" s="202"/>
     </row>
     <row r="17" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="200"/>
-      <c r="B17" s="478" t="s">
+      <c r="B17" s="479" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="351"/>
-      <c r="D17" s="480" t="s">
+      <c r="C17" s="343"/>
+      <c r="D17" s="477" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="351"/>
-      <c r="F17" s="480" t="s">
+      <c r="E17" s="343"/>
+      <c r="F17" s="477" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="351"/>
-      <c r="H17" s="350"/>
-      <c r="I17" s="363"/>
-      <c r="J17" s="363"/>
-      <c r="K17" s="363"/>
-      <c r="L17" s="351"/>
+      <c r="G17" s="343"/>
+      <c r="H17" s="422"/>
+      <c r="I17" s="342"/>
+      <c r="J17" s="342"/>
+      <c r="K17" s="342"/>
+      <c r="L17" s="343"/>
       <c r="M17" s="202"/>
     </row>
     <row r="18" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="200"/>
-      <c r="B18" s="478" t="s">
+      <c r="B18" s="479" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="351"/>
-      <c r="D18" s="480" t="s">
+      <c r="C18" s="343"/>
+      <c r="D18" s="477" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="351"/>
-      <c r="F18" s="480" t="s">
+      <c r="E18" s="343"/>
+      <c r="F18" s="477" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="351"/>
-      <c r="H18" s="350"/>
-      <c r="I18" s="363"/>
-      <c r="J18" s="363"/>
-      <c r="K18" s="363"/>
-      <c r="L18" s="351"/>
+      <c r="G18" s="343"/>
+      <c r="H18" s="422"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="343"/>
       <c r="M18" s="202"/>
     </row>
     <row r="19" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="200"/>
-      <c r="B19" s="478" t="s">
+      <c r="B19" s="479" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="351"/>
-      <c r="D19" s="480" t="s">
+      <c r="C19" s="343"/>
+      <c r="D19" s="477" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="351"/>
-      <c r="F19" s="480" t="s">
+      <c r="E19" s="343"/>
+      <c r="F19" s="477" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="351"/>
-      <c r="H19" s="441"/>
-      <c r="I19" s="363"/>
-      <c r="J19" s="363"/>
-      <c r="K19" s="363"/>
-      <c r="L19" s="351"/>
+      <c r="G19" s="343"/>
+      <c r="H19" s="453"/>
+      <c r="I19" s="342"/>
+      <c r="J19" s="342"/>
+      <c r="K19" s="342"/>
+      <c r="L19" s="343"/>
       <c r="M19" s="202"/>
     </row>
     <row r="20" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="478" t="s">
+      <c r="B20" s="479" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="351"/>
-      <c r="D20" s="481" t="s">
+      <c r="C20" s="343"/>
+      <c r="D20" s="478" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="481" t="s">
+      <c r="E20" s="343"/>
+      <c r="F20" s="478" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="351"/>
-      <c r="H20" s="441"/>
-      <c r="I20" s="363"/>
-      <c r="J20" s="363"/>
-      <c r="K20" s="363"/>
-      <c r="L20" s="351"/>
+      <c r="G20" s="343"/>
+      <c r="H20" s="453"/>
+      <c r="I20" s="342"/>
+      <c r="J20" s="342"/>
+      <c r="K20" s="342"/>
+      <c r="L20" s="343"/>
       <c r="M20" s="202"/>
     </row>
     <row r="21" spans="1:13" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="203"/>
       <c r="B21" s="483"/>
-      <c r="C21" s="373"/>
-      <c r="D21" s="373"/>
-      <c r="E21" s="373"/>
-      <c r="F21" s="373"/>
-      <c r="G21" s="373"/>
-      <c r="H21" s="373"/>
-      <c r="I21" s="373"/>
-      <c r="J21" s="373"/>
-      <c r="K21" s="373"/>
-      <c r="L21" s="373"/>
+      <c r="C21" s="413"/>
+      <c r="D21" s="413"/>
+      <c r="E21" s="413"/>
+      <c r="F21" s="413"/>
+      <c r="G21" s="413"/>
+      <c r="H21" s="413"/>
+      <c r="I21" s="413"/>
+      <c r="J21" s="413"/>
+      <c r="K21" s="413"/>
+      <c r="L21" s="413"/>
       <c r="M21" s="204"/>
     </row>
     <row r="22" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="H17:L17"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="H12:L12"/>
     <mergeCell ref="B21:L21"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="D13:E13"/>
@@ -4777,22 +4781,18 @@
     <mergeCell ref="H18:L18"/>
     <mergeCell ref="H14:L14"/>
     <mergeCell ref="F14:G14"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="H17:L17"/>
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="H15:L15"/>
     <mergeCell ref="D14:E14"/>
@@ -4818,65 +4818,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="364"/>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
-      <c r="I1" s="365"/>
-      <c r="J1" s="365"/>
-      <c r="K1" s="365"/>
-      <c r="L1" s="365"/>
+      <c r="B1" s="408"/>
+      <c r="C1" s="409"/>
+      <c r="D1" s="409"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="409"/>
+      <c r="J1" s="409"/>
+      <c r="K1" s="409"/>
+      <c r="L1" s="409"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="431" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
-      <c r="H2" s="367"/>
-      <c r="I2" s="367"/>
-      <c r="J2" s="367"/>
-      <c r="K2" s="367"/>
-      <c r="L2" s="368"/>
+      <c r="B2" s="438" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="337"/>
+      <c r="D2" s="337"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="337"/>
+      <c r="K2" s="337"/>
+      <c r="L2" s="338"/>
       <c r="M2" s="282"/>
     </row>
     <row r="3" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="344" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="370"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="339"/>
+      <c r="I3" s="339"/>
+      <c r="J3" s="339"/>
+      <c r="K3" s="339"/>
+      <c r="L3" s="340"/>
       <c r="M3" s="282"/>
     </row>
     <row r="4" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="428" t="s">
+      <c r="B4" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="351"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="343"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -4889,36 +4889,36 @@
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="484" t="s">
+      <c r="B5" s="476" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="368"/>
-      <c r="D5" s="470" t="str">
+      <c r="C5" s="338"/>
+      <c r="D5" s="475" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="367"/>
-      <c r="F5" s="367"/>
-      <c r="G5" s="367"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="368"/>
-      <c r="J5" s="425" t="s">
+      <c r="E5" s="337"/>
+      <c r="F5" s="337"/>
+      <c r="G5" s="337"/>
+      <c r="H5" s="337"/>
+      <c r="I5" s="338"/>
+      <c r="J5" s="449" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="363"/>
-      <c r="L5" s="351"/>
+      <c r="K5" s="342"/>
+      <c r="L5" s="343"/>
       <c r="M5" s="213"/>
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="369"/>
-      <c r="C6" s="370"/>
-      <c r="D6" s="369"/>
-      <c r="E6" s="359"/>
-      <c r="F6" s="359"/>
-      <c r="G6" s="359"/>
-      <c r="H6" s="359"/>
-      <c r="I6" s="370"/>
+      <c r="B6" s="351"/>
+      <c r="C6" s="340"/>
+      <c r="D6" s="351"/>
+      <c r="E6" s="339"/>
+      <c r="F6" s="339"/>
+      <c r="G6" s="339"/>
+      <c r="H6" s="339"/>
+      <c r="I6" s="340"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -4931,21 +4931,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="428" t="s">
+      <c r="B7" s="345" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
-      <c r="E7" s="363"/>
-      <c r="F7" s="363"/>
-      <c r="G7" s="351"/>
-      <c r="H7" s="428" t="s">
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="342"/>
+      <c r="G7" s="343"/>
+      <c r="H7" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="363"/>
-      <c r="J7" s="363"/>
-      <c r="K7" s="363"/>
-      <c r="L7" s="351"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="342"/>
+      <c r="K7" s="342"/>
+      <c r="L7" s="343"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -5005,11 +5005,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="436" t="str">
+      <c r="J10" s="462" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="359"/>
+      <c r="K10" s="339"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -5024,24 +5024,24 @@
     </row>
     <row r="12" spans="1:13" s="25" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="285"/>
-      <c r="B12" s="482" t="s">
+      <c r="B12" s="480" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="477"/>
-      <c r="D12" s="476" t="s">
+      <c r="C12" s="481"/>
+      <c r="D12" s="482" t="s">
         <v>353</v>
       </c>
-      <c r="E12" s="479"/>
-      <c r="F12" s="477"/>
-      <c r="G12" s="476" t="s">
+      <c r="E12" s="488"/>
+      <c r="F12" s="481"/>
+      <c r="G12" s="482" t="s">
         <v>354</v>
       </c>
-      <c r="H12" s="479"/>
-      <c r="I12" s="477"/>
-      <c r="J12" s="476" t="s">
+      <c r="H12" s="488"/>
+      <c r="I12" s="481"/>
+      <c r="J12" s="482" t="s">
         <v>355</v>
       </c>
-      <c r="K12" s="477"/>
+      <c r="K12" s="481"/>
       <c r="L12" s="291" t="s">
         <v>356</v>
       </c>
@@ -5049,155 +5049,155 @@
     </row>
     <row r="13" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="285"/>
-      <c r="B13" s="490" t="s">
+      <c r="B13" s="495" t="s">
         <v>357</v>
       </c>
-      <c r="C13" s="491"/>
-      <c r="D13" s="492" t="s">
+      <c r="C13" s="493"/>
+      <c r="D13" s="491" t="s">
         <v>358</v>
       </c>
-      <c r="E13" s="493"/>
-      <c r="F13" s="491"/>
-      <c r="G13" s="492" t="s">
+      <c r="E13" s="492"/>
+      <c r="F13" s="493"/>
+      <c r="G13" s="491" t="s">
         <v>359</v>
       </c>
-      <c r="H13" s="493"/>
-      <c r="I13" s="491"/>
-      <c r="J13" s="492" t="s">
+      <c r="H13" s="492"/>
+      <c r="I13" s="493"/>
+      <c r="J13" s="491" t="s">
         <v>360</v>
       </c>
-      <c r="K13" s="491"/>
+      <c r="K13" s="493"/>
       <c r="L13" s="279"/>
       <c r="M13" s="286"/>
     </row>
     <row r="14" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="285"/>
-      <c r="B14" s="486" t="s">
+      <c r="B14" s="490" t="s">
         <v>197</v>
       </c>
-      <c r="C14" s="376"/>
-      <c r="D14" s="488" t="s">
+      <c r="C14" s="405"/>
+      <c r="D14" s="489" t="s">
         <v>358</v>
       </c>
-      <c r="E14" s="489"/>
-      <c r="F14" s="376"/>
-      <c r="G14" s="488" t="s">
+      <c r="E14" s="494"/>
+      <c r="F14" s="405"/>
+      <c r="G14" s="489" t="s">
         <v>359</v>
       </c>
-      <c r="H14" s="489"/>
-      <c r="I14" s="376"/>
-      <c r="J14" s="488" t="s">
+      <c r="H14" s="494"/>
+      <c r="I14" s="405"/>
+      <c r="J14" s="489" t="s">
         <v>360</v>
       </c>
-      <c r="K14" s="376"/>
+      <c r="K14" s="405"/>
       <c r="L14" s="280"/>
       <c r="M14" s="286"/>
     </row>
     <row r="15" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="285"/>
-      <c r="B15" s="486" t="s">
+      <c r="B15" s="490" t="s">
         <v>361</v>
       </c>
-      <c r="C15" s="376"/>
-      <c r="D15" s="488" t="s">
+      <c r="C15" s="405"/>
+      <c r="D15" s="489" t="s">
         <v>358</v>
       </c>
-      <c r="E15" s="489"/>
-      <c r="F15" s="376"/>
-      <c r="G15" s="488" t="s">
+      <c r="E15" s="494"/>
+      <c r="F15" s="405"/>
+      <c r="G15" s="489" t="s">
         <v>362</v>
       </c>
-      <c r="H15" s="489"/>
-      <c r="I15" s="376"/>
-      <c r="J15" s="488" t="s">
+      <c r="H15" s="494"/>
+      <c r="I15" s="405"/>
+      <c r="J15" s="489" t="s">
         <v>360</v>
       </c>
-      <c r="K15" s="376"/>
+      <c r="K15" s="405"/>
       <c r="L15" s="280"/>
       <c r="M15" s="286"/>
     </row>
     <row r="16" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="285"/>
-      <c r="B16" s="486" t="s">
+      <c r="B16" s="490" t="s">
         <v>363</v>
       </c>
-      <c r="C16" s="376"/>
-      <c r="D16" s="488" t="s">
+      <c r="C16" s="405"/>
+      <c r="D16" s="489" t="s">
         <v>358</v>
       </c>
-      <c r="E16" s="489"/>
-      <c r="F16" s="376"/>
-      <c r="G16" s="488" t="s">
+      <c r="E16" s="494"/>
+      <c r="F16" s="405"/>
+      <c r="G16" s="489" t="s">
         <v>362</v>
       </c>
-      <c r="H16" s="489"/>
-      <c r="I16" s="376"/>
-      <c r="J16" s="488" t="s">
+      <c r="H16" s="494"/>
+      <c r="I16" s="405"/>
+      <c r="J16" s="489" t="s">
         <v>360</v>
       </c>
-      <c r="K16" s="376"/>
+      <c r="K16" s="405"/>
       <c r="L16" s="280"/>
       <c r="M16" s="286"/>
     </row>
     <row r="17" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="285"/>
-      <c r="B17" s="486" t="s">
+      <c r="B17" s="490" t="s">
         <v>364</v>
       </c>
-      <c r="C17" s="376"/>
-      <c r="D17" s="488" t="s">
+      <c r="C17" s="405"/>
+      <c r="D17" s="489" t="s">
         <v>358</v>
       </c>
-      <c r="E17" s="489"/>
-      <c r="F17" s="376"/>
-      <c r="G17" s="488" t="s">
+      <c r="E17" s="494"/>
+      <c r="F17" s="405"/>
+      <c r="G17" s="489" t="s">
         <v>365</v>
       </c>
-      <c r="H17" s="489"/>
-      <c r="I17" s="376"/>
-      <c r="J17" s="488" t="s">
+      <c r="H17" s="494"/>
+      <c r="I17" s="405"/>
+      <c r="J17" s="489" t="s">
         <v>360</v>
       </c>
-      <c r="K17" s="376"/>
+      <c r="K17" s="405"/>
       <c r="L17" s="280"/>
       <c r="M17" s="286"/>
     </row>
     <row r="18" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="285"/>
-      <c r="B18" s="472" t="s">
+      <c r="B18" s="485" t="s">
         <v>366</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="488" t="s">
+      <c r="C18" s="340"/>
+      <c r="D18" s="489" t="s">
         <v>358</v>
       </c>
-      <c r="E18" s="489"/>
-      <c r="F18" s="376"/>
-      <c r="G18" s="487" t="s">
+      <c r="E18" s="494"/>
+      <c r="F18" s="405"/>
+      <c r="G18" s="497" t="s">
         <v>362</v>
       </c>
-      <c r="H18" s="359"/>
-      <c r="I18" s="370"/>
-      <c r="J18" s="487" t="s">
+      <c r="H18" s="339"/>
+      <c r="I18" s="340"/>
+      <c r="J18" s="497" t="s">
         <v>360</v>
       </c>
-      <c r="K18" s="370"/>
+      <c r="K18" s="340"/>
       <c r="L18" s="281"/>
       <c r="M18" s="286"/>
     </row>
     <row r="19" spans="1:13" s="25" customFormat="1" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="287"/>
-      <c r="B19" s="485"/>
-      <c r="C19" s="373"/>
-      <c r="D19" s="373"/>
-      <c r="E19" s="373"/>
-      <c r="F19" s="373"/>
-      <c r="G19" s="373"/>
-      <c r="H19" s="373"/>
-      <c r="I19" s="373"/>
-      <c r="J19" s="373"/>
-      <c r="K19" s="373"/>
-      <c r="L19" s="373"/>
+      <c r="B19" s="496"/>
+      <c r="C19" s="413"/>
+      <c r="D19" s="413"/>
+      <c r="E19" s="413"/>
+      <c r="F19" s="413"/>
+      <c r="G19" s="413"/>
+      <c r="H19" s="413"/>
+      <c r="I19" s="413"/>
+      <c r="J19" s="413"/>
+      <c r="K19" s="413"/>
+      <c r="L19" s="413"/>
       <c r="M19" s="288"/>
     </row>
     <row r="20" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -5492,29 +5492,6 @@
     <row r="309" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G15:I15"/>
     <mergeCell ref="B19:L19"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="B7:G7"/>
@@ -5531,6 +5508,29 @@
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="B5:C6"/>
     <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D13:F13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -5557,65 +5557,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="13.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="364"/>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
-      <c r="I1" s="365"/>
-      <c r="J1" s="365"/>
-      <c r="K1" s="365"/>
-      <c r="L1" s="365"/>
+      <c r="B1" s="408"/>
+      <c r="C1" s="409"/>
+      <c r="D1" s="409"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="409"/>
+      <c r="J1" s="409"/>
+      <c r="K1" s="409"/>
+      <c r="L1" s="409"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="431" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
-      <c r="H2" s="367"/>
-      <c r="I2" s="367"/>
-      <c r="J2" s="367"/>
-      <c r="K2" s="367"/>
-      <c r="L2" s="368"/>
+      <c r="B2" s="438" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="337"/>
+      <c r="D2" s="337"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="337"/>
+      <c r="K2" s="337"/>
+      <c r="L2" s="338"/>
       <c r="M2" s="282"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="344" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="370"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="339"/>
+      <c r="I3" s="339"/>
+      <c r="J3" s="339"/>
+      <c r="K3" s="339"/>
+      <c r="L3" s="340"/>
       <c r="M3" s="282"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="428" t="s">
+      <c r="B4" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="351"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="343"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -5625,36 +5625,36 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="484" t="s">
+      <c r="B5" s="476" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="368"/>
-      <c r="D5" s="470" t="str">
+      <c r="C5" s="338"/>
+      <c r="D5" s="475" t="str">
         <f>'QUADRO I'!D5:O6</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="367"/>
-      <c r="F5" s="367"/>
-      <c r="G5" s="367"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="368"/>
-      <c r="J5" s="425" t="s">
+      <c r="E5" s="337"/>
+      <c r="F5" s="337"/>
+      <c r="G5" s="337"/>
+      <c r="H5" s="337"/>
+      <c r="I5" s="338"/>
+      <c r="J5" s="449" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="363"/>
-      <c r="L5" s="351"/>
+      <c r="K5" s="342"/>
+      <c r="L5" s="343"/>
       <c r="M5" s="213"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="369"/>
-      <c r="C6" s="370"/>
-      <c r="D6" s="369"/>
-      <c r="E6" s="359"/>
-      <c r="F6" s="359"/>
-      <c r="G6" s="359"/>
-      <c r="H6" s="359"/>
-      <c r="I6" s="370"/>
+      <c r="B6" s="351"/>
+      <c r="C6" s="340"/>
+      <c r="D6" s="351"/>
+      <c r="E6" s="339"/>
+      <c r="F6" s="339"/>
+      <c r="G6" s="339"/>
+      <c r="H6" s="339"/>
+      <c r="I6" s="340"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -5666,21 +5666,21 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="428" t="s">
+      <c r="B7" s="345" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
-      <c r="E7" s="363"/>
-      <c r="F7" s="363"/>
-      <c r="G7" s="351"/>
-      <c r="H7" s="428" t="s">
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="342"/>
+      <c r="G7" s="343"/>
+      <c r="H7" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="363"/>
-      <c r="J7" s="363"/>
-      <c r="K7" s="363"/>
-      <c r="L7" s="351"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="342"/>
+      <c r="K7" s="342"/>
+      <c r="L7" s="343"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -5688,14 +5688,14 @@
       <c r="B8" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="496" t="str">
+      <c r="C8" s="500" t="str">
         <f>'QUADRO VII'!C8</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="D8" s="367"/>
-      <c r="E8" s="367"/>
-      <c r="F8" s="367"/>
-      <c r="G8" s="368"/>
+      <c r="D8" s="337"/>
+      <c r="E8" s="337"/>
+      <c r="F8" s="337"/>
+      <c r="G8" s="338"/>
       <c r="H8" s="19" t="s">
         <v>9</v>
       </c>
@@ -5747,11 +5747,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="436" t="str">
+      <c r="J10" s="462" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="359"/>
+      <c r="K10" s="339"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -5760,24 +5760,24 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="441" t="s">
+      <c r="B11" s="453" t="s">
         <v>352</v>
       </c>
-      <c r="C11" s="351"/>
-      <c r="D11" s="441" t="s">
+      <c r="C11" s="343"/>
+      <c r="D11" s="453" t="s">
         <v>353</v>
       </c>
-      <c r="E11" s="363"/>
-      <c r="F11" s="351"/>
-      <c r="G11" s="441" t="s">
+      <c r="E11" s="342"/>
+      <c r="F11" s="343"/>
+      <c r="G11" s="453" t="s">
         <v>354</v>
       </c>
-      <c r="H11" s="363"/>
-      <c r="I11" s="351"/>
-      <c r="J11" s="441" t="s">
+      <c r="H11" s="342"/>
+      <c r="I11" s="343"/>
+      <c r="J11" s="453" t="s">
         <v>355</v>
       </c>
-      <c r="K11" s="351"/>
+      <c r="K11" s="343"/>
       <c r="L11" s="306" t="s">
         <v>356</v>
       </c>
@@ -5785,162 +5785,162 @@
     </row>
     <row r="12" spans="1:13" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="285"/>
-      <c r="B12" s="437" t="s">
+      <c r="B12" s="450" t="s">
         <v>368</v>
       </c>
-      <c r="C12" s="368"/>
-      <c r="D12" s="437" t="s">
+      <c r="C12" s="338"/>
+      <c r="D12" s="450" t="s">
         <v>369</v>
       </c>
-      <c r="E12" s="367"/>
-      <c r="F12" s="368"/>
-      <c r="G12" s="437" t="s">
+      <c r="E12" s="337"/>
+      <c r="F12" s="338"/>
+      <c r="G12" s="450" t="s">
         <v>370</v>
       </c>
-      <c r="H12" s="367"/>
-      <c r="I12" s="368"/>
-      <c r="J12" s="437" t="s">
+      <c r="H12" s="337"/>
+      <c r="I12" s="338"/>
+      <c r="J12" s="450" t="s">
         <v>371</v>
       </c>
-      <c r="K12" s="368"/>
+      <c r="K12" s="338"/>
       <c r="L12" s="307"/>
       <c r="M12" s="286"/>
     </row>
     <row r="13" spans="1:13" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="285"/>
-      <c r="B13" s="494" t="s">
+      <c r="B13" s="498" t="s">
         <v>372</v>
       </c>
-      <c r="C13" s="376"/>
-      <c r="D13" s="494" t="s">
+      <c r="C13" s="405"/>
+      <c r="D13" s="498" t="s">
         <v>369</v>
       </c>
-      <c r="E13" s="495"/>
-      <c r="F13" s="376"/>
-      <c r="G13" s="494" t="s">
+      <c r="E13" s="499"/>
+      <c r="F13" s="405"/>
+      <c r="G13" s="498" t="s">
         <v>370</v>
       </c>
-      <c r="H13" s="495"/>
-      <c r="I13" s="376"/>
-      <c r="J13" s="494" t="s">
+      <c r="H13" s="499"/>
+      <c r="I13" s="405"/>
+      <c r="J13" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K13" s="376"/>
+      <c r="K13" s="405"/>
       <c r="L13" s="280"/>
       <c r="M13" s="286"/>
     </row>
     <row r="14" spans="1:13" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="285"/>
-      <c r="B14" s="494" t="s">
+      <c r="B14" s="498" t="s">
         <v>373</v>
       </c>
-      <c r="C14" s="376"/>
-      <c r="D14" s="494" t="s">
+      <c r="C14" s="405"/>
+      <c r="D14" s="498" t="s">
         <v>369</v>
       </c>
-      <c r="E14" s="495"/>
-      <c r="F14" s="376"/>
-      <c r="G14" s="494" t="s">
+      <c r="E14" s="499"/>
+      <c r="F14" s="405"/>
+      <c r="G14" s="498" t="s">
         <v>369</v>
       </c>
-      <c r="H14" s="495"/>
-      <c r="I14" s="376"/>
-      <c r="J14" s="494" t="s">
+      <c r="H14" s="499"/>
+      <c r="I14" s="405"/>
+      <c r="J14" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K14" s="376"/>
+      <c r="K14" s="405"/>
       <c r="L14" s="280"/>
       <c r="M14" s="286"/>
     </row>
     <row r="15" spans="1:13" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="285"/>
-      <c r="B15" s="494" t="s">
+      <c r="B15" s="498" t="s">
         <v>374</v>
       </c>
-      <c r="C15" s="376"/>
-      <c r="D15" s="494" t="s">
+      <c r="C15" s="405"/>
+      <c r="D15" s="498" t="s">
         <v>369</v>
       </c>
-      <c r="E15" s="495"/>
-      <c r="F15" s="376"/>
-      <c r="G15" s="494" t="s">
+      <c r="E15" s="499"/>
+      <c r="F15" s="405"/>
+      <c r="G15" s="498" t="s">
         <v>369</v>
       </c>
-      <c r="H15" s="495"/>
-      <c r="I15" s="376"/>
-      <c r="J15" s="494" t="s">
+      <c r="H15" s="499"/>
+      <c r="I15" s="405"/>
+      <c r="J15" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K15" s="376"/>
+      <c r="K15" s="405"/>
       <c r="L15" s="280"/>
       <c r="M15" s="286"/>
     </row>
     <row r="16" spans="1:13" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="285"/>
-      <c r="B16" s="494" t="s">
+      <c r="B16" s="498" t="s">
         <v>375</v>
       </c>
-      <c r="C16" s="376"/>
-      <c r="D16" s="494" t="s">
+      <c r="C16" s="405"/>
+      <c r="D16" s="498" t="s">
         <v>369</v>
       </c>
-      <c r="E16" s="495"/>
-      <c r="F16" s="376"/>
-      <c r="G16" s="494" t="s">
+      <c r="E16" s="499"/>
+      <c r="F16" s="405"/>
+      <c r="G16" s="498" t="s">
         <v>370</v>
       </c>
-      <c r="H16" s="495"/>
-      <c r="I16" s="376"/>
-      <c r="J16" s="494" t="s">
+      <c r="H16" s="499"/>
+      <c r="I16" s="405"/>
+      <c r="J16" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K16" s="376"/>
+      <c r="K16" s="405"/>
       <c r="L16" s="280"/>
       <c r="M16" s="286"/>
     </row>
     <row r="17" spans="1:13" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="285"/>
-      <c r="B17" s="494" t="s">
+      <c r="B17" s="498" t="s">
         <v>376</v>
       </c>
-      <c r="C17" s="376"/>
-      <c r="D17" s="494" t="s">
+      <c r="C17" s="405"/>
+      <c r="D17" s="498" t="s">
         <v>369</v>
       </c>
-      <c r="E17" s="495"/>
-      <c r="F17" s="376"/>
-      <c r="G17" s="494" t="s">
+      <c r="E17" s="499"/>
+      <c r="F17" s="405"/>
+      <c r="G17" s="498" t="s">
         <v>369</v>
       </c>
-      <c r="H17" s="495"/>
-      <c r="I17" s="376"/>
-      <c r="J17" s="494" t="s">
+      <c r="H17" s="499"/>
+      <c r="I17" s="405"/>
+      <c r="J17" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K17" s="376"/>
+      <c r="K17" s="405"/>
       <c r="L17" s="280"/>
       <c r="M17" s="286"/>
     </row>
     <row r="18" spans="1:13" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="285"/>
-      <c r="B18" s="494" t="s">
+      <c r="B18" s="498" t="s">
         <v>377</v>
       </c>
-      <c r="C18" s="376"/>
-      <c r="D18" s="494" t="s">
+      <c r="C18" s="405"/>
+      <c r="D18" s="498" t="s">
         <v>378</v>
       </c>
-      <c r="E18" s="495"/>
-      <c r="F18" s="376"/>
-      <c r="G18" s="494" t="s">
+      <c r="E18" s="499"/>
+      <c r="F18" s="405"/>
+      <c r="G18" s="498" t="s">
         <v>369</v>
       </c>
-      <c r="H18" s="495"/>
-      <c r="I18" s="376"/>
-      <c r="J18" s="494" t="s">
+      <c r="H18" s="499"/>
+      <c r="I18" s="405"/>
+      <c r="J18" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K18" s="376"/>
+      <c r="K18" s="405"/>
       <c r="L18" s="280"/>
       <c r="M18" s="286"/>
     </row>
@@ -6096,95 +6096,98 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="285"/>
-      <c r="B29" s="497"/>
-      <c r="C29" s="367"/>
-      <c r="D29" s="367"/>
-      <c r="E29" s="367"/>
-      <c r="F29" s="367"/>
-      <c r="G29" s="367"/>
-      <c r="H29" s="367"/>
-      <c r="I29" s="367"/>
-      <c r="J29" s="367"/>
-      <c r="K29" s="367"/>
-      <c r="L29" s="368"/>
+      <c r="B29" s="501"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
+      <c r="G29" s="337"/>
+      <c r="H29" s="337"/>
+      <c r="I29" s="337"/>
+      <c r="J29" s="337"/>
+      <c r="K29" s="337"/>
+      <c r="L29" s="338"/>
       <c r="M29" s="286"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="285"/>
-      <c r="B30" s="418"/>
-      <c r="C30" s="495"/>
-      <c r="D30" s="495"/>
-      <c r="E30" s="495"/>
-      <c r="F30" s="495"/>
-      <c r="G30" s="495"/>
-      <c r="H30" s="495"/>
-      <c r="I30" s="495"/>
-      <c r="J30" s="495"/>
-      <c r="K30" s="495"/>
-      <c r="L30" s="376"/>
+      <c r="B30" s="429"/>
+      <c r="C30" s="499"/>
+      <c r="D30" s="499"/>
+      <c r="E30" s="499"/>
+      <c r="F30" s="499"/>
+      <c r="G30" s="499"/>
+      <c r="H30" s="499"/>
+      <c r="I30" s="499"/>
+      <c r="J30" s="499"/>
+      <c r="K30" s="499"/>
+      <c r="L30" s="405"/>
       <c r="M30" s="286"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="285"/>
-      <c r="B31" s="418"/>
-      <c r="C31" s="495"/>
-      <c r="D31" s="495"/>
-      <c r="E31" s="495"/>
-      <c r="F31" s="495"/>
-      <c r="G31" s="495"/>
-      <c r="H31" s="495"/>
-      <c r="I31" s="495"/>
-      <c r="J31" s="495"/>
-      <c r="K31" s="495"/>
-      <c r="L31" s="376"/>
+      <c r="B31" s="429"/>
+      <c r="C31" s="499"/>
+      <c r="D31" s="499"/>
+      <c r="E31" s="499"/>
+      <c r="F31" s="499"/>
+      <c r="G31" s="499"/>
+      <c r="H31" s="499"/>
+      <c r="I31" s="499"/>
+      <c r="J31" s="499"/>
+      <c r="K31" s="499"/>
+      <c r="L31" s="405"/>
       <c r="M31" s="286"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="285"/>
-      <c r="B32" s="369"/>
-      <c r="C32" s="359"/>
-      <c r="D32" s="359"/>
-      <c r="E32" s="359"/>
-      <c r="F32" s="359"/>
-      <c r="G32" s="359"/>
-      <c r="H32" s="359"/>
-      <c r="I32" s="359"/>
-      <c r="J32" s="359"/>
-      <c r="K32" s="359"/>
-      <c r="L32" s="370"/>
+      <c r="B32" s="351"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
+      <c r="G32" s="339"/>
+      <c r="H32" s="339"/>
+      <c r="I32" s="339"/>
+      <c r="J32" s="339"/>
+      <c r="K32" s="339"/>
+      <c r="L32" s="340"/>
       <c r="M32" s="286"/>
     </row>
     <row r="33" spans="1:13" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="287"/>
-      <c r="B33" s="485"/>
-      <c r="C33" s="373"/>
-      <c r="D33" s="373"/>
-      <c r="E33" s="373"/>
-      <c r="F33" s="373"/>
-      <c r="G33" s="373"/>
-      <c r="H33" s="373"/>
-      <c r="I33" s="373"/>
-      <c r="J33" s="373"/>
-      <c r="K33" s="373"/>
-      <c r="L33" s="373"/>
+      <c r="B33" s="496"/>
+      <c r="C33" s="413"/>
+      <c r="D33" s="413"/>
+      <c r="E33" s="413"/>
+      <c r="F33" s="413"/>
+      <c r="G33" s="413"/>
+      <c r="H33" s="413"/>
+      <c r="I33" s="413"/>
+      <c r="J33" s="413"/>
+      <c r="K33" s="413"/>
+      <c r="L33" s="413"/>
       <c r="M33" s="288"/>
     </row>
     <row r="34" spans="1:13" ht="13.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="B33:L33"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B29:L32"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="D18:F18"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="G16:I16"/>
@@ -6201,22 +6204,19 @@
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B33:L33"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B29:L32"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="G13:I13"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -6245,32 +6245,32 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="364"/>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
-      <c r="I1" s="365"/>
-      <c r="J1" s="365"/>
-      <c r="K1" s="365"/>
-      <c r="L1" s="365"/>
+      <c r="B1" s="408"/>
+      <c r="C1" s="409"/>
+      <c r="D1" s="409"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="409"/>
+      <c r="J1" s="409"/>
+      <c r="K1" s="409"/>
+      <c r="L1" s="409"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="366" t="s">
+      <c r="B2" s="410" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
-      <c r="H2" s="367"/>
-      <c r="I2" s="367"/>
-      <c r="J2" s="368"/>
+      <c r="C2" s="337"/>
+      <c r="D2" s="337"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="338"/>
       <c r="K2" s="152" t="s">
         <v>58</v>
       </c>
@@ -6281,17 +6281,17 @@
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="369"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="370"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="351"/>
+      <c r="B3" s="351"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="339"/>
+      <c r="I3" s="339"/>
+      <c r="J3" s="340"/>
+      <c r="K3" s="422"/>
+      <c r="L3" s="343"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6299,18 +6299,18 @@
       <c r="B4" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="362" t="s">
+      <c r="C4" s="395" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
-      <c r="L4" s="351"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="342"/>
+      <c r="J4" s="342"/>
+      <c r="K4" s="342"/>
+      <c r="L4" s="343"/>
       <c r="M4" s="202"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6319,19 +6319,19 @@
       <c r="C5" s="140" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="357" t="s">
+      <c r="D5" s="399" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="353"/>
-      <c r="F5" s="352" t="s">
+      <c r="E5" s="391"/>
+      <c r="F5" s="418" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="353"/>
-      <c r="H5" s="353"/>
-      <c r="I5" s="353"/>
-      <c r="J5" s="353"/>
-      <c r="K5" s="353"/>
-      <c r="L5" s="354"/>
+      <c r="G5" s="391"/>
+      <c r="H5" s="391"/>
+      <c r="I5" s="391"/>
+      <c r="J5" s="391"/>
+      <c r="K5" s="391"/>
+      <c r="L5" s="392"/>
       <c r="M5" s="202"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6340,19 +6340,19 @@
       <c r="C6" s="141" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="355" t="s">
+      <c r="D6" s="388" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="371" t="s">
+      <c r="E6" s="381"/>
+      <c r="F6" s="411" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="356"/>
-      <c r="H6" s="356"/>
-      <c r="I6" s="356"/>
-      <c r="J6" s="356"/>
-      <c r="K6" s="356"/>
-      <c r="L6" s="361"/>
+      <c r="G6" s="381"/>
+      <c r="H6" s="381"/>
+      <c r="I6" s="381"/>
+      <c r="J6" s="381"/>
+      <c r="K6" s="381"/>
+      <c r="L6" s="382"/>
       <c r="M6" s="202"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6361,17 +6361,17 @@
       <c r="C7" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="378" t="s">
+      <c r="D7" s="416" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="379"/>
-      <c r="F7" s="400"/>
-      <c r="G7" s="379"/>
-      <c r="H7" s="379"/>
-      <c r="I7" s="379"/>
-      <c r="J7" s="379"/>
-      <c r="K7" s="379"/>
-      <c r="L7" s="401"/>
+      <c r="E7" s="384"/>
+      <c r="F7" s="383"/>
+      <c r="G7" s="384"/>
+      <c r="H7" s="384"/>
+      <c r="I7" s="384"/>
+      <c r="J7" s="384"/>
+      <c r="K7" s="384"/>
+      <c r="L7" s="385"/>
       <c r="M7" s="202"/>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6380,13 +6380,13 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="359"/>
-      <c r="G8" s="359"/>
-      <c r="H8" s="359"/>
-      <c r="I8" s="359"/>
-      <c r="J8" s="359"/>
-      <c r="K8" s="359"/>
-      <c r="L8" s="370"/>
+      <c r="F8" s="339"/>
+      <c r="G8" s="339"/>
+      <c r="H8" s="339"/>
+      <c r="I8" s="339"/>
+      <c r="J8" s="339"/>
+      <c r="K8" s="339"/>
+      <c r="L8" s="340"/>
       <c r="M8" s="202"/>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6394,18 +6394,18 @@
       <c r="B9" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="362" t="s">
+      <c r="C9" s="395" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="363"/>
-      <c r="E9" s="363"/>
-      <c r="F9" s="363"/>
-      <c r="G9" s="363"/>
-      <c r="H9" s="363"/>
-      <c r="I9" s="363"/>
-      <c r="J9" s="363"/>
-      <c r="K9" s="363"/>
-      <c r="L9" s="351"/>
+      <c r="D9" s="342"/>
+      <c r="E9" s="342"/>
+      <c r="F9" s="342"/>
+      <c r="G9" s="342"/>
+      <c r="H9" s="342"/>
+      <c r="I9" s="342"/>
+      <c r="J9" s="342"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="343"/>
       <c r="M9" s="202"/>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6414,20 +6414,20 @@
       <c r="C10" s="140" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="357" t="s">
+      <c r="D10" s="399" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="G10" s="393" t="str">
+      <c r="E10" s="391"/>
+      <c r="F10" s="391"/>
+      <c r="G10" s="390" t="str">
         <f>CAPA!A14</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="H10" s="353"/>
-      <c r="I10" s="353"/>
-      <c r="J10" s="353"/>
-      <c r="K10" s="353"/>
-      <c r="L10" s="354"/>
+      <c r="H10" s="391"/>
+      <c r="I10" s="391"/>
+      <c r="J10" s="391"/>
+      <c r="K10" s="391"/>
+      <c r="L10" s="392"/>
       <c r="M10" s="202"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6436,20 +6436,20 @@
       <c r="C11" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="355" t="s">
+      <c r="D11" s="388" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
-      <c r="G11" s="360" t="str">
+      <c r="E11" s="381"/>
+      <c r="F11" s="381"/>
+      <c r="G11" s="401" t="str">
         <f>CAPA!A15</f>
         <v>{CREA}</v>
       </c>
-      <c r="H11" s="356"/>
-      <c r="I11" s="356"/>
-      <c r="J11" s="356"/>
-      <c r="K11" s="356"/>
-      <c r="L11" s="361"/>
+      <c r="H11" s="381"/>
+      <c r="I11" s="381"/>
+      <c r="J11" s="381"/>
+      <c r="K11" s="381"/>
+      <c r="L11" s="382"/>
       <c r="M11" s="202"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6458,30 +6458,30 @@
       <c r="C12" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="355" t="s">
+      <c r="D12" s="388" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
-      <c r="G12" s="360"/>
-      <c r="H12" s="356"/>
-      <c r="I12" s="356"/>
-      <c r="J12" s="356"/>
-      <c r="K12" s="356"/>
-      <c r="L12" s="361"/>
+      <c r="E12" s="381"/>
+      <c r="F12" s="381"/>
+      <c r="G12" s="401"/>
+      <c r="H12" s="381"/>
+      <c r="I12" s="381"/>
+      <c r="J12" s="381"/>
+      <c r="K12" s="381"/>
+      <c r="L12" s="382"/>
       <c r="M12" s="202"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="200"/>
-      <c r="B13" s="385"/>
-      <c r="C13" s="358" t="s">
+      <c r="B13" s="402"/>
+      <c r="C13" s="415" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="358" t="s">
+      <c r="D13" s="415" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="379"/>
-      <c r="F13" s="379"/>
+      <c r="E13" s="384"/>
+      <c r="F13" s="384"/>
       <c r="G13" s="187"/>
       <c r="H13" s="187"/>
       <c r="I13" s="187"/>
@@ -6492,11 +6492,11 @@
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="200"/>
-      <c r="B14" s="369"/>
-      <c r="C14" s="359"/>
-      <c r="D14" s="359"/>
-      <c r="E14" s="359"/>
-      <c r="F14" s="359"/>
+      <c r="B14" s="351"/>
+      <c r="C14" s="339"/>
+      <c r="D14" s="339"/>
+      <c r="E14" s="339"/>
+      <c r="F14" s="339"/>
       <c r="G14" s="188"/>
       <c r="H14" s="188"/>
       <c r="I14" s="188"/>
@@ -6510,18 +6510,18 @@
       <c r="B15" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="362" t="s">
+      <c r="C15" s="395" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="363"/>
-      <c r="E15" s="363"/>
-      <c r="F15" s="363"/>
-      <c r="G15" s="363"/>
-      <c r="H15" s="363"/>
-      <c r="I15" s="363"/>
-      <c r="J15" s="363"/>
-      <c r="K15" s="363"/>
-      <c r="L15" s="351"/>
+      <c r="D15" s="342"/>
+      <c r="E15" s="342"/>
+      <c r="F15" s="342"/>
+      <c r="G15" s="342"/>
+      <c r="H15" s="342"/>
+      <c r="I15" s="342"/>
+      <c r="J15" s="342"/>
+      <c r="K15" s="342"/>
+      <c r="L15" s="343"/>
       <c r="M15" s="202"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6530,19 +6530,19 @@
       <c r="C16" s="140" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="357" t="s">
+      <c r="D16" s="399" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="353"/>
-      <c r="F16" s="353"/>
-      <c r="G16" s="380" t="s">
+      <c r="E16" s="391"/>
+      <c r="F16" s="391"/>
+      <c r="G16" s="417" t="s">
         <v>80</v>
       </c>
-      <c r="H16" s="367"/>
-      <c r="I16" s="367"/>
-      <c r="J16" s="367"/>
-      <c r="K16" s="367"/>
-      <c r="L16" s="368"/>
+      <c r="H16" s="337"/>
+      <c r="I16" s="337"/>
+      <c r="J16" s="337"/>
+      <c r="K16" s="337"/>
+      <c r="L16" s="338"/>
       <c r="M16" s="202"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6551,20 +6551,20 @@
       <c r="C17" s="141" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="355" t="s">
+      <c r="D17" s="388" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="356"/>
-      <c r="F17" s="356"/>
-      <c r="G17" s="387" t="str">
+      <c r="E17" s="381"/>
+      <c r="F17" s="381"/>
+      <c r="G17" s="404" t="str">
         <f>CAPA!C3</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="H17" s="375"/>
-      <c r="I17" s="375"/>
-      <c r="J17" s="375"/>
-      <c r="K17" s="375"/>
-      <c r="L17" s="376"/>
+      <c r="H17" s="348"/>
+      <c r="I17" s="348"/>
+      <c r="J17" s="348"/>
+      <c r="K17" s="348"/>
+      <c r="L17" s="405"/>
       <c r="M17" s="202"/>
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6574,12 +6574,12 @@
       <c r="D18" s="310"/>
       <c r="E18" s="310"/>
       <c r="F18" s="310"/>
-      <c r="G18" s="388"/>
-      <c r="H18" s="388"/>
-      <c r="I18" s="388"/>
-      <c r="J18" s="388"/>
-      <c r="K18" s="388"/>
-      <c r="L18" s="389"/>
+      <c r="G18" s="387"/>
+      <c r="H18" s="387"/>
+      <c r="I18" s="387"/>
+      <c r="J18" s="387"/>
+      <c r="K18" s="387"/>
+      <c r="L18" s="406"/>
       <c r="M18" s="202"/>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6588,18 +6588,18 @@
       <c r="C19" s="141" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="355" t="s">
+      <c r="D19" s="388" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="356"/>
-      <c r="F19" s="356"/>
-      <c r="G19" s="386" t="s">
+      <c r="E19" s="381"/>
+      <c r="F19" s="381"/>
+      <c r="G19" s="403" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="377"/>
-      <c r="I19" s="377"/>
-      <c r="J19" s="377"/>
-      <c r="K19" s="377"/>
+      <c r="H19" s="397"/>
+      <c r="I19" s="397"/>
+      <c r="J19" s="397"/>
+      <c r="K19" s="397"/>
       <c r="L19" s="207" t="s">
         <v>86</v>
       </c>
@@ -6607,15 +6607,15 @@
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="382"/>
-      <c r="C20" s="355" t="s">
+      <c r="B20" s="420"/>
+      <c r="C20" s="388" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="402" t="s">
+      <c r="D20" s="386" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="379"/>
-      <c r="F20" s="379"/>
+      <c r="E20" s="384"/>
+      <c r="F20" s="384"/>
       <c r="G20" s="72" t="s">
         <v>89</v>
       </c>
@@ -6634,11 +6634,11 @@
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="200"/>
-      <c r="B21" s="383"/>
-      <c r="C21" s="388"/>
-      <c r="D21" s="388"/>
-      <c r="E21" s="388"/>
-      <c r="F21" s="388"/>
+      <c r="B21" s="421"/>
+      <c r="C21" s="387"/>
+      <c r="D21" s="387"/>
+      <c r="E21" s="387"/>
+      <c r="F21" s="387"/>
       <c r="G21" s="72" t="s">
         <v>93</v>
       </c>
@@ -6659,19 +6659,19 @@
       <c r="C22" s="141" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="355" t="s">
+      <c r="D22" s="388" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="356"/>
-      <c r="F22" s="356"/>
-      <c r="G22" s="352" t="s">
+      <c r="E22" s="381"/>
+      <c r="F22" s="381"/>
+      <c r="G22" s="418" t="s">
         <v>98</v>
       </c>
-      <c r="H22" s="353"/>
-      <c r="I22" s="353"/>
-      <c r="J22" s="353"/>
-      <c r="K22" s="353"/>
-      <c r="L22" s="354"/>
+      <c r="H22" s="391"/>
+      <c r="I22" s="391"/>
+      <c r="J22" s="391"/>
+      <c r="K22" s="391"/>
+      <c r="L22" s="392"/>
       <c r="M22" s="202"/>
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6680,19 +6680,19 @@
       <c r="C23" s="141" t="s">
         <v>99</v>
       </c>
-      <c r="D23" s="355" t="s">
+      <c r="D23" s="388" t="s">
         <v>100</v>
       </c>
-      <c r="E23" s="356"/>
-      <c r="F23" s="356"/>
-      <c r="G23" s="360" t="s">
+      <c r="E23" s="381"/>
+      <c r="F23" s="381"/>
+      <c r="G23" s="401" t="s">
         <v>101</v>
       </c>
-      <c r="H23" s="356"/>
-      <c r="I23" s="356"/>
-      <c r="J23" s="356"/>
-      <c r="K23" s="356"/>
-      <c r="L23" s="361"/>
+      <c r="H23" s="381"/>
+      <c r="I23" s="381"/>
+      <c r="J23" s="381"/>
+      <c r="K23" s="381"/>
+      <c r="L23" s="382"/>
       <c r="M23" s="202"/>
     </row>
     <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6701,19 +6701,19 @@
       <c r="C24" s="141" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="355" t="s">
+      <c r="D24" s="388" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="356"/>
-      <c r="F24" s="356"/>
-      <c r="G24" s="360" t="s">
+      <c r="E24" s="381"/>
+      <c r="F24" s="381"/>
+      <c r="G24" s="401" t="s">
         <v>104</v>
       </c>
-      <c r="H24" s="356"/>
-      <c r="I24" s="356"/>
-      <c r="J24" s="356"/>
-      <c r="K24" s="356"/>
-      <c r="L24" s="361"/>
+      <c r="H24" s="381"/>
+      <c r="I24" s="381"/>
+      <c r="J24" s="381"/>
+      <c r="K24" s="381"/>
+      <c r="L24" s="382"/>
       <c r="M24" s="202"/>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6722,17 +6722,17 @@
       <c r="C25" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="D25" s="390" t="s">
+      <c r="D25" s="407" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="356"/>
-      <c r="F25" s="356"/>
-      <c r="G25" s="356"/>
-      <c r="H25" s="356"/>
-      <c r="I25" s="356"/>
-      <c r="J25" s="356"/>
-      <c r="K25" s="356"/>
-      <c r="L25" s="361"/>
+      <c r="E25" s="381"/>
+      <c r="F25" s="381"/>
+      <c r="G25" s="381"/>
+      <c r="H25" s="381"/>
+      <c r="I25" s="381"/>
+      <c r="J25" s="381"/>
+      <c r="K25" s="381"/>
+      <c r="L25" s="382"/>
       <c r="M25" s="202"/>
     </row>
     <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6742,18 +6742,18 @@
       <c r="D26" s="141" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="355" t="s">
+      <c r="E26" s="388" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="356"/>
-      <c r="G26" s="356"/>
-      <c r="H26" s="356"/>
-      <c r="I26" s="360" t="s">
+      <c r="F26" s="381"/>
+      <c r="G26" s="381"/>
+      <c r="H26" s="381"/>
+      <c r="I26" s="401" t="s">
         <v>109</v>
       </c>
-      <c r="J26" s="356"/>
-      <c r="K26" s="356"/>
-      <c r="L26" s="361"/>
+      <c r="J26" s="381"/>
+      <c r="K26" s="381"/>
+      <c r="L26" s="382"/>
       <c r="M26" s="202"/>
     </row>
     <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6763,16 +6763,16 @@
       <c r="D27" s="141" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="355" t="s">
+      <c r="E27" s="388" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="356"/>
-      <c r="G27" s="356"/>
-      <c r="H27" s="356"/>
-      <c r="I27" s="391"/>
-      <c r="J27" s="356"/>
-      <c r="K27" s="356"/>
-      <c r="L27" s="361"/>
+      <c r="F27" s="381"/>
+      <c r="G27" s="381"/>
+      <c r="H27" s="381"/>
+      <c r="I27" s="380"/>
+      <c r="J27" s="381"/>
+      <c r="K27" s="381"/>
+      <c r="L27" s="382"/>
       <c r="M27" s="202"/>
     </row>
     <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6782,12 +6782,12 @@
       <c r="D28" s="141" t="s">
         <v>112</v>
       </c>
-      <c r="E28" s="355" t="s">
+      <c r="E28" s="388" t="s">
         <v>113</v>
       </c>
-      <c r="F28" s="356"/>
-      <c r="G28" s="356"/>
-      <c r="H28" s="356"/>
+      <c r="F28" s="381"/>
+      <c r="G28" s="381"/>
+      <c r="H28" s="381"/>
       <c r="I28" s="186"/>
       <c r="J28" s="141"/>
       <c r="K28" s="141"/>
@@ -6800,17 +6800,17 @@
       <c r="C29" s="141" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="355" t="s">
+      <c r="D29" s="388" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="356"/>
-      <c r="F29" s="356"/>
-      <c r="G29" s="356"/>
-      <c r="H29" s="394">
+      <c r="E29" s="381"/>
+      <c r="F29" s="381"/>
+      <c r="G29" s="381"/>
+      <c r="H29" s="393">
         <f>CAPA!D4</f>
         <v>0</v>
       </c>
-      <c r="I29" s="356"/>
+      <c r="I29" s="381"/>
       <c r="J29" s="308" t="s">
         <v>40</v>
       </c>
@@ -6824,17 +6824,17 @@
       <c r="C30" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="355" t="s">
+      <c r="D30" s="388" t="s">
         <v>117</v>
       </c>
-      <c r="E30" s="356"/>
-      <c r="F30" s="356"/>
-      <c r="G30" s="356"/>
-      <c r="H30" s="391"/>
-      <c r="I30" s="356"/>
-      <c r="J30" s="356"/>
-      <c r="K30" s="356"/>
-      <c r="L30" s="361"/>
+      <c r="E30" s="381"/>
+      <c r="F30" s="381"/>
+      <c r="G30" s="381"/>
+      <c r="H30" s="380"/>
+      <c r="I30" s="381"/>
+      <c r="J30" s="381"/>
+      <c r="K30" s="381"/>
+      <c r="L30" s="382"/>
       <c r="M30" s="202"/>
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6843,16 +6843,16 @@
       <c r="C31" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="358" t="s">
+      <c r="D31" s="415" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="377"/>
-      <c r="F31" s="377"/>
-      <c r="G31" s="377"/>
-      <c r="H31" s="397"/>
-      <c r="I31" s="377"/>
-      <c r="J31" s="377"/>
-      <c r="K31" s="377"/>
+      <c r="E31" s="397"/>
+      <c r="F31" s="397"/>
+      <c r="G31" s="397"/>
+      <c r="H31" s="396"/>
+      <c r="I31" s="397"/>
+      <c r="J31" s="397"/>
+      <c r="K31" s="397"/>
       <c r="L31" s="398"/>
       <c r="M31" s="202"/>
     </row>
@@ -6861,73 +6861,73 @@
       <c r="B32" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="C32" s="362" t="s">
+      <c r="C32" s="395" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="363"/>
-      <c r="E32" s="363"/>
-      <c r="F32" s="363"/>
-      <c r="G32" s="363"/>
-      <c r="H32" s="363"/>
-      <c r="I32" s="363"/>
-      <c r="J32" s="363"/>
-      <c r="K32" s="363"/>
-      <c r="L32" s="351"/>
+      <c r="D32" s="342"/>
+      <c r="E32" s="342"/>
+      <c r="F32" s="342"/>
+      <c r="G32" s="342"/>
+      <c r="H32" s="342"/>
+      <c r="I32" s="342"/>
+      <c r="J32" s="342"/>
+      <c r="K32" s="342"/>
+      <c r="L32" s="343"/>
       <c r="M32" s="202"/>
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
-      <c r="B33" s="396" t="s">
+      <c r="B33" s="394" t="s">
         <v>122</v>
       </c>
-      <c r="C33" s="367"/>
-      <c r="D33" s="367"/>
-      <c r="E33" s="367"/>
+      <c r="C33" s="337"/>
+      <c r="D33" s="337"/>
+      <c r="E33" s="337"/>
       <c r="F33" s="72">
         <v>10</v>
       </c>
-      <c r="G33" s="384" t="s">
+      <c r="G33" s="400" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="367"/>
-      <c r="I33" s="367"/>
-      <c r="J33" s="367"/>
-      <c r="K33" s="367"/>
-      <c r="L33" s="368"/>
+      <c r="H33" s="337"/>
+      <c r="I33" s="337"/>
+      <c r="J33" s="337"/>
+      <c r="K33" s="337"/>
+      <c r="L33" s="338"/>
       <c r="M33" s="202"/>
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="200"/>
-      <c r="B34" s="381" t="s">
+      <c r="B34" s="419" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="375"/>
-      <c r="D34" s="375"/>
-      <c r="E34" s="375"/>
-      <c r="F34" s="375"/>
-      <c r="G34" s="375"/>
-      <c r="H34" s="375"/>
-      <c r="I34" s="375"/>
-      <c r="J34" s="375"/>
-      <c r="K34" s="375"/>
-      <c r="L34" s="376"/>
+      <c r="C34" s="348"/>
+      <c r="D34" s="348"/>
+      <c r="E34" s="348"/>
+      <c r="F34" s="348"/>
+      <c r="G34" s="348"/>
+      <c r="H34" s="348"/>
+      <c r="I34" s="348"/>
+      <c r="J34" s="348"/>
+      <c r="K34" s="348"/>
+      <c r="L34" s="405"/>
       <c r="M34" s="202"/>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="200"/>
-      <c r="B35" s="399" t="s">
+      <c r="B35" s="379" t="s">
         <v>125</v>
       </c>
-      <c r="C35" s="359"/>
-      <c r="D35" s="359"/>
-      <c r="E35" s="359"/>
-      <c r="F35" s="359"/>
-      <c r="G35" s="359"/>
-      <c r="H35" s="359"/>
-      <c r="I35" s="359"/>
-      <c r="J35" s="359"/>
-      <c r="K35" s="359"/>
-      <c r="L35" s="370"/>
+      <c r="C35" s="339"/>
+      <c r="D35" s="339"/>
+      <c r="E35" s="339"/>
+      <c r="F35" s="339"/>
+      <c r="G35" s="339"/>
+      <c r="H35" s="339"/>
+      <c r="I35" s="339"/>
+      <c r="J35" s="339"/>
+      <c r="K35" s="339"/>
+      <c r="L35" s="340"/>
       <c r="M35" s="202"/>
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6935,18 +6935,18 @@
       <c r="B36" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="C36" s="362" t="s">
+      <c r="C36" s="395" t="s">
         <v>127</v>
       </c>
-      <c r="D36" s="363"/>
-      <c r="E36" s="363"/>
-      <c r="F36" s="363"/>
-      <c r="G36" s="363"/>
-      <c r="H36" s="363"/>
-      <c r="I36" s="363"/>
-      <c r="J36" s="363"/>
-      <c r="K36" s="363"/>
-      <c r="L36" s="351"/>
+      <c r="D36" s="342"/>
+      <c r="E36" s="342"/>
+      <c r="F36" s="342"/>
+      <c r="G36" s="342"/>
+      <c r="H36" s="342"/>
+      <c r="I36" s="342"/>
+      <c r="J36" s="342"/>
+      <c r="K36" s="342"/>
+      <c r="L36" s="343"/>
       <c r="M36" s="202"/>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6990,27 +6990,27 @@
       <c r="B41" s="209" t="s">
         <v>128</v>
       </c>
-      <c r="G41" s="392" t="s">
+      <c r="G41" s="389" t="s">
         <v>54</v>
       </c>
-      <c r="H41" s="375"/>
-      <c r="I41" s="375"/>
-      <c r="J41" s="375"/>
-      <c r="K41" s="375"/>
+      <c r="H41" s="348"/>
+      <c r="I41" s="348"/>
+      <c r="J41" s="348"/>
+      <c r="K41" s="348"/>
       <c r="L41" s="4"/>
       <c r="M41" s="202"/>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="200"/>
       <c r="B42" s="12"/>
-      <c r="G42" s="395" t="str">
+      <c r="G42" s="377" t="str">
         <f>F5</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="H42" s="375"/>
-      <c r="I42" s="375"/>
-      <c r="J42" s="375"/>
-      <c r="K42" s="375"/>
+      <c r="H42" s="348"/>
+      <c r="I42" s="348"/>
+      <c r="J42" s="348"/>
+      <c r="K42" s="348"/>
       <c r="L42" s="4"/>
       <c r="M42" s="202"/>
     </row>
@@ -7043,27 +7043,27 @@
       <c r="B47" s="209" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="392" t="s">
+      <c r="G47" s="389" t="s">
         <v>54</v>
       </c>
-      <c r="H47" s="375"/>
-      <c r="I47" s="375"/>
-      <c r="J47" s="375"/>
-      <c r="K47" s="375"/>
+      <c r="H47" s="348"/>
+      <c r="I47" s="348"/>
+      <c r="J47" s="348"/>
+      <c r="K47" s="348"/>
       <c r="L47" s="4"/>
       <c r="M47" s="202"/>
     </row>
     <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="200"/>
       <c r="B48" s="12"/>
-      <c r="G48" s="395" t="str">
+      <c r="G48" s="377" t="str">
         <f>CAPA!A14</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="H48" s="375"/>
-      <c r="I48" s="375"/>
-      <c r="J48" s="375"/>
-      <c r="K48" s="375"/>
+      <c r="H48" s="348"/>
+      <c r="I48" s="348"/>
+      <c r="J48" s="348"/>
+      <c r="K48" s="348"/>
       <c r="L48" s="4"/>
       <c r="M48" s="202"/>
     </row>
@@ -7081,73 +7081,96 @@
     </row>
     <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="200"/>
-      <c r="B51" s="374" t="s">
+      <c r="B51" s="414" t="s">
         <v>130</v>
       </c>
-      <c r="C51" s="375"/>
-      <c r="D51" s="375"/>
-      <c r="E51" s="375"/>
-      <c r="F51" s="375"/>
-      <c r="G51" s="375"/>
-      <c r="H51" s="375"/>
-      <c r="I51" s="375"/>
-      <c r="J51" s="375"/>
-      <c r="K51" s="375"/>
-      <c r="L51" s="376"/>
+      <c r="C51" s="348"/>
+      <c r="D51" s="348"/>
+      <c r="E51" s="348"/>
+      <c r="F51" s="348"/>
+      <c r="G51" s="348"/>
+      <c r="H51" s="348"/>
+      <c r="I51" s="348"/>
+      <c r="J51" s="348"/>
+      <c r="K51" s="348"/>
+      <c r="L51" s="405"/>
       <c r="M51" s="202"/>
     </row>
     <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="200"/>
-      <c r="B52" s="369"/>
-      <c r="C52" s="359"/>
-      <c r="D52" s="359"/>
-      <c r="E52" s="359"/>
-      <c r="F52" s="359"/>
-      <c r="G52" s="359"/>
-      <c r="H52" s="359"/>
-      <c r="I52" s="359"/>
-      <c r="J52" s="359"/>
-      <c r="K52" s="359"/>
-      <c r="L52" s="370"/>
+      <c r="B52" s="351"/>
+      <c r="C52" s="339"/>
+      <c r="D52" s="339"/>
+      <c r="E52" s="339"/>
+      <c r="F52" s="339"/>
+      <c r="G52" s="339"/>
+      <c r="H52" s="339"/>
+      <c r="I52" s="339"/>
+      <c r="J52" s="339"/>
+      <c r="K52" s="339"/>
+      <c r="L52" s="340"/>
       <c r="M52" s="202"/>
     </row>
     <row r="53" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="203"/>
-      <c r="B53" s="372"/>
-      <c r="C53" s="373"/>
-      <c r="D53" s="373"/>
-      <c r="E53" s="373"/>
-      <c r="F53" s="373"/>
-      <c r="G53" s="373"/>
-      <c r="H53" s="373"/>
-      <c r="I53" s="373"/>
-      <c r="J53" s="373"/>
-      <c r="K53" s="373"/>
-      <c r="L53" s="373"/>
+      <c r="B53" s="412"/>
+      <c r="C53" s="413"/>
+      <c r="D53" s="413"/>
+      <c r="E53" s="413"/>
+      <c r="F53" s="413"/>
+      <c r="G53" s="413"/>
+      <c r="H53" s="413"/>
+      <c r="I53" s="413"/>
+      <c r="J53" s="413"/>
+      <c r="K53" s="413"/>
+      <c r="L53" s="413"/>
       <c r="M53" s="204"/>
     </row>
     <row r="54" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
-      <c r="B54" s="392"/>
-      <c r="C54" s="375"/>
-      <c r="D54" s="375"/>
-      <c r="E54" s="375"/>
-      <c r="F54" s="375"/>
-      <c r="G54" s="375"/>
-      <c r="H54" s="375"/>
-      <c r="I54" s="375"/>
-      <c r="J54" s="375"/>
-      <c r="K54" s="375"/>
-      <c r="L54" s="375"/>
+      <c r="B54" s="389"/>
+      <c r="C54" s="348"/>
+      <c r="D54" s="348"/>
+      <c r="E54" s="348"/>
+      <c r="F54" s="348"/>
+      <c r="G54" s="348"/>
+      <c r="H54" s="348"/>
+      <c r="I54" s="348"/>
+      <c r="J54" s="348"/>
+      <c r="K54" s="348"/>
+      <c r="L54" s="348"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="B35:L35"/>
-    <mergeCell ref="H30:L30"/>
-    <mergeCell ref="F7:L8"/>
-    <mergeCell ref="D20:F21"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B2:J3"/>
+    <mergeCell ref="F6:L6"/>
+    <mergeCell ref="B53:L53"/>
+    <mergeCell ref="B51:L52"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G16:L16"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D13:F14"/>
     <mergeCell ref="B54:L54"/>
     <mergeCell ref="G10:L10"/>
     <mergeCell ref="C20:C21"/>
@@ -7164,6 +7187,12 @@
     <mergeCell ref="G47:K47"/>
     <mergeCell ref="G41:K41"/>
     <mergeCell ref="C36:L36"/>
+    <mergeCell ref="B35:L35"/>
+    <mergeCell ref="H30:L30"/>
+    <mergeCell ref="F7:L8"/>
+    <mergeCell ref="D20:F21"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="E26:H26"/>
     <mergeCell ref="G33:L33"/>
     <mergeCell ref="G24:L24"/>
     <mergeCell ref="B13:B14"/>
@@ -7174,35 +7203,6 @@
     <mergeCell ref="D25:L25"/>
     <mergeCell ref="I27:L27"/>
     <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B2:J3"/>
-    <mergeCell ref="F6:L6"/>
-    <mergeCell ref="B53:L53"/>
-    <mergeCell ref="B51:L52"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="C9:L9"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -7226,95 +7226,95 @@
   <sheetData>
     <row r="1" spans="1:30" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="210"/>
-      <c r="B1" s="409"/>
-      <c r="C1" s="339"/>
-      <c r="D1" s="339"/>
-      <c r="E1" s="339"/>
-      <c r="F1" s="339"/>
-      <c r="G1" s="339"/>
-      <c r="H1" s="339"/>
-      <c r="I1" s="339"/>
-      <c r="J1" s="339"/>
-      <c r="K1" s="339"/>
-      <c r="L1" s="339"/>
-      <c r="M1" s="339"/>
-      <c r="N1" s="339"/>
-      <c r="O1" s="339"/>
-      <c r="P1" s="339"/>
-      <c r="Q1" s="339"/>
-      <c r="R1" s="339"/>
-      <c r="S1" s="339"/>
-      <c r="T1" s="339"/>
+      <c r="B1" s="435"/>
+      <c r="C1" s="334"/>
+      <c r="D1" s="334"/>
+      <c r="E1" s="334"/>
+      <c r="F1" s="334"/>
+      <c r="G1" s="334"/>
+      <c r="H1" s="334"/>
+      <c r="I1" s="334"/>
+      <c r="J1" s="334"/>
+      <c r="K1" s="334"/>
+      <c r="L1" s="334"/>
+      <c r="M1" s="334"/>
+      <c r="N1" s="334"/>
+      <c r="O1" s="334"/>
+      <c r="P1" s="334"/>
+      <c r="Q1" s="334"/>
+      <c r="R1" s="334"/>
+      <c r="S1" s="334"/>
+      <c r="T1" s="334"/>
       <c r="U1" s="211"/>
     </row>
     <row r="2" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="212"/>
-      <c r="B2" s="403" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="404"/>
-      <c r="D2" s="404"/>
-      <c r="E2" s="404"/>
-      <c r="F2" s="404"/>
-      <c r="G2" s="404"/>
-      <c r="H2" s="404"/>
-      <c r="I2" s="404"/>
-      <c r="J2" s="404"/>
-      <c r="K2" s="404"/>
-      <c r="L2" s="404"/>
-      <c r="M2" s="404"/>
-      <c r="N2" s="404"/>
-      <c r="O2" s="404"/>
-      <c r="P2" s="404"/>
-      <c r="Q2" s="404"/>
-      <c r="R2" s="404"/>
-      <c r="S2" s="404"/>
-      <c r="T2" s="404"/>
+      <c r="B2" s="432" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="433"/>
+      <c r="D2" s="433"/>
+      <c r="E2" s="433"/>
+      <c r="F2" s="433"/>
+      <c r="G2" s="433"/>
+      <c r="H2" s="433"/>
+      <c r="I2" s="433"/>
+      <c r="J2" s="433"/>
+      <c r="K2" s="433"/>
+      <c r="L2" s="433"/>
+      <c r="M2" s="433"/>
+      <c r="N2" s="433"/>
+      <c r="O2" s="433"/>
+      <c r="P2" s="433"/>
+      <c r="Q2" s="433"/>
+      <c r="R2" s="433"/>
+      <c r="S2" s="433"/>
+      <c r="T2" s="433"/>
       <c r="U2" s="213"/>
     </row>
     <row r="3" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="212"/>
-      <c r="B3" s="413" t="s">
+      <c r="B3" s="437" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="359"/>
-      <c r="N3" s="359"/>
-      <c r="O3" s="359"/>
-      <c r="P3" s="359"/>
-      <c r="Q3" s="359"/>
-      <c r="R3" s="359"/>
-      <c r="S3" s="359"/>
-      <c r="T3" s="359"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="339"/>
+      <c r="I3" s="339"/>
+      <c r="J3" s="339"/>
+      <c r="K3" s="339"/>
+      <c r="L3" s="339"/>
+      <c r="M3" s="339"/>
+      <c r="N3" s="339"/>
+      <c r="O3" s="339"/>
+      <c r="P3" s="339"/>
+      <c r="Q3" s="339"/>
+      <c r="R3" s="339"/>
+      <c r="S3" s="339"/>
+      <c r="T3" s="339"/>
       <c r="U3" s="213"/>
     </row>
     <row r="4" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="212"/>
-      <c r="B4" s="414" t="s">
+      <c r="B4" s="425" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
-      <c r="L4" s="363"/>
-      <c r="M4" s="363"/>
-      <c r="N4" s="363"/>
-      <c r="O4" s="351"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="342"/>
+      <c r="J4" s="342"/>
+      <c r="K4" s="342"/>
+      <c r="L4" s="342"/>
+      <c r="M4" s="342"/>
+      <c r="N4" s="342"/>
+      <c r="O4" s="343"/>
       <c r="P4" s="259" t="s">
         <v>58</v>
       </c>
@@ -7329,50 +7329,50 @@
     </row>
     <row r="5" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="212"/>
-      <c r="B5" s="419" t="s">
+      <c r="B5" s="431" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="367"/>
-      <c r="D5" s="417" t="str">
+      <c r="C5" s="337"/>
+      <c r="D5" s="428" t="str">
         <f>CAPA!C3</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="367"/>
-      <c r="F5" s="367"/>
-      <c r="G5" s="367"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="367"/>
-      <c r="K5" s="367"/>
-      <c r="L5" s="367"/>
-      <c r="M5" s="367"/>
-      <c r="N5" s="367"/>
-      <c r="O5" s="368"/>
-      <c r="P5" s="411" t="s">
+      <c r="E5" s="337"/>
+      <c r="F5" s="337"/>
+      <c r="G5" s="337"/>
+      <c r="H5" s="337"/>
+      <c r="I5" s="337"/>
+      <c r="J5" s="337"/>
+      <c r="K5" s="337"/>
+      <c r="L5" s="337"/>
+      <c r="M5" s="337"/>
+      <c r="N5" s="337"/>
+      <c r="O5" s="338"/>
+      <c r="P5" s="349" t="s">
         <v>5</v>
       </c>
-      <c r="Q5" s="367"/>
-      <c r="R5" s="367"/>
-      <c r="S5" s="367"/>
-      <c r="T5" s="368"/>
+      <c r="Q5" s="337"/>
+      <c r="R5" s="337"/>
+      <c r="S5" s="337"/>
+      <c r="T5" s="338"/>
       <c r="U5" s="213"/>
     </row>
     <row r="6" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="212"/>
-      <c r="B6" s="369"/>
-      <c r="C6" s="359"/>
-      <c r="D6" s="359"/>
-      <c r="E6" s="359"/>
-      <c r="F6" s="359"/>
-      <c r="G6" s="359"/>
-      <c r="H6" s="359"/>
-      <c r="I6" s="359"/>
-      <c r="J6" s="359"/>
-      <c r="K6" s="359"/>
-      <c r="L6" s="359"/>
-      <c r="M6" s="359"/>
-      <c r="N6" s="359"/>
-      <c r="O6" s="370"/>
+      <c r="B6" s="351"/>
+      <c r="C6" s="339"/>
+      <c r="D6" s="339"/>
+      <c r="E6" s="339"/>
+      <c r="F6" s="339"/>
+      <c r="G6" s="339"/>
+      <c r="H6" s="339"/>
+      <c r="I6" s="339"/>
+      <c r="J6" s="339"/>
+      <c r="K6" s="339"/>
+      <c r="L6" s="339"/>
+      <c r="M6" s="339"/>
+      <c r="N6" s="339"/>
+      <c r="O6" s="340"/>
       <c r="P6" s="75" t="s">
         <v>6</v>
       </c>
@@ -7386,29 +7386,29 @@
     </row>
     <row r="7" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="212"/>
-      <c r="B7" s="407" t="s">
+      <c r="B7" s="434" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
-      <c r="E7" s="363"/>
-      <c r="F7" s="363"/>
-      <c r="G7" s="363"/>
-      <c r="H7" s="363"/>
-      <c r="I7" s="363"/>
-      <c r="J7" s="363"/>
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="342"/>
+      <c r="G7" s="342"/>
+      <c r="H7" s="342"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="342"/>
       <c r="K7" s="267"/>
       <c r="L7" s="268"/>
-      <c r="M7" s="414" t="s">
+      <c r="M7" s="425" t="s">
         <v>8</v>
       </c>
-      <c r="N7" s="363"/>
-      <c r="O7" s="363"/>
-      <c r="P7" s="363"/>
-      <c r="Q7" s="363"/>
-      <c r="R7" s="363"/>
-      <c r="S7" s="363"/>
-      <c r="T7" s="351"/>
+      <c r="N7" s="342"/>
+      <c r="O7" s="342"/>
+      <c r="P7" s="342"/>
+      <c r="Q7" s="342"/>
+      <c r="R7" s="342"/>
+      <c r="S7" s="342"/>
+      <c r="T7" s="343"/>
       <c r="U7" s="213"/>
     </row>
     <row r="8" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7497,110 +7497,110 @@
     <row r="11" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="214"/>
       <c r="B11" s="159"/>
-      <c r="C11" s="412" t="s">
+      <c r="C11" s="436" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="363"/>
-      <c r="E11" s="363"/>
-      <c r="F11" s="363"/>
-      <c r="G11" s="363"/>
-      <c r="H11" s="363"/>
-      <c r="I11" s="363"/>
-      <c r="J11" s="363"/>
-      <c r="K11" s="363"/>
-      <c r="L11" s="351"/>
-      <c r="M11" s="408" t="s">
+      <c r="D11" s="342"/>
+      <c r="E11" s="342"/>
+      <c r="F11" s="342"/>
+      <c r="G11" s="342"/>
+      <c r="H11" s="342"/>
+      <c r="I11" s="342"/>
+      <c r="J11" s="342"/>
+      <c r="K11" s="342"/>
+      <c r="L11" s="343"/>
+      <c r="M11" s="430" t="s">
         <v>136</v>
       </c>
-      <c r="N11" s="363"/>
-      <c r="O11" s="363"/>
-      <c r="P11" s="363"/>
-      <c r="Q11" s="351"/>
-      <c r="R11" s="405" t="s">
+      <c r="N11" s="342"/>
+      <c r="O11" s="342"/>
+      <c r="P11" s="342"/>
+      <c r="Q11" s="343"/>
+      <c r="R11" s="424" t="s">
         <v>137</v>
       </c>
-      <c r="S11" s="368"/>
-      <c r="T11" s="416" t="s">
+      <c r="S11" s="338"/>
+      <c r="T11" s="426" t="s">
         <v>138</v>
       </c>
       <c r="U11" s="215"/>
     </row>
     <row r="12" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="214"/>
-      <c r="B12" s="405" t="s">
+      <c r="B12" s="424" t="s">
         <v>139</v>
       </c>
-      <c r="C12" s="412" t="s">
+      <c r="C12" s="436" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="363"/>
-      <c r="E12" s="363"/>
-      <c r="F12" s="363"/>
-      <c r="G12" s="351"/>
-      <c r="H12" s="408" t="s">
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
+      <c r="G12" s="343"/>
+      <c r="H12" s="430" t="s">
         <v>141</v>
       </c>
-      <c r="I12" s="363"/>
-      <c r="J12" s="363"/>
-      <c r="K12" s="363"/>
-      <c r="L12" s="351"/>
-      <c r="M12" s="408" t="s">
+      <c r="I12" s="342"/>
+      <c r="J12" s="342"/>
+      <c r="K12" s="342"/>
+      <c r="L12" s="343"/>
+      <c r="M12" s="430" t="s">
         <v>142</v>
       </c>
-      <c r="N12" s="363"/>
-      <c r="O12" s="363"/>
-      <c r="P12" s="363"/>
-      <c r="Q12" s="351"/>
-      <c r="R12" s="418"/>
-      <c r="S12" s="376"/>
-      <c r="T12" s="415"/>
+      <c r="N12" s="342"/>
+      <c r="O12" s="342"/>
+      <c r="P12" s="342"/>
+      <c r="Q12" s="343"/>
+      <c r="R12" s="429"/>
+      <c r="S12" s="405"/>
+      <c r="T12" s="427"/>
       <c r="U12" s="215"/>
     </row>
     <row r="13" spans="1:30" s="53" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="216"/>
-      <c r="B13" s="415"/>
-      <c r="C13" s="405" t="s">
+      <c r="B13" s="427"/>
+      <c r="C13" s="424" t="s">
         <v>143</v>
       </c>
-      <c r="D13" s="405" t="s">
+      <c r="D13" s="424" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="351"/>
-      <c r="F13" s="410" t="s">
+      <c r="E13" s="343"/>
+      <c r="F13" s="423" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="351"/>
-      <c r="H13" s="405" t="s">
+      <c r="G13" s="343"/>
+      <c r="H13" s="424" t="s">
         <v>143</v>
       </c>
-      <c r="I13" s="405" t="s">
+      <c r="I13" s="424" t="s">
         <v>144</v>
       </c>
-      <c r="J13" s="351"/>
-      <c r="K13" s="410" t="s">
+      <c r="J13" s="343"/>
+      <c r="K13" s="423" t="s">
         <v>145</v>
       </c>
-      <c r="L13" s="351"/>
-      <c r="M13" s="405" t="s">
+      <c r="L13" s="343"/>
+      <c r="M13" s="424" t="s">
         <v>143</v>
       </c>
-      <c r="N13" s="405" t="s">
+      <c r="N13" s="424" t="s">
         <v>144</v>
       </c>
-      <c r="O13" s="351"/>
-      <c r="P13" s="410" t="s">
+      <c r="O13" s="343"/>
+      <c r="P13" s="423" t="s">
         <v>145</v>
       </c>
-      <c r="Q13" s="351"/>
-      <c r="R13" s="369"/>
-      <c r="S13" s="370"/>
-      <c r="T13" s="415"/>
+      <c r="Q13" s="343"/>
+      <c r="R13" s="351"/>
+      <c r="S13" s="340"/>
+      <c r="T13" s="427"/>
       <c r="U13" s="217"/>
     </row>
     <row r="14" spans="1:30" s="53" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="216"/>
-      <c r="B14" s="406"/>
-      <c r="C14" s="406"/>
+      <c r="B14" s="353"/>
+      <c r="C14" s="353"/>
       <c r="D14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7613,7 +7613,7 @@
       <c r="G14" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="H14" s="406"/>
+      <c r="H14" s="353"/>
       <c r="I14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7626,7 +7626,7 @@
       <c r="L14" s="151" t="s">
         <v>151</v>
       </c>
-      <c r="M14" s="406"/>
+      <c r="M14" s="353"/>
       <c r="N14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7645,7 +7645,7 @@
       <c r="S14" s="151" t="s">
         <v>155</v>
       </c>
-      <c r="T14" s="415"/>
+      <c r="T14" s="427"/>
       <c r="U14" s="217"/>
     </row>
     <row r="15" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7704,7 +7704,7 @@
       <c r="S15" s="15">
         <v>18</v>
       </c>
-      <c r="T15" s="406"/>
+      <c r="T15" s="353"/>
       <c r="U15" s="201"/>
       <c r="V15" s="10"/>
       <c r="W15" s="10"/>
@@ -8915,16 +8915,6 @@
     <row r="42" spans="1:21" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="T11:T15"/>
-    <mergeCell ref="D5:O6"/>
-    <mergeCell ref="R11:S13"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="M11:Q11"/>
-    <mergeCell ref="B5:C6"/>
     <mergeCell ref="B2:T2"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="B7:J7"/>
@@ -8941,6 +8931,16 @@
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="T11:T15"/>
+    <mergeCell ref="D5:O6"/>
+    <mergeCell ref="R11:S13"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="B5:C6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -8981,103 +8981,103 @@
   <sheetData>
     <row r="1" spans="1:23" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="223"/>
-      <c r="B1" s="426"/>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
-      <c r="I1" s="365"/>
-      <c r="J1" s="365"/>
-      <c r="K1" s="365"/>
-      <c r="L1" s="365"/>
-      <c r="M1" s="365"/>
-      <c r="N1" s="365"/>
-      <c r="O1" s="365"/>
-      <c r="P1" s="365"/>
-      <c r="Q1" s="365"/>
-      <c r="R1" s="365"/>
-      <c r="S1" s="365"/>
-      <c r="T1" s="365"/>
-      <c r="U1" s="365"/>
-      <c r="V1" s="365"/>
+      <c r="B1" s="443"/>
+      <c r="C1" s="409"/>
+      <c r="D1" s="409"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="409"/>
+      <c r="J1" s="409"/>
+      <c r="K1" s="409"/>
+      <c r="L1" s="409"/>
+      <c r="M1" s="409"/>
+      <c r="N1" s="409"/>
+      <c r="O1" s="409"/>
+      <c r="P1" s="409"/>
+      <c r="Q1" s="409"/>
+      <c r="R1" s="409"/>
+      <c r="S1" s="409"/>
+      <c r="T1" s="409"/>
+      <c r="U1" s="409"/>
+      <c r="V1" s="409"/>
       <c r="W1" s="224"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="431" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
-      <c r="H2" s="367"/>
-      <c r="I2" s="367"/>
-      <c r="J2" s="367"/>
-      <c r="K2" s="367"/>
-      <c r="L2" s="367"/>
-      <c r="M2" s="367"/>
-      <c r="N2" s="367"/>
-      <c r="O2" s="367"/>
-      <c r="P2" s="367"/>
-      <c r="Q2" s="367"/>
-      <c r="R2" s="367"/>
-      <c r="S2" s="367"/>
-      <c r="T2" s="367"/>
-      <c r="U2" s="367"/>
-      <c r="V2" s="368"/>
+      <c r="B2" s="438" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="337"/>
+      <c r="D2" s="337"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="337"/>
+      <c r="K2" s="337"/>
+      <c r="L2" s="337"/>
+      <c r="M2" s="337"/>
+      <c r="N2" s="337"/>
+      <c r="O2" s="337"/>
+      <c r="P2" s="337"/>
+      <c r="Q2" s="337"/>
+      <c r="R2" s="337"/>
+      <c r="S2" s="337"/>
+      <c r="T2" s="337"/>
+      <c r="U2" s="337"/>
+      <c r="V2" s="338"/>
       <c r="W2" s="202"/>
     </row>
     <row r="3" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="344" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="359"/>
-      <c r="N3" s="359"/>
-      <c r="O3" s="359"/>
-      <c r="P3" s="359"/>
-      <c r="Q3" s="359"/>
-      <c r="R3" s="359"/>
-      <c r="S3" s="359"/>
-      <c r="T3" s="359"/>
-      <c r="U3" s="359"/>
-      <c r="V3" s="370"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="339"/>
+      <c r="I3" s="339"/>
+      <c r="J3" s="339"/>
+      <c r="K3" s="339"/>
+      <c r="L3" s="339"/>
+      <c r="M3" s="339"/>
+      <c r="N3" s="339"/>
+      <c r="O3" s="339"/>
+      <c r="P3" s="339"/>
+      <c r="Q3" s="339"/>
+      <c r="R3" s="339"/>
+      <c r="S3" s="339"/>
+      <c r="T3" s="339"/>
+      <c r="U3" s="339"/>
+      <c r="V3" s="340"/>
       <c r="W3" s="202"/>
     </row>
     <row r="4" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="428" t="s">
+      <c r="B4" s="345" t="s">
         <v>160</v>
       </c>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
-      <c r="L4" s="363"/>
-      <c r="M4" s="363"/>
-      <c r="N4" s="363"/>
-      <c r="O4" s="363"/>
-      <c r="P4" s="363"/>
-      <c r="Q4" s="351"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="342"/>
+      <c r="J4" s="342"/>
+      <c r="K4" s="342"/>
+      <c r="L4" s="342"/>
+      <c r="M4" s="342"/>
+      <c r="N4" s="342"/>
+      <c r="O4" s="342"/>
+      <c r="P4" s="342"/>
+      <c r="Q4" s="343"/>
       <c r="R4" s="259" t="s">
         <v>58</v>
       </c>
@@ -9092,54 +9092,54 @@
     </row>
     <row r="5" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="427" t="s">
+      <c r="B5" s="444" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="367"/>
-      <c r="D5" s="417" t="str">
+      <c r="C5" s="337"/>
+      <c r="D5" s="428" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="367"/>
-      <c r="F5" s="367"/>
-      <c r="G5" s="367"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="367"/>
-      <c r="K5" s="367"/>
-      <c r="L5" s="367"/>
-      <c r="M5" s="367"/>
-      <c r="N5" s="367"/>
-      <c r="O5" s="367"/>
-      <c r="P5" s="367"/>
-      <c r="Q5" s="368"/>
-      <c r="R5" s="425" t="s">
+      <c r="E5" s="337"/>
+      <c r="F5" s="337"/>
+      <c r="G5" s="337"/>
+      <c r="H5" s="337"/>
+      <c r="I5" s="337"/>
+      <c r="J5" s="337"/>
+      <c r="K5" s="337"/>
+      <c r="L5" s="337"/>
+      <c r="M5" s="337"/>
+      <c r="N5" s="337"/>
+      <c r="O5" s="337"/>
+      <c r="P5" s="337"/>
+      <c r="Q5" s="338"/>
+      <c r="R5" s="449" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="363"/>
-      <c r="T5" s="363"/>
-      <c r="U5" s="363"/>
-      <c r="V5" s="351"/>
+      <c r="S5" s="342"/>
+      <c r="T5" s="342"/>
+      <c r="U5" s="342"/>
+      <c r="V5" s="343"/>
       <c r="W5" s="202"/>
     </row>
     <row r="6" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="225"/>
-      <c r="B6" s="369"/>
-      <c r="C6" s="359"/>
-      <c r="D6" s="359"/>
-      <c r="E6" s="359"/>
-      <c r="F6" s="359"/>
-      <c r="G6" s="359"/>
-      <c r="H6" s="359"/>
-      <c r="I6" s="359"/>
-      <c r="J6" s="359"/>
-      <c r="K6" s="359"/>
-      <c r="L6" s="359"/>
-      <c r="M6" s="359"/>
-      <c r="N6" s="359"/>
-      <c r="O6" s="359"/>
-      <c r="P6" s="359"/>
-      <c r="Q6" s="370"/>
+      <c r="B6" s="351"/>
+      <c r="C6" s="339"/>
+      <c r="D6" s="339"/>
+      <c r="E6" s="339"/>
+      <c r="F6" s="339"/>
+      <c r="G6" s="339"/>
+      <c r="H6" s="339"/>
+      <c r="I6" s="339"/>
+      <c r="J6" s="339"/>
+      <c r="K6" s="339"/>
+      <c r="L6" s="339"/>
+      <c r="M6" s="339"/>
+      <c r="N6" s="339"/>
+      <c r="O6" s="339"/>
+      <c r="P6" s="339"/>
+      <c r="Q6" s="340"/>
       <c r="R6" s="49" t="s">
         <v>6</v>
       </c>
@@ -9154,31 +9154,31 @@
     </row>
     <row r="7" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="225"/>
-      <c r="B7" s="433" t="s">
+      <c r="B7" s="442" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
-      <c r="E7" s="363"/>
-      <c r="F7" s="363"/>
-      <c r="G7" s="363"/>
-      <c r="H7" s="363"/>
-      <c r="I7" s="363"/>
-      <c r="J7" s="363"/>
-      <c r="K7" s="363"/>
-      <c r="L7" s="363"/>
-      <c r="M7" s="351"/>
-      <c r="N7" s="433" t="s">
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="342"/>
+      <c r="G7" s="342"/>
+      <c r="H7" s="342"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="342"/>
+      <c r="K7" s="342"/>
+      <c r="L7" s="342"/>
+      <c r="M7" s="343"/>
+      <c r="N7" s="442" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="363"/>
-      <c r="P7" s="363"/>
-      <c r="Q7" s="363"/>
-      <c r="R7" s="363"/>
-      <c r="S7" s="363"/>
-      <c r="T7" s="363"/>
-      <c r="U7" s="363"/>
-      <c r="V7" s="351"/>
+      <c r="O7" s="342"/>
+      <c r="P7" s="342"/>
+      <c r="Q7" s="342"/>
+      <c r="R7" s="342"/>
+      <c r="S7" s="342"/>
+      <c r="T7" s="342"/>
+      <c r="U7" s="342"/>
+      <c r="V7" s="343"/>
       <c r="W7" s="226"/>
     </row>
     <row r="8" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9272,184 +9272,184 @@
     </row>
     <row r="11" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="296"/>
-      <c r="B11" s="421" t="s">
+      <c r="B11" s="439" t="s">
         <v>161</v>
       </c>
-      <c r="C11" s="429" t="s">
+      <c r="C11" s="445" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="363"/>
-      <c r="E11" s="363"/>
-      <c r="F11" s="363"/>
-      <c r="G11" s="363"/>
-      <c r="H11" s="363"/>
-      <c r="I11" s="363"/>
-      <c r="J11" s="363"/>
-      <c r="K11" s="363"/>
-      <c r="L11" s="363"/>
-      <c r="M11" s="351"/>
-      <c r="N11" s="423" t="s">
+      <c r="D11" s="342"/>
+      <c r="E11" s="342"/>
+      <c r="F11" s="342"/>
+      <c r="G11" s="342"/>
+      <c r="H11" s="342"/>
+      <c r="I11" s="342"/>
+      <c r="J11" s="342"/>
+      <c r="K11" s="342"/>
+      <c r="L11" s="342"/>
+      <c r="M11" s="343"/>
+      <c r="N11" s="446" t="s">
         <v>162</v>
       </c>
-      <c r="O11" s="420" t="s">
+      <c r="O11" s="440" t="s">
         <v>136</v>
       </c>
-      <c r="P11" s="363"/>
-      <c r="Q11" s="363"/>
-      <c r="R11" s="363"/>
-      <c r="S11" s="351"/>
-      <c r="T11" s="432" t="s">
+      <c r="P11" s="342"/>
+      <c r="Q11" s="342"/>
+      <c r="R11" s="342"/>
+      <c r="S11" s="343"/>
+      <c r="T11" s="441" t="s">
         <v>163</v>
       </c>
-      <c r="U11" s="368"/>
-      <c r="V11" s="430" t="s">
+      <c r="U11" s="338"/>
+      <c r="V11" s="447" t="s">
         <v>164</v>
       </c>
       <c r="W11" s="227"/>
     </row>
     <row r="12" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="296"/>
-      <c r="B12" s="415"/>
-      <c r="C12" s="429" t="s">
+      <c r="B12" s="427"/>
+      <c r="C12" s="445" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="363"/>
-      <c r="E12" s="363"/>
-      <c r="F12" s="363"/>
-      <c r="G12" s="351"/>
-      <c r="H12" s="420" t="s">
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
+      <c r="G12" s="343"/>
+      <c r="H12" s="440" t="s">
         <v>141</v>
       </c>
-      <c r="I12" s="363"/>
-      <c r="J12" s="363"/>
-      <c r="K12" s="363"/>
-      <c r="L12" s="351"/>
-      <c r="M12" s="423" t="s">
+      <c r="I12" s="342"/>
+      <c r="J12" s="342"/>
+      <c r="K12" s="342"/>
+      <c r="L12" s="343"/>
+      <c r="M12" s="446" t="s">
         <v>165</v>
       </c>
-      <c r="N12" s="415"/>
-      <c r="O12" s="420" t="s">
+      <c r="N12" s="427"/>
+      <c r="O12" s="440" t="s">
         <v>142</v>
       </c>
-      <c r="P12" s="363"/>
-      <c r="Q12" s="363"/>
-      <c r="R12" s="363"/>
-      <c r="S12" s="351"/>
-      <c r="T12" s="418"/>
-      <c r="U12" s="376"/>
-      <c r="V12" s="415"/>
+      <c r="P12" s="342"/>
+      <c r="Q12" s="342"/>
+      <c r="R12" s="342"/>
+      <c r="S12" s="343"/>
+      <c r="T12" s="429"/>
+      <c r="U12" s="405"/>
+      <c r="V12" s="427"/>
       <c r="W12" s="227"/>
     </row>
     <row r="13" spans="1:23" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="296"/>
-      <c r="B13" s="415"/>
-      <c r="C13" s="405" t="s">
+      <c r="B13" s="427"/>
+      <c r="C13" s="424" t="s">
         <v>166</v>
       </c>
-      <c r="D13" s="405" t="s">
+      <c r="D13" s="424" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="351"/>
-      <c r="F13" s="424" t="s">
+      <c r="E13" s="343"/>
+      <c r="F13" s="448" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="368"/>
-      <c r="H13" s="405" t="s">
+      <c r="G13" s="338"/>
+      <c r="H13" s="424" t="s">
         <v>166</v>
       </c>
-      <c r="I13" s="405" t="s">
+      <c r="I13" s="424" t="s">
         <v>144</v>
       </c>
-      <c r="J13" s="351"/>
-      <c r="K13" s="424" t="s">
+      <c r="J13" s="343"/>
+      <c r="K13" s="448" t="s">
         <v>145</v>
       </c>
-      <c r="L13" s="368"/>
-      <c r="M13" s="415"/>
-      <c r="N13" s="415"/>
-      <c r="O13" s="405" t="s">
+      <c r="L13" s="338"/>
+      <c r="M13" s="427"/>
+      <c r="N13" s="427"/>
+      <c r="O13" s="424" t="s">
         <v>167</v>
       </c>
-      <c r="P13" s="405" t="s">
+      <c r="P13" s="424" t="s">
         <v>144</v>
       </c>
-      <c r="Q13" s="351"/>
-      <c r="R13" s="421" t="s">
+      <c r="Q13" s="343"/>
+      <c r="R13" s="439" t="s">
         <v>145</v>
       </c>
-      <c r="S13" s="351"/>
-      <c r="T13" s="369"/>
-      <c r="U13" s="370"/>
-      <c r="V13" s="415"/>
+      <c r="S13" s="343"/>
+      <c r="T13" s="351"/>
+      <c r="U13" s="340"/>
+      <c r="V13" s="427"/>
       <c r="W13" s="227"/>
     </row>
     <row r="14" spans="1:23" s="36" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="296"/>
-      <c r="B14" s="415"/>
-      <c r="C14" s="415"/>
-      <c r="D14" s="421" t="s">
+      <c r="B14" s="427"/>
+      <c r="C14" s="427"/>
+      <c r="D14" s="439" t="s">
         <v>146</v>
       </c>
-      <c r="E14" s="405" t="s">
+      <c r="E14" s="424" t="s">
         <v>168</v>
       </c>
-      <c r="F14" s="405" t="s">
+      <c r="F14" s="424" t="s">
         <v>169</v>
       </c>
-      <c r="G14" s="405" t="s">
+      <c r="G14" s="424" t="s">
         <v>170</v>
       </c>
-      <c r="H14" s="415"/>
-      <c r="I14" s="421" t="s">
+      <c r="H14" s="427"/>
+      <c r="I14" s="439" t="s">
         <v>146</v>
       </c>
-      <c r="J14" s="405" t="s">
+      <c r="J14" s="424" t="s">
         <v>168</v>
       </c>
-      <c r="K14" s="405" t="s">
+      <c r="K14" s="424" t="s">
         <v>171</v>
       </c>
-      <c r="L14" s="405" t="s">
+      <c r="L14" s="424" t="s">
         <v>172</v>
       </c>
-      <c r="M14" s="415"/>
-      <c r="N14" s="406"/>
-      <c r="O14" s="406"/>
+      <c r="M14" s="427"/>
+      <c r="N14" s="353"/>
+      <c r="O14" s="353"/>
       <c r="P14" s="159" t="s">
         <v>173</v>
       </c>
       <c r="Q14" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="R14" s="405" t="s">
+      <c r="R14" s="424" t="s">
         <v>174</v>
       </c>
-      <c r="S14" s="405" t="s">
+      <c r="S14" s="424" t="s">
         <v>175</v>
       </c>
-      <c r="T14" s="405" t="s">
+      <c r="T14" s="424" t="s">
         <v>176</v>
       </c>
-      <c r="U14" s="405" t="s">
+      <c r="U14" s="424" t="s">
         <v>177</v>
       </c>
-      <c r="V14" s="415"/>
+      <c r="V14" s="427"/>
       <c r="W14" s="227"/>
     </row>
     <row r="15" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="296"/>
-      <c r="B15" s="406"/>
-      <c r="C15" s="406"/>
-      <c r="D15" s="406"/>
-      <c r="E15" s="406"/>
-      <c r="F15" s="406"/>
-      <c r="G15" s="406"/>
-      <c r="H15" s="406"/>
-      <c r="I15" s="406"/>
-      <c r="J15" s="406"/>
-      <c r="K15" s="406"/>
-      <c r="L15" s="406"/>
-      <c r="M15" s="406"/>
+      <c r="B15" s="353"/>
+      <c r="C15" s="353"/>
+      <c r="D15" s="353"/>
+      <c r="E15" s="353"/>
+      <c r="F15" s="353"/>
+      <c r="G15" s="353"/>
+      <c r="H15" s="353"/>
+      <c r="I15" s="353"/>
+      <c r="J15" s="353"/>
+      <c r="K15" s="353"/>
+      <c r="L15" s="353"/>
+      <c r="M15" s="353"/>
       <c r="N15" s="150" t="s">
         <v>178</v>
       </c>
@@ -9462,11 +9462,11 @@
       <c r="Q15" s="151" t="s">
         <v>181</v>
       </c>
-      <c r="R15" s="406"/>
-      <c r="S15" s="406"/>
-      <c r="T15" s="406"/>
-      <c r="U15" s="406"/>
-      <c r="V15" s="415"/>
+      <c r="R15" s="353"/>
+      <c r="S15" s="353"/>
+      <c r="T15" s="353"/>
+      <c r="U15" s="353"/>
+      <c r="V15" s="427"/>
       <c r="W15" s="227"/>
     </row>
     <row r="16" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9531,7 +9531,7 @@
       <c r="U16" s="38">
         <v>38</v>
       </c>
-      <c r="V16" s="406"/>
+      <c r="V16" s="353"/>
       <c r="W16" s="227"/>
     </row>
     <row r="17" spans="1:98" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9860,6 +9860,30 @@
     <row r="22" spans="1:98" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="B3:V3"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="N11:N14"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B1:V1"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="D5:Q6"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="M12:M15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="C11:M11"/>
+    <mergeCell ref="V11:V16"/>
+    <mergeCell ref="F13:G13"/>
     <mergeCell ref="B2:V2"/>
     <mergeCell ref="S14:S15"/>
     <mergeCell ref="T14:T15"/>
@@ -9876,30 +9900,6 @@
     <mergeCell ref="H12:L12"/>
     <mergeCell ref="R14:R15"/>
     <mergeCell ref="O13:O14"/>
-    <mergeCell ref="B1:V1"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="D5:Q6"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="M12:M15"/>
-    <mergeCell ref="U14:U15"/>
-    <mergeCell ref="C11:M11"/>
-    <mergeCell ref="V11:V16"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="B3:V3"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="N11:N14"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -9934,90 +9934,90 @@
   <sheetData>
     <row r="1" spans="1:14" ht="5.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="364"/>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
-      <c r="I1" s="365"/>
-      <c r="J1" s="365"/>
-      <c r="K1" s="365"/>
-      <c r="L1" s="365"/>
-      <c r="M1" s="365"/>
+      <c r="B1" s="408"/>
+      <c r="C1" s="409"/>
+      <c r="D1" s="409"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="409"/>
+      <c r="J1" s="409"/>
+      <c r="K1" s="409"/>
+      <c r="L1" s="409"/>
+      <c r="M1" s="409"/>
       <c r="N1" s="199"/>
     </row>
     <row r="2" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="249"/>
-      <c r="B2" s="431" t="s">
+      <c r="B2" s="438" t="s">
         <v>185</v>
       </c>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
-      <c r="H2" s="367"/>
-      <c r="I2" s="367"/>
-      <c r="J2" s="367"/>
-      <c r="K2" s="367"/>
-      <c r="L2" s="367"/>
-      <c r="M2" s="368"/>
+      <c r="C2" s="337"/>
+      <c r="D2" s="337"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="337"/>
+      <c r="K2" s="337"/>
+      <c r="L2" s="337"/>
+      <c r="M2" s="338"/>
       <c r="N2" s="201"/>
     </row>
     <row r="3" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="249"/>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="344" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="370"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="339"/>
+      <c r="I3" s="339"/>
+      <c r="J3" s="339"/>
+      <c r="K3" s="339"/>
+      <c r="L3" s="339"/>
+      <c r="M3" s="340"/>
       <c r="N3" s="201"/>
     </row>
     <row r="4" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="249"/>
-      <c r="B4" s="428" t="s">
+      <c r="B4" s="345" t="s">
         <v>186</v>
       </c>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="351"/>
-      <c r="I4" s="445" t="s">
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="343"/>
+      <c r="I4" s="459" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
-      <c r="L4" s="363"/>
-      <c r="M4" s="351"/>
+      <c r="J4" s="342"/>
+      <c r="K4" s="342"/>
+      <c r="L4" s="342"/>
+      <c r="M4" s="343"/>
       <c r="N4" s="201"/>
     </row>
     <row r="5" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="249"/>
-      <c r="B5" s="427" t="s">
+      <c r="B5" s="444" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="367"/>
-      <c r="D5" s="417" t="str">
+      <c r="C5" s="337"/>
+      <c r="D5" s="428" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="367"/>
-      <c r="F5" s="367"/>
-      <c r="G5" s="367"/>
-      <c r="H5" s="368"/>
+      <c r="E5" s="337"/>
+      <c r="F5" s="337"/>
+      <c r="G5" s="337"/>
+      <c r="H5" s="338"/>
       <c r="I5" s="136" t="s">
         <v>6</v>
       </c>
@@ -10032,17 +10032,17 @@
     </row>
     <row r="6" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="249"/>
-      <c r="B6" s="369"/>
-      <c r="C6" s="359"/>
-      <c r="D6" s="359"/>
-      <c r="E6" s="359"/>
-      <c r="F6" s="359"/>
-      <c r="G6" s="359"/>
-      <c r="H6" s="370"/>
-      <c r="I6" s="447" t="s">
+      <c r="B6" s="351"/>
+      <c r="C6" s="339"/>
+      <c r="D6" s="339"/>
+      <c r="E6" s="339"/>
+      <c r="F6" s="339"/>
+      <c r="G6" s="339"/>
+      <c r="H6" s="340"/>
+      <c r="I6" s="451" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="351"/>
+      <c r="J6" s="343"/>
       <c r="K6" s="156"/>
       <c r="L6" s="148">
         <f>('QUADRO II'!T4)+1</f>
@@ -10054,21 +10054,21 @@
     <row r="7" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="249"/>
       <c r="B7" s="259"/>
-      <c r="C7" s="448" t="s">
+      <c r="C7" s="454" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="363"/>
-      <c r="E7" s="363"/>
-      <c r="F7" s="363"/>
-      <c r="G7" s="428" t="s">
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="342"/>
+      <c r="G7" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="363"/>
-      <c r="I7" s="363"/>
-      <c r="J7" s="363"/>
-      <c r="K7" s="363"/>
-      <c r="L7" s="363"/>
-      <c r="M7" s="351"/>
+      <c r="H7" s="342"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="342"/>
+      <c r="K7" s="342"/>
+      <c r="L7" s="342"/>
+      <c r="M7" s="343"/>
       <c r="N7" s="201"/>
     </row>
     <row r="8" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10077,24 +10077,24 @@
         <v>9</v>
       </c>
       <c r="C8" s="76"/>
-      <c r="D8" s="443" t="str">
+      <c r="D8" s="457" t="str">
         <f>('QUADRO I'!$C$8)</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="E8" s="367"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="337"/>
+      <c r="F8" s="338"/>
       <c r="G8" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="444" t="str">
+      <c r="H8" s="458" t="str">
         <f>('QUADRO I'!$N$8)</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="I8" s="367"/>
-      <c r="J8" s="367"/>
-      <c r="K8" s="367"/>
-      <c r="L8" s="367"/>
-      <c r="M8" s="368"/>
+      <c r="I8" s="337"/>
+      <c r="J8" s="337"/>
+      <c r="K8" s="337"/>
+      <c r="L8" s="337"/>
+      <c r="M8" s="338"/>
       <c r="N8" s="201"/>
     </row>
     <row r="9" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10103,18 +10103,18 @@
         <v>10</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="442"/>
-      <c r="E9" s="439"/>
-      <c r="F9" s="376"/>
+      <c r="D9" s="455"/>
+      <c r="E9" s="456"/>
+      <c r="F9" s="405"/>
       <c r="G9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="446"/>
-      <c r="I9" s="439"/>
-      <c r="J9" s="439"/>
-      <c r="K9" s="439"/>
-      <c r="L9" s="439"/>
-      <c r="M9" s="376"/>
+      <c r="H9" s="460"/>
+      <c r="I9" s="456"/>
+      <c r="J9" s="456"/>
+      <c r="K9" s="456"/>
+      <c r="L9" s="456"/>
+      <c r="M9" s="405"/>
       <c r="N9" s="201"/>
     </row>
     <row r="10" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10123,12 +10123,12 @@
         <v>11</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="438" t="str">
+      <c r="D10" s="463" t="str">
         <f>('QUADRO I'!$C$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="E10" s="359"/>
-      <c r="F10" s="370"/>
+      <c r="E10" s="339"/>
+      <c r="F10" s="340"/>
       <c r="G10" s="5" t="s">
         <v>11</v>
       </c>
@@ -10136,12 +10136,12 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="I10" s="436" t="str">
+      <c r="I10" s="462" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="J10" s="359"/>
-      <c r="K10" s="359"/>
+      <c r="J10" s="339"/>
+      <c r="K10" s="339"/>
       <c r="L10" s="67" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -10151,7 +10151,7 @@
     </row>
     <row r="11" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="434" t="s">
+      <c r="B11" s="461" t="s">
         <v>188</v>
       </c>
       <c r="C11" s="163" t="s">
@@ -10171,132 +10171,132 @@
     </row>
     <row r="12" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="249"/>
-      <c r="B12" s="415"/>
-      <c r="C12" s="440" t="s">
+      <c r="B12" s="427"/>
+      <c r="C12" s="464" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="363"/>
-      <c r="E12" s="363"/>
-      <c r="F12" s="363"/>
-      <c r="G12" s="441" t="s">
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
+      <c r="G12" s="453" t="s">
         <v>191</v>
       </c>
-      <c r="H12" s="363"/>
-      <c r="I12" s="363"/>
-      <c r="J12" s="363"/>
-      <c r="K12" s="363"/>
-      <c r="L12" s="363"/>
-      <c r="M12" s="351"/>
+      <c r="H12" s="342"/>
+      <c r="I12" s="342"/>
+      <c r="J12" s="342"/>
+      <c r="K12" s="342"/>
+      <c r="L12" s="342"/>
+      <c r="M12" s="343"/>
       <c r="N12" s="201"/>
     </row>
     <row r="13" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="249"/>
-      <c r="B13" s="415"/>
-      <c r="C13" s="435" t="s">
+      <c r="B13" s="427"/>
+      <c r="C13" s="452" t="s">
         <v>192</v>
       </c>
-      <c r="D13" s="435" t="s">
+      <c r="D13" s="452" t="s">
         <v>193</v>
       </c>
-      <c r="E13" s="435" t="s">
+      <c r="E13" s="452" t="s">
         <v>194</v>
       </c>
-      <c r="F13" s="435" t="s">
+      <c r="F13" s="452" t="s">
         <v>195</v>
       </c>
-      <c r="G13" s="441" t="s">
+      <c r="G13" s="453" t="s">
         <v>196</v>
       </c>
-      <c r="H13" s="367"/>
-      <c r="I13" s="367"/>
-      <c r="J13" s="367"/>
-      <c r="K13" s="367"/>
-      <c r="L13" s="367"/>
-      <c r="M13" s="368"/>
+      <c r="H13" s="337"/>
+      <c r="I13" s="337"/>
+      <c r="J13" s="337"/>
+      <c r="K13" s="337"/>
+      <c r="L13" s="337"/>
+      <c r="M13" s="338"/>
       <c r="N13" s="201"/>
     </row>
     <row r="14" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="249"/>
-      <c r="B14" s="415"/>
-      <c r="C14" s="415"/>
-      <c r="D14" s="415"/>
-      <c r="E14" s="415"/>
-      <c r="F14" s="415"/>
-      <c r="G14" s="369"/>
-      <c r="H14" s="359"/>
-      <c r="I14" s="359"/>
-      <c r="J14" s="359"/>
-      <c r="K14" s="359"/>
-      <c r="L14" s="359"/>
-      <c r="M14" s="370"/>
+      <c r="B14" s="427"/>
+      <c r="C14" s="427"/>
+      <c r="D14" s="427"/>
+      <c r="E14" s="427"/>
+      <c r="F14" s="427"/>
+      <c r="G14" s="351"/>
+      <c r="H14" s="339"/>
+      <c r="I14" s="339"/>
+      <c r="J14" s="339"/>
+      <c r="K14" s="339"/>
+      <c r="L14" s="339"/>
+      <c r="M14" s="340"/>
       <c r="N14" s="201"/>
     </row>
     <row r="15" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="249"/>
-      <c r="B15" s="415"/>
-      <c r="C15" s="415"/>
-      <c r="D15" s="415"/>
-      <c r="E15" s="415"/>
-      <c r="F15" s="415"/>
-      <c r="G15" s="441" t="s">
+      <c r="B15" s="427"/>
+      <c r="C15" s="427"/>
+      <c r="D15" s="427"/>
+      <c r="E15" s="427"/>
+      <c r="F15" s="427"/>
+      <c r="G15" s="453" t="s">
         <v>197</v>
       </c>
-      <c r="H15" s="441" t="s">
+      <c r="H15" s="453" t="s">
         <v>198</v>
       </c>
-      <c r="I15" s="435" t="s">
+      <c r="I15" s="452" t="s">
         <v>199</v>
       </c>
-      <c r="J15" s="368"/>
-      <c r="K15" s="435" t="s">
+      <c r="J15" s="338"/>
+      <c r="K15" s="452" t="s">
         <v>200</v>
       </c>
-      <c r="L15" s="367"/>
-      <c r="M15" s="368"/>
+      <c r="L15" s="337"/>
+      <c r="M15" s="338"/>
       <c r="N15" s="201"/>
     </row>
     <row r="16" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="249"/>
-      <c r="B16" s="415"/>
-      <c r="C16" s="415"/>
-      <c r="D16" s="415"/>
-      <c r="E16" s="415"/>
-      <c r="F16" s="415"/>
-      <c r="G16" s="415"/>
-      <c r="H16" s="415"/>
-      <c r="I16" s="418"/>
-      <c r="J16" s="376"/>
-      <c r="K16" s="418"/>
-      <c r="L16" s="439"/>
-      <c r="M16" s="376"/>
+      <c r="B16" s="427"/>
+      <c r="C16" s="427"/>
+      <c r="D16" s="427"/>
+      <c r="E16" s="427"/>
+      <c r="F16" s="427"/>
+      <c r="G16" s="427"/>
+      <c r="H16" s="427"/>
+      <c r="I16" s="429"/>
+      <c r="J16" s="405"/>
+      <c r="K16" s="429"/>
+      <c r="L16" s="456"/>
+      <c r="M16" s="405"/>
       <c r="N16" s="201"/>
     </row>
     <row r="17" spans="1:14" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="249"/>
-      <c r="B17" s="415"/>
-      <c r="C17" s="406"/>
-      <c r="D17" s="406"/>
-      <c r="E17" s="406"/>
-      <c r="F17" s="406"/>
-      <c r="G17" s="406"/>
-      <c r="H17" s="406"/>
-      <c r="I17" s="369"/>
-      <c r="J17" s="370"/>
-      <c r="K17" s="369"/>
-      <c r="L17" s="359"/>
-      <c r="M17" s="370"/>
+      <c r="B17" s="427"/>
+      <c r="C17" s="353"/>
+      <c r="D17" s="353"/>
+      <c r="E17" s="353"/>
+      <c r="F17" s="353"/>
+      <c r="G17" s="353"/>
+      <c r="H17" s="353"/>
+      <c r="I17" s="351"/>
+      <c r="J17" s="340"/>
+      <c r="K17" s="351"/>
+      <c r="L17" s="339"/>
+      <c r="M17" s="340"/>
       <c r="N17" s="201"/>
     </row>
     <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="200"/>
-      <c r="B18" s="415"/>
-      <c r="C18" s="437" t="s">
+      <c r="B18" s="427"/>
+      <c r="C18" s="450" t="s">
         <v>201</v>
       </c>
-      <c r="D18" s="437" t="s">
+      <c r="D18" s="450" t="s">
         <v>202</v>
       </c>
-      <c r="E18" s="437">
+      <c r="E18" s="450">
         <v>1</v>
       </c>
       <c r="F18" s="234" t="str">
@@ -10309,68 +10309,68 @@
       <c r="H18" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="I18" s="435" t="s">
+      <c r="I18" s="452" t="s">
         <v>203</v>
       </c>
-      <c r="J18" s="351"/>
-      <c r="K18" s="435" t="s">
+      <c r="J18" s="343"/>
+      <c r="K18" s="452" t="s">
         <v>203</v>
       </c>
-      <c r="L18" s="363"/>
-      <c r="M18" s="351"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="343"/>
       <c r="N18" s="202"/>
     </row>
     <row r="19" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="200"/>
-      <c r="B19" s="415"/>
-      <c r="C19" s="415"/>
-      <c r="D19" s="415"/>
-      <c r="E19" s="415"/>
+      <c r="B19" s="427"/>
+      <c r="C19" s="427"/>
+      <c r="D19" s="427"/>
+      <c r="E19" s="427"/>
       <c r="F19" s="234"/>
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
-      <c r="I19" s="435"/>
-      <c r="J19" s="351"/>
-      <c r="K19" s="435"/>
-      <c r="L19" s="363"/>
-      <c r="M19" s="351"/>
+      <c r="I19" s="452"/>
+      <c r="J19" s="343"/>
+      <c r="K19" s="452"/>
+      <c r="L19" s="342"/>
+      <c r="M19" s="343"/>
       <c r="N19" s="202"/>
     </row>
     <row r="20" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="415"/>
-      <c r="C20" s="415"/>
-      <c r="D20" s="415"/>
-      <c r="E20" s="415"/>
+      <c r="B20" s="427"/>
+      <c r="C20" s="427"/>
+      <c r="D20" s="427"/>
+      <c r="E20" s="427"/>
       <c r="F20" s="234"/>
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
-      <c r="I20" s="435"/>
-      <c r="J20" s="351"/>
-      <c r="K20" s="435"/>
-      <c r="L20" s="363"/>
-      <c r="M20" s="351"/>
+      <c r="I20" s="452"/>
+      <c r="J20" s="343"/>
+      <c r="K20" s="452"/>
+      <c r="L20" s="342"/>
+      <c r="M20" s="343"/>
       <c r="N20" s="202"/>
     </row>
     <row r="21" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="200"/>
-      <c r="B21" s="415"/>
-      <c r="C21" s="415"/>
-      <c r="D21" s="415"/>
-      <c r="E21" s="415"/>
+      <c r="B21" s="427"/>
+      <c r="C21" s="427"/>
+      <c r="D21" s="427"/>
+      <c r="E21" s="427"/>
       <c r="F21" s="234"/>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="435"/>
-      <c r="J21" s="351"/>
-      <c r="K21" s="435"/>
-      <c r="L21" s="363"/>
-      <c r="M21" s="351"/>
+      <c r="I21" s="452"/>
+      <c r="J21" s="343"/>
+      <c r="K21" s="452"/>
+      <c r="L21" s="342"/>
+      <c r="M21" s="343"/>
       <c r="N21" s="202"/>
     </row>
     <row r="22" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="200"/>
-      <c r="B22" s="415"/>
+      <c r="B22" s="427"/>
       <c r="C22" s="56" t="s">
         <v>204</v>
       </c>
@@ -10390,7 +10390,7 @@
     </row>
     <row r="23" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="200"/>
-      <c r="B23" s="415"/>
+      <c r="B23" s="427"/>
       <c r="C23" s="56" t="s">
         <v>206</v>
       </c>
@@ -10416,7 +10416,7 @@
     </row>
     <row r="24" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="200"/>
-      <c r="B24" s="415"/>
+      <c r="B24" s="427"/>
       <c r="C24" s="45" t="s">
         <v>209</v>
       </c>
@@ -10434,7 +10434,7 @@
     </row>
     <row r="25" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="200"/>
-      <c r="B25" s="415"/>
+      <c r="B25" s="427"/>
       <c r="C25" s="239"/>
       <c r="D25" s="25" t="s">
         <v>210</v>
@@ -10460,7 +10460,7 @@
     </row>
     <row r="26" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="200"/>
-      <c r="B26" s="415"/>
+      <c r="B26" s="427"/>
       <c r="C26" s="239"/>
       <c r="D26" s="25" t="s">
         <v>213</v>
@@ -10486,7 +10486,7 @@
     </row>
     <row r="27" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="200"/>
-      <c r="B27" s="415"/>
+      <c r="B27" s="427"/>
       <c r="C27" s="239"/>
       <c r="D27" s="25" t="s">
         <v>214</v>
@@ -10511,7 +10511,7 @@
     </row>
     <row r="28" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="200"/>
-      <c r="B28" s="415"/>
+      <c r="B28" s="427"/>
       <c r="C28" s="239"/>
       <c r="D28" s="25" t="s">
         <v>215</v>
@@ -10537,7 +10537,7 @@
     </row>
     <row r="29" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="200"/>
-      <c r="B29" s="415"/>
+      <c r="B29" s="427"/>
       <c r="C29" s="239"/>
       <c r="D29" s="25" t="s">
         <v>216</v>
@@ -10563,7 +10563,7 @@
     </row>
     <row r="30" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="200"/>
-      <c r="B30" s="415"/>
+      <c r="B30" s="427"/>
       <c r="C30" s="239"/>
       <c r="D30" s="25" t="s">
         <v>217</v>
@@ -10588,7 +10588,7 @@
     </row>
     <row r="31" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="200"/>
-      <c r="B31" s="406"/>
+      <c r="B31" s="353"/>
       <c r="C31" s="30"/>
       <c r="D31" s="154" t="s">
         <v>218</v>
@@ -10606,7 +10606,7 @@
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="200"/>
-      <c r="B32" s="434" t="s">
+      <c r="B32" s="461" t="s">
         <v>219</v>
       </c>
       <c r="C32" s="56" t="s">
@@ -10631,7 +10631,7 @@
     </row>
     <row r="33" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
-      <c r="B33" s="415"/>
+      <c r="B33" s="427"/>
       <c r="C33" s="45"/>
       <c r="D33" s="27" t="s">
         <v>222</v>
@@ -10649,7 +10649,7 @@
     </row>
     <row r="34" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="200"/>
-      <c r="B34" s="415"/>
+      <c r="B34" s="427"/>
       <c r="C34" s="239"/>
       <c r="E34" s="1" t="s">
         <v>223</v>
@@ -10677,7 +10677,7 @@
     </row>
     <row r="35" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="200"/>
-      <c r="B35" s="415"/>
+      <c r="B35" s="427"/>
       <c r="C35" s="30"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2" t="s">
@@ -10709,7 +10709,7 @@
     </row>
     <row r="36" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="200"/>
-      <c r="B36" s="415"/>
+      <c r="B36" s="427"/>
       <c r="C36" s="56" t="s">
         <v>225</v>
       </c>
@@ -10727,7 +10727,7 @@
     </row>
     <row r="37" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="200"/>
-      <c r="B37" s="415"/>
+      <c r="B37" s="427"/>
       <c r="C37" s="45"/>
       <c r="D37" s="246" t="s">
         <v>226</v>
@@ -10747,7 +10747,7 @@
     </row>
     <row r="38" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="200"/>
-      <c r="B38" s="415"/>
+      <c r="B38" s="427"/>
       <c r="C38" s="239"/>
       <c r="D38" s="1" t="s">
         <v>227</v>
@@ -10763,7 +10763,7 @@
     </row>
     <row r="39" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="200"/>
-      <c r="B39" s="415"/>
+      <c r="B39" s="427"/>
       <c r="C39" s="239"/>
       <c r="D39" s="1" t="s">
         <v>228</v>
@@ -10777,7 +10777,7 @@
     </row>
     <row r="40" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="200"/>
-      <c r="B40" s="415"/>
+      <c r="B40" s="427"/>
       <c r="C40" s="239"/>
       <c r="E40" s="1" t="s">
         <v>229</v>
@@ -10793,7 +10793,7 @@
     </row>
     <row r="41" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="200"/>
-      <c r="B41" s="415"/>
+      <c r="B41" s="427"/>
       <c r="C41" s="239"/>
       <c r="E41" s="1" t="s">
         <v>230</v>
@@ -10809,7 +10809,7 @@
     </row>
     <row r="42" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="200"/>
-      <c r="B42" s="415"/>
+      <c r="B42" s="427"/>
       <c r="C42" s="239"/>
       <c r="E42" s="1" t="s">
         <v>231</v>
@@ -10825,7 +10825,7 @@
     </row>
     <row r="43" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="200"/>
-      <c r="B43" s="415"/>
+      <c r="B43" s="427"/>
       <c r="C43" s="239"/>
       <c r="E43" s="1" t="s">
         <v>232</v>
@@ -10841,7 +10841,7 @@
     </row>
     <row r="44" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="200"/>
-      <c r="B44" s="415"/>
+      <c r="B44" s="427"/>
       <c r="C44" s="239"/>
       <c r="E44" s="1" t="s">
         <v>233</v>
@@ -10857,7 +10857,7 @@
     </row>
     <row r="45" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="200"/>
-      <c r="B45" s="415"/>
+      <c r="B45" s="427"/>
       <c r="C45" s="239"/>
       <c r="E45" s="1" t="s">
         <v>234</v>
@@ -10873,7 +10873,7 @@
     </row>
     <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="200"/>
-      <c r="B46" s="415"/>
+      <c r="B46" s="427"/>
       <c r="C46" s="239"/>
       <c r="E46" s="1" t="s">
         <v>235</v>
@@ -10889,7 +10889,7 @@
     </row>
     <row r="47" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="200"/>
-      <c r="B47" s="415"/>
+      <c r="B47" s="427"/>
       <c r="C47" s="239"/>
       <c r="E47" s="1" t="s">
         <v>236</v>
@@ -10905,7 +10905,7 @@
     </row>
     <row r="48" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="200"/>
-      <c r="B48" s="415"/>
+      <c r="B48" s="427"/>
       <c r="C48" s="239"/>
       <c r="D48" s="1" t="s">
         <v>237</v>
@@ -10921,7 +10921,7 @@
     </row>
     <row r="49" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="200"/>
-      <c r="B49" s="415"/>
+      <c r="B49" s="427"/>
       <c r="C49" s="248"/>
       <c r="D49" s="1" t="s">
         <v>238</v>
@@ -10935,7 +10935,7 @@
     </row>
     <row r="50" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="200"/>
-      <c r="B50" s="415"/>
+      <c r="B50" s="427"/>
       <c r="C50" s="239"/>
       <c r="E50" s="1" t="s">
         <v>239</v>
@@ -10951,7 +10951,7 @@
     </row>
     <row r="51" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="200"/>
-      <c r="B51" s="415"/>
+      <c r="B51" s="427"/>
       <c r="C51" s="239"/>
       <c r="E51" s="1" t="s">
         <v>240</v>
@@ -10967,7 +10967,7 @@
     </row>
     <row r="52" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="200"/>
-      <c r="B52" s="415"/>
+      <c r="B52" s="427"/>
       <c r="C52" s="239"/>
       <c r="E52" s="1" t="s">
         <v>241</v>
@@ -10983,7 +10983,7 @@
     </row>
     <row r="53" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="200"/>
-      <c r="B53" s="415"/>
+      <c r="B53" s="427"/>
       <c r="C53" s="239"/>
       <c r="E53" s="1" t="s">
         <v>242</v>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="54" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="200"/>
-      <c r="B54" s="415"/>
+      <c r="B54" s="427"/>
       <c r="C54" s="239"/>
       <c r="E54" s="1" t="s">
         <v>243</v>
@@ -11015,7 +11015,7 @@
     </row>
     <row r="55" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="200"/>
-      <c r="B55" s="415"/>
+      <c r="B55" s="427"/>
       <c r="C55" s="30"/>
       <c r="D55" s="2" t="s">
         <v>244</v>
@@ -11035,7 +11035,7 @@
     </row>
     <row r="56" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="200"/>
-      <c r="B56" s="415"/>
+      <c r="B56" s="427"/>
       <c r="C56" s="56" t="s">
         <v>245</v>
       </c>
@@ -11058,7 +11058,7 @@
     </row>
     <row r="57" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="200"/>
-      <c r="B57" s="415"/>
+      <c r="B57" s="427"/>
       <c r="C57" s="45" t="s">
         <v>246</v>
       </c>
@@ -11078,7 +11078,7 @@
     </row>
     <row r="58" spans="1:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="200"/>
-      <c r="B58" s="415"/>
+      <c r="B58" s="427"/>
       <c r="C58" s="239" t="s">
         <v>247</v>
       </c>
@@ -11091,7 +11091,7 @@
     </row>
     <row r="59" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="200"/>
-      <c r="B59" s="415"/>
+      <c r="B59" s="427"/>
       <c r="C59" s="239"/>
       <c r="E59" s="1" t="s">
         <v>248</v>
@@ -11107,7 +11107,7 @@
     </row>
     <row r="60" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="200"/>
-      <c r="B60" s="415"/>
+      <c r="B60" s="427"/>
       <c r="C60" s="239"/>
       <c r="E60" s="1" t="s">
         <v>249</v>
@@ -11123,7 +11123,7 @@
     </row>
     <row r="61" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="200"/>
-      <c r="B61" s="415"/>
+      <c r="B61" s="427"/>
       <c r="C61" s="239"/>
       <c r="E61" s="1" t="s">
         <v>250</v>
@@ -11139,7 +11139,7 @@
     </row>
     <row r="62" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="200"/>
-      <c r="B62" s="415"/>
+      <c r="B62" s="427"/>
       <c r="C62" s="239"/>
       <c r="E62" s="1" t="s">
         <v>251</v>
@@ -11155,7 +11155,7 @@
     </row>
     <row r="63" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="200"/>
-      <c r="B63" s="415"/>
+      <c r="B63" s="427"/>
       <c r="C63" s="56" t="s">
         <v>252</v>
       </c>
@@ -11178,7 +11178,7 @@
     </row>
     <row r="64" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="200"/>
-      <c r="B64" s="415"/>
+      <c r="B64" s="427"/>
       <c r="C64" s="45" t="s">
         <v>253</v>
       </c>
@@ -11202,7 +11202,7 @@
     </row>
     <row r="65" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="200"/>
-      <c r="B65" s="415"/>
+      <c r="B65" s="427"/>
       <c r="C65" s="30" t="s">
         <v>254</v>
       </c>
@@ -11226,7 +11226,7 @@
     </row>
     <row r="66" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="200"/>
-      <c r="B66" s="415"/>
+      <c r="B66" s="427"/>
       <c r="C66" s="56" t="s">
         <v>255</v>
       </c>
@@ -11249,7 +11249,7 @@
     </row>
     <row r="67" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="200"/>
-      <c r="B67" s="406"/>
+      <c r="B67" s="353"/>
       <c r="C67" s="56" t="s">
         <v>256</v>
       </c>
@@ -11291,30 +11291,6 @@
     <row r="69" spans="1:16" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="D13:D17"/>
-    <mergeCell ref="I15:J17"/>
-    <mergeCell ref="G13:M14"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="F13:F17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="G12:M12"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G7:M7"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="H9:M9"/>
     <mergeCell ref="B32:B67"/>
     <mergeCell ref="B11:B31"/>
     <mergeCell ref="I18:J18"/>
@@ -11331,6 +11307,30 @@
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="K21:M21"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="F13:F17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="G12:M12"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G7:M7"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="I15:J17"/>
+    <mergeCell ref="G13:M14"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="C18:C21"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -11358,59 +11358,59 @@
   <sheetData>
     <row r="1" spans="1:56" ht="13.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="449" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="339"/>
-      <c r="D1" s="339"/>
-      <c r="E1" s="339"/>
-      <c r="F1" s="339"/>
-      <c r="G1" s="339"/>
-      <c r="H1" s="339"/>
-      <c r="I1" s="339"/>
-      <c r="J1" s="339"/>
-      <c r="K1" s="339"/>
-      <c r="L1" s="339"/>
-      <c r="M1" s="339"/>
-      <c r="N1" s="339"/>
-      <c r="O1" s="450"/>
+      <c r="B1" s="333" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="334"/>
+      <c r="D1" s="334"/>
+      <c r="E1" s="334"/>
+      <c r="F1" s="334"/>
+      <c r="G1" s="334"/>
+      <c r="H1" s="334"/>
+      <c r="I1" s="334"/>
+      <c r="J1" s="334"/>
+      <c r="K1" s="334"/>
+      <c r="L1" s="334"/>
+      <c r="M1" s="334"/>
+      <c r="N1" s="334"/>
+      <c r="O1" s="335"/>
       <c r="P1" s="199"/>
     </row>
     <row r="2" spans="1:56" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="422" t="s">
+      <c r="B2" s="344" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
-      <c r="M2" s="359"/>
-      <c r="N2" s="359"/>
-      <c r="O2" s="370"/>
+      <c r="C2" s="339"/>
+      <c r="D2" s="339"/>
+      <c r="E2" s="339"/>
+      <c r="F2" s="339"/>
+      <c r="G2" s="339"/>
+      <c r="H2" s="339"/>
+      <c r="I2" s="339"/>
+      <c r="J2" s="339"/>
+      <c r="K2" s="339"/>
+      <c r="L2" s="339"/>
+      <c r="M2" s="339"/>
+      <c r="N2" s="339"/>
+      <c r="O2" s="340"/>
       <c r="P2" s="202"/>
     </row>
     <row r="3" spans="1:56" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="453" t="s">
+      <c r="B3" s="346" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="367"/>
-      <c r="D3" s="367"/>
-      <c r="E3" s="367"/>
-      <c r="F3" s="367"/>
-      <c r="G3" s="367"/>
-      <c r="H3" s="367"/>
-      <c r="I3" s="367"/>
-      <c r="J3" s="367"/>
-      <c r="K3" s="367"/>
-      <c r="L3" s="368"/>
+      <c r="C3" s="337"/>
+      <c r="D3" s="337"/>
+      <c r="E3" s="337"/>
+      <c r="F3" s="337"/>
+      <c r="G3" s="337"/>
+      <c r="H3" s="337"/>
+      <c r="I3" s="337"/>
+      <c r="J3" s="337"/>
+      <c r="K3" s="337"/>
+      <c r="L3" s="338"/>
       <c r="M3" s="259" t="s">
         <v>3</v>
       </c>
@@ -11423,42 +11423,42 @@
     </row>
     <row r="4" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="455" t="s">
+      <c r="B4" s="350" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="367"/>
-      <c r="D4" s="451" t="str">
+      <c r="C4" s="337"/>
+      <c r="D4" s="336" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E4" s="367"/>
-      <c r="F4" s="367"/>
-      <c r="G4" s="367"/>
-      <c r="H4" s="367"/>
-      <c r="I4" s="367"/>
-      <c r="J4" s="367"/>
-      <c r="K4" s="367"/>
-      <c r="L4" s="368"/>
-      <c r="M4" s="411" t="s">
+      <c r="E4" s="337"/>
+      <c r="F4" s="337"/>
+      <c r="G4" s="337"/>
+      <c r="H4" s="337"/>
+      <c r="I4" s="337"/>
+      <c r="J4" s="337"/>
+      <c r="K4" s="337"/>
+      <c r="L4" s="338"/>
+      <c r="M4" s="349" t="s">
         <v>259</v>
       </c>
-      <c r="N4" s="367"/>
-      <c r="O4" s="368"/>
+      <c r="N4" s="337"/>
+      <c r="O4" s="338"/>
       <c r="P4" s="202"/>
     </row>
     <row r="5" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="369"/>
-      <c r="C5" s="359"/>
-      <c r="D5" s="359"/>
-      <c r="E5" s="359"/>
-      <c r="F5" s="359"/>
-      <c r="G5" s="359"/>
-      <c r="H5" s="359"/>
-      <c r="I5" s="359"/>
-      <c r="J5" s="359"/>
-      <c r="K5" s="359"/>
-      <c r="L5" s="370"/>
+      <c r="B5" s="351"/>
+      <c r="C5" s="339"/>
+      <c r="D5" s="339"/>
+      <c r="E5" s="339"/>
+      <c r="F5" s="339"/>
+      <c r="G5" s="339"/>
+      <c r="H5" s="339"/>
+      <c r="I5" s="339"/>
+      <c r="J5" s="339"/>
+      <c r="K5" s="339"/>
+      <c r="L5" s="340"/>
       <c r="M5" s="75" t="s">
         <v>6</v>
       </c>
@@ -11471,24 +11471,24 @@
     </row>
     <row r="6" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="428" t="s">
+      <c r="B6" s="345" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="363"/>
-      <c r="D6" s="363"/>
-      <c r="E6" s="363"/>
-      <c r="F6" s="363"/>
-      <c r="G6" s="351"/>
-      <c r="H6" s="428" t="s">
+      <c r="C6" s="342"/>
+      <c r="D6" s="342"/>
+      <c r="E6" s="342"/>
+      <c r="F6" s="342"/>
+      <c r="G6" s="343"/>
+      <c r="H6" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="363"/>
-      <c r="J6" s="363"/>
-      <c r="K6" s="363"/>
-      <c r="L6" s="363"/>
-      <c r="M6" s="363"/>
-      <c r="N6" s="363"/>
-      <c r="O6" s="351"/>
+      <c r="I6" s="342"/>
+      <c r="J6" s="342"/>
+      <c r="K6" s="342"/>
+      <c r="L6" s="342"/>
+      <c r="M6" s="342"/>
+      <c r="N6" s="342"/>
+      <c r="O6" s="343"/>
       <c r="P6" s="202"/>
     </row>
     <row r="7" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -11550,11 +11550,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="K9" s="454" t="str">
+      <c r="K9" s="347" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="L9" s="375"/>
+      <c r="L9" s="348"/>
       <c r="M9" s="67" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -11565,33 +11565,33 @@
     </row>
     <row r="10" spans="1:56" s="10" customFormat="1" ht="13.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="249"/>
-      <c r="B10" s="456" t="s">
+      <c r="B10" s="352" t="s">
         <v>260</v>
       </c>
-      <c r="C10" s="460" t="s">
+      <c r="C10" s="357" t="s">
         <v>261</v>
       </c>
-      <c r="D10" s="367"/>
-      <c r="E10" s="367"/>
-      <c r="F10" s="457" t="s">
+      <c r="D10" s="337"/>
+      <c r="E10" s="337"/>
+      <c r="F10" s="354" t="s">
         <v>262</v>
       </c>
-      <c r="G10" s="458"/>
-      <c r="H10" s="458"/>
-      <c r="I10" s="458"/>
-      <c r="J10" s="458"/>
-      <c r="K10" s="458"/>
-      <c r="L10" s="459"/>
-      <c r="M10" s="452" t="s">
+      <c r="G10" s="355"/>
+      <c r="H10" s="355"/>
+      <c r="I10" s="355"/>
+      <c r="J10" s="355"/>
+      <c r="K10" s="355"/>
+      <c r="L10" s="356"/>
+      <c r="M10" s="341" t="s">
         <v>263</v>
       </c>
-      <c r="N10" s="363"/>
-      <c r="O10" s="351"/>
+      <c r="N10" s="342"/>
+      <c r="O10" s="343"/>
       <c r="P10" s="201"/>
     </row>
     <row r="11" spans="1:56" s="10" customFormat="1" ht="105" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="406"/>
+      <c r="B11" s="353"/>
       <c r="C11" s="166" t="s">
         <v>264</v>
       </c>
@@ -16005,58 +16005,58 @@
   <sheetData>
     <row r="1" spans="1:11" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="364"/>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
-      <c r="I1" s="365"/>
-      <c r="J1" s="365"/>
+      <c r="B1" s="408"/>
+      <c r="C1" s="409"/>
+      <c r="D1" s="409"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="409"/>
+      <c r="J1" s="409"/>
       <c r="K1" s="199"/>
     </row>
     <row r="2" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="431" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
-      <c r="H2" s="367"/>
-      <c r="I2" s="367"/>
-      <c r="J2" s="368"/>
+      <c r="B2" s="438" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="337"/>
+      <c r="D2" s="337"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="338"/>
       <c r="K2" s="202"/>
     </row>
     <row r="3" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="344" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="370"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="339"/>
+      <c r="I3" s="339"/>
+      <c r="J3" s="340"/>
       <c r="K3" s="202"/>
     </row>
     <row r="4" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="461" t="s">
+      <c r="B4" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="351"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="343"/>
       <c r="I4" s="144" t="s">
         <v>3</v>
       </c>
@@ -16068,33 +16068,33 @@
     </row>
     <row r="5" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="455" t="s">
+      <c r="B5" s="350" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="451" t="str">
+      <c r="C5" s="336" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="D5" s="367"/>
-      <c r="E5" s="367"/>
-      <c r="F5" s="367"/>
-      <c r="G5" s="367"/>
-      <c r="H5" s="368"/>
-      <c r="I5" s="411" t="s">
+      <c r="D5" s="337"/>
+      <c r="E5" s="337"/>
+      <c r="F5" s="337"/>
+      <c r="G5" s="337"/>
+      <c r="H5" s="338"/>
+      <c r="I5" s="349" t="s">
         <v>259</v>
       </c>
-      <c r="J5" s="368"/>
+      <c r="J5" s="338"/>
       <c r="K5" s="202"/>
     </row>
     <row r="6" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="369"/>
-      <c r="C6" s="359"/>
-      <c r="D6" s="359"/>
-      <c r="E6" s="359"/>
-      <c r="F6" s="359"/>
-      <c r="G6" s="359"/>
-      <c r="H6" s="370"/>
+      <c r="B6" s="351"/>
+      <c r="C6" s="339"/>
+      <c r="D6" s="339"/>
+      <c r="E6" s="339"/>
+      <c r="F6" s="339"/>
+      <c r="G6" s="339"/>
+      <c r="H6" s="340"/>
       <c r="I6" s="75" t="s">
         <v>6</v>
       </c>
@@ -16106,19 +16106,19 @@
     </row>
     <row r="7" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="461" t="s">
+      <c r="B7" s="465" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
-      <c r="E7" s="363"/>
-      <c r="F7" s="351"/>
-      <c r="G7" s="461" t="s">
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="343"/>
+      <c r="G7" s="465" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="363"/>
-      <c r="I7" s="363"/>
-      <c r="J7" s="351"/>
+      <c r="H7" s="342"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="343"/>
       <c r="K7" s="202"/>
     </row>
     <row r="8" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -16188,18 +16188,18 @@
     <row r="11" spans="1:11" s="10" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
       <c r="B11" s="164"/>
-      <c r="C11" s="441" t="s">
+      <c r="C11" s="453" t="s">
         <v>295</v>
       </c>
-      <c r="D11" s="363"/>
-      <c r="E11" s="363"/>
-      <c r="F11" s="363"/>
-      <c r="G11" s="351"/>
+      <c r="D11" s="342"/>
+      <c r="E11" s="342"/>
+      <c r="F11" s="342"/>
+      <c r="G11" s="343"/>
       <c r="H11" s="164"/>
-      <c r="I11" s="462" t="s">
+      <c r="I11" s="466" t="s">
         <v>164</v>
       </c>
-      <c r="J11" s="435" t="s">
+      <c r="J11" s="452" t="s">
         <v>159</v>
       </c>
       <c r="K11" s="201"/>
@@ -16227,8 +16227,8 @@
       <c r="H12" s="164" t="s">
         <v>302</v>
       </c>
-      <c r="I12" s="415"/>
-      <c r="J12" s="406"/>
+      <c r="I12" s="427"/>
+      <c r="J12" s="353"/>
       <c r="K12" s="201"/>
     </row>
     <row r="13" spans="1:11" s="10" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -16254,7 +16254,7 @@
       <c r="H13" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="I13" s="406"/>
+      <c r="I13" s="353"/>
       <c r="J13" s="167"/>
       <c r="K13" s="201"/>
     </row>
@@ -18725,69 +18725,69 @@
   <sheetData>
     <row r="1" spans="1:14" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="364"/>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
-      <c r="I1" s="365"/>
-      <c r="J1" s="365"/>
-      <c r="K1" s="365"/>
-      <c r="L1" s="365"/>
-      <c r="M1" s="365"/>
+      <c r="B1" s="408"/>
+      <c r="C1" s="409"/>
+      <c r="D1" s="409"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="409"/>
+      <c r="J1" s="409"/>
+      <c r="K1" s="409"/>
+      <c r="L1" s="409"/>
+      <c r="M1" s="409"/>
       <c r="N1" s="199"/>
     </row>
     <row r="2" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="431" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
-      <c r="H2" s="367"/>
-      <c r="I2" s="367"/>
-      <c r="J2" s="367"/>
-      <c r="K2" s="367"/>
-      <c r="L2" s="367"/>
-      <c r="M2" s="368"/>
+      <c r="B2" s="438" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="337"/>
+      <c r="D2" s="337"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="337"/>
+      <c r="K2" s="337"/>
+      <c r="L2" s="337"/>
+      <c r="M2" s="338"/>
       <c r="N2" s="202"/>
     </row>
     <row r="3" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="344" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="370"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="339"/>
+      <c r="I3" s="339"/>
+      <c r="J3" s="339"/>
+      <c r="K3" s="339"/>
+      <c r="L3" s="339"/>
+      <c r="M3" s="340"/>
       <c r="N3" s="202"/>
     </row>
     <row r="4" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="461" t="s">
+      <c r="B4" s="465" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="351"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="342"/>
+      <c r="J4" s="343"/>
       <c r="K4" s="144" t="s">
         <v>3</v>
       </c>
@@ -18799,38 +18799,38 @@
     </row>
     <row r="5" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="455" t="s">
+      <c r="B5" s="350" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="367"/>
-      <c r="D5" s="417" t="str">
+      <c r="C5" s="337"/>
+      <c r="D5" s="428" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="367"/>
-      <c r="F5" s="367"/>
-      <c r="G5" s="367"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="368"/>
-      <c r="K5" s="411" t="s">
+      <c r="E5" s="337"/>
+      <c r="F5" s="337"/>
+      <c r="G5" s="337"/>
+      <c r="H5" s="337"/>
+      <c r="I5" s="337"/>
+      <c r="J5" s="338"/>
+      <c r="K5" s="349" t="s">
         <v>259</v>
       </c>
-      <c r="L5" s="367"/>
-      <c r="M5" s="368"/>
+      <c r="L5" s="337"/>
+      <c r="M5" s="338"/>
       <c r="N5" s="202"/>
     </row>
     <row r="6" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="369"/>
-      <c r="C6" s="359"/>
-      <c r="D6" s="359"/>
-      <c r="E6" s="359"/>
-      <c r="F6" s="359"/>
-      <c r="G6" s="359"/>
-      <c r="H6" s="359"/>
-      <c r="I6" s="359"/>
-      <c r="J6" s="370"/>
+      <c r="B6" s="351"/>
+      <c r="C6" s="339"/>
+      <c r="D6" s="339"/>
+      <c r="E6" s="339"/>
+      <c r="F6" s="339"/>
+      <c r="G6" s="339"/>
+      <c r="H6" s="339"/>
+      <c r="I6" s="339"/>
+      <c r="J6" s="340"/>
       <c r="K6" s="75" t="s">
         <v>6</v>
       </c>
@@ -18843,22 +18843,22 @@
     </row>
     <row r="7" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="461" t="s">
+      <c r="B7" s="465" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
-      <c r="E7" s="363"/>
-      <c r="F7" s="363"/>
-      <c r="G7" s="351"/>
-      <c r="H7" s="461" t="s">
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="342"/>
+      <c r="G7" s="343"/>
+      <c r="H7" s="465" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="363"/>
-      <c r="J7" s="363"/>
-      <c r="K7" s="363"/>
-      <c r="L7" s="363"/>
-      <c r="M7" s="351"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="342"/>
+      <c r="K7" s="342"/>
+      <c r="L7" s="342"/>
+      <c r="M7" s="343"/>
       <c r="N7" s="202"/>
     </row>
     <row r="8" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18920,11 +18920,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="436" t="str">
+      <c r="J10" s="462" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="359"/>
+      <c r="K10" s="339"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -18934,77 +18934,77 @@
     <row r="11" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
       <c r="B11" s="167"/>
-      <c r="C11" s="441" t="s">
+      <c r="C11" s="453" t="s">
         <v>295</v>
       </c>
-      <c r="D11" s="363"/>
-      <c r="E11" s="363"/>
-      <c r="F11" s="363"/>
-      <c r="G11" s="351"/>
-      <c r="H11" s="441" t="s">
+      <c r="D11" s="342"/>
+      <c r="E11" s="342"/>
+      <c r="F11" s="342"/>
+      <c r="G11" s="343"/>
+      <c r="H11" s="453" t="s">
         <v>321</v>
       </c>
-      <c r="I11" s="363"/>
-      <c r="J11" s="351"/>
+      <c r="I11" s="342"/>
+      <c r="J11" s="343"/>
       <c r="K11" s="167"/>
-      <c r="L11" s="462" t="s">
+      <c r="L11" s="466" t="s">
         <v>164</v>
       </c>
-      <c r="M11" s="463" t="s">
+      <c r="M11" s="467" t="s">
         <v>159</v>
       </c>
       <c r="N11" s="201"/>
     </row>
     <row r="12" spans="1:14" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="249"/>
-      <c r="B12" s="435" t="s">
+      <c r="B12" s="452" t="s">
         <v>296</v>
       </c>
-      <c r="C12" s="435" t="s">
+      <c r="C12" s="452" t="s">
         <v>297</v>
       </c>
-      <c r="D12" s="435" t="s">
+      <c r="D12" s="452" t="s">
         <v>298</v>
       </c>
-      <c r="E12" s="435" t="s">
+      <c r="E12" s="452" t="s">
         <v>299</v>
       </c>
-      <c r="F12" s="435" t="s">
+      <c r="F12" s="452" t="s">
         <v>300</v>
       </c>
-      <c r="G12" s="435" t="s">
+      <c r="G12" s="452" t="s">
         <v>322</v>
       </c>
-      <c r="H12" s="435" t="s">
+      <c r="H12" s="452" t="s">
         <v>323</v>
       </c>
-      <c r="I12" s="435" t="s">
+      <c r="I12" s="452" t="s">
         <v>324</v>
       </c>
-      <c r="J12" s="435" t="s">
+      <c r="J12" s="452" t="s">
         <v>325</v>
       </c>
-      <c r="K12" s="435" t="s">
+      <c r="K12" s="452" t="s">
         <v>326</v>
       </c>
-      <c r="L12" s="415"/>
-      <c r="M12" s="415"/>
+      <c r="L12" s="427"/>
+      <c r="M12" s="427"/>
       <c r="N12" s="201"/>
     </row>
     <row r="13" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="249"/>
-      <c r="B13" s="406"/>
-      <c r="C13" s="406"/>
-      <c r="D13" s="406"/>
-      <c r="E13" s="406"/>
-      <c r="F13" s="406"/>
-      <c r="G13" s="406"/>
-      <c r="H13" s="406"/>
-      <c r="I13" s="406"/>
-      <c r="J13" s="406"/>
-      <c r="K13" s="406"/>
-      <c r="L13" s="415"/>
-      <c r="M13" s="415"/>
+      <c r="B13" s="353"/>
+      <c r="C13" s="353"/>
+      <c r="D13" s="353"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
+      <c r="G13" s="353"/>
+      <c r="H13" s="353"/>
+      <c r="I13" s="353"/>
+      <c r="J13" s="353"/>
+      <c r="K13" s="353"/>
+      <c r="L13" s="427"/>
+      <c r="M13" s="427"/>
       <c r="N13" s="201"/>
     </row>
     <row r="14" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19039,7 +19039,7 @@
       <c r="K14" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="L14" s="406"/>
+      <c r="L14" s="353"/>
       <c r="M14" s="167"/>
       <c r="N14" s="201"/>
     </row>
@@ -22000,6 +22000,14 @@
     <row r="81" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="D5:J6"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="L11:L14"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="H7:M7"/>
@@ -22016,14 +22024,6 @@
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="L11:L14"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="D5:J6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -22053,87 +22053,87 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="465"/>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
-      <c r="I1" s="365"/>
-      <c r="J1" s="365"/>
-      <c r="K1" s="365"/>
-      <c r="L1" s="365"/>
+      <c r="B1" s="471"/>
+      <c r="C1" s="409"/>
+      <c r="D1" s="409"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="409"/>
+      <c r="J1" s="409"/>
+      <c r="K1" s="409"/>
+      <c r="L1" s="409"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="431" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
-      <c r="H2" s="367"/>
-      <c r="I2" s="367"/>
-      <c r="J2" s="367"/>
-      <c r="K2" s="367"/>
-      <c r="L2" s="368"/>
+      <c r="B2" s="438" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="337"/>
+      <c r="D2" s="337"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="337"/>
+      <c r="K2" s="337"/>
+      <c r="L2" s="338"/>
       <c r="M2" s="202"/>
     </row>
     <row r="3" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="422" t="s">
+      <c r="B3" s="344" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="370"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="G3" s="339"/>
+      <c r="H3" s="339"/>
+      <c r="I3" s="339"/>
+      <c r="J3" s="339"/>
+      <c r="K3" s="339"/>
+      <c r="L3" s="340"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="428" t="s">
+      <c r="B4" s="345" t="s">
         <v>333</v>
       </c>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="351"/>
-      <c r="J4" s="471" t="s">
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="343"/>
+      <c r="J4" s="468" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="363"/>
-      <c r="L4" s="351"/>
+      <c r="K4" s="342"/>
+      <c r="L4" s="343"/>
       <c r="M4" s="202"/>
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="447" t="s">
+      <c r="B5" s="451" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="368"/>
-      <c r="D5" s="470" t="str">
+      <c r="C5" s="338"/>
+      <c r="D5" s="475" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="367"/>
-      <c r="F5" s="367"/>
-      <c r="G5" s="367"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="368"/>
+      <c r="E5" s="337"/>
+      <c r="F5" s="337"/>
+      <c r="G5" s="337"/>
+      <c r="H5" s="337"/>
+      <c r="I5" s="338"/>
       <c r="J5" s="49" t="s">
         <v>6</v>
       </c>
@@ -22145,14 +22145,14 @@
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="369"/>
-      <c r="C6" s="370"/>
-      <c r="D6" s="369"/>
-      <c r="E6" s="359"/>
-      <c r="F6" s="359"/>
-      <c r="G6" s="359"/>
-      <c r="H6" s="359"/>
-      <c r="I6" s="370"/>
+      <c r="B6" s="351"/>
+      <c r="C6" s="340"/>
+      <c r="D6" s="351"/>
+      <c r="E6" s="339"/>
+      <c r="F6" s="339"/>
+      <c r="G6" s="339"/>
+      <c r="H6" s="339"/>
+      <c r="I6" s="340"/>
       <c r="J6" s="31" t="s">
         <v>3</v>
       </c>
@@ -22164,21 +22164,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="428" t="s">
+      <c r="B7" s="345" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
-      <c r="E7" s="363"/>
-      <c r="F7" s="363"/>
-      <c r="G7" s="351"/>
-      <c r="H7" s="428" t="s">
+      <c r="C7" s="342"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="342"/>
+      <c r="G7" s="343"/>
+      <c r="H7" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="363"/>
-      <c r="J7" s="363"/>
-      <c r="K7" s="363"/>
-      <c r="L7" s="351"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="342"/>
+      <c r="K7" s="342"/>
+      <c r="L7" s="343"/>
       <c r="M7" s="202"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -22238,11 +22238,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="436" t="str">
+      <c r="J10" s="462" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="359"/>
+      <c r="K10" s="339"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -22370,42 +22370,42 @@
     </row>
     <row r="25" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="200"/>
-      <c r="B25" s="467" t="s">
+      <c r="B25" s="472" t="s">
         <v>340</v>
       </c>
-      <c r="C25" s="439"/>
-      <c r="D25" s="375"/>
-      <c r="E25" s="375"/>
-      <c r="F25" s="375"/>
-      <c r="G25" s="375"/>
-      <c r="H25" s="375"/>
-      <c r="I25" s="375"/>
-      <c r="J25" s="375"/>
-      <c r="K25" s="375"/>
-      <c r="L25" s="376"/>
+      <c r="C25" s="456"/>
+      <c r="D25" s="348"/>
+      <c r="E25" s="348"/>
+      <c r="F25" s="348"/>
+      <c r="G25" s="348"/>
+      <c r="H25" s="348"/>
+      <c r="I25" s="348"/>
+      <c r="J25" s="348"/>
+      <c r="K25" s="348"/>
+      <c r="L25" s="405"/>
       <c r="M25" s="202"/>
     </row>
     <row r="26" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="200"/>
-      <c r="B26" s="418"/>
-      <c r="C26" s="439"/>
-      <c r="D26" s="375"/>
-      <c r="E26" s="375"/>
-      <c r="F26" s="375"/>
-      <c r="G26" s="375"/>
-      <c r="H26" s="375"/>
-      <c r="I26" s="375"/>
-      <c r="J26" s="375"/>
-      <c r="K26" s="375"/>
-      <c r="L26" s="376"/>
+      <c r="B26" s="429"/>
+      <c r="C26" s="456"/>
+      <c r="D26" s="348"/>
+      <c r="E26" s="348"/>
+      <c r="F26" s="348"/>
+      <c r="G26" s="348"/>
+      <c r="H26" s="348"/>
+      <c r="I26" s="348"/>
+      <c r="J26" s="348"/>
+      <c r="K26" s="348"/>
+      <c r="L26" s="405"/>
       <c r="M26" s="202"/>
     </row>
     <row r="27" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="200"/>
-      <c r="B27" s="466" t="s">
+      <c r="B27" s="469" t="s">
         <v>341</v>
       </c>
-      <c r="C27" s="439"/>
+      <c r="C27" s="456"/>
       <c r="D27" s="324" t="e">
         <f>'QUADRO II'!F17</f>
         <v>#VALUE!</v>
@@ -22426,10 +22426,10 @@
     </row>
     <row r="28" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="200"/>
-      <c r="B28" s="466" t="s">
+      <c r="B28" s="469" t="s">
         <v>344</v>
       </c>
-      <c r="C28" s="439"/>
+      <c r="C28" s="456"/>
       <c r="D28" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22449,10 +22449,10 @@
     </row>
     <row r="29" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="200"/>
-      <c r="B29" s="466" t="s">
+      <c r="B29" s="469" t="s">
         <v>345</v>
       </c>
-      <c r="C29" s="439"/>
+      <c r="C29" s="456"/>
       <c r="D29" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22472,10 +22472,10 @@
     </row>
     <row r="30" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="200"/>
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="469" t="s">
         <v>346</v>
       </c>
-      <c r="C30" s="439"/>
+      <c r="C30" s="456"/>
       <c r="D30" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22495,10 +22495,10 @@
     </row>
     <row r="31" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="200"/>
-      <c r="B31" s="466" t="s">
+      <c r="B31" s="469" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="439"/>
+      <c r="C31" s="456"/>
       <c r="D31" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22518,10 +22518,10 @@
     </row>
     <row r="32" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="200"/>
-      <c r="B32" s="466" t="s">
+      <c r="B32" s="469" t="s">
         <v>348</v>
       </c>
-      <c r="C32" s="439"/>
+      <c r="C32" s="456"/>
       <c r="D32" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22557,70 +22557,70 @@
     <row r="35" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="200"/>
       <c r="B35" s="271"/>
-      <c r="D35" s="469"/>
-      <c r="E35" s="375"/>
+      <c r="D35" s="474"/>
+      <c r="E35" s="348"/>
       <c r="L35" s="4"/>
       <c r="M35" s="202"/>
     </row>
     <row r="36" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="200"/>
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="470" t="s">
         <v>350</v>
       </c>
-      <c r="C36" s="367"/>
-      <c r="D36" s="367"/>
-      <c r="E36" s="367"/>
-      <c r="F36" s="368"/>
-      <c r="G36" s="468"/>
-      <c r="H36" s="367"/>
-      <c r="I36" s="367"/>
-      <c r="J36" s="367"/>
-      <c r="K36" s="368"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="338"/>
+      <c r="G36" s="473"/>
+      <c r="H36" s="337"/>
+      <c r="I36" s="337"/>
+      <c r="J36" s="337"/>
+      <c r="K36" s="338"/>
       <c r="L36" s="4"/>
       <c r="M36" s="202"/>
     </row>
     <row r="37" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="200"/>
-      <c r="B37" s="418"/>
-      <c r="C37" s="439"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="376"/>
-      <c r="G37" s="418"/>
-      <c r="H37" s="375"/>
-      <c r="I37" s="375"/>
-      <c r="J37" s="375"/>
-      <c r="K37" s="376"/>
+      <c r="B37" s="429"/>
+      <c r="C37" s="456"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="405"/>
+      <c r="G37" s="429"/>
+      <c r="H37" s="348"/>
+      <c r="I37" s="348"/>
+      <c r="J37" s="348"/>
+      <c r="K37" s="405"/>
       <c r="L37" s="4"/>
       <c r="M37" s="202"/>
     </row>
     <row r="38" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="200"/>
-      <c r="B38" s="418"/>
-      <c r="C38" s="439"/>
-      <c r="D38" s="375"/>
-      <c r="E38" s="375"/>
-      <c r="F38" s="376"/>
-      <c r="G38" s="418"/>
-      <c r="H38" s="375"/>
-      <c r="I38" s="375"/>
-      <c r="J38" s="375"/>
-      <c r="K38" s="376"/>
+      <c r="B38" s="429"/>
+      <c r="C38" s="456"/>
+      <c r="D38" s="348"/>
+      <c r="E38" s="348"/>
+      <c r="F38" s="405"/>
+      <c r="G38" s="429"/>
+      <c r="H38" s="348"/>
+      <c r="I38" s="348"/>
+      <c r="J38" s="348"/>
+      <c r="K38" s="405"/>
       <c r="L38" s="4"/>
       <c r="M38" s="202"/>
     </row>
     <row r="39" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="200"/>
-      <c r="B39" s="369"/>
-      <c r="C39" s="359"/>
-      <c r="D39" s="359"/>
-      <c r="E39" s="359"/>
-      <c r="F39" s="370"/>
-      <c r="G39" s="369"/>
-      <c r="H39" s="359"/>
-      <c r="I39" s="359"/>
-      <c r="J39" s="359"/>
-      <c r="K39" s="370"/>
+      <c r="B39" s="351"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="340"/>
+      <c r="G39" s="351"/>
+      <c r="H39" s="339"/>
+      <c r="I39" s="339"/>
+      <c r="J39" s="339"/>
+      <c r="K39" s="340"/>
       <c r="L39" s="4"/>
       <c r="M39" s="202"/>
     </row>
@@ -22664,11 +22664,6 @@
     <row r="43" spans="1:13" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="B2:L2"/>
     <mergeCell ref="B36:F39"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B29:C29"/>
@@ -22684,6 +22679,11 @@
     <mergeCell ref="D5:I6"/>
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="B3:L3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="B2:L2"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>

--- a/QUADROS ABNT.xlsx
+++ b/QUADROS ABNT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Desktop\DOCUMENTOS APROVAÇÃO EMPREEDIMENTOS\DOCUMENTOS INCIAIS\5 - QUADROS ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6740D1-A7EA-4142-B3C7-42CC07421633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D097D1A-7D02-492D-BF92-1C0D7326E169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="976" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="379">
   <si>
     <t>INFORMAÇÕES PARA ARQUIVO NO REGISTRO DE IMÓVEIS</t>
   </si>
@@ -3301,69 +3301,46 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3376,84 +3353,107 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3463,170 +3463,170 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="39" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="39" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="39" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="39" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="39" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3638,97 +3638,97 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="39" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4057,15 +4057,15 @@
   <sheetData>
     <row r="1" spans="1:9" ht="40.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A1" s="168"/>
-      <c r="B1" s="360" t="s">
+      <c r="B1" s="345" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="334"/>
-      <c r="D1" s="334"/>
-      <c r="E1" s="334"/>
-      <c r="F1" s="334"/>
-      <c r="G1" s="334"/>
-      <c r="H1" s="334"/>
+      <c r="C1" s="346"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
       <c r="I1" s="169"/>
     </row>
     <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4082,15 +4082,15 @@
       <c r="B3" s="178" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="361" t="s">
+      <c r="C3" s="347" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="362"/>
-      <c r="E3" s="362"/>
-      <c r="F3" s="362"/>
-      <c r="G3" s="362"/>
-      <c r="H3" s="362"/>
-      <c r="I3" s="363"/>
+      <c r="D3" s="334"/>
+      <c r="E3" s="334"/>
+      <c r="F3" s="334"/>
+      <c r="G3" s="334"/>
+      <c r="H3" s="334"/>
+      <c r="I3" s="348"/>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="170"/>
@@ -4135,32 +4135,32 @@
     </row>
     <row r="7" spans="1:9" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="170"/>
-      <c r="B7" s="364" t="s">
+      <c r="B7" s="349" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="365"/>
-      <c r="D7" s="371" t="s">
+      <c r="C7" s="350"/>
+      <c r="D7" s="335" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="372" t="s">
+      <c r="E7" s="337" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="358" t="s">
+      <c r="F7" s="344" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="368" t="s">
+      <c r="G7" s="353" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="369"/>
+      <c r="H7" s="354"/>
       <c r="I7" s="171"/>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="170"/>
-      <c r="B8" s="366"/>
-      <c r="C8" s="367"/>
-      <c r="D8" s="359"/>
-      <c r="E8" s="359"/>
-      <c r="F8" s="359"/>
+      <c r="B8" s="351"/>
+      <c r="C8" s="352"/>
+      <c r="D8" s="336"/>
+      <c r="E8" s="336"/>
+      <c r="F8" s="336"/>
       <c r="G8" s="177" t="s">
         <v>45</v>
       </c>
@@ -4226,17 +4226,17 @@
       <c r="I10" s="171"/>
     </row>
     <row r="11" spans="1:9" ht="38.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="376" t="s">
+      <c r="A11" s="341" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="377"/>
-      <c r="C11" s="377"/>
-      <c r="D11" s="377"/>
-      <c r="E11" s="377"/>
-      <c r="F11" s="377"/>
-      <c r="G11" s="377"/>
-      <c r="H11" s="377"/>
-      <c r="I11" s="378"/>
+      <c r="B11" s="342"/>
+      <c r="C11" s="342"/>
+      <c r="D11" s="342"/>
+      <c r="E11" s="342"/>
+      <c r="F11" s="342"/>
+      <c r="G11" s="342"/>
+      <c r="H11" s="342"/>
+      <c r="I11" s="343"/>
     </row>
     <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="170"/>
@@ -4244,42 +4244,42 @@
     </row>
     <row r="13" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="170"/>
-      <c r="B13" s="370" t="s">
+      <c r="B13" s="333" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="362"/>
-      <c r="D13" s="362"/>
-      <c r="E13" s="362"/>
-      <c r="F13" s="362"/>
-      <c r="G13" s="362"/>
-      <c r="H13" s="362"/>
+      <c r="C13" s="334"/>
+      <c r="D13" s="334"/>
+      <c r="E13" s="334"/>
+      <c r="F13" s="334"/>
+      <c r="G13" s="334"/>
+      <c r="H13" s="334"/>
       <c r="I13" s="171"/>
     </row>
     <row r="14" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="373" t="s">
+      <c r="A14" s="338" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="374"/>
-      <c r="C14" s="374"/>
-      <c r="D14" s="374"/>
-      <c r="E14" s="374"/>
-      <c r="F14" s="374"/>
-      <c r="G14" s="374"/>
-      <c r="H14" s="374"/>
-      <c r="I14" s="375"/>
+      <c r="B14" s="339"/>
+      <c r="C14" s="339"/>
+      <c r="D14" s="339"/>
+      <c r="E14" s="339"/>
+      <c r="F14" s="339"/>
+      <c r="G14" s="339"/>
+      <c r="H14" s="339"/>
+      <c r="I14" s="340"/>
     </row>
     <row r="15" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="373" t="s">
+      <c r="A15" s="338" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="374"/>
-      <c r="C15" s="374"/>
-      <c r="D15" s="374"/>
-      <c r="E15" s="374"/>
-      <c r="F15" s="374"/>
-      <c r="G15" s="374"/>
-      <c r="H15" s="374"/>
-      <c r="I15" s="375"/>
+      <c r="B15" s="339"/>
+      <c r="C15" s="339"/>
+      <c r="D15" s="339"/>
+      <c r="E15" s="339"/>
+      <c r="F15" s="339"/>
+      <c r="G15" s="339"/>
+      <c r="H15" s="339"/>
+      <c r="I15" s="340"/>
     </row>
     <row r="16" spans="1:9" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="172"/>
@@ -4296,6 +4296,10 @@
     <row r="18" ht="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
@@ -4303,10 +4307,6 @@
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A11:I11"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="G7:H7"/>
   </mergeCells>
   <pageMargins left="1.181102362204725" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait"/>
@@ -4334,65 +4334,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="408"/>
-      <c r="C1" s="409"/>
-      <c r="D1" s="409"/>
-      <c r="E1" s="409"/>
-      <c r="F1" s="409"/>
-      <c r="G1" s="409"/>
-      <c r="H1" s="409"/>
-      <c r="I1" s="409"/>
-      <c r="J1" s="409"/>
-      <c r="K1" s="409"/>
-      <c r="L1" s="409"/>
+      <c r="B1" s="369"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+      <c r="E1" s="370"/>
+      <c r="F1" s="370"/>
+      <c r="G1" s="370"/>
+      <c r="H1" s="370"/>
+      <c r="I1" s="370"/>
+      <c r="J1" s="370"/>
+      <c r="K1" s="370"/>
+      <c r="L1" s="370"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="438" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="338"/>
+      <c r="B2" s="435" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="372"/>
+      <c r="D2" s="372"/>
+      <c r="E2" s="372"/>
+      <c r="F2" s="372"/>
+      <c r="G2" s="372"/>
+      <c r="H2" s="372"/>
+      <c r="I2" s="372"/>
+      <c r="J2" s="372"/>
+      <c r="K2" s="372"/>
+      <c r="L2" s="373"/>
       <c r="M2" s="202"/>
     </row>
     <row r="3" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="344" t="s">
+      <c r="B3" s="426" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339"/>
-      <c r="E3" s="339"/>
-      <c r="F3" s="339"/>
-      <c r="G3" s="339"/>
-      <c r="H3" s="339"/>
-      <c r="I3" s="339"/>
-      <c r="J3" s="339"/>
-      <c r="K3" s="339"/>
-      <c r="L3" s="340"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
+      <c r="L3" s="375"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="345" t="s">
+      <c r="B4" s="432" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="343"/>
+      <c r="C4" s="368"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="368"/>
+      <c r="F4" s="368"/>
+      <c r="G4" s="368"/>
+      <c r="H4" s="368"/>
+      <c r="I4" s="356"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -4405,36 +4405,36 @@
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="476" t="s">
+      <c r="B5" s="487" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="338"/>
-      <c r="D5" s="475" t="str">
+      <c r="C5" s="373"/>
+      <c r="D5" s="474" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="338"/>
-      <c r="J5" s="449" t="s">
+      <c r="E5" s="372"/>
+      <c r="F5" s="372"/>
+      <c r="G5" s="372"/>
+      <c r="H5" s="372"/>
+      <c r="I5" s="373"/>
+      <c r="J5" s="429" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="342"/>
-      <c r="L5" s="343"/>
+      <c r="K5" s="368"/>
+      <c r="L5" s="356"/>
       <c r="M5" s="202"/>
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="340"/>
-      <c r="D6" s="351"/>
-      <c r="E6" s="339"/>
-      <c r="F6" s="339"/>
-      <c r="G6" s="339"/>
-      <c r="H6" s="339"/>
-      <c r="I6" s="340"/>
+      <c r="B6" s="374"/>
+      <c r="C6" s="375"/>
+      <c r="D6" s="374"/>
+      <c r="E6" s="364"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="364"/>
+      <c r="I6" s="375"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -4447,21 +4447,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="345" t="s">
+      <c r="B7" s="432" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="342"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
-      <c r="F7" s="342"/>
-      <c r="G7" s="343"/>
-      <c r="H7" s="345" t="s">
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
+      <c r="E7" s="368"/>
+      <c r="F7" s="368"/>
+      <c r="G7" s="356"/>
+      <c r="H7" s="432" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="342"/>
-      <c r="J7" s="342"/>
-      <c r="K7" s="342"/>
-      <c r="L7" s="343"/>
+      <c r="I7" s="368"/>
+      <c r="J7" s="368"/>
+      <c r="K7" s="368"/>
+      <c r="L7" s="356"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -4521,11 +4521,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="462" t="str">
+      <c r="J10" s="440" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="339"/>
+      <c r="K10" s="364"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -4540,215 +4540,246 @@
     </row>
     <row r="12" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="200"/>
-      <c r="B12" s="480" t="s">
+      <c r="B12" s="488" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="481"/>
-      <c r="D12" s="482" t="s">
+      <c r="C12" s="482"/>
+      <c r="D12" s="481" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="481"/>
-      <c r="F12" s="482" t="s">
+      <c r="E12" s="482"/>
+      <c r="F12" s="481" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="481"/>
-      <c r="H12" s="482" t="s">
+      <c r="G12" s="482"/>
+      <c r="H12" s="481" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="488"/>
-      <c r="J12" s="488"/>
-      <c r="K12" s="488"/>
-      <c r="L12" s="481"/>
+      <c r="I12" s="483"/>
+      <c r="J12" s="483"/>
+      <c r="K12" s="483"/>
+      <c r="L12" s="482"/>
       <c r="M12" s="202"/>
     </row>
     <row r="13" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="200"/>
-      <c r="B13" s="485" t="s">
+      <c r="B13" s="477" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="340"/>
-      <c r="D13" s="484" t="s">
+      <c r="C13" s="375"/>
+      <c r="D13" s="480" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="340"/>
-      <c r="F13" s="484" t="s">
+      <c r="E13" s="375"/>
+      <c r="F13" s="480" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="340"/>
-      <c r="H13" s="487" t="s">
+      <c r="G13" s="375"/>
+      <c r="H13" s="479" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="339"/>
-      <c r="J13" s="339"/>
-      <c r="K13" s="339"/>
-      <c r="L13" s="340"/>
+      <c r="I13" s="364"/>
+      <c r="J13" s="364"/>
+      <c r="K13" s="364"/>
+      <c r="L13" s="375"/>
       <c r="M13" s="202"/>
     </row>
     <row r="14" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="200"/>
-      <c r="B14" s="479" t="s">
+      <c r="B14" s="476" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="343"/>
-      <c r="D14" s="477" t="s">
+      <c r="C14" s="356"/>
+      <c r="D14" s="485" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="343"/>
-      <c r="F14" s="477" t="s">
+      <c r="E14" s="356"/>
+      <c r="F14" s="485" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="343"/>
-      <c r="H14" s="422"/>
-      <c r="I14" s="342"/>
-      <c r="J14" s="342"/>
-      <c r="K14" s="342"/>
-      <c r="L14" s="343"/>
+      <c r="G14" s="356"/>
+      <c r="H14" s="355"/>
+      <c r="I14" s="368"/>
+      <c r="J14" s="368"/>
+      <c r="K14" s="368"/>
+      <c r="L14" s="356"/>
       <c r="M14" s="202"/>
     </row>
     <row r="15" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="200"/>
-      <c r="B15" s="479" t="s">
+      <c r="B15" s="476" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="343"/>
-      <c r="D15" s="477" t="s">
+      <c r="C15" s="356"/>
+      <c r="D15" s="485" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="343"/>
-      <c r="F15" s="477" t="s">
+      <c r="E15" s="356"/>
+      <c r="F15" s="485" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="343"/>
-      <c r="H15" s="422"/>
-      <c r="I15" s="342"/>
-      <c r="J15" s="342"/>
-      <c r="K15" s="342"/>
-      <c r="L15" s="343"/>
+      <c r="G15" s="356"/>
+      <c r="H15" s="355"/>
+      <c r="I15" s="368"/>
+      <c r="J15" s="368"/>
+      <c r="K15" s="368"/>
+      <c r="L15" s="356"/>
       <c r="M15" s="202"/>
     </row>
     <row r="16" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="200"/>
-      <c r="B16" s="479" t="s">
+      <c r="B16" s="476" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="343"/>
-      <c r="D16" s="486" t="s">
+      <c r="C16" s="356"/>
+      <c r="D16" s="478" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="343"/>
-      <c r="F16" s="478" t="s">
+      <c r="E16" s="356"/>
+      <c r="F16" s="486" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="343"/>
-      <c r="H16" s="422"/>
-      <c r="I16" s="342"/>
-      <c r="J16" s="342"/>
-      <c r="K16" s="342"/>
-      <c r="L16" s="343"/>
+      <c r="G16" s="356"/>
+      <c r="H16" s="355"/>
+      <c r="I16" s="368"/>
+      <c r="J16" s="368"/>
+      <c r="K16" s="368"/>
+      <c r="L16" s="356"/>
       <c r="M16" s="202"/>
     </row>
     <row r="17" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="200"/>
-      <c r="B17" s="479" t="s">
+      <c r="B17" s="476" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="343"/>
-      <c r="D17" s="477" t="s">
+      <c r="C17" s="356"/>
+      <c r="D17" s="485" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="343"/>
-      <c r="F17" s="477" t="s">
+      <c r="E17" s="356"/>
+      <c r="F17" s="485" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="343"/>
-      <c r="H17" s="422"/>
-      <c r="I17" s="342"/>
-      <c r="J17" s="342"/>
-      <c r="K17" s="342"/>
-      <c r="L17" s="343"/>
+      <c r="G17" s="356"/>
+      <c r="H17" s="355"/>
+      <c r="I17" s="368"/>
+      <c r="J17" s="368"/>
+      <c r="K17" s="368"/>
+      <c r="L17" s="356"/>
       <c r="M17" s="202"/>
     </row>
     <row r="18" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="200"/>
-      <c r="B18" s="479" t="s">
+      <c r="B18" s="476" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="477" t="s">
+      <c r="C18" s="356"/>
+      <c r="D18" s="485" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="343"/>
-      <c r="F18" s="477" t="s">
+      <c r="E18" s="356"/>
+      <c r="F18" s="485" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="343"/>
-      <c r="H18" s="422"/>
-      <c r="I18" s="342"/>
-      <c r="J18" s="342"/>
-      <c r="K18" s="342"/>
-      <c r="L18" s="343"/>
+      <c r="G18" s="356"/>
+      <c r="H18" s="355"/>
+      <c r="I18" s="368"/>
+      <c r="J18" s="368"/>
+      <c r="K18" s="368"/>
+      <c r="L18" s="356"/>
       <c r="M18" s="202"/>
     </row>
     <row r="19" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="200"/>
-      <c r="B19" s="479" t="s">
+      <c r="B19" s="476" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="343"/>
-      <c r="D19" s="477" t="s">
+      <c r="C19" s="356"/>
+      <c r="D19" s="485" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="343"/>
-      <c r="F19" s="477" t="s">
+      <c r="E19" s="356"/>
+      <c r="F19" s="485" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="343"/>
-      <c r="H19" s="453"/>
-      <c r="I19" s="342"/>
-      <c r="J19" s="342"/>
-      <c r="K19" s="342"/>
-      <c r="L19" s="343"/>
+      <c r="G19" s="356"/>
+      <c r="H19" s="445"/>
+      <c r="I19" s="368"/>
+      <c r="J19" s="368"/>
+      <c r="K19" s="368"/>
+      <c r="L19" s="356"/>
       <c r="M19" s="202"/>
     </row>
     <row r="20" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="479" t="s">
+      <c r="B20" s="476" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="343"/>
-      <c r="D20" s="478" t="s">
+      <c r="C20" s="356"/>
+      <c r="D20" s="486" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="343"/>
-      <c r="F20" s="478" t="s">
+      <c r="E20" s="356"/>
+      <c r="F20" s="486" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="343"/>
-      <c r="H20" s="453"/>
-      <c r="I20" s="342"/>
-      <c r="J20" s="342"/>
-      <c r="K20" s="342"/>
-      <c r="L20" s="343"/>
+      <c r="G20" s="356"/>
+      <c r="H20" s="445"/>
+      <c r="I20" s="368"/>
+      <c r="J20" s="368"/>
+      <c r="K20" s="368"/>
+      <c r="L20" s="356"/>
       <c r="M20" s="202"/>
     </row>
     <row r="21" spans="1:13" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="203"/>
-      <c r="B21" s="483"/>
-      <c r="C21" s="413"/>
-      <c r="D21" s="413"/>
-      <c r="E21" s="413"/>
-      <c r="F21" s="413"/>
-      <c r="G21" s="413"/>
-      <c r="H21" s="413"/>
-      <c r="I21" s="413"/>
-      <c r="J21" s="413"/>
-      <c r="K21" s="413"/>
-      <c r="L21" s="413"/>
+      <c r="B21" s="484"/>
+      <c r="C21" s="378"/>
+      <c r="D21" s="378"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
+      <c r="G21" s="378"/>
+      <c r="H21" s="378"/>
+      <c r="I21" s="378"/>
+      <c r="J21" s="378"/>
+      <c r="K21" s="378"/>
+      <c r="L21" s="378"/>
       <c r="M21" s="204"/>
     </row>
     <row r="22" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="F14:G14"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B18:C18"/>
@@ -4765,37 +4796,6 @@
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="H12:L12"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="D14:E14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -4818,65 +4818,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="408"/>
-      <c r="C1" s="409"/>
-      <c r="D1" s="409"/>
-      <c r="E1" s="409"/>
-      <c r="F1" s="409"/>
-      <c r="G1" s="409"/>
-      <c r="H1" s="409"/>
-      <c r="I1" s="409"/>
-      <c r="J1" s="409"/>
-      <c r="K1" s="409"/>
-      <c r="L1" s="409"/>
+      <c r="B1" s="369"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+      <c r="E1" s="370"/>
+      <c r="F1" s="370"/>
+      <c r="G1" s="370"/>
+      <c r="H1" s="370"/>
+      <c r="I1" s="370"/>
+      <c r="J1" s="370"/>
+      <c r="K1" s="370"/>
+      <c r="L1" s="370"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="438" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="338"/>
+      <c r="B2" s="435" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="372"/>
+      <c r="D2" s="372"/>
+      <c r="E2" s="372"/>
+      <c r="F2" s="372"/>
+      <c r="G2" s="372"/>
+      <c r="H2" s="372"/>
+      <c r="I2" s="372"/>
+      <c r="J2" s="372"/>
+      <c r="K2" s="372"/>
+      <c r="L2" s="373"/>
       <c r="M2" s="282"/>
     </row>
     <row r="3" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="344" t="s">
+      <c r="B3" s="426" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339"/>
-      <c r="E3" s="339"/>
-      <c r="F3" s="339"/>
-      <c r="G3" s="339"/>
-      <c r="H3" s="339"/>
-      <c r="I3" s="339"/>
-      <c r="J3" s="339"/>
-      <c r="K3" s="339"/>
-      <c r="L3" s="340"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
+      <c r="L3" s="375"/>
       <c r="M3" s="282"/>
     </row>
     <row r="4" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="345" t="s">
+      <c r="B4" s="432" t="s">
         <v>351</v>
       </c>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="343"/>
+      <c r="C4" s="368"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="368"/>
+      <c r="F4" s="368"/>
+      <c r="G4" s="368"/>
+      <c r="H4" s="368"/>
+      <c r="I4" s="356"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -4889,36 +4889,36 @@
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="476" t="s">
+      <c r="B5" s="487" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="338"/>
-      <c r="D5" s="475" t="str">
+      <c r="C5" s="373"/>
+      <c r="D5" s="474" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="338"/>
-      <c r="J5" s="449" t="s">
+      <c r="E5" s="372"/>
+      <c r="F5" s="372"/>
+      <c r="G5" s="372"/>
+      <c r="H5" s="372"/>
+      <c r="I5" s="373"/>
+      <c r="J5" s="429" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="342"/>
-      <c r="L5" s="343"/>
+      <c r="K5" s="368"/>
+      <c r="L5" s="356"/>
       <c r="M5" s="213"/>
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="340"/>
-      <c r="D6" s="351"/>
-      <c r="E6" s="339"/>
-      <c r="F6" s="339"/>
-      <c r="G6" s="339"/>
-      <c r="H6" s="339"/>
-      <c r="I6" s="340"/>
+      <c r="B6" s="374"/>
+      <c r="C6" s="375"/>
+      <c r="D6" s="374"/>
+      <c r="E6" s="364"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="364"/>
+      <c r="I6" s="375"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -4931,21 +4931,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="345" t="s">
+      <c r="B7" s="432" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="342"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
-      <c r="F7" s="342"/>
-      <c r="G7" s="343"/>
-      <c r="H7" s="345" t="s">
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
+      <c r="E7" s="368"/>
+      <c r="F7" s="368"/>
+      <c r="G7" s="356"/>
+      <c r="H7" s="432" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="342"/>
-      <c r="J7" s="342"/>
-      <c r="K7" s="342"/>
-      <c r="L7" s="343"/>
+      <c r="I7" s="368"/>
+      <c r="J7" s="368"/>
+      <c r="K7" s="368"/>
+      <c r="L7" s="356"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -5005,11 +5005,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="462" t="str">
+      <c r="J10" s="440" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="339"/>
+      <c r="K10" s="364"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -5024,24 +5024,24 @@
     </row>
     <row r="12" spans="1:13" s="25" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="285"/>
-      <c r="B12" s="480" t="s">
+      <c r="B12" s="488" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="481"/>
-      <c r="D12" s="482" t="s">
+      <c r="C12" s="482"/>
+      <c r="D12" s="481" t="s">
         <v>353</v>
       </c>
-      <c r="E12" s="488"/>
-      <c r="F12" s="481"/>
-      <c r="G12" s="482" t="s">
+      <c r="E12" s="483"/>
+      <c r="F12" s="482"/>
+      <c r="G12" s="481" t="s">
         <v>354</v>
       </c>
-      <c r="H12" s="488"/>
-      <c r="I12" s="481"/>
-      <c r="J12" s="482" t="s">
+      <c r="H12" s="483"/>
+      <c r="I12" s="482"/>
+      <c r="J12" s="481" t="s">
         <v>355</v>
       </c>
-      <c r="K12" s="481"/>
+      <c r="K12" s="482"/>
       <c r="L12" s="291" t="s">
         <v>356</v>
       </c>
@@ -5049,24 +5049,24 @@
     </row>
     <row r="13" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="285"/>
-      <c r="B13" s="495" t="s">
+      <c r="B13" s="494" t="s">
         <v>357</v>
       </c>
-      <c r="C13" s="493"/>
-      <c r="D13" s="491" t="s">
+      <c r="C13" s="495"/>
+      <c r="D13" s="496" t="s">
         <v>358</v>
       </c>
-      <c r="E13" s="492"/>
-      <c r="F13" s="493"/>
-      <c r="G13" s="491" t="s">
+      <c r="E13" s="497"/>
+      <c r="F13" s="495"/>
+      <c r="G13" s="496" t="s">
         <v>359</v>
       </c>
-      <c r="H13" s="492"/>
-      <c r="I13" s="493"/>
-      <c r="J13" s="491" t="s">
+      <c r="H13" s="497"/>
+      <c r="I13" s="495"/>
+      <c r="J13" s="496" t="s">
         <v>360</v>
       </c>
-      <c r="K13" s="493"/>
+      <c r="K13" s="495"/>
       <c r="L13" s="279"/>
       <c r="M13" s="286"/>
     </row>
@@ -5075,21 +5075,21 @@
       <c r="B14" s="490" t="s">
         <v>197</v>
       </c>
-      <c r="C14" s="405"/>
-      <c r="D14" s="489" t="s">
+      <c r="C14" s="381"/>
+      <c r="D14" s="492" t="s">
         <v>358</v>
       </c>
-      <c r="E14" s="494"/>
-      <c r="F14" s="405"/>
-      <c r="G14" s="489" t="s">
+      <c r="E14" s="493"/>
+      <c r="F14" s="381"/>
+      <c r="G14" s="492" t="s">
         <v>359</v>
       </c>
-      <c r="H14" s="494"/>
-      <c r="I14" s="405"/>
-      <c r="J14" s="489" t="s">
+      <c r="H14" s="493"/>
+      <c r="I14" s="381"/>
+      <c r="J14" s="492" t="s">
         <v>360</v>
       </c>
-      <c r="K14" s="405"/>
+      <c r="K14" s="381"/>
       <c r="L14" s="280"/>
       <c r="M14" s="286"/>
     </row>
@@ -5098,21 +5098,21 @@
       <c r="B15" s="490" t="s">
         <v>361</v>
       </c>
-      <c r="C15" s="405"/>
-      <c r="D15" s="489" t="s">
+      <c r="C15" s="381"/>
+      <c r="D15" s="492" t="s">
         <v>358</v>
       </c>
-      <c r="E15" s="494"/>
-      <c r="F15" s="405"/>
-      <c r="G15" s="489" t="s">
+      <c r="E15" s="493"/>
+      <c r="F15" s="381"/>
+      <c r="G15" s="492" t="s">
         <v>362</v>
       </c>
-      <c r="H15" s="494"/>
-      <c r="I15" s="405"/>
-      <c r="J15" s="489" t="s">
+      <c r="H15" s="493"/>
+      <c r="I15" s="381"/>
+      <c r="J15" s="492" t="s">
         <v>360</v>
       </c>
-      <c r="K15" s="405"/>
+      <c r="K15" s="381"/>
       <c r="L15" s="280"/>
       <c r="M15" s="286"/>
     </row>
@@ -5121,21 +5121,21 @@
       <c r="B16" s="490" t="s">
         <v>363</v>
       </c>
-      <c r="C16" s="405"/>
-      <c r="D16" s="489" t="s">
+      <c r="C16" s="381"/>
+      <c r="D16" s="492" t="s">
         <v>358</v>
       </c>
-      <c r="E16" s="494"/>
-      <c r="F16" s="405"/>
-      <c r="G16" s="489" t="s">
+      <c r="E16" s="493"/>
+      <c r="F16" s="381"/>
+      <c r="G16" s="492" t="s">
         <v>362</v>
       </c>
-      <c r="H16" s="494"/>
-      <c r="I16" s="405"/>
-      <c r="J16" s="489" t="s">
+      <c r="H16" s="493"/>
+      <c r="I16" s="381"/>
+      <c r="J16" s="492" t="s">
         <v>360</v>
       </c>
-      <c r="K16" s="405"/>
+      <c r="K16" s="381"/>
       <c r="L16" s="280"/>
       <c r="M16" s="286"/>
     </row>
@@ -5144,60 +5144,60 @@
       <c r="B17" s="490" t="s">
         <v>364</v>
       </c>
-      <c r="C17" s="405"/>
-      <c r="D17" s="489" t="s">
+      <c r="C17" s="381"/>
+      <c r="D17" s="492" t="s">
         <v>358</v>
       </c>
-      <c r="E17" s="494"/>
-      <c r="F17" s="405"/>
-      <c r="G17" s="489" t="s">
+      <c r="E17" s="493"/>
+      <c r="F17" s="381"/>
+      <c r="G17" s="492" t="s">
         <v>365</v>
       </c>
-      <c r="H17" s="494"/>
-      <c r="I17" s="405"/>
-      <c r="J17" s="489" t="s">
+      <c r="H17" s="493"/>
+      <c r="I17" s="381"/>
+      <c r="J17" s="492" t="s">
         <v>360</v>
       </c>
-      <c r="K17" s="405"/>
+      <c r="K17" s="381"/>
       <c r="L17" s="280"/>
       <c r="M17" s="286"/>
     </row>
     <row r="18" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="285"/>
-      <c r="B18" s="485" t="s">
+      <c r="B18" s="477" t="s">
         <v>366</v>
       </c>
-      <c r="C18" s="340"/>
-      <c r="D18" s="489" t="s">
+      <c r="C18" s="375"/>
+      <c r="D18" s="492" t="s">
         <v>358</v>
       </c>
-      <c r="E18" s="494"/>
-      <c r="F18" s="405"/>
-      <c r="G18" s="497" t="s">
+      <c r="E18" s="493"/>
+      <c r="F18" s="381"/>
+      <c r="G18" s="491" t="s">
         <v>362</v>
       </c>
-      <c r="H18" s="339"/>
-      <c r="I18" s="340"/>
-      <c r="J18" s="497" t="s">
+      <c r="H18" s="364"/>
+      <c r="I18" s="375"/>
+      <c r="J18" s="491" t="s">
         <v>360</v>
       </c>
-      <c r="K18" s="340"/>
+      <c r="K18" s="375"/>
       <c r="L18" s="281"/>
       <c r="M18" s="286"/>
     </row>
     <row r="19" spans="1:13" s="25" customFormat="1" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="287"/>
-      <c r="B19" s="496"/>
-      <c r="C19" s="413"/>
-      <c r="D19" s="413"/>
-      <c r="E19" s="413"/>
-      <c r="F19" s="413"/>
-      <c r="G19" s="413"/>
-      <c r="H19" s="413"/>
-      <c r="I19" s="413"/>
-      <c r="J19" s="413"/>
-      <c r="K19" s="413"/>
-      <c r="L19" s="413"/>
+      <c r="B19" s="489"/>
+      <c r="C19" s="378"/>
+      <c r="D19" s="378"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
+      <c r="G19" s="378"/>
+      <c r="H19" s="378"/>
+      <c r="I19" s="378"/>
+      <c r="J19" s="378"/>
+      <c r="K19" s="378"/>
+      <c r="L19" s="378"/>
       <c r="M19" s="288"/>
     </row>
     <row r="20" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -5492,6 +5492,29 @@
     <row r="309" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B19:L19"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="B7:G7"/>
@@ -5508,29 +5531,6 @@
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="B5:C6"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D13:F13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -5557,65 +5557,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="13.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="408"/>
-      <c r="C1" s="409"/>
-      <c r="D1" s="409"/>
-      <c r="E1" s="409"/>
-      <c r="F1" s="409"/>
-      <c r="G1" s="409"/>
-      <c r="H1" s="409"/>
-      <c r="I1" s="409"/>
-      <c r="J1" s="409"/>
-      <c r="K1" s="409"/>
-      <c r="L1" s="409"/>
+      <c r="B1" s="369"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+      <c r="E1" s="370"/>
+      <c r="F1" s="370"/>
+      <c r="G1" s="370"/>
+      <c r="H1" s="370"/>
+      <c r="I1" s="370"/>
+      <c r="J1" s="370"/>
+      <c r="K1" s="370"/>
+      <c r="L1" s="370"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="438" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="338"/>
+      <c r="B2" s="435" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="372"/>
+      <c r="D2" s="372"/>
+      <c r="E2" s="372"/>
+      <c r="F2" s="372"/>
+      <c r="G2" s="372"/>
+      <c r="H2" s="372"/>
+      <c r="I2" s="372"/>
+      <c r="J2" s="372"/>
+      <c r="K2" s="372"/>
+      <c r="L2" s="373"/>
       <c r="M2" s="282"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="344" t="s">
+      <c r="B3" s="426" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339"/>
-      <c r="E3" s="339"/>
-      <c r="F3" s="339"/>
-      <c r="G3" s="339"/>
-      <c r="H3" s="339"/>
-      <c r="I3" s="339"/>
-      <c r="J3" s="339"/>
-      <c r="K3" s="339"/>
-      <c r="L3" s="340"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
+      <c r="L3" s="375"/>
       <c r="M3" s="282"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="345" t="s">
+      <c r="B4" s="432" t="s">
         <v>367</v>
       </c>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="343"/>
+      <c r="C4" s="368"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="368"/>
+      <c r="F4" s="368"/>
+      <c r="G4" s="368"/>
+      <c r="H4" s="368"/>
+      <c r="I4" s="356"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -5625,36 +5625,36 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="476" t="s">
+      <c r="B5" s="487" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="338"/>
-      <c r="D5" s="475" t="str">
+      <c r="C5" s="373"/>
+      <c r="D5" s="474" t="str">
         <f>'QUADRO I'!D5:O6</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="338"/>
-      <c r="J5" s="449" t="s">
+      <c r="E5" s="372"/>
+      <c r="F5" s="372"/>
+      <c r="G5" s="372"/>
+      <c r="H5" s="372"/>
+      <c r="I5" s="373"/>
+      <c r="J5" s="429" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="342"/>
-      <c r="L5" s="343"/>
+      <c r="K5" s="368"/>
+      <c r="L5" s="356"/>
       <c r="M5" s="213"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="340"/>
-      <c r="D6" s="351"/>
-      <c r="E6" s="339"/>
-      <c r="F6" s="339"/>
-      <c r="G6" s="339"/>
-      <c r="H6" s="339"/>
-      <c r="I6" s="340"/>
+      <c r="B6" s="374"/>
+      <c r="C6" s="375"/>
+      <c r="D6" s="374"/>
+      <c r="E6" s="364"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="364"/>
+      <c r="I6" s="375"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -5666,21 +5666,21 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="345" t="s">
+      <c r="B7" s="432" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="342"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
-      <c r="F7" s="342"/>
-      <c r="G7" s="343"/>
-      <c r="H7" s="345" t="s">
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
+      <c r="E7" s="368"/>
+      <c r="F7" s="368"/>
+      <c r="G7" s="356"/>
+      <c r="H7" s="432" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="342"/>
-      <c r="J7" s="342"/>
-      <c r="K7" s="342"/>
-      <c r="L7" s="343"/>
+      <c r="I7" s="368"/>
+      <c r="J7" s="368"/>
+      <c r="K7" s="368"/>
+      <c r="L7" s="356"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -5688,14 +5688,14 @@
       <c r="B8" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="500" t="str">
+      <c r="C8" s="501" t="str">
         <f>'QUADRO VII'!C8</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="D8" s="337"/>
-      <c r="E8" s="337"/>
-      <c r="F8" s="337"/>
-      <c r="G8" s="338"/>
+      <c r="D8" s="372"/>
+      <c r="E8" s="372"/>
+      <c r="F8" s="372"/>
+      <c r="G8" s="373"/>
       <c r="H8" s="19" t="s">
         <v>9</v>
       </c>
@@ -5747,11 +5747,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="462" t="str">
+      <c r="J10" s="440" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="339"/>
+      <c r="K10" s="364"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -5760,24 +5760,24 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="453" t="s">
+      <c r="B11" s="445" t="s">
         <v>352</v>
       </c>
-      <c r="C11" s="343"/>
-      <c r="D11" s="453" t="s">
+      <c r="C11" s="356"/>
+      <c r="D11" s="445" t="s">
         <v>353</v>
       </c>
-      <c r="E11" s="342"/>
-      <c r="F11" s="343"/>
-      <c r="G11" s="453" t="s">
+      <c r="E11" s="368"/>
+      <c r="F11" s="356"/>
+      <c r="G11" s="445" t="s">
         <v>354</v>
       </c>
-      <c r="H11" s="342"/>
-      <c r="I11" s="343"/>
-      <c r="J11" s="453" t="s">
+      <c r="H11" s="368"/>
+      <c r="I11" s="356"/>
+      <c r="J11" s="445" t="s">
         <v>355</v>
       </c>
-      <c r="K11" s="343"/>
+      <c r="K11" s="356"/>
       <c r="L11" s="306" t="s">
         <v>356</v>
       </c>
@@ -5785,24 +5785,24 @@
     </row>
     <row r="12" spans="1:13" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="285"/>
-      <c r="B12" s="450" t="s">
+      <c r="B12" s="441" t="s">
         <v>368</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="450" t="s">
+      <c r="C12" s="373"/>
+      <c r="D12" s="441" t="s">
         <v>369</v>
       </c>
-      <c r="E12" s="337"/>
-      <c r="F12" s="338"/>
-      <c r="G12" s="450" t="s">
+      <c r="E12" s="372"/>
+      <c r="F12" s="373"/>
+      <c r="G12" s="441" t="s">
         <v>370</v>
       </c>
-      <c r="H12" s="337"/>
-      <c r="I12" s="338"/>
-      <c r="J12" s="450" t="s">
+      <c r="H12" s="372"/>
+      <c r="I12" s="373"/>
+      <c r="J12" s="441" t="s">
         <v>371</v>
       </c>
-      <c r="K12" s="338"/>
+      <c r="K12" s="373"/>
       <c r="L12" s="307"/>
       <c r="M12" s="286"/>
     </row>
@@ -5811,21 +5811,21 @@
       <c r="B13" s="498" t="s">
         <v>372</v>
       </c>
-      <c r="C13" s="405"/>
+      <c r="C13" s="381"/>
       <c r="D13" s="498" t="s">
         <v>369</v>
       </c>
       <c r="E13" s="499"/>
-      <c r="F13" s="405"/>
+      <c r="F13" s="381"/>
       <c r="G13" s="498" t="s">
         <v>370</v>
       </c>
       <c r="H13" s="499"/>
-      <c r="I13" s="405"/>
+      <c r="I13" s="381"/>
       <c r="J13" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K13" s="405"/>
+      <c r="K13" s="381"/>
       <c r="L13" s="280"/>
       <c r="M13" s="286"/>
     </row>
@@ -5834,21 +5834,21 @@
       <c r="B14" s="498" t="s">
         <v>373</v>
       </c>
-      <c r="C14" s="405"/>
+      <c r="C14" s="381"/>
       <c r="D14" s="498" t="s">
         <v>369</v>
       </c>
       <c r="E14" s="499"/>
-      <c r="F14" s="405"/>
+      <c r="F14" s="381"/>
       <c r="G14" s="498" t="s">
         <v>369</v>
       </c>
       <c r="H14" s="499"/>
-      <c r="I14" s="405"/>
+      <c r="I14" s="381"/>
       <c r="J14" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K14" s="405"/>
+      <c r="K14" s="381"/>
       <c r="L14" s="280"/>
       <c r="M14" s="286"/>
     </row>
@@ -5857,21 +5857,21 @@
       <c r="B15" s="498" t="s">
         <v>374</v>
       </c>
-      <c r="C15" s="405"/>
+      <c r="C15" s="381"/>
       <c r="D15" s="498" t="s">
         <v>369</v>
       </c>
       <c r="E15" s="499"/>
-      <c r="F15" s="405"/>
+      <c r="F15" s="381"/>
       <c r="G15" s="498" t="s">
         <v>369</v>
       </c>
       <c r="H15" s="499"/>
-      <c r="I15" s="405"/>
+      <c r="I15" s="381"/>
       <c r="J15" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K15" s="405"/>
+      <c r="K15" s="381"/>
       <c r="L15" s="280"/>
       <c r="M15" s="286"/>
     </row>
@@ -5880,21 +5880,21 @@
       <c r="B16" s="498" t="s">
         <v>375</v>
       </c>
-      <c r="C16" s="405"/>
+      <c r="C16" s="381"/>
       <c r="D16" s="498" t="s">
         <v>369</v>
       </c>
       <c r="E16" s="499"/>
-      <c r="F16" s="405"/>
+      <c r="F16" s="381"/>
       <c r="G16" s="498" t="s">
         <v>370</v>
       </c>
       <c r="H16" s="499"/>
-      <c r="I16" s="405"/>
+      <c r="I16" s="381"/>
       <c r="J16" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K16" s="405"/>
+      <c r="K16" s="381"/>
       <c r="L16" s="280"/>
       <c r="M16" s="286"/>
     </row>
@@ -5903,21 +5903,21 @@
       <c r="B17" s="498" t="s">
         <v>376</v>
       </c>
-      <c r="C17" s="405"/>
+      <c r="C17" s="381"/>
       <c r="D17" s="498" t="s">
         <v>369</v>
       </c>
       <c r="E17" s="499"/>
-      <c r="F17" s="405"/>
+      <c r="F17" s="381"/>
       <c r="G17" s="498" t="s">
         <v>369</v>
       </c>
       <c r="H17" s="499"/>
-      <c r="I17" s="405"/>
+      <c r="I17" s="381"/>
       <c r="J17" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K17" s="405"/>
+      <c r="K17" s="381"/>
       <c r="L17" s="280"/>
       <c r="M17" s="286"/>
     </row>
@@ -5926,21 +5926,21 @@
       <c r="B18" s="498" t="s">
         <v>377</v>
       </c>
-      <c r="C18" s="405"/>
+      <c r="C18" s="381"/>
       <c r="D18" s="498" t="s">
         <v>378</v>
       </c>
       <c r="E18" s="499"/>
-      <c r="F18" s="405"/>
+      <c r="F18" s="381"/>
       <c r="G18" s="498" t="s">
         <v>369</v>
       </c>
       <c r="H18" s="499"/>
-      <c r="I18" s="405"/>
+      <c r="I18" s="381"/>
       <c r="J18" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K18" s="405"/>
+      <c r="K18" s="381"/>
       <c r="L18" s="280"/>
       <c r="M18" s="286"/>
     </row>
@@ -6096,22 +6096,22 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="285"/>
-      <c r="B29" s="501"/>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
-      <c r="G29" s="337"/>
-      <c r="H29" s="337"/>
-      <c r="I29" s="337"/>
-      <c r="J29" s="337"/>
-      <c r="K29" s="337"/>
-      <c r="L29" s="338"/>
+      <c r="B29" s="500"/>
+      <c r="C29" s="372"/>
+      <c r="D29" s="372"/>
+      <c r="E29" s="372"/>
+      <c r="F29" s="372"/>
+      <c r="G29" s="372"/>
+      <c r="H29" s="372"/>
+      <c r="I29" s="372"/>
+      <c r="J29" s="372"/>
+      <c r="K29" s="372"/>
+      <c r="L29" s="373"/>
       <c r="M29" s="286"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="285"/>
-      <c r="B30" s="429"/>
+      <c r="B30" s="422"/>
       <c r="C30" s="499"/>
       <c r="D30" s="499"/>
       <c r="E30" s="499"/>
@@ -6121,12 +6121,12 @@
       <c r="I30" s="499"/>
       <c r="J30" s="499"/>
       <c r="K30" s="499"/>
-      <c r="L30" s="405"/>
+      <c r="L30" s="381"/>
       <c r="M30" s="286"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="285"/>
-      <c r="B31" s="429"/>
+      <c r="B31" s="422"/>
       <c r="C31" s="499"/>
       <c r="D31" s="499"/>
       <c r="E31" s="499"/>
@@ -6136,42 +6136,71 @@
       <c r="I31" s="499"/>
       <c r="J31" s="499"/>
       <c r="K31" s="499"/>
-      <c r="L31" s="405"/>
+      <c r="L31" s="381"/>
       <c r="M31" s="286"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="285"/>
-      <c r="B32" s="351"/>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
-      <c r="G32" s="339"/>
-      <c r="H32" s="339"/>
-      <c r="I32" s="339"/>
-      <c r="J32" s="339"/>
-      <c r="K32" s="339"/>
-      <c r="L32" s="340"/>
+      <c r="B32" s="374"/>
+      <c r="C32" s="364"/>
+      <c r="D32" s="364"/>
+      <c r="E32" s="364"/>
+      <c r="F32" s="364"/>
+      <c r="G32" s="364"/>
+      <c r="H32" s="364"/>
+      <c r="I32" s="364"/>
+      <c r="J32" s="364"/>
+      <c r="K32" s="364"/>
+      <c r="L32" s="375"/>
       <c r="M32" s="286"/>
     </row>
     <row r="33" spans="1:13" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="287"/>
-      <c r="B33" s="496"/>
-      <c r="C33" s="413"/>
-      <c r="D33" s="413"/>
-      <c r="E33" s="413"/>
-      <c r="F33" s="413"/>
-      <c r="G33" s="413"/>
-      <c r="H33" s="413"/>
-      <c r="I33" s="413"/>
-      <c r="J33" s="413"/>
-      <c r="K33" s="413"/>
-      <c r="L33" s="413"/>
+      <c r="B33" s="489"/>
+      <c r="C33" s="378"/>
+      <c r="D33" s="378"/>
+      <c r="E33" s="378"/>
+      <c r="F33" s="378"/>
+      <c r="G33" s="378"/>
+      <c r="H33" s="378"/>
+      <c r="I33" s="378"/>
+      <c r="J33" s="378"/>
+      <c r="K33" s="378"/>
+      <c r="L33" s="378"/>
       <c r="M33" s="288"/>
     </row>
     <row r="34" spans="1:13" ht="13.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="B33:L33"/>
     <mergeCell ref="J18:K18"/>
     <mergeCell ref="G17:I17"/>
@@ -6188,35 +6217,6 @@
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="G13:I13"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -6245,32 +6245,32 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="408"/>
-      <c r="C1" s="409"/>
-      <c r="D1" s="409"/>
-      <c r="E1" s="409"/>
-      <c r="F1" s="409"/>
-      <c r="G1" s="409"/>
-      <c r="H1" s="409"/>
-      <c r="I1" s="409"/>
-      <c r="J1" s="409"/>
-      <c r="K1" s="409"/>
-      <c r="L1" s="409"/>
+      <c r="B1" s="369"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+      <c r="E1" s="370"/>
+      <c r="F1" s="370"/>
+      <c r="G1" s="370"/>
+      <c r="H1" s="370"/>
+      <c r="I1" s="370"/>
+      <c r="J1" s="370"/>
+      <c r="K1" s="370"/>
+      <c r="L1" s="370"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="410" t="s">
+      <c r="B2" s="371" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="338"/>
+      <c r="C2" s="372"/>
+      <c r="D2" s="372"/>
+      <c r="E2" s="372"/>
+      <c r="F2" s="372"/>
+      <c r="G2" s="372"/>
+      <c r="H2" s="372"/>
+      <c r="I2" s="372"/>
+      <c r="J2" s="373"/>
       <c r="K2" s="152" t="s">
         <v>58</v>
       </c>
@@ -6281,17 +6281,17 @@
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="351"/>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339"/>
-      <c r="E3" s="339"/>
-      <c r="F3" s="339"/>
-      <c r="G3" s="339"/>
-      <c r="H3" s="339"/>
-      <c r="I3" s="339"/>
-      <c r="J3" s="340"/>
-      <c r="K3" s="422"/>
-      <c r="L3" s="343"/>
+      <c r="B3" s="374"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="375"/>
+      <c r="K3" s="355"/>
+      <c r="L3" s="356"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6299,18 +6299,18 @@
       <c r="B4" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="395" t="s">
+      <c r="C4" s="367" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="342"/>
-      <c r="J4" s="342"/>
-      <c r="K4" s="342"/>
-      <c r="L4" s="343"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="368"/>
+      <c r="F4" s="368"/>
+      <c r="G4" s="368"/>
+      <c r="H4" s="368"/>
+      <c r="I4" s="368"/>
+      <c r="J4" s="368"/>
+      <c r="K4" s="368"/>
+      <c r="L4" s="356"/>
       <c r="M4" s="202"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6319,19 +6319,19 @@
       <c r="C5" s="140" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="399" t="s">
+      <c r="D5" s="362" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="391"/>
-      <c r="F5" s="418" t="s">
+      <c r="E5" s="358"/>
+      <c r="F5" s="357" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="391"/>
-      <c r="H5" s="391"/>
-      <c r="I5" s="391"/>
-      <c r="J5" s="391"/>
-      <c r="K5" s="391"/>
-      <c r="L5" s="392"/>
+      <c r="G5" s="358"/>
+      <c r="H5" s="358"/>
+      <c r="I5" s="358"/>
+      <c r="J5" s="358"/>
+      <c r="K5" s="358"/>
+      <c r="L5" s="359"/>
       <c r="M5" s="202"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6340,19 +6340,19 @@
       <c r="C6" s="141" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="388" t="s">
+      <c r="D6" s="360" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="381"/>
-      <c r="F6" s="411" t="s">
+      <c r="E6" s="361"/>
+      <c r="F6" s="376" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="381"/>
-      <c r="H6" s="381"/>
-      <c r="I6" s="381"/>
-      <c r="J6" s="381"/>
-      <c r="K6" s="381"/>
-      <c r="L6" s="382"/>
+      <c r="G6" s="361"/>
+      <c r="H6" s="361"/>
+      <c r="I6" s="361"/>
+      <c r="J6" s="361"/>
+      <c r="K6" s="361"/>
+      <c r="L6" s="366"/>
       <c r="M6" s="202"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6361,17 +6361,17 @@
       <c r="C7" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="416" t="s">
+      <c r="D7" s="383" t="s">
         <v>66</v>
       </c>
       <c r="E7" s="384"/>
-      <c r="F7" s="383"/>
+      <c r="F7" s="398"/>
       <c r="G7" s="384"/>
       <c r="H7" s="384"/>
       <c r="I7" s="384"/>
       <c r="J7" s="384"/>
       <c r="K7" s="384"/>
-      <c r="L7" s="385"/>
+      <c r="L7" s="399"/>
       <c r="M7" s="202"/>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6380,13 +6380,13 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="339"/>
-      <c r="G8" s="339"/>
-      <c r="H8" s="339"/>
-      <c r="I8" s="339"/>
-      <c r="J8" s="339"/>
-      <c r="K8" s="339"/>
-      <c r="L8" s="340"/>
+      <c r="F8" s="364"/>
+      <c r="G8" s="364"/>
+      <c r="H8" s="364"/>
+      <c r="I8" s="364"/>
+      <c r="J8" s="364"/>
+      <c r="K8" s="364"/>
+      <c r="L8" s="375"/>
       <c r="M8" s="202"/>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6394,18 +6394,18 @@
       <c r="B9" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="395" t="s">
+      <c r="C9" s="367" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="342"/>
-      <c r="E9" s="342"/>
-      <c r="F9" s="342"/>
-      <c r="G9" s="342"/>
-      <c r="H9" s="342"/>
-      <c r="I9" s="342"/>
-      <c r="J9" s="342"/>
-      <c r="K9" s="342"/>
-      <c r="L9" s="343"/>
+      <c r="D9" s="368"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
+      <c r="G9" s="368"/>
+      <c r="H9" s="368"/>
+      <c r="I9" s="368"/>
+      <c r="J9" s="368"/>
+      <c r="K9" s="368"/>
+      <c r="L9" s="356"/>
       <c r="M9" s="202"/>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6414,20 +6414,20 @@
       <c r="C10" s="140" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="399" t="s">
+      <c r="D10" s="362" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="391"/>
-      <c r="F10" s="391"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="G10" s="390" t="str">
         <f>CAPA!A14</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="H10" s="391"/>
-      <c r="I10" s="391"/>
-      <c r="J10" s="391"/>
-      <c r="K10" s="391"/>
-      <c r="L10" s="392"/>
+      <c r="H10" s="358"/>
+      <c r="I10" s="358"/>
+      <c r="J10" s="358"/>
+      <c r="K10" s="358"/>
+      <c r="L10" s="359"/>
       <c r="M10" s="202"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6436,20 +6436,20 @@
       <c r="C11" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="388" t="s">
+      <c r="D11" s="360" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="381"/>
-      <c r="F11" s="381"/>
-      <c r="G11" s="401" t="str">
+      <c r="E11" s="361"/>
+      <c r="F11" s="361"/>
+      <c r="G11" s="365" t="str">
         <f>CAPA!A15</f>
         <v>{CREA}</v>
       </c>
-      <c r="H11" s="381"/>
-      <c r="I11" s="381"/>
-      <c r="J11" s="381"/>
-      <c r="K11" s="381"/>
-      <c r="L11" s="382"/>
+      <c r="H11" s="361"/>
+      <c r="I11" s="361"/>
+      <c r="J11" s="361"/>
+      <c r="K11" s="361"/>
+      <c r="L11" s="366"/>
       <c r="M11" s="202"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6458,26 +6458,26 @@
       <c r="C12" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="388" t="s">
+      <c r="D12" s="360" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="381"/>
-      <c r="F12" s="381"/>
-      <c r="G12" s="401"/>
-      <c r="H12" s="381"/>
-      <c r="I12" s="381"/>
-      <c r="J12" s="381"/>
-      <c r="K12" s="381"/>
-      <c r="L12" s="382"/>
+      <c r="E12" s="361"/>
+      <c r="F12" s="361"/>
+      <c r="G12" s="365"/>
+      <c r="H12" s="361"/>
+      <c r="I12" s="361"/>
+      <c r="J12" s="361"/>
+      <c r="K12" s="361"/>
+      <c r="L12" s="366"/>
       <c r="M12" s="202"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="200"/>
       <c r="B13" s="402"/>
-      <c r="C13" s="415" t="s">
+      <c r="C13" s="363" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="415" t="s">
+      <c r="D13" s="363" t="s">
         <v>66</v>
       </c>
       <c r="E13" s="384"/>
@@ -6492,11 +6492,11 @@
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="200"/>
-      <c r="B14" s="351"/>
-      <c r="C14" s="339"/>
-      <c r="D14" s="339"/>
-      <c r="E14" s="339"/>
-      <c r="F14" s="339"/>
+      <c r="B14" s="374"/>
+      <c r="C14" s="364"/>
+      <c r="D14" s="364"/>
+      <c r="E14" s="364"/>
+      <c r="F14" s="364"/>
       <c r="G14" s="188"/>
       <c r="H14" s="188"/>
       <c r="I14" s="188"/>
@@ -6510,18 +6510,18 @@
       <c r="B15" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="395" t="s">
+      <c r="C15" s="367" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="342"/>
-      <c r="E15" s="342"/>
-      <c r="F15" s="342"/>
-      <c r="G15" s="342"/>
-      <c r="H15" s="342"/>
-      <c r="I15" s="342"/>
-      <c r="J15" s="342"/>
-      <c r="K15" s="342"/>
-      <c r="L15" s="343"/>
+      <c r="D15" s="368"/>
+      <c r="E15" s="368"/>
+      <c r="F15" s="368"/>
+      <c r="G15" s="368"/>
+      <c r="H15" s="368"/>
+      <c r="I15" s="368"/>
+      <c r="J15" s="368"/>
+      <c r="K15" s="368"/>
+      <c r="L15" s="356"/>
       <c r="M15" s="202"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6530,19 +6530,19 @@
       <c r="C16" s="140" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="399" t="s">
+      <c r="D16" s="362" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="391"/>
-      <c r="F16" s="391"/>
-      <c r="G16" s="417" t="s">
+      <c r="E16" s="358"/>
+      <c r="F16" s="358"/>
+      <c r="G16" s="385" t="s">
         <v>80</v>
       </c>
-      <c r="H16" s="337"/>
-      <c r="I16" s="337"/>
-      <c r="J16" s="337"/>
-      <c r="K16" s="337"/>
-      <c r="L16" s="338"/>
+      <c r="H16" s="372"/>
+      <c r="I16" s="372"/>
+      <c r="J16" s="372"/>
+      <c r="K16" s="372"/>
+      <c r="L16" s="373"/>
       <c r="M16" s="202"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6551,20 +6551,20 @@
       <c r="C17" s="141" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="388" t="s">
+      <c r="D17" s="360" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="381"/>
-      <c r="F17" s="381"/>
+      <c r="E17" s="361"/>
+      <c r="F17" s="361"/>
       <c r="G17" s="404" t="str">
         <f>CAPA!C3</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="H17" s="348"/>
-      <c r="I17" s="348"/>
-      <c r="J17" s="348"/>
-      <c r="K17" s="348"/>
-      <c r="L17" s="405"/>
+      <c r="H17" s="380"/>
+      <c r="I17" s="380"/>
+      <c r="J17" s="380"/>
+      <c r="K17" s="380"/>
+      <c r="L17" s="381"/>
       <c r="M17" s="202"/>
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6574,12 +6574,12 @@
       <c r="D18" s="310"/>
       <c r="E18" s="310"/>
       <c r="F18" s="310"/>
-      <c r="G18" s="387"/>
-      <c r="H18" s="387"/>
-      <c r="I18" s="387"/>
-      <c r="J18" s="387"/>
-      <c r="K18" s="387"/>
-      <c r="L18" s="406"/>
+      <c r="G18" s="391"/>
+      <c r="H18" s="391"/>
+      <c r="I18" s="391"/>
+      <c r="J18" s="391"/>
+      <c r="K18" s="391"/>
+      <c r="L18" s="405"/>
       <c r="M18" s="202"/>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6588,18 +6588,18 @@
       <c r="C19" s="141" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="388" t="s">
+      <c r="D19" s="360" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="381"/>
-      <c r="F19" s="381"/>
+      <c r="E19" s="361"/>
+      <c r="F19" s="361"/>
       <c r="G19" s="403" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="397"/>
-      <c r="I19" s="397"/>
-      <c r="J19" s="397"/>
-      <c r="K19" s="397"/>
+      <c r="H19" s="382"/>
+      <c r="I19" s="382"/>
+      <c r="J19" s="382"/>
+      <c r="K19" s="382"/>
       <c r="L19" s="207" t="s">
         <v>86</v>
       </c>
@@ -6607,11 +6607,11 @@
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="420"/>
-      <c r="C20" s="388" t="s">
+      <c r="B20" s="387"/>
+      <c r="C20" s="360" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="386" t="s">
+      <c r="D20" s="400" t="s">
         <v>88</v>
       </c>
       <c r="E20" s="384"/>
@@ -6634,11 +6634,11 @@
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="200"/>
-      <c r="B21" s="421"/>
-      <c r="C21" s="387"/>
-      <c r="D21" s="387"/>
-      <c r="E21" s="387"/>
-      <c r="F21" s="387"/>
+      <c r="B21" s="388"/>
+      <c r="C21" s="391"/>
+      <c r="D21" s="391"/>
+      <c r="E21" s="391"/>
+      <c r="F21" s="391"/>
       <c r="G21" s="72" t="s">
         <v>93</v>
       </c>
@@ -6659,19 +6659,19 @@
       <c r="C22" s="141" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="388" t="s">
+      <c r="D22" s="360" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="381"/>
-      <c r="F22" s="381"/>
-      <c r="G22" s="418" t="s">
+      <c r="E22" s="361"/>
+      <c r="F22" s="361"/>
+      <c r="G22" s="357" t="s">
         <v>98</v>
       </c>
-      <c r="H22" s="391"/>
-      <c r="I22" s="391"/>
-      <c r="J22" s="391"/>
-      <c r="K22" s="391"/>
-      <c r="L22" s="392"/>
+      <c r="H22" s="358"/>
+      <c r="I22" s="358"/>
+      <c r="J22" s="358"/>
+      <c r="K22" s="358"/>
+      <c r="L22" s="359"/>
       <c r="M22" s="202"/>
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6680,19 +6680,19 @@
       <c r="C23" s="141" t="s">
         <v>99</v>
       </c>
-      <c r="D23" s="388" t="s">
+      <c r="D23" s="360" t="s">
         <v>100</v>
       </c>
-      <c r="E23" s="381"/>
-      <c r="F23" s="381"/>
-      <c r="G23" s="401" t="s">
+      <c r="E23" s="361"/>
+      <c r="F23" s="361"/>
+      <c r="G23" s="365" t="s">
         <v>101</v>
       </c>
-      <c r="H23" s="381"/>
-      <c r="I23" s="381"/>
-      <c r="J23" s="381"/>
-      <c r="K23" s="381"/>
-      <c r="L23" s="382"/>
+      <c r="H23" s="361"/>
+      <c r="I23" s="361"/>
+      <c r="J23" s="361"/>
+      <c r="K23" s="361"/>
+      <c r="L23" s="366"/>
       <c r="M23" s="202"/>
     </row>
     <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6701,19 +6701,19 @@
       <c r="C24" s="141" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="388" t="s">
+      <c r="D24" s="360" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="381"/>
-      <c r="F24" s="381"/>
-      <c r="G24" s="401" t="s">
+      <c r="E24" s="361"/>
+      <c r="F24" s="361"/>
+      <c r="G24" s="365" t="s">
         <v>104</v>
       </c>
-      <c r="H24" s="381"/>
-      <c r="I24" s="381"/>
-      <c r="J24" s="381"/>
-      <c r="K24" s="381"/>
-      <c r="L24" s="382"/>
+      <c r="H24" s="361"/>
+      <c r="I24" s="361"/>
+      <c r="J24" s="361"/>
+      <c r="K24" s="361"/>
+      <c r="L24" s="366"/>
       <c r="M24" s="202"/>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6722,17 +6722,17 @@
       <c r="C25" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="D25" s="407" t="s">
+      <c r="D25" s="406" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="381"/>
-      <c r="F25" s="381"/>
-      <c r="G25" s="381"/>
-      <c r="H25" s="381"/>
-      <c r="I25" s="381"/>
-      <c r="J25" s="381"/>
-      <c r="K25" s="381"/>
-      <c r="L25" s="382"/>
+      <c r="E25" s="361"/>
+      <c r="F25" s="361"/>
+      <c r="G25" s="361"/>
+      <c r="H25" s="361"/>
+      <c r="I25" s="361"/>
+      <c r="J25" s="361"/>
+      <c r="K25" s="361"/>
+      <c r="L25" s="366"/>
       <c r="M25" s="202"/>
     </row>
     <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6742,18 +6742,18 @@
       <c r="D26" s="141" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="388" t="s">
+      <c r="E26" s="360" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="381"/>
-      <c r="G26" s="381"/>
-      <c r="H26" s="381"/>
-      <c r="I26" s="401" t="s">
+      <c r="F26" s="361"/>
+      <c r="G26" s="361"/>
+      <c r="H26" s="361"/>
+      <c r="I26" s="365" t="s">
         <v>109</v>
       </c>
-      <c r="J26" s="381"/>
-      <c r="K26" s="381"/>
-      <c r="L26" s="382"/>
+      <c r="J26" s="361"/>
+      <c r="K26" s="361"/>
+      <c r="L26" s="366"/>
       <c r="M26" s="202"/>
     </row>
     <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6763,16 +6763,16 @@
       <c r="D27" s="141" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="388" t="s">
+      <c r="E27" s="360" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="381"/>
-      <c r="G27" s="381"/>
-      <c r="H27" s="381"/>
-      <c r="I27" s="380"/>
-      <c r="J27" s="381"/>
-      <c r="K27" s="381"/>
-      <c r="L27" s="382"/>
+      <c r="F27" s="361"/>
+      <c r="G27" s="361"/>
+      <c r="H27" s="361"/>
+      <c r="I27" s="397"/>
+      <c r="J27" s="361"/>
+      <c r="K27" s="361"/>
+      <c r="L27" s="366"/>
       <c r="M27" s="202"/>
     </row>
     <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6782,12 +6782,12 @@
       <c r="D28" s="141" t="s">
         <v>112</v>
       </c>
-      <c r="E28" s="388" t="s">
+      <c r="E28" s="360" t="s">
         <v>113</v>
       </c>
-      <c r="F28" s="381"/>
-      <c r="G28" s="381"/>
-      <c r="H28" s="381"/>
+      <c r="F28" s="361"/>
+      <c r="G28" s="361"/>
+      <c r="H28" s="361"/>
       <c r="I28" s="186"/>
       <c r="J28" s="141"/>
       <c r="K28" s="141"/>
@@ -6800,17 +6800,17 @@
       <c r="C29" s="141" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="388" t="s">
+      <c r="D29" s="360" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="381"/>
-      <c r="F29" s="381"/>
-      <c r="G29" s="381"/>
-      <c r="H29" s="393">
+      <c r="E29" s="361"/>
+      <c r="F29" s="361"/>
+      <c r="G29" s="361"/>
+      <c r="H29" s="392">
         <f>CAPA!D4</f>
         <v>0</v>
       </c>
-      <c r="I29" s="381"/>
+      <c r="I29" s="361"/>
       <c r="J29" s="308" t="s">
         <v>40</v>
       </c>
@@ -6824,17 +6824,17 @@
       <c r="C30" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="388" t="s">
+      <c r="D30" s="360" t="s">
         <v>117</v>
       </c>
-      <c r="E30" s="381"/>
-      <c r="F30" s="381"/>
-      <c r="G30" s="381"/>
-      <c r="H30" s="380"/>
-      <c r="I30" s="381"/>
-      <c r="J30" s="381"/>
-      <c r="K30" s="381"/>
-      <c r="L30" s="382"/>
+      <c r="E30" s="361"/>
+      <c r="F30" s="361"/>
+      <c r="G30" s="361"/>
+      <c r="H30" s="397"/>
+      <c r="I30" s="361"/>
+      <c r="J30" s="361"/>
+      <c r="K30" s="361"/>
+      <c r="L30" s="366"/>
       <c r="M30" s="202"/>
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6843,17 +6843,17 @@
       <c r="C31" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="415" t="s">
+      <c r="D31" s="363" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="397"/>
-      <c r="F31" s="397"/>
-      <c r="G31" s="397"/>
-      <c r="H31" s="396"/>
-      <c r="I31" s="397"/>
-      <c r="J31" s="397"/>
-      <c r="K31" s="397"/>
-      <c r="L31" s="398"/>
+      <c r="E31" s="382"/>
+      <c r="F31" s="382"/>
+      <c r="G31" s="382"/>
+      <c r="H31" s="394"/>
+      <c r="I31" s="382"/>
+      <c r="J31" s="382"/>
+      <c r="K31" s="382"/>
+      <c r="L31" s="395"/>
       <c r="M31" s="202"/>
     </row>
     <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6861,73 +6861,73 @@
       <c r="B32" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="C32" s="395" t="s">
+      <c r="C32" s="367" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="342"/>
-      <c r="E32" s="342"/>
-      <c r="F32" s="342"/>
-      <c r="G32" s="342"/>
-      <c r="H32" s="342"/>
-      <c r="I32" s="342"/>
-      <c r="J32" s="342"/>
-      <c r="K32" s="342"/>
-      <c r="L32" s="343"/>
+      <c r="D32" s="368"/>
+      <c r="E32" s="368"/>
+      <c r="F32" s="368"/>
+      <c r="G32" s="368"/>
+      <c r="H32" s="368"/>
+      <c r="I32" s="368"/>
+      <c r="J32" s="368"/>
+      <c r="K32" s="368"/>
+      <c r="L32" s="356"/>
       <c r="M32" s="202"/>
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
-      <c r="B33" s="394" t="s">
+      <c r="B33" s="393" t="s">
         <v>122</v>
       </c>
-      <c r="C33" s="337"/>
-      <c r="D33" s="337"/>
-      <c r="E33" s="337"/>
+      <c r="C33" s="372"/>
+      <c r="D33" s="372"/>
+      <c r="E33" s="372"/>
       <c r="F33" s="72">
         <v>10</v>
       </c>
-      <c r="G33" s="400" t="s">
+      <c r="G33" s="401" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="337"/>
-      <c r="I33" s="337"/>
-      <c r="J33" s="337"/>
-      <c r="K33" s="337"/>
-      <c r="L33" s="338"/>
+      <c r="H33" s="372"/>
+      <c r="I33" s="372"/>
+      <c r="J33" s="372"/>
+      <c r="K33" s="372"/>
+      <c r="L33" s="373"/>
       <c r="M33" s="202"/>
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="200"/>
-      <c r="B34" s="419" t="s">
+      <c r="B34" s="386" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="348"/>
-      <c r="D34" s="348"/>
-      <c r="E34" s="348"/>
-      <c r="F34" s="348"/>
-      <c r="G34" s="348"/>
-      <c r="H34" s="348"/>
-      <c r="I34" s="348"/>
-      <c r="J34" s="348"/>
-      <c r="K34" s="348"/>
-      <c r="L34" s="405"/>
+      <c r="C34" s="380"/>
+      <c r="D34" s="380"/>
+      <c r="E34" s="380"/>
+      <c r="F34" s="380"/>
+      <c r="G34" s="380"/>
+      <c r="H34" s="380"/>
+      <c r="I34" s="380"/>
+      <c r="J34" s="380"/>
+      <c r="K34" s="380"/>
+      <c r="L34" s="381"/>
       <c r="M34" s="202"/>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="200"/>
-      <c r="B35" s="379" t="s">
+      <c r="B35" s="396" t="s">
         <v>125</v>
       </c>
-      <c r="C35" s="339"/>
-      <c r="D35" s="339"/>
-      <c r="E35" s="339"/>
-      <c r="F35" s="339"/>
-      <c r="G35" s="339"/>
-      <c r="H35" s="339"/>
-      <c r="I35" s="339"/>
-      <c r="J35" s="339"/>
-      <c r="K35" s="339"/>
-      <c r="L35" s="340"/>
+      <c r="C35" s="364"/>
+      <c r="D35" s="364"/>
+      <c r="E35" s="364"/>
+      <c r="F35" s="364"/>
+      <c r="G35" s="364"/>
+      <c r="H35" s="364"/>
+      <c r="I35" s="364"/>
+      <c r="J35" s="364"/>
+      <c r="K35" s="364"/>
+      <c r="L35" s="375"/>
       <c r="M35" s="202"/>
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6935,18 +6935,18 @@
       <c r="B36" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="C36" s="395" t="s">
+      <c r="C36" s="367" t="s">
         <v>127</v>
       </c>
-      <c r="D36" s="342"/>
-      <c r="E36" s="342"/>
-      <c r="F36" s="342"/>
-      <c r="G36" s="342"/>
-      <c r="H36" s="342"/>
-      <c r="I36" s="342"/>
-      <c r="J36" s="342"/>
-      <c r="K36" s="342"/>
-      <c r="L36" s="343"/>
+      <c r="D36" s="368"/>
+      <c r="E36" s="368"/>
+      <c r="F36" s="368"/>
+      <c r="G36" s="368"/>
+      <c r="H36" s="368"/>
+      <c r="I36" s="368"/>
+      <c r="J36" s="368"/>
+      <c r="K36" s="368"/>
+      <c r="L36" s="356"/>
       <c r="M36" s="202"/>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6993,24 +6993,24 @@
       <c r="G41" s="389" t="s">
         <v>54</v>
       </c>
-      <c r="H41" s="348"/>
-      <c r="I41" s="348"/>
-      <c r="J41" s="348"/>
-      <c r="K41" s="348"/>
+      <c r="H41" s="380"/>
+      <c r="I41" s="380"/>
+      <c r="J41" s="380"/>
+      <c r="K41" s="380"/>
       <c r="L41" s="4"/>
       <c r="M41" s="202"/>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="200"/>
       <c r="B42" s="12"/>
-      <c r="G42" s="377" t="str">
+      <c r="G42" s="342" t="str">
         <f>F5</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="H42" s="348"/>
-      <c r="I42" s="348"/>
-      <c r="J42" s="348"/>
-      <c r="K42" s="348"/>
+      <c r="H42" s="380"/>
+      <c r="I42" s="380"/>
+      <c r="J42" s="380"/>
+      <c r="K42" s="380"/>
       <c r="L42" s="4"/>
       <c r="M42" s="202"/>
     </row>
@@ -7046,24 +7046,23 @@
       <c r="G47" s="389" t="s">
         <v>54</v>
       </c>
-      <c r="H47" s="348"/>
-      <c r="I47" s="348"/>
-      <c r="J47" s="348"/>
-      <c r="K47" s="348"/>
+      <c r="H47" s="380"/>
+      <c r="I47" s="380"/>
+      <c r="J47" s="380"/>
+      <c r="K47" s="380"/>
       <c r="L47" s="4"/>
       <c r="M47" s="202"/>
     </row>
     <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="200"/>
       <c r="B48" s="12"/>
-      <c r="G48" s="377" t="str">
-        <f>CAPA!A14</f>
-        <v>{RESPONSÁVEL TÉCNICO}</v>
-      </c>
-      <c r="H48" s="348"/>
-      <c r="I48" s="348"/>
-      <c r="J48" s="348"/>
-      <c r="K48" s="348"/>
+      <c r="G48" s="342" t="s">
+        <v>55</v>
+      </c>
+      <c r="H48" s="380"/>
+      <c r="I48" s="380"/>
+      <c r="J48" s="380"/>
+      <c r="K48" s="380"/>
       <c r="L48" s="4"/>
       <c r="M48" s="202"/>
     </row>
@@ -7081,80 +7080,99 @@
     </row>
     <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="200"/>
-      <c r="B51" s="414" t="s">
+      <c r="B51" s="379" t="s">
         <v>130</v>
       </c>
-      <c r="C51" s="348"/>
-      <c r="D51" s="348"/>
-      <c r="E51" s="348"/>
-      <c r="F51" s="348"/>
-      <c r="G51" s="348"/>
-      <c r="H51" s="348"/>
-      <c r="I51" s="348"/>
-      <c r="J51" s="348"/>
-      <c r="K51" s="348"/>
-      <c r="L51" s="405"/>
+      <c r="C51" s="380"/>
+      <c r="D51" s="380"/>
+      <c r="E51" s="380"/>
+      <c r="F51" s="380"/>
+      <c r="G51" s="380"/>
+      <c r="H51" s="380"/>
+      <c r="I51" s="380"/>
+      <c r="J51" s="380"/>
+      <c r="K51" s="380"/>
+      <c r="L51" s="381"/>
       <c r="M51" s="202"/>
     </row>
     <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="200"/>
-      <c r="B52" s="351"/>
-      <c r="C52" s="339"/>
-      <c r="D52" s="339"/>
-      <c r="E52" s="339"/>
-      <c r="F52" s="339"/>
-      <c r="G52" s="339"/>
-      <c r="H52" s="339"/>
-      <c r="I52" s="339"/>
-      <c r="J52" s="339"/>
-      <c r="K52" s="339"/>
-      <c r="L52" s="340"/>
+      <c r="B52" s="374"/>
+      <c r="C52" s="364"/>
+      <c r="D52" s="364"/>
+      <c r="E52" s="364"/>
+      <c r="F52" s="364"/>
+      <c r="G52" s="364"/>
+      <c r="H52" s="364"/>
+      <c r="I52" s="364"/>
+      <c r="J52" s="364"/>
+      <c r="K52" s="364"/>
+      <c r="L52" s="375"/>
       <c r="M52" s="202"/>
     </row>
     <row r="53" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="203"/>
-      <c r="B53" s="412"/>
-      <c r="C53" s="413"/>
-      <c r="D53" s="413"/>
-      <c r="E53" s="413"/>
-      <c r="F53" s="413"/>
-      <c r="G53" s="413"/>
-      <c r="H53" s="413"/>
-      <c r="I53" s="413"/>
-      <c r="J53" s="413"/>
-      <c r="K53" s="413"/>
-      <c r="L53" s="413"/>
+      <c r="B53" s="377"/>
+      <c r="C53" s="378"/>
+      <c r="D53" s="378"/>
+      <c r="E53" s="378"/>
+      <c r="F53" s="378"/>
+      <c r="G53" s="378"/>
+      <c r="H53" s="378"/>
+      <c r="I53" s="378"/>
+      <c r="J53" s="378"/>
+      <c r="K53" s="378"/>
+      <c r="L53" s="378"/>
       <c r="M53" s="204"/>
     </row>
     <row r="54" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
       <c r="B54" s="389"/>
-      <c r="C54" s="348"/>
-      <c r="D54" s="348"/>
-      <c r="E54" s="348"/>
-      <c r="F54" s="348"/>
-      <c r="G54" s="348"/>
-      <c r="H54" s="348"/>
-      <c r="I54" s="348"/>
-      <c r="J54" s="348"/>
-      <c r="K54" s="348"/>
-      <c r="L54" s="348"/>
+      <c r="C54" s="380"/>
+      <c r="D54" s="380"/>
+      <c r="E54" s="380"/>
+      <c r="F54" s="380"/>
+      <c r="G54" s="380"/>
+      <c r="H54" s="380"/>
+      <c r="I54" s="380"/>
+      <c r="J54" s="380"/>
+      <c r="K54" s="380"/>
+      <c r="L54" s="380"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="C9:L9"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B35:L35"/>
+    <mergeCell ref="H30:L30"/>
+    <mergeCell ref="F7:L8"/>
+    <mergeCell ref="D20:F21"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="G17:L18"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="H31:L31"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="G47:K47"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="C36:L36"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="B2:J3"/>
@@ -7171,38 +7189,19 @@
     <mergeCell ref="B34:L34"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="D13:F14"/>
-    <mergeCell ref="B54:L54"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="G42:K42"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="H31:L31"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G48:K48"/>
-    <mergeCell ref="G47:K47"/>
-    <mergeCell ref="G41:K41"/>
-    <mergeCell ref="C36:L36"/>
-    <mergeCell ref="B35:L35"/>
-    <mergeCell ref="H30:L30"/>
-    <mergeCell ref="F7:L8"/>
-    <mergeCell ref="D20:F21"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="G17:L18"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -7226,95 +7225,95 @@
   <sheetData>
     <row r="1" spans="1:30" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="210"/>
-      <c r="B1" s="435"/>
-      <c r="C1" s="334"/>
-      <c r="D1" s="334"/>
-      <c r="E1" s="334"/>
-      <c r="F1" s="334"/>
-      <c r="G1" s="334"/>
-      <c r="H1" s="334"/>
-      <c r="I1" s="334"/>
-      <c r="J1" s="334"/>
-      <c r="K1" s="334"/>
-      <c r="L1" s="334"/>
-      <c r="M1" s="334"/>
-      <c r="N1" s="334"/>
-      <c r="O1" s="334"/>
-      <c r="P1" s="334"/>
-      <c r="Q1" s="334"/>
-      <c r="R1" s="334"/>
-      <c r="S1" s="334"/>
-      <c r="T1" s="334"/>
+      <c r="B1" s="413"/>
+      <c r="C1" s="346"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
+      <c r="I1" s="346"/>
+      <c r="J1" s="346"/>
+      <c r="K1" s="346"/>
+      <c r="L1" s="346"/>
+      <c r="M1" s="346"/>
+      <c r="N1" s="346"/>
+      <c r="O1" s="346"/>
+      <c r="P1" s="346"/>
+      <c r="Q1" s="346"/>
+      <c r="R1" s="346"/>
+      <c r="S1" s="346"/>
+      <c r="T1" s="346"/>
       <c r="U1" s="211"/>
     </row>
     <row r="2" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="212"/>
-      <c r="B2" s="432" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="433"/>
-      <c r="D2" s="433"/>
-      <c r="E2" s="433"/>
-      <c r="F2" s="433"/>
-      <c r="G2" s="433"/>
-      <c r="H2" s="433"/>
-      <c r="I2" s="433"/>
-      <c r="J2" s="433"/>
-      <c r="K2" s="433"/>
-      <c r="L2" s="433"/>
-      <c r="M2" s="433"/>
-      <c r="N2" s="433"/>
-      <c r="O2" s="433"/>
-      <c r="P2" s="433"/>
-      <c r="Q2" s="433"/>
-      <c r="R2" s="433"/>
-      <c r="S2" s="433"/>
-      <c r="T2" s="433"/>
+      <c r="B2" s="407" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="408"/>
+      <c r="D2" s="408"/>
+      <c r="E2" s="408"/>
+      <c r="F2" s="408"/>
+      <c r="G2" s="408"/>
+      <c r="H2" s="408"/>
+      <c r="I2" s="408"/>
+      <c r="J2" s="408"/>
+      <c r="K2" s="408"/>
+      <c r="L2" s="408"/>
+      <c r="M2" s="408"/>
+      <c r="N2" s="408"/>
+      <c r="O2" s="408"/>
+      <c r="P2" s="408"/>
+      <c r="Q2" s="408"/>
+      <c r="R2" s="408"/>
+      <c r="S2" s="408"/>
+      <c r="T2" s="408"/>
       <c r="U2" s="213"/>
     </row>
     <row r="3" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="212"/>
-      <c r="B3" s="437" t="s">
+      <c r="B3" s="417" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339"/>
-      <c r="E3" s="339"/>
-      <c r="F3" s="339"/>
-      <c r="G3" s="339"/>
-      <c r="H3" s="339"/>
-      <c r="I3" s="339"/>
-      <c r="J3" s="339"/>
-      <c r="K3" s="339"/>
-      <c r="L3" s="339"/>
-      <c r="M3" s="339"/>
-      <c r="N3" s="339"/>
-      <c r="O3" s="339"/>
-      <c r="P3" s="339"/>
-      <c r="Q3" s="339"/>
-      <c r="R3" s="339"/>
-      <c r="S3" s="339"/>
-      <c r="T3" s="339"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
+      <c r="L3" s="364"/>
+      <c r="M3" s="364"/>
+      <c r="N3" s="364"/>
+      <c r="O3" s="364"/>
+      <c r="P3" s="364"/>
+      <c r="Q3" s="364"/>
+      <c r="R3" s="364"/>
+      <c r="S3" s="364"/>
+      <c r="T3" s="364"/>
       <c r="U3" s="213"/>
     </row>
     <row r="4" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="212"/>
-      <c r="B4" s="425" t="s">
+      <c r="B4" s="418" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="342"/>
-      <c r="J4" s="342"/>
-      <c r="K4" s="342"/>
-      <c r="L4" s="342"/>
-      <c r="M4" s="342"/>
-      <c r="N4" s="342"/>
-      <c r="O4" s="343"/>
+      <c r="C4" s="368"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="368"/>
+      <c r="F4" s="368"/>
+      <c r="G4" s="368"/>
+      <c r="H4" s="368"/>
+      <c r="I4" s="368"/>
+      <c r="J4" s="368"/>
+      <c r="K4" s="368"/>
+      <c r="L4" s="368"/>
+      <c r="M4" s="368"/>
+      <c r="N4" s="368"/>
+      <c r="O4" s="356"/>
       <c r="P4" s="259" t="s">
         <v>58</v>
       </c>
@@ -7329,50 +7328,50 @@
     </row>
     <row r="5" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="212"/>
-      <c r="B5" s="431" t="s">
+      <c r="B5" s="423" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="337"/>
-      <c r="D5" s="428" t="str">
+      <c r="C5" s="372"/>
+      <c r="D5" s="421" t="str">
         <f>CAPA!C3</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="337"/>
-      <c r="J5" s="337"/>
-      <c r="K5" s="337"/>
-      <c r="L5" s="337"/>
-      <c r="M5" s="337"/>
-      <c r="N5" s="337"/>
-      <c r="O5" s="338"/>
-      <c r="P5" s="349" t="s">
+      <c r="E5" s="372"/>
+      <c r="F5" s="372"/>
+      <c r="G5" s="372"/>
+      <c r="H5" s="372"/>
+      <c r="I5" s="372"/>
+      <c r="J5" s="372"/>
+      <c r="K5" s="372"/>
+      <c r="L5" s="372"/>
+      <c r="M5" s="372"/>
+      <c r="N5" s="372"/>
+      <c r="O5" s="373"/>
+      <c r="P5" s="415" t="s">
         <v>5</v>
       </c>
-      <c r="Q5" s="337"/>
-      <c r="R5" s="337"/>
-      <c r="S5" s="337"/>
-      <c r="T5" s="338"/>
+      <c r="Q5" s="372"/>
+      <c r="R5" s="372"/>
+      <c r="S5" s="372"/>
+      <c r="T5" s="373"/>
       <c r="U5" s="213"/>
     </row>
     <row r="6" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="212"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="339"/>
-      <c r="D6" s="339"/>
-      <c r="E6" s="339"/>
-      <c r="F6" s="339"/>
-      <c r="G6" s="339"/>
-      <c r="H6" s="339"/>
-      <c r="I6" s="339"/>
-      <c r="J6" s="339"/>
-      <c r="K6" s="339"/>
-      <c r="L6" s="339"/>
-      <c r="M6" s="339"/>
-      <c r="N6" s="339"/>
-      <c r="O6" s="340"/>
+      <c r="B6" s="374"/>
+      <c r="C6" s="364"/>
+      <c r="D6" s="364"/>
+      <c r="E6" s="364"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="364"/>
+      <c r="I6" s="364"/>
+      <c r="J6" s="364"/>
+      <c r="K6" s="364"/>
+      <c r="L6" s="364"/>
+      <c r="M6" s="364"/>
+      <c r="N6" s="364"/>
+      <c r="O6" s="375"/>
       <c r="P6" s="75" t="s">
         <v>6</v>
       </c>
@@ -7386,29 +7385,29 @@
     </row>
     <row r="7" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="212"/>
-      <c r="B7" s="434" t="s">
+      <c r="B7" s="411" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="342"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
-      <c r="F7" s="342"/>
-      <c r="G7" s="342"/>
-      <c r="H7" s="342"/>
-      <c r="I7" s="342"/>
-      <c r="J7" s="342"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
+      <c r="E7" s="368"/>
+      <c r="F7" s="368"/>
+      <c r="G7" s="368"/>
+      <c r="H7" s="368"/>
+      <c r="I7" s="368"/>
+      <c r="J7" s="368"/>
       <c r="K7" s="267"/>
       <c r="L7" s="268"/>
-      <c r="M7" s="425" t="s">
+      <c r="M7" s="418" t="s">
         <v>8</v>
       </c>
-      <c r="N7" s="342"/>
-      <c r="O7" s="342"/>
-      <c r="P7" s="342"/>
-      <c r="Q7" s="342"/>
-      <c r="R7" s="342"/>
-      <c r="S7" s="342"/>
-      <c r="T7" s="343"/>
+      <c r="N7" s="368"/>
+      <c r="O7" s="368"/>
+      <c r="P7" s="368"/>
+      <c r="Q7" s="368"/>
+      <c r="R7" s="368"/>
+      <c r="S7" s="368"/>
+      <c r="T7" s="356"/>
       <c r="U7" s="213"/>
     </row>
     <row r="8" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7497,110 +7496,110 @@
     <row r="11" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="214"/>
       <c r="B11" s="159"/>
-      <c r="C11" s="436" t="s">
+      <c r="C11" s="416" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="342"/>
-      <c r="E11" s="342"/>
-      <c r="F11" s="342"/>
-      <c r="G11" s="342"/>
-      <c r="H11" s="342"/>
-      <c r="I11" s="342"/>
-      <c r="J11" s="342"/>
-      <c r="K11" s="342"/>
-      <c r="L11" s="343"/>
-      <c r="M11" s="430" t="s">
+      <c r="D11" s="368"/>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
+      <c r="G11" s="368"/>
+      <c r="H11" s="368"/>
+      <c r="I11" s="368"/>
+      <c r="J11" s="368"/>
+      <c r="K11" s="368"/>
+      <c r="L11" s="356"/>
+      <c r="M11" s="412" t="s">
         <v>136</v>
       </c>
-      <c r="N11" s="342"/>
-      <c r="O11" s="342"/>
-      <c r="P11" s="342"/>
-      <c r="Q11" s="343"/>
-      <c r="R11" s="424" t="s">
+      <c r="N11" s="368"/>
+      <c r="O11" s="368"/>
+      <c r="P11" s="368"/>
+      <c r="Q11" s="356"/>
+      <c r="R11" s="409" t="s">
         <v>137</v>
       </c>
-      <c r="S11" s="338"/>
-      <c r="T11" s="426" t="s">
+      <c r="S11" s="373"/>
+      <c r="T11" s="420" t="s">
         <v>138</v>
       </c>
       <c r="U11" s="215"/>
     </row>
     <row r="12" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="214"/>
-      <c r="B12" s="424" t="s">
+      <c r="B12" s="409" t="s">
         <v>139</v>
       </c>
-      <c r="C12" s="436" t="s">
+      <c r="C12" s="416" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-      <c r="G12" s="343"/>
-      <c r="H12" s="430" t="s">
+      <c r="D12" s="368"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
+      <c r="G12" s="356"/>
+      <c r="H12" s="412" t="s">
         <v>141</v>
       </c>
-      <c r="I12" s="342"/>
-      <c r="J12" s="342"/>
-      <c r="K12" s="342"/>
-      <c r="L12" s="343"/>
-      <c r="M12" s="430" t="s">
+      <c r="I12" s="368"/>
+      <c r="J12" s="368"/>
+      <c r="K12" s="368"/>
+      <c r="L12" s="356"/>
+      <c r="M12" s="412" t="s">
         <v>142</v>
       </c>
-      <c r="N12" s="342"/>
-      <c r="O12" s="342"/>
-      <c r="P12" s="342"/>
-      <c r="Q12" s="343"/>
-      <c r="R12" s="429"/>
-      <c r="S12" s="405"/>
-      <c r="T12" s="427"/>
+      <c r="N12" s="368"/>
+      <c r="O12" s="368"/>
+      <c r="P12" s="368"/>
+      <c r="Q12" s="356"/>
+      <c r="R12" s="422"/>
+      <c r="S12" s="381"/>
+      <c r="T12" s="419"/>
       <c r="U12" s="215"/>
     </row>
     <row r="13" spans="1:30" s="53" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="216"/>
-      <c r="B13" s="427"/>
-      <c r="C13" s="424" t="s">
+      <c r="B13" s="419"/>
+      <c r="C13" s="409" t="s">
         <v>143</v>
       </c>
-      <c r="D13" s="424" t="s">
+      <c r="D13" s="409" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="343"/>
-      <c r="F13" s="423" t="s">
+      <c r="E13" s="356"/>
+      <c r="F13" s="414" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="343"/>
-      <c r="H13" s="424" t="s">
+      <c r="G13" s="356"/>
+      <c r="H13" s="409" t="s">
         <v>143</v>
       </c>
-      <c r="I13" s="424" t="s">
+      <c r="I13" s="409" t="s">
         <v>144</v>
       </c>
-      <c r="J13" s="343"/>
-      <c r="K13" s="423" t="s">
+      <c r="J13" s="356"/>
+      <c r="K13" s="414" t="s">
         <v>145</v>
       </c>
-      <c r="L13" s="343"/>
-      <c r="M13" s="424" t="s">
+      <c r="L13" s="356"/>
+      <c r="M13" s="409" t="s">
         <v>143</v>
       </c>
-      <c r="N13" s="424" t="s">
+      <c r="N13" s="409" t="s">
         <v>144</v>
       </c>
-      <c r="O13" s="343"/>
-      <c r="P13" s="423" t="s">
+      <c r="O13" s="356"/>
+      <c r="P13" s="414" t="s">
         <v>145</v>
       </c>
-      <c r="Q13" s="343"/>
-      <c r="R13" s="351"/>
-      <c r="S13" s="340"/>
-      <c r="T13" s="427"/>
+      <c r="Q13" s="356"/>
+      <c r="R13" s="374"/>
+      <c r="S13" s="375"/>
+      <c r="T13" s="419"/>
       <c r="U13" s="217"/>
     </row>
     <row r="14" spans="1:30" s="53" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="216"/>
-      <c r="B14" s="353"/>
-      <c r="C14" s="353"/>
+      <c r="B14" s="410"/>
+      <c r="C14" s="410"/>
       <c r="D14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7613,7 +7612,7 @@
       <c r="G14" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="H14" s="353"/>
+      <c r="H14" s="410"/>
       <c r="I14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7626,7 +7625,7 @@
       <c r="L14" s="151" t="s">
         <v>151</v>
       </c>
-      <c r="M14" s="353"/>
+      <c r="M14" s="410"/>
       <c r="N14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7645,7 +7644,7 @@
       <c r="S14" s="151" t="s">
         <v>155</v>
       </c>
-      <c r="T14" s="427"/>
+      <c r="T14" s="419"/>
       <c r="U14" s="217"/>
     </row>
     <row r="15" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7704,7 +7703,7 @@
       <c r="S15" s="15">
         <v>18</v>
       </c>
-      <c r="T15" s="353"/>
+      <c r="T15" s="410"/>
       <c r="U15" s="201"/>
       <c r="V15" s="10"/>
       <c r="W15" s="10"/>
@@ -8915,6 +8914,16 @@
     <row r="42" spans="1:21" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="T11:T15"/>
+    <mergeCell ref="D5:O6"/>
+    <mergeCell ref="R11:S13"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="B5:C6"/>
     <mergeCell ref="B2:T2"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="B7:J7"/>
@@ -8931,16 +8940,6 @@
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="T11:T15"/>
-    <mergeCell ref="D5:O6"/>
-    <mergeCell ref="R11:S13"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="M11:Q11"/>
-    <mergeCell ref="B5:C6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -8981,103 +8980,103 @@
   <sheetData>
     <row r="1" spans="1:23" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="223"/>
-      <c r="B1" s="443"/>
-      <c r="C1" s="409"/>
-      <c r="D1" s="409"/>
-      <c r="E1" s="409"/>
-      <c r="F1" s="409"/>
-      <c r="G1" s="409"/>
-      <c r="H1" s="409"/>
-      <c r="I1" s="409"/>
-      <c r="J1" s="409"/>
-      <c r="K1" s="409"/>
-      <c r="L1" s="409"/>
-      <c r="M1" s="409"/>
-      <c r="N1" s="409"/>
-      <c r="O1" s="409"/>
-      <c r="P1" s="409"/>
-      <c r="Q1" s="409"/>
-      <c r="R1" s="409"/>
-      <c r="S1" s="409"/>
-      <c r="T1" s="409"/>
-      <c r="U1" s="409"/>
-      <c r="V1" s="409"/>
+      <c r="B1" s="430"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+      <c r="E1" s="370"/>
+      <c r="F1" s="370"/>
+      <c r="G1" s="370"/>
+      <c r="H1" s="370"/>
+      <c r="I1" s="370"/>
+      <c r="J1" s="370"/>
+      <c r="K1" s="370"/>
+      <c r="L1" s="370"/>
+      <c r="M1" s="370"/>
+      <c r="N1" s="370"/>
+      <c r="O1" s="370"/>
+      <c r="P1" s="370"/>
+      <c r="Q1" s="370"/>
+      <c r="R1" s="370"/>
+      <c r="S1" s="370"/>
+      <c r="T1" s="370"/>
+      <c r="U1" s="370"/>
+      <c r="V1" s="370"/>
       <c r="W1" s="224"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="438" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="337"/>
-      <c r="M2" s="337"/>
-      <c r="N2" s="337"/>
-      <c r="O2" s="337"/>
-      <c r="P2" s="337"/>
-      <c r="Q2" s="337"/>
-      <c r="R2" s="337"/>
-      <c r="S2" s="337"/>
-      <c r="T2" s="337"/>
-      <c r="U2" s="337"/>
-      <c r="V2" s="338"/>
+      <c r="B2" s="435" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="372"/>
+      <c r="D2" s="372"/>
+      <c r="E2" s="372"/>
+      <c r="F2" s="372"/>
+      <c r="G2" s="372"/>
+      <c r="H2" s="372"/>
+      <c r="I2" s="372"/>
+      <c r="J2" s="372"/>
+      <c r="K2" s="372"/>
+      <c r="L2" s="372"/>
+      <c r="M2" s="372"/>
+      <c r="N2" s="372"/>
+      <c r="O2" s="372"/>
+      <c r="P2" s="372"/>
+      <c r="Q2" s="372"/>
+      <c r="R2" s="372"/>
+      <c r="S2" s="372"/>
+      <c r="T2" s="372"/>
+      <c r="U2" s="372"/>
+      <c r="V2" s="373"/>
       <c r="W2" s="202"/>
     </row>
     <row r="3" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="344" t="s">
+      <c r="B3" s="426" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339"/>
-      <c r="E3" s="339"/>
-      <c r="F3" s="339"/>
-      <c r="G3" s="339"/>
-      <c r="H3" s="339"/>
-      <c r="I3" s="339"/>
-      <c r="J3" s="339"/>
-      <c r="K3" s="339"/>
-      <c r="L3" s="339"/>
-      <c r="M3" s="339"/>
-      <c r="N3" s="339"/>
-      <c r="O3" s="339"/>
-      <c r="P3" s="339"/>
-      <c r="Q3" s="339"/>
-      <c r="R3" s="339"/>
-      <c r="S3" s="339"/>
-      <c r="T3" s="339"/>
-      <c r="U3" s="339"/>
-      <c r="V3" s="340"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
+      <c r="L3" s="364"/>
+      <c r="M3" s="364"/>
+      <c r="N3" s="364"/>
+      <c r="O3" s="364"/>
+      <c r="P3" s="364"/>
+      <c r="Q3" s="364"/>
+      <c r="R3" s="364"/>
+      <c r="S3" s="364"/>
+      <c r="T3" s="364"/>
+      <c r="U3" s="364"/>
+      <c r="V3" s="375"/>
       <c r="W3" s="202"/>
     </row>
     <row r="4" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="345" t="s">
+      <c r="B4" s="432" t="s">
         <v>160</v>
       </c>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="342"/>
-      <c r="J4" s="342"/>
-      <c r="K4" s="342"/>
-      <c r="L4" s="342"/>
-      <c r="M4" s="342"/>
-      <c r="N4" s="342"/>
-      <c r="O4" s="342"/>
-      <c r="P4" s="342"/>
-      <c r="Q4" s="343"/>
+      <c r="C4" s="368"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="368"/>
+      <c r="F4" s="368"/>
+      <c r="G4" s="368"/>
+      <c r="H4" s="368"/>
+      <c r="I4" s="368"/>
+      <c r="J4" s="368"/>
+      <c r="K4" s="368"/>
+      <c r="L4" s="368"/>
+      <c r="M4" s="368"/>
+      <c r="N4" s="368"/>
+      <c r="O4" s="368"/>
+      <c r="P4" s="368"/>
+      <c r="Q4" s="356"/>
       <c r="R4" s="259" t="s">
         <v>58</v>
       </c>
@@ -9092,54 +9091,54 @@
     </row>
     <row r="5" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="444" t="s">
+      <c r="B5" s="431" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="337"/>
-      <c r="D5" s="428" t="str">
+      <c r="C5" s="372"/>
+      <c r="D5" s="421" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="337"/>
-      <c r="J5" s="337"/>
-      <c r="K5" s="337"/>
-      <c r="L5" s="337"/>
-      <c r="M5" s="337"/>
-      <c r="N5" s="337"/>
-      <c r="O5" s="337"/>
-      <c r="P5" s="337"/>
-      <c r="Q5" s="338"/>
-      <c r="R5" s="449" t="s">
+      <c r="E5" s="372"/>
+      <c r="F5" s="372"/>
+      <c r="G5" s="372"/>
+      <c r="H5" s="372"/>
+      <c r="I5" s="372"/>
+      <c r="J5" s="372"/>
+      <c r="K5" s="372"/>
+      <c r="L5" s="372"/>
+      <c r="M5" s="372"/>
+      <c r="N5" s="372"/>
+      <c r="O5" s="372"/>
+      <c r="P5" s="372"/>
+      <c r="Q5" s="373"/>
+      <c r="R5" s="429" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="342"/>
-      <c r="T5" s="342"/>
-      <c r="U5" s="342"/>
-      <c r="V5" s="343"/>
+      <c r="S5" s="368"/>
+      <c r="T5" s="368"/>
+      <c r="U5" s="368"/>
+      <c r="V5" s="356"/>
       <c r="W5" s="202"/>
     </row>
     <row r="6" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="225"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="339"/>
-      <c r="D6" s="339"/>
-      <c r="E6" s="339"/>
-      <c r="F6" s="339"/>
-      <c r="G6" s="339"/>
-      <c r="H6" s="339"/>
-      <c r="I6" s="339"/>
-      <c r="J6" s="339"/>
-      <c r="K6" s="339"/>
-      <c r="L6" s="339"/>
-      <c r="M6" s="339"/>
-      <c r="N6" s="339"/>
-      <c r="O6" s="339"/>
-      <c r="P6" s="339"/>
-      <c r="Q6" s="340"/>
+      <c r="B6" s="374"/>
+      <c r="C6" s="364"/>
+      <c r="D6" s="364"/>
+      <c r="E6" s="364"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="364"/>
+      <c r="I6" s="364"/>
+      <c r="J6" s="364"/>
+      <c r="K6" s="364"/>
+      <c r="L6" s="364"/>
+      <c r="M6" s="364"/>
+      <c r="N6" s="364"/>
+      <c r="O6" s="364"/>
+      <c r="P6" s="364"/>
+      <c r="Q6" s="375"/>
       <c r="R6" s="49" t="s">
         <v>6</v>
       </c>
@@ -9154,31 +9153,31 @@
     </row>
     <row r="7" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="225"/>
-      <c r="B7" s="442" t="s">
+      <c r="B7" s="437" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="342"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
-      <c r="F7" s="342"/>
-      <c r="G7" s="342"/>
-      <c r="H7" s="342"/>
-      <c r="I7" s="342"/>
-      <c r="J7" s="342"/>
-      <c r="K7" s="342"/>
-      <c r="L7" s="342"/>
-      <c r="M7" s="343"/>
-      <c r="N7" s="442" t="s">
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
+      <c r="E7" s="368"/>
+      <c r="F7" s="368"/>
+      <c r="G7" s="368"/>
+      <c r="H7" s="368"/>
+      <c r="I7" s="368"/>
+      <c r="J7" s="368"/>
+      <c r="K7" s="368"/>
+      <c r="L7" s="368"/>
+      <c r="M7" s="356"/>
+      <c r="N7" s="437" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="342"/>
-      <c r="P7" s="342"/>
-      <c r="Q7" s="342"/>
-      <c r="R7" s="342"/>
-      <c r="S7" s="342"/>
-      <c r="T7" s="342"/>
-      <c r="U7" s="342"/>
-      <c r="V7" s="343"/>
+      <c r="O7" s="368"/>
+      <c r="P7" s="368"/>
+      <c r="Q7" s="368"/>
+      <c r="R7" s="368"/>
+      <c r="S7" s="368"/>
+      <c r="T7" s="368"/>
+      <c r="U7" s="368"/>
+      <c r="V7" s="356"/>
       <c r="W7" s="226"/>
     </row>
     <row r="8" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9272,184 +9271,184 @@
     </row>
     <row r="11" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="296"/>
-      <c r="B11" s="439" t="s">
+      <c r="B11" s="425" t="s">
         <v>161</v>
       </c>
-      <c r="C11" s="445" t="s">
+      <c r="C11" s="433" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="342"/>
-      <c r="E11" s="342"/>
-      <c r="F11" s="342"/>
-      <c r="G11" s="342"/>
-      <c r="H11" s="342"/>
-      <c r="I11" s="342"/>
-      <c r="J11" s="342"/>
-      <c r="K11" s="342"/>
-      <c r="L11" s="342"/>
-      <c r="M11" s="343"/>
-      <c r="N11" s="446" t="s">
+      <c r="D11" s="368"/>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
+      <c r="G11" s="368"/>
+      <c r="H11" s="368"/>
+      <c r="I11" s="368"/>
+      <c r="J11" s="368"/>
+      <c r="K11" s="368"/>
+      <c r="L11" s="368"/>
+      <c r="M11" s="356"/>
+      <c r="N11" s="427" t="s">
         <v>162</v>
       </c>
-      <c r="O11" s="440" t="s">
+      <c r="O11" s="424" t="s">
         <v>136</v>
       </c>
-      <c r="P11" s="342"/>
-      <c r="Q11" s="342"/>
-      <c r="R11" s="342"/>
-      <c r="S11" s="343"/>
-      <c r="T11" s="441" t="s">
+      <c r="P11" s="368"/>
+      <c r="Q11" s="368"/>
+      <c r="R11" s="368"/>
+      <c r="S11" s="356"/>
+      <c r="T11" s="436" t="s">
         <v>163</v>
       </c>
-      <c r="U11" s="338"/>
-      <c r="V11" s="447" t="s">
+      <c r="U11" s="373"/>
+      <c r="V11" s="434" t="s">
         <v>164</v>
       </c>
       <c r="W11" s="227"/>
     </row>
     <row r="12" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="296"/>
-      <c r="B12" s="427"/>
-      <c r="C12" s="445" t="s">
+      <c r="B12" s="419"/>
+      <c r="C12" s="433" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-      <c r="G12" s="343"/>
-      <c r="H12" s="440" t="s">
+      <c r="D12" s="368"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
+      <c r="G12" s="356"/>
+      <c r="H12" s="424" t="s">
         <v>141</v>
       </c>
-      <c r="I12" s="342"/>
-      <c r="J12" s="342"/>
-      <c r="K12" s="342"/>
-      <c r="L12" s="343"/>
-      <c r="M12" s="446" t="s">
+      <c r="I12" s="368"/>
+      <c r="J12" s="368"/>
+      <c r="K12" s="368"/>
+      <c r="L12" s="356"/>
+      <c r="M12" s="427" t="s">
         <v>165</v>
       </c>
-      <c r="N12" s="427"/>
-      <c r="O12" s="440" t="s">
+      <c r="N12" s="419"/>
+      <c r="O12" s="424" t="s">
         <v>142</v>
       </c>
-      <c r="P12" s="342"/>
-      <c r="Q12" s="342"/>
-      <c r="R12" s="342"/>
-      <c r="S12" s="343"/>
-      <c r="T12" s="429"/>
-      <c r="U12" s="405"/>
-      <c r="V12" s="427"/>
+      <c r="P12" s="368"/>
+      <c r="Q12" s="368"/>
+      <c r="R12" s="368"/>
+      <c r="S12" s="356"/>
+      <c r="T12" s="422"/>
+      <c r="U12" s="381"/>
+      <c r="V12" s="419"/>
       <c r="W12" s="227"/>
     </row>
     <row r="13" spans="1:23" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="296"/>
-      <c r="B13" s="427"/>
-      <c r="C13" s="424" t="s">
+      <c r="B13" s="419"/>
+      <c r="C13" s="409" t="s">
         <v>166</v>
       </c>
-      <c r="D13" s="424" t="s">
+      <c r="D13" s="409" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="343"/>
-      <c r="F13" s="448" t="s">
+      <c r="E13" s="356"/>
+      <c r="F13" s="428" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="338"/>
-      <c r="H13" s="424" t="s">
+      <c r="G13" s="373"/>
+      <c r="H13" s="409" t="s">
         <v>166</v>
       </c>
-      <c r="I13" s="424" t="s">
+      <c r="I13" s="409" t="s">
         <v>144</v>
       </c>
-      <c r="J13" s="343"/>
-      <c r="K13" s="448" t="s">
+      <c r="J13" s="356"/>
+      <c r="K13" s="428" t="s">
         <v>145</v>
       </c>
-      <c r="L13" s="338"/>
-      <c r="M13" s="427"/>
-      <c r="N13" s="427"/>
-      <c r="O13" s="424" t="s">
+      <c r="L13" s="373"/>
+      <c r="M13" s="419"/>
+      <c r="N13" s="419"/>
+      <c r="O13" s="409" t="s">
         <v>167</v>
       </c>
-      <c r="P13" s="424" t="s">
+      <c r="P13" s="409" t="s">
         <v>144</v>
       </c>
-      <c r="Q13" s="343"/>
-      <c r="R13" s="439" t="s">
+      <c r="Q13" s="356"/>
+      <c r="R13" s="425" t="s">
         <v>145</v>
       </c>
-      <c r="S13" s="343"/>
-      <c r="T13" s="351"/>
-      <c r="U13" s="340"/>
-      <c r="V13" s="427"/>
+      <c r="S13" s="356"/>
+      <c r="T13" s="374"/>
+      <c r="U13" s="375"/>
+      <c r="V13" s="419"/>
       <c r="W13" s="227"/>
     </row>
     <row r="14" spans="1:23" s="36" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="296"/>
-      <c r="B14" s="427"/>
-      <c r="C14" s="427"/>
-      <c r="D14" s="439" t="s">
+      <c r="B14" s="419"/>
+      <c r="C14" s="419"/>
+      <c r="D14" s="425" t="s">
         <v>146</v>
       </c>
-      <c r="E14" s="424" t="s">
+      <c r="E14" s="409" t="s">
         <v>168</v>
       </c>
-      <c r="F14" s="424" t="s">
+      <c r="F14" s="409" t="s">
         <v>169</v>
       </c>
-      <c r="G14" s="424" t="s">
+      <c r="G14" s="409" t="s">
         <v>170</v>
       </c>
-      <c r="H14" s="427"/>
-      <c r="I14" s="439" t="s">
+      <c r="H14" s="419"/>
+      <c r="I14" s="425" t="s">
         <v>146</v>
       </c>
-      <c r="J14" s="424" t="s">
+      <c r="J14" s="409" t="s">
         <v>168</v>
       </c>
-      <c r="K14" s="424" t="s">
+      <c r="K14" s="409" t="s">
         <v>171</v>
       </c>
-      <c r="L14" s="424" t="s">
+      <c r="L14" s="409" t="s">
         <v>172</v>
       </c>
-      <c r="M14" s="427"/>
-      <c r="N14" s="353"/>
-      <c r="O14" s="353"/>
+      <c r="M14" s="419"/>
+      <c r="N14" s="410"/>
+      <c r="O14" s="410"/>
       <c r="P14" s="159" t="s">
         <v>173</v>
       </c>
       <c r="Q14" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="R14" s="424" t="s">
+      <c r="R14" s="409" t="s">
         <v>174</v>
       </c>
-      <c r="S14" s="424" t="s">
+      <c r="S14" s="409" t="s">
         <v>175</v>
       </c>
-      <c r="T14" s="424" t="s">
+      <c r="T14" s="409" t="s">
         <v>176</v>
       </c>
-      <c r="U14" s="424" t="s">
+      <c r="U14" s="409" t="s">
         <v>177</v>
       </c>
-      <c r="V14" s="427"/>
+      <c r="V14" s="419"/>
       <c r="W14" s="227"/>
     </row>
     <row r="15" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="296"/>
-      <c r="B15" s="353"/>
-      <c r="C15" s="353"/>
-      <c r="D15" s="353"/>
-      <c r="E15" s="353"/>
-      <c r="F15" s="353"/>
-      <c r="G15" s="353"/>
-      <c r="H15" s="353"/>
-      <c r="I15" s="353"/>
-      <c r="J15" s="353"/>
-      <c r="K15" s="353"/>
-      <c r="L15" s="353"/>
-      <c r="M15" s="353"/>
+      <c r="B15" s="410"/>
+      <c r="C15" s="410"/>
+      <c r="D15" s="410"/>
+      <c r="E15" s="410"/>
+      <c r="F15" s="410"/>
+      <c r="G15" s="410"/>
+      <c r="H15" s="410"/>
+      <c r="I15" s="410"/>
+      <c r="J15" s="410"/>
+      <c r="K15" s="410"/>
+      <c r="L15" s="410"/>
+      <c r="M15" s="410"/>
       <c r="N15" s="150" t="s">
         <v>178</v>
       </c>
@@ -9462,11 +9461,11 @@
       <c r="Q15" s="151" t="s">
         <v>181</v>
       </c>
-      <c r="R15" s="353"/>
-      <c r="S15" s="353"/>
-      <c r="T15" s="353"/>
-      <c r="U15" s="353"/>
-      <c r="V15" s="427"/>
+      <c r="R15" s="410"/>
+      <c r="S15" s="410"/>
+      <c r="T15" s="410"/>
+      <c r="U15" s="410"/>
+      <c r="V15" s="419"/>
       <c r="W15" s="227"/>
     </row>
     <row r="16" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9531,7 +9530,7 @@
       <c r="U16" s="38">
         <v>38</v>
       </c>
-      <c r="V16" s="353"/>
+      <c r="V16" s="410"/>
       <c r="W16" s="227"/>
     </row>
     <row r="17" spans="1:98" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9860,14 +9859,22 @@
     <row r="22" spans="1:98" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="B3:V3"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="N11:N14"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="T11:U13"/>
+    <mergeCell ref="N7:V7"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="O13:O14"/>
     <mergeCell ref="B1:V1"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="L14:L15"/>
@@ -9884,22 +9891,14 @@
     <mergeCell ref="C11:M11"/>
     <mergeCell ref="V11:V16"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="O12:S12"/>
-    <mergeCell ref="T11:U13"/>
-    <mergeCell ref="N7:V7"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="B7:M7"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="B3:V3"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="N11:N14"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -9934,90 +9933,90 @@
   <sheetData>
     <row r="1" spans="1:14" ht="5.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="408"/>
-      <c r="C1" s="409"/>
-      <c r="D1" s="409"/>
-      <c r="E1" s="409"/>
-      <c r="F1" s="409"/>
-      <c r="G1" s="409"/>
-      <c r="H1" s="409"/>
-      <c r="I1" s="409"/>
-      <c r="J1" s="409"/>
-      <c r="K1" s="409"/>
-      <c r="L1" s="409"/>
-      <c r="M1" s="409"/>
+      <c r="B1" s="369"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+      <c r="E1" s="370"/>
+      <c r="F1" s="370"/>
+      <c r="G1" s="370"/>
+      <c r="H1" s="370"/>
+      <c r="I1" s="370"/>
+      <c r="J1" s="370"/>
+      <c r="K1" s="370"/>
+      <c r="L1" s="370"/>
+      <c r="M1" s="370"/>
       <c r="N1" s="199"/>
     </row>
     <row r="2" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="249"/>
-      <c r="B2" s="438" t="s">
+      <c r="B2" s="435" t="s">
         <v>185</v>
       </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="337"/>
-      <c r="M2" s="338"/>
+      <c r="C2" s="372"/>
+      <c r="D2" s="372"/>
+      <c r="E2" s="372"/>
+      <c r="F2" s="372"/>
+      <c r="G2" s="372"/>
+      <c r="H2" s="372"/>
+      <c r="I2" s="372"/>
+      <c r="J2" s="372"/>
+      <c r="K2" s="372"/>
+      <c r="L2" s="372"/>
+      <c r="M2" s="373"/>
       <c r="N2" s="201"/>
     </row>
     <row r="3" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="249"/>
-      <c r="B3" s="344" t="s">
+      <c r="B3" s="426" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339"/>
-      <c r="E3" s="339"/>
-      <c r="F3" s="339"/>
-      <c r="G3" s="339"/>
-      <c r="H3" s="339"/>
-      <c r="I3" s="339"/>
-      <c r="J3" s="339"/>
-      <c r="K3" s="339"/>
-      <c r="L3" s="339"/>
-      <c r="M3" s="340"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
+      <c r="L3" s="364"/>
+      <c r="M3" s="375"/>
       <c r="N3" s="201"/>
     </row>
     <row r="4" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="249"/>
-      <c r="B4" s="345" t="s">
+      <c r="B4" s="432" t="s">
         <v>186</v>
       </c>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="343"/>
-      <c r="I4" s="459" t="s">
+      <c r="C4" s="368"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="368"/>
+      <c r="F4" s="368"/>
+      <c r="G4" s="368"/>
+      <c r="H4" s="356"/>
+      <c r="I4" s="449" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="342"/>
-      <c r="K4" s="342"/>
-      <c r="L4" s="342"/>
-      <c r="M4" s="343"/>
+      <c r="J4" s="368"/>
+      <c r="K4" s="368"/>
+      <c r="L4" s="368"/>
+      <c r="M4" s="356"/>
       <c r="N4" s="201"/>
     </row>
     <row r="5" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="249"/>
-      <c r="B5" s="444" t="s">
+      <c r="B5" s="431" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="337"/>
-      <c r="D5" s="428" t="str">
+      <c r="C5" s="372"/>
+      <c r="D5" s="421" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="338"/>
+      <c r="E5" s="372"/>
+      <c r="F5" s="372"/>
+      <c r="G5" s="372"/>
+      <c r="H5" s="373"/>
       <c r="I5" s="136" t="s">
         <v>6</v>
       </c>
@@ -10032,17 +10031,17 @@
     </row>
     <row r="6" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="249"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="339"/>
-      <c r="D6" s="339"/>
-      <c r="E6" s="339"/>
-      <c r="F6" s="339"/>
-      <c r="G6" s="339"/>
-      <c r="H6" s="340"/>
+      <c r="B6" s="374"/>
+      <c r="C6" s="364"/>
+      <c r="D6" s="364"/>
+      <c r="E6" s="364"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="375"/>
       <c r="I6" s="451" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="343"/>
+      <c r="J6" s="356"/>
       <c r="K6" s="156"/>
       <c r="L6" s="148">
         <f>('QUADRO II'!T4)+1</f>
@@ -10054,21 +10053,21 @@
     <row r="7" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="249"/>
       <c r="B7" s="259"/>
-      <c r="C7" s="454" t="s">
+      <c r="C7" s="452" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
-      <c r="F7" s="342"/>
-      <c r="G7" s="345" t="s">
+      <c r="D7" s="368"/>
+      <c r="E7" s="368"/>
+      <c r="F7" s="368"/>
+      <c r="G7" s="432" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="342"/>
-      <c r="I7" s="342"/>
-      <c r="J7" s="342"/>
-      <c r="K7" s="342"/>
-      <c r="L7" s="342"/>
-      <c r="M7" s="343"/>
+      <c r="H7" s="368"/>
+      <c r="I7" s="368"/>
+      <c r="J7" s="368"/>
+      <c r="K7" s="368"/>
+      <c r="L7" s="368"/>
+      <c r="M7" s="356"/>
       <c r="N7" s="201"/>
     </row>
     <row r="8" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10077,24 +10076,24 @@
         <v>9</v>
       </c>
       <c r="C8" s="76"/>
-      <c r="D8" s="457" t="str">
+      <c r="D8" s="447" t="str">
         <f>('QUADRO I'!$C$8)</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="E8" s="337"/>
-      <c r="F8" s="338"/>
+      <c r="E8" s="372"/>
+      <c r="F8" s="373"/>
       <c r="G8" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="458" t="str">
+      <c r="H8" s="448" t="str">
         <f>('QUADRO I'!$N$8)</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="I8" s="337"/>
-      <c r="J8" s="337"/>
-      <c r="K8" s="337"/>
-      <c r="L8" s="337"/>
-      <c r="M8" s="338"/>
+      <c r="I8" s="372"/>
+      <c r="J8" s="372"/>
+      <c r="K8" s="372"/>
+      <c r="L8" s="372"/>
+      <c r="M8" s="373"/>
       <c r="N8" s="201"/>
     </row>
     <row r="9" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10103,18 +10102,18 @@
         <v>10</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="455"/>
-      <c r="E9" s="456"/>
-      <c r="F9" s="405"/>
+      <c r="D9" s="446"/>
+      <c r="E9" s="443"/>
+      <c r="F9" s="381"/>
       <c r="G9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="460"/>
-      <c r="I9" s="456"/>
-      <c r="J9" s="456"/>
-      <c r="K9" s="456"/>
-      <c r="L9" s="456"/>
-      <c r="M9" s="405"/>
+      <c r="H9" s="450"/>
+      <c r="I9" s="443"/>
+      <c r="J9" s="443"/>
+      <c r="K9" s="443"/>
+      <c r="L9" s="443"/>
+      <c r="M9" s="381"/>
       <c r="N9" s="201"/>
     </row>
     <row r="10" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10123,12 +10122,12 @@
         <v>11</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="463" t="str">
+      <c r="D10" s="442" t="str">
         <f>('QUADRO I'!$C$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="E10" s="339"/>
-      <c r="F10" s="340"/>
+      <c r="E10" s="364"/>
+      <c r="F10" s="375"/>
       <c r="G10" s="5" t="s">
         <v>11</v>
       </c>
@@ -10136,12 +10135,12 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="I10" s="462" t="str">
+      <c r="I10" s="440" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="J10" s="339"/>
-      <c r="K10" s="339"/>
+      <c r="J10" s="364"/>
+      <c r="K10" s="364"/>
       <c r="L10" s="67" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -10151,7 +10150,7 @@
     </row>
     <row r="11" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="461" t="s">
+      <c r="B11" s="438" t="s">
         <v>188</v>
       </c>
       <c r="C11" s="163" t="s">
@@ -10171,132 +10170,132 @@
     </row>
     <row r="12" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="249"/>
-      <c r="B12" s="427"/>
-      <c r="C12" s="464" t="s">
+      <c r="B12" s="419"/>
+      <c r="C12" s="444" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-      <c r="G12" s="453" t="s">
+      <c r="D12" s="368"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
+      <c r="G12" s="445" t="s">
         <v>191</v>
       </c>
-      <c r="H12" s="342"/>
-      <c r="I12" s="342"/>
-      <c r="J12" s="342"/>
-      <c r="K12" s="342"/>
-      <c r="L12" s="342"/>
-      <c r="M12" s="343"/>
+      <c r="H12" s="368"/>
+      <c r="I12" s="368"/>
+      <c r="J12" s="368"/>
+      <c r="K12" s="368"/>
+      <c r="L12" s="368"/>
+      <c r="M12" s="356"/>
       <c r="N12" s="201"/>
     </row>
     <row r="13" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="249"/>
-      <c r="B13" s="427"/>
-      <c r="C13" s="452" t="s">
+      <c r="B13" s="419"/>
+      <c r="C13" s="439" t="s">
         <v>192</v>
       </c>
-      <c r="D13" s="452" t="s">
+      <c r="D13" s="439" t="s">
         <v>193</v>
       </c>
-      <c r="E13" s="452" t="s">
+      <c r="E13" s="439" t="s">
         <v>194</v>
       </c>
-      <c r="F13" s="452" t="s">
+      <c r="F13" s="439" t="s">
         <v>195</v>
       </c>
-      <c r="G13" s="453" t="s">
+      <c r="G13" s="445" t="s">
         <v>196</v>
       </c>
-      <c r="H13" s="337"/>
-      <c r="I13" s="337"/>
-      <c r="J13" s="337"/>
-      <c r="K13" s="337"/>
-      <c r="L13" s="337"/>
-      <c r="M13" s="338"/>
+      <c r="H13" s="372"/>
+      <c r="I13" s="372"/>
+      <c r="J13" s="372"/>
+      <c r="K13" s="372"/>
+      <c r="L13" s="372"/>
+      <c r="M13" s="373"/>
       <c r="N13" s="201"/>
     </row>
     <row r="14" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="249"/>
-      <c r="B14" s="427"/>
-      <c r="C14" s="427"/>
-      <c r="D14" s="427"/>
-      <c r="E14" s="427"/>
-      <c r="F14" s="427"/>
-      <c r="G14" s="351"/>
-      <c r="H14" s="339"/>
-      <c r="I14" s="339"/>
-      <c r="J14" s="339"/>
-      <c r="K14" s="339"/>
-      <c r="L14" s="339"/>
-      <c r="M14" s="340"/>
+      <c r="B14" s="419"/>
+      <c r="C14" s="419"/>
+      <c r="D14" s="419"/>
+      <c r="E14" s="419"/>
+      <c r="F14" s="419"/>
+      <c r="G14" s="374"/>
+      <c r="H14" s="364"/>
+      <c r="I14" s="364"/>
+      <c r="J14" s="364"/>
+      <c r="K14" s="364"/>
+      <c r="L14" s="364"/>
+      <c r="M14" s="375"/>
       <c r="N14" s="201"/>
     </row>
     <row r="15" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="249"/>
-      <c r="B15" s="427"/>
-      <c r="C15" s="427"/>
-      <c r="D15" s="427"/>
-      <c r="E15" s="427"/>
-      <c r="F15" s="427"/>
-      <c r="G15" s="453" t="s">
+      <c r="B15" s="419"/>
+      <c r="C15" s="419"/>
+      <c r="D15" s="419"/>
+      <c r="E15" s="419"/>
+      <c r="F15" s="419"/>
+      <c r="G15" s="445" t="s">
         <v>197</v>
       </c>
-      <c r="H15" s="453" t="s">
+      <c r="H15" s="445" t="s">
         <v>198</v>
       </c>
-      <c r="I15" s="452" t="s">
+      <c r="I15" s="439" t="s">
         <v>199</v>
       </c>
-      <c r="J15" s="338"/>
-      <c r="K15" s="452" t="s">
+      <c r="J15" s="373"/>
+      <c r="K15" s="439" t="s">
         <v>200</v>
       </c>
-      <c r="L15" s="337"/>
-      <c r="M15" s="338"/>
+      <c r="L15" s="372"/>
+      <c r="M15" s="373"/>
       <c r="N15" s="201"/>
     </row>
     <row r="16" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="249"/>
-      <c r="B16" s="427"/>
-      <c r="C16" s="427"/>
-      <c r="D16" s="427"/>
-      <c r="E16" s="427"/>
-      <c r="F16" s="427"/>
-      <c r="G16" s="427"/>
-      <c r="H16" s="427"/>
-      <c r="I16" s="429"/>
-      <c r="J16" s="405"/>
-      <c r="K16" s="429"/>
-      <c r="L16" s="456"/>
-      <c r="M16" s="405"/>
+      <c r="B16" s="419"/>
+      <c r="C16" s="419"/>
+      <c r="D16" s="419"/>
+      <c r="E16" s="419"/>
+      <c r="F16" s="419"/>
+      <c r="G16" s="419"/>
+      <c r="H16" s="419"/>
+      <c r="I16" s="422"/>
+      <c r="J16" s="381"/>
+      <c r="K16" s="422"/>
+      <c r="L16" s="443"/>
+      <c r="M16" s="381"/>
       <c r="N16" s="201"/>
     </row>
     <row r="17" spans="1:14" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="249"/>
-      <c r="B17" s="427"/>
-      <c r="C17" s="353"/>
-      <c r="D17" s="353"/>
-      <c r="E17" s="353"/>
-      <c r="F17" s="353"/>
-      <c r="G17" s="353"/>
-      <c r="H17" s="353"/>
-      <c r="I17" s="351"/>
-      <c r="J17" s="340"/>
-      <c r="K17" s="351"/>
-      <c r="L17" s="339"/>
-      <c r="M17" s="340"/>
+      <c r="B17" s="419"/>
+      <c r="C17" s="410"/>
+      <c r="D17" s="410"/>
+      <c r="E17" s="410"/>
+      <c r="F17" s="410"/>
+      <c r="G17" s="410"/>
+      <c r="H17" s="410"/>
+      <c r="I17" s="374"/>
+      <c r="J17" s="375"/>
+      <c r="K17" s="374"/>
+      <c r="L17" s="364"/>
+      <c r="M17" s="375"/>
       <c r="N17" s="201"/>
     </row>
     <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="200"/>
-      <c r="B18" s="427"/>
-      <c r="C18" s="450" t="s">
+      <c r="B18" s="419"/>
+      <c r="C18" s="441" t="s">
         <v>201</v>
       </c>
-      <c r="D18" s="450" t="s">
+      <c r="D18" s="441" t="s">
         <v>202</v>
       </c>
-      <c r="E18" s="450">
+      <c r="E18" s="441">
         <v>1</v>
       </c>
       <c r="F18" s="234" t="str">
@@ -10309,68 +10308,68 @@
       <c r="H18" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="I18" s="452" t="s">
+      <c r="I18" s="439" t="s">
         <v>203</v>
       </c>
-      <c r="J18" s="343"/>
-      <c r="K18" s="452" t="s">
+      <c r="J18" s="356"/>
+      <c r="K18" s="439" t="s">
         <v>203</v>
       </c>
-      <c r="L18" s="342"/>
-      <c r="M18" s="343"/>
+      <c r="L18" s="368"/>
+      <c r="M18" s="356"/>
       <c r="N18" s="202"/>
     </row>
     <row r="19" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="200"/>
-      <c r="B19" s="427"/>
-      <c r="C19" s="427"/>
-      <c r="D19" s="427"/>
-      <c r="E19" s="427"/>
+      <c r="B19" s="419"/>
+      <c r="C19" s="419"/>
+      <c r="D19" s="419"/>
+      <c r="E19" s="419"/>
       <c r="F19" s="234"/>
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
-      <c r="I19" s="452"/>
-      <c r="J19" s="343"/>
-      <c r="K19" s="452"/>
-      <c r="L19" s="342"/>
-      <c r="M19" s="343"/>
+      <c r="I19" s="439"/>
+      <c r="J19" s="356"/>
+      <c r="K19" s="439"/>
+      <c r="L19" s="368"/>
+      <c r="M19" s="356"/>
       <c r="N19" s="202"/>
     </row>
     <row r="20" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="427"/>
-      <c r="C20" s="427"/>
-      <c r="D20" s="427"/>
-      <c r="E20" s="427"/>
+      <c r="B20" s="419"/>
+      <c r="C20" s="419"/>
+      <c r="D20" s="419"/>
+      <c r="E20" s="419"/>
       <c r="F20" s="234"/>
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
-      <c r="I20" s="452"/>
-      <c r="J20" s="343"/>
-      <c r="K20" s="452"/>
-      <c r="L20" s="342"/>
-      <c r="M20" s="343"/>
+      <c r="I20" s="439"/>
+      <c r="J20" s="356"/>
+      <c r="K20" s="439"/>
+      <c r="L20" s="368"/>
+      <c r="M20" s="356"/>
       <c r="N20" s="202"/>
     </row>
     <row r="21" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="200"/>
-      <c r="B21" s="427"/>
-      <c r="C21" s="427"/>
-      <c r="D21" s="427"/>
-      <c r="E21" s="427"/>
+      <c r="B21" s="419"/>
+      <c r="C21" s="419"/>
+      <c r="D21" s="419"/>
+      <c r="E21" s="419"/>
       <c r="F21" s="234"/>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="452"/>
-      <c r="J21" s="343"/>
-      <c r="K21" s="452"/>
-      <c r="L21" s="342"/>
-      <c r="M21" s="343"/>
+      <c r="I21" s="439"/>
+      <c r="J21" s="356"/>
+      <c r="K21" s="439"/>
+      <c r="L21" s="368"/>
+      <c r="M21" s="356"/>
       <c r="N21" s="202"/>
     </row>
     <row r="22" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="200"/>
-      <c r="B22" s="427"/>
+      <c r="B22" s="419"/>
       <c r="C22" s="56" t="s">
         <v>204</v>
       </c>
@@ -10390,7 +10389,7 @@
     </row>
     <row r="23" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="200"/>
-      <c r="B23" s="427"/>
+      <c r="B23" s="419"/>
       <c r="C23" s="56" t="s">
         <v>206</v>
       </c>
@@ -10416,7 +10415,7 @@
     </row>
     <row r="24" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="200"/>
-      <c r="B24" s="427"/>
+      <c r="B24" s="419"/>
       <c r="C24" s="45" t="s">
         <v>209</v>
       </c>
@@ -10434,7 +10433,7 @@
     </row>
     <row r="25" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="200"/>
-      <c r="B25" s="427"/>
+      <c r="B25" s="419"/>
       <c r="C25" s="239"/>
       <c r="D25" s="25" t="s">
         <v>210</v>
@@ -10460,7 +10459,7 @@
     </row>
     <row r="26" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="200"/>
-      <c r="B26" s="427"/>
+      <c r="B26" s="419"/>
       <c r="C26" s="239"/>
       <c r="D26" s="25" t="s">
         <v>213</v>
@@ -10486,7 +10485,7 @@
     </row>
     <row r="27" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="200"/>
-      <c r="B27" s="427"/>
+      <c r="B27" s="419"/>
       <c r="C27" s="239"/>
       <c r="D27" s="25" t="s">
         <v>214</v>
@@ -10511,7 +10510,7 @@
     </row>
     <row r="28" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="200"/>
-      <c r="B28" s="427"/>
+      <c r="B28" s="419"/>
       <c r="C28" s="239"/>
       <c r="D28" s="25" t="s">
         <v>215</v>
@@ -10537,7 +10536,7 @@
     </row>
     <row r="29" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="200"/>
-      <c r="B29" s="427"/>
+      <c r="B29" s="419"/>
       <c r="C29" s="239"/>
       <c r="D29" s="25" t="s">
         <v>216</v>
@@ -10563,7 +10562,7 @@
     </row>
     <row r="30" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="200"/>
-      <c r="B30" s="427"/>
+      <c r="B30" s="419"/>
       <c r="C30" s="239"/>
       <c r="D30" s="25" t="s">
         <v>217</v>
@@ -10588,7 +10587,7 @@
     </row>
     <row r="31" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="200"/>
-      <c r="B31" s="353"/>
+      <c r="B31" s="410"/>
       <c r="C31" s="30"/>
       <c r="D31" s="154" t="s">
         <v>218</v>
@@ -10606,7 +10605,7 @@
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="200"/>
-      <c r="B32" s="461" t="s">
+      <c r="B32" s="438" t="s">
         <v>219</v>
       </c>
       <c r="C32" s="56" t="s">
@@ -10631,7 +10630,7 @@
     </row>
     <row r="33" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
-      <c r="B33" s="427"/>
+      <c r="B33" s="419"/>
       <c r="C33" s="45"/>
       <c r="D33" s="27" t="s">
         <v>222</v>
@@ -10649,7 +10648,7 @@
     </row>
     <row r="34" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="200"/>
-      <c r="B34" s="427"/>
+      <c r="B34" s="419"/>
       <c r="C34" s="239"/>
       <c r="E34" s="1" t="s">
         <v>223</v>
@@ -10677,7 +10676,7 @@
     </row>
     <row r="35" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="200"/>
-      <c r="B35" s="427"/>
+      <c r="B35" s="419"/>
       <c r="C35" s="30"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2" t="s">
@@ -10709,7 +10708,7 @@
     </row>
     <row r="36" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="200"/>
-      <c r="B36" s="427"/>
+      <c r="B36" s="419"/>
       <c r="C36" s="56" t="s">
         <v>225</v>
       </c>
@@ -10727,7 +10726,7 @@
     </row>
     <row r="37" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="200"/>
-      <c r="B37" s="427"/>
+      <c r="B37" s="419"/>
       <c r="C37" s="45"/>
       <c r="D37" s="246" t="s">
         <v>226</v>
@@ -10747,7 +10746,7 @@
     </row>
     <row r="38" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="200"/>
-      <c r="B38" s="427"/>
+      <c r="B38" s="419"/>
       <c r="C38" s="239"/>
       <c r="D38" s="1" t="s">
         <v>227</v>
@@ -10763,7 +10762,7 @@
     </row>
     <row r="39" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="200"/>
-      <c r="B39" s="427"/>
+      <c r="B39" s="419"/>
       <c r="C39" s="239"/>
       <c r="D39" s="1" t="s">
         <v>228</v>
@@ -10777,7 +10776,7 @@
     </row>
     <row r="40" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="200"/>
-      <c r="B40" s="427"/>
+      <c r="B40" s="419"/>
       <c r="C40" s="239"/>
       <c r="E40" s="1" t="s">
         <v>229</v>
@@ -10793,7 +10792,7 @@
     </row>
     <row r="41" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="200"/>
-      <c r="B41" s="427"/>
+      <c r="B41" s="419"/>
       <c r="C41" s="239"/>
       <c r="E41" s="1" t="s">
         <v>230</v>
@@ -10809,7 +10808,7 @@
     </row>
     <row r="42" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="200"/>
-      <c r="B42" s="427"/>
+      <c r="B42" s="419"/>
       <c r="C42" s="239"/>
       <c r="E42" s="1" t="s">
         <v>231</v>
@@ -10825,7 +10824,7 @@
     </row>
     <row r="43" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="200"/>
-      <c r="B43" s="427"/>
+      <c r="B43" s="419"/>
       <c r="C43" s="239"/>
       <c r="E43" s="1" t="s">
         <v>232</v>
@@ -10841,7 +10840,7 @@
     </row>
     <row r="44" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="200"/>
-      <c r="B44" s="427"/>
+      <c r="B44" s="419"/>
       <c r="C44" s="239"/>
       <c r="E44" s="1" t="s">
         <v>233</v>
@@ -10857,7 +10856,7 @@
     </row>
     <row r="45" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="200"/>
-      <c r="B45" s="427"/>
+      <c r="B45" s="419"/>
       <c r="C45" s="239"/>
       <c r="E45" s="1" t="s">
         <v>234</v>
@@ -10873,7 +10872,7 @@
     </row>
     <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="200"/>
-      <c r="B46" s="427"/>
+      <c r="B46" s="419"/>
       <c r="C46" s="239"/>
       <c r="E46" s="1" t="s">
         <v>235</v>
@@ -10889,7 +10888,7 @@
     </row>
     <row r="47" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="200"/>
-      <c r="B47" s="427"/>
+      <c r="B47" s="419"/>
       <c r="C47" s="239"/>
       <c r="E47" s="1" t="s">
         <v>236</v>
@@ -10905,7 +10904,7 @@
     </row>
     <row r="48" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="200"/>
-      <c r="B48" s="427"/>
+      <c r="B48" s="419"/>
       <c r="C48" s="239"/>
       <c r="D48" s="1" t="s">
         <v>237</v>
@@ -10921,7 +10920,7 @@
     </row>
     <row r="49" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="200"/>
-      <c r="B49" s="427"/>
+      <c r="B49" s="419"/>
       <c r="C49" s="248"/>
       <c r="D49" s="1" t="s">
         <v>238</v>
@@ -10935,7 +10934,7 @@
     </row>
     <row r="50" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="200"/>
-      <c r="B50" s="427"/>
+      <c r="B50" s="419"/>
       <c r="C50" s="239"/>
       <c r="E50" s="1" t="s">
         <v>239</v>
@@ -10951,7 +10950,7 @@
     </row>
     <row r="51" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="200"/>
-      <c r="B51" s="427"/>
+      <c r="B51" s="419"/>
       <c r="C51" s="239"/>
       <c r="E51" s="1" t="s">
         <v>240</v>
@@ -10967,7 +10966,7 @@
     </row>
     <row r="52" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="200"/>
-      <c r="B52" s="427"/>
+      <c r="B52" s="419"/>
       <c r="C52" s="239"/>
       <c r="E52" s="1" t="s">
         <v>241</v>
@@ -10983,7 +10982,7 @@
     </row>
     <row r="53" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="200"/>
-      <c r="B53" s="427"/>
+      <c r="B53" s="419"/>
       <c r="C53" s="239"/>
       <c r="E53" s="1" t="s">
         <v>242</v>
@@ -10999,7 +10998,7 @@
     </row>
     <row r="54" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="200"/>
-      <c r="B54" s="427"/>
+      <c r="B54" s="419"/>
       <c r="C54" s="239"/>
       <c r="E54" s="1" t="s">
         <v>243</v>
@@ -11015,7 +11014,7 @@
     </row>
     <row r="55" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="200"/>
-      <c r="B55" s="427"/>
+      <c r="B55" s="419"/>
       <c r="C55" s="30"/>
       <c r="D55" s="2" t="s">
         <v>244</v>
@@ -11035,7 +11034,7 @@
     </row>
     <row r="56" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="200"/>
-      <c r="B56" s="427"/>
+      <c r="B56" s="419"/>
       <c r="C56" s="56" t="s">
         <v>245</v>
       </c>
@@ -11058,7 +11057,7 @@
     </row>
     <row r="57" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="200"/>
-      <c r="B57" s="427"/>
+      <c r="B57" s="419"/>
       <c r="C57" s="45" t="s">
         <v>246</v>
       </c>
@@ -11078,7 +11077,7 @@
     </row>
     <row r="58" spans="1:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="200"/>
-      <c r="B58" s="427"/>
+      <c r="B58" s="419"/>
       <c r="C58" s="239" t="s">
         <v>247</v>
       </c>
@@ -11091,7 +11090,7 @@
     </row>
     <row r="59" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="200"/>
-      <c r="B59" s="427"/>
+      <c r="B59" s="419"/>
       <c r="C59" s="239"/>
       <c r="E59" s="1" t="s">
         <v>248</v>
@@ -11107,7 +11106,7 @@
     </row>
     <row r="60" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="200"/>
-      <c r="B60" s="427"/>
+      <c r="B60" s="419"/>
       <c r="C60" s="239"/>
       <c r="E60" s="1" t="s">
         <v>249</v>
@@ -11123,7 +11122,7 @@
     </row>
     <row r="61" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="200"/>
-      <c r="B61" s="427"/>
+      <c r="B61" s="419"/>
       <c r="C61" s="239"/>
       <c r="E61" s="1" t="s">
         <v>250</v>
@@ -11139,7 +11138,7 @@
     </row>
     <row r="62" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="200"/>
-      <c r="B62" s="427"/>
+      <c r="B62" s="419"/>
       <c r="C62" s="239"/>
       <c r="E62" s="1" t="s">
         <v>251</v>
@@ -11155,7 +11154,7 @@
     </row>
     <row r="63" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="200"/>
-      <c r="B63" s="427"/>
+      <c r="B63" s="419"/>
       <c r="C63" s="56" t="s">
         <v>252</v>
       </c>
@@ -11178,7 +11177,7 @@
     </row>
     <row r="64" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="200"/>
-      <c r="B64" s="427"/>
+      <c r="B64" s="419"/>
       <c r="C64" s="45" t="s">
         <v>253</v>
       </c>
@@ -11202,7 +11201,7 @@
     </row>
     <row r="65" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="200"/>
-      <c r="B65" s="427"/>
+      <c r="B65" s="419"/>
       <c r="C65" s="30" t="s">
         <v>254</v>
       </c>
@@ -11226,7 +11225,7 @@
     </row>
     <row r="66" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="200"/>
-      <c r="B66" s="427"/>
+      <c r="B66" s="419"/>
       <c r="C66" s="56" t="s">
         <v>255</v>
       </c>
@@ -11249,7 +11248,7 @@
     </row>
     <row r="67" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="200"/>
-      <c r="B67" s="353"/>
+      <c r="B67" s="410"/>
       <c r="C67" s="56" t="s">
         <v>256</v>
       </c>
@@ -11291,6 +11290,30 @@
     <row r="69" spans="1:16" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="I15:J17"/>
+    <mergeCell ref="G13:M14"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="F13:F17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="G12:M12"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G7:M7"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="H9:M9"/>
     <mergeCell ref="B32:B67"/>
     <mergeCell ref="B11:B31"/>
     <mergeCell ref="I18:J18"/>
@@ -11307,30 +11330,6 @@
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="K21:M21"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="F13:F17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="G12:M12"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G7:M7"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="D13:D17"/>
-    <mergeCell ref="I15:J17"/>
-    <mergeCell ref="G13:M14"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="C18:C21"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -11358,59 +11357,59 @@
   <sheetData>
     <row r="1" spans="1:56" ht="13.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="333" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="334"/>
-      <c r="D1" s="334"/>
-      <c r="E1" s="334"/>
-      <c r="F1" s="334"/>
-      <c r="G1" s="334"/>
-      <c r="H1" s="334"/>
-      <c r="I1" s="334"/>
-      <c r="J1" s="334"/>
-      <c r="K1" s="334"/>
-      <c r="L1" s="334"/>
-      <c r="M1" s="334"/>
-      <c r="N1" s="334"/>
-      <c r="O1" s="335"/>
+      <c r="B1" s="453" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="346"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
+      <c r="I1" s="346"/>
+      <c r="J1" s="346"/>
+      <c r="K1" s="346"/>
+      <c r="L1" s="346"/>
+      <c r="M1" s="346"/>
+      <c r="N1" s="346"/>
+      <c r="O1" s="454"/>
       <c r="P1" s="199"/>
     </row>
     <row r="2" spans="1:56" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="344" t="s">
+      <c r="B2" s="426" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="339"/>
-      <c r="D2" s="339"/>
-      <c r="E2" s="339"/>
-      <c r="F2" s="339"/>
-      <c r="G2" s="339"/>
-      <c r="H2" s="339"/>
-      <c r="I2" s="339"/>
-      <c r="J2" s="339"/>
-      <c r="K2" s="339"/>
-      <c r="L2" s="339"/>
-      <c r="M2" s="339"/>
-      <c r="N2" s="339"/>
-      <c r="O2" s="340"/>
+      <c r="C2" s="364"/>
+      <c r="D2" s="364"/>
+      <c r="E2" s="364"/>
+      <c r="F2" s="364"/>
+      <c r="G2" s="364"/>
+      <c r="H2" s="364"/>
+      <c r="I2" s="364"/>
+      <c r="J2" s="364"/>
+      <c r="K2" s="364"/>
+      <c r="L2" s="364"/>
+      <c r="M2" s="364"/>
+      <c r="N2" s="364"/>
+      <c r="O2" s="375"/>
       <c r="P2" s="202"/>
     </row>
     <row r="3" spans="1:56" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="346" t="s">
+      <c r="B3" s="457" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="337"/>
-      <c r="D3" s="337"/>
-      <c r="E3" s="337"/>
-      <c r="F3" s="337"/>
-      <c r="G3" s="337"/>
-      <c r="H3" s="337"/>
-      <c r="I3" s="337"/>
-      <c r="J3" s="337"/>
-      <c r="K3" s="337"/>
-      <c r="L3" s="338"/>
+      <c r="C3" s="372"/>
+      <c r="D3" s="372"/>
+      <c r="E3" s="372"/>
+      <c r="F3" s="372"/>
+      <c r="G3" s="372"/>
+      <c r="H3" s="372"/>
+      <c r="I3" s="372"/>
+      <c r="J3" s="372"/>
+      <c r="K3" s="372"/>
+      <c r="L3" s="373"/>
       <c r="M3" s="259" t="s">
         <v>3</v>
       </c>
@@ -11423,42 +11422,42 @@
     </row>
     <row r="4" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="350" t="s">
+      <c r="B4" s="459" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="337"/>
-      <c r="D4" s="336" t="str">
+      <c r="C4" s="372"/>
+      <c r="D4" s="455" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E4" s="337"/>
-      <c r="F4" s="337"/>
-      <c r="G4" s="337"/>
-      <c r="H4" s="337"/>
-      <c r="I4" s="337"/>
-      <c r="J4" s="337"/>
-      <c r="K4" s="337"/>
-      <c r="L4" s="338"/>
-      <c r="M4" s="349" t="s">
+      <c r="E4" s="372"/>
+      <c r="F4" s="372"/>
+      <c r="G4" s="372"/>
+      <c r="H4" s="372"/>
+      <c r="I4" s="372"/>
+      <c r="J4" s="372"/>
+      <c r="K4" s="372"/>
+      <c r="L4" s="373"/>
+      <c r="M4" s="415" t="s">
         <v>259</v>
       </c>
-      <c r="N4" s="337"/>
-      <c r="O4" s="338"/>
+      <c r="N4" s="372"/>
+      <c r="O4" s="373"/>
       <c r="P4" s="202"/>
     </row>
     <row r="5" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="351"/>
-      <c r="C5" s="339"/>
-      <c r="D5" s="339"/>
-      <c r="E5" s="339"/>
-      <c r="F5" s="339"/>
-      <c r="G5" s="339"/>
-      <c r="H5" s="339"/>
-      <c r="I5" s="339"/>
-      <c r="J5" s="339"/>
-      <c r="K5" s="339"/>
-      <c r="L5" s="340"/>
+      <c r="B5" s="374"/>
+      <c r="C5" s="364"/>
+      <c r="D5" s="364"/>
+      <c r="E5" s="364"/>
+      <c r="F5" s="364"/>
+      <c r="G5" s="364"/>
+      <c r="H5" s="364"/>
+      <c r="I5" s="364"/>
+      <c r="J5" s="364"/>
+      <c r="K5" s="364"/>
+      <c r="L5" s="375"/>
       <c r="M5" s="75" t="s">
         <v>6</v>
       </c>
@@ -11471,24 +11470,24 @@
     </row>
     <row r="6" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="345" t="s">
+      <c r="B6" s="432" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="342"/>
-      <c r="D6" s="342"/>
-      <c r="E6" s="342"/>
-      <c r="F6" s="342"/>
-      <c r="G6" s="343"/>
-      <c r="H6" s="345" t="s">
+      <c r="C6" s="368"/>
+      <c r="D6" s="368"/>
+      <c r="E6" s="368"/>
+      <c r="F6" s="368"/>
+      <c r="G6" s="356"/>
+      <c r="H6" s="432" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="342"/>
-      <c r="J6" s="342"/>
-      <c r="K6" s="342"/>
-      <c r="L6" s="342"/>
-      <c r="M6" s="342"/>
-      <c r="N6" s="342"/>
-      <c r="O6" s="343"/>
+      <c r="I6" s="368"/>
+      <c r="J6" s="368"/>
+      <c r="K6" s="368"/>
+      <c r="L6" s="368"/>
+      <c r="M6" s="368"/>
+      <c r="N6" s="368"/>
+      <c r="O6" s="356"/>
       <c r="P6" s="202"/>
     </row>
     <row r="7" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -11550,11 +11549,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="K9" s="347" t="str">
+      <c r="K9" s="458" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="L9" s="348"/>
+      <c r="L9" s="380"/>
       <c r="M9" s="67" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -11565,33 +11564,33 @@
     </row>
     <row r="10" spans="1:56" s="10" customFormat="1" ht="13.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="249"/>
-      <c r="B10" s="352" t="s">
+      <c r="B10" s="460" t="s">
         <v>260</v>
       </c>
-      <c r="C10" s="357" t="s">
+      <c r="C10" s="464" t="s">
         <v>261</v>
       </c>
-      <c r="D10" s="337"/>
-      <c r="E10" s="337"/>
-      <c r="F10" s="354" t="s">
+      <c r="D10" s="372"/>
+      <c r="E10" s="372"/>
+      <c r="F10" s="461" t="s">
         <v>262</v>
       </c>
-      <c r="G10" s="355"/>
-      <c r="H10" s="355"/>
-      <c r="I10" s="355"/>
-      <c r="J10" s="355"/>
-      <c r="K10" s="355"/>
-      <c r="L10" s="356"/>
-      <c r="M10" s="341" t="s">
+      <c r="G10" s="462"/>
+      <c r="H10" s="462"/>
+      <c r="I10" s="462"/>
+      <c r="J10" s="462"/>
+      <c r="K10" s="462"/>
+      <c r="L10" s="463"/>
+      <c r="M10" s="456" t="s">
         <v>263</v>
       </c>
-      <c r="N10" s="342"/>
-      <c r="O10" s="343"/>
+      <c r="N10" s="368"/>
+      <c r="O10" s="356"/>
       <c r="P10" s="201"/>
     </row>
     <row r="11" spans="1:56" s="10" customFormat="1" ht="105" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="353"/>
+      <c r="B11" s="410"/>
       <c r="C11" s="166" t="s">
         <v>264</v>
       </c>
@@ -16005,45 +16004,45 @@
   <sheetData>
     <row r="1" spans="1:11" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="408"/>
-      <c r="C1" s="409"/>
-      <c r="D1" s="409"/>
-      <c r="E1" s="409"/>
-      <c r="F1" s="409"/>
-      <c r="G1" s="409"/>
-      <c r="H1" s="409"/>
-      <c r="I1" s="409"/>
-      <c r="J1" s="409"/>
+      <c r="B1" s="369"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+      <c r="E1" s="370"/>
+      <c r="F1" s="370"/>
+      <c r="G1" s="370"/>
+      <c r="H1" s="370"/>
+      <c r="I1" s="370"/>
+      <c r="J1" s="370"/>
       <c r="K1" s="199"/>
     </row>
     <row r="2" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="438" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="338"/>
+      <c r="B2" s="435" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="372"/>
+      <c r="D2" s="372"/>
+      <c r="E2" s="372"/>
+      <c r="F2" s="372"/>
+      <c r="G2" s="372"/>
+      <c r="H2" s="372"/>
+      <c r="I2" s="372"/>
+      <c r="J2" s="373"/>
       <c r="K2" s="202"/>
     </row>
     <row r="3" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="344" t="s">
+      <c r="B3" s="426" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339"/>
-      <c r="E3" s="339"/>
-      <c r="F3" s="339"/>
-      <c r="G3" s="339"/>
-      <c r="H3" s="339"/>
-      <c r="I3" s="339"/>
-      <c r="J3" s="340"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="375"/>
       <c r="K3" s="202"/>
     </row>
     <row r="4" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -16051,12 +16050,12 @@
       <c r="B4" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="343"/>
+      <c r="C4" s="368"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="368"/>
+      <c r="F4" s="368"/>
+      <c r="G4" s="368"/>
+      <c r="H4" s="356"/>
       <c r="I4" s="144" t="s">
         <v>3</v>
       </c>
@@ -16068,33 +16067,33 @@
     </row>
     <row r="5" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="350" t="s">
+      <c r="B5" s="459" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="336" t="str">
+      <c r="C5" s="455" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="D5" s="337"/>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="338"/>
-      <c r="I5" s="349" t="s">
+      <c r="D5" s="372"/>
+      <c r="E5" s="372"/>
+      <c r="F5" s="372"/>
+      <c r="G5" s="372"/>
+      <c r="H5" s="373"/>
+      <c r="I5" s="415" t="s">
         <v>259</v>
       </c>
-      <c r="J5" s="338"/>
+      <c r="J5" s="373"/>
       <c r="K5" s="202"/>
     </row>
     <row r="6" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="339"/>
-      <c r="D6" s="339"/>
-      <c r="E6" s="339"/>
-      <c r="F6" s="339"/>
-      <c r="G6" s="339"/>
-      <c r="H6" s="340"/>
+      <c r="B6" s="374"/>
+      <c r="C6" s="364"/>
+      <c r="D6" s="364"/>
+      <c r="E6" s="364"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="375"/>
       <c r="I6" s="75" t="s">
         <v>6</v>
       </c>
@@ -16109,16 +16108,16 @@
       <c r="B7" s="465" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="342"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
-      <c r="F7" s="343"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
+      <c r="E7" s="368"/>
+      <c r="F7" s="356"/>
       <c r="G7" s="465" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="342"/>
-      <c r="I7" s="342"/>
-      <c r="J7" s="343"/>
+      <c r="H7" s="368"/>
+      <c r="I7" s="368"/>
+      <c r="J7" s="356"/>
       <c r="K7" s="202"/>
     </row>
     <row r="8" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -16188,18 +16187,18 @@
     <row r="11" spans="1:11" s="10" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
       <c r="B11" s="164"/>
-      <c r="C11" s="453" t="s">
+      <c r="C11" s="445" t="s">
         <v>295</v>
       </c>
-      <c r="D11" s="342"/>
-      <c r="E11" s="342"/>
-      <c r="F11" s="342"/>
-      <c r="G11" s="343"/>
+      <c r="D11" s="368"/>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
+      <c r="G11" s="356"/>
       <c r="H11" s="164"/>
       <c r="I11" s="466" t="s">
         <v>164</v>
       </c>
-      <c r="J11" s="452" t="s">
+      <c r="J11" s="439" t="s">
         <v>159</v>
       </c>
       <c r="K11" s="201"/>
@@ -16227,8 +16226,8 @@
       <c r="H12" s="164" t="s">
         <v>302</v>
       </c>
-      <c r="I12" s="427"/>
-      <c r="J12" s="353"/>
+      <c r="I12" s="419"/>
+      <c r="J12" s="410"/>
       <c r="K12" s="201"/>
     </row>
     <row r="13" spans="1:11" s="10" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -16254,7 +16253,7 @@
       <c r="H13" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="I13" s="353"/>
+      <c r="I13" s="410"/>
       <c r="J13" s="167"/>
       <c r="K13" s="201"/>
     </row>
@@ -18725,54 +18724,54 @@
   <sheetData>
     <row r="1" spans="1:14" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="408"/>
-      <c r="C1" s="409"/>
-      <c r="D1" s="409"/>
-      <c r="E1" s="409"/>
-      <c r="F1" s="409"/>
-      <c r="G1" s="409"/>
-      <c r="H1" s="409"/>
-      <c r="I1" s="409"/>
-      <c r="J1" s="409"/>
-      <c r="K1" s="409"/>
-      <c r="L1" s="409"/>
-      <c r="M1" s="409"/>
+      <c r="B1" s="369"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+      <c r="E1" s="370"/>
+      <c r="F1" s="370"/>
+      <c r="G1" s="370"/>
+      <c r="H1" s="370"/>
+      <c r="I1" s="370"/>
+      <c r="J1" s="370"/>
+      <c r="K1" s="370"/>
+      <c r="L1" s="370"/>
+      <c r="M1" s="370"/>
       <c r="N1" s="199"/>
     </row>
     <row r="2" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="438" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="337"/>
-      <c r="M2" s="338"/>
+      <c r="B2" s="435" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="372"/>
+      <c r="D2" s="372"/>
+      <c r="E2" s="372"/>
+      <c r="F2" s="372"/>
+      <c r="G2" s="372"/>
+      <c r="H2" s="372"/>
+      <c r="I2" s="372"/>
+      <c r="J2" s="372"/>
+      <c r="K2" s="372"/>
+      <c r="L2" s="372"/>
+      <c r="M2" s="373"/>
       <c r="N2" s="202"/>
     </row>
     <row r="3" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="344" t="s">
+      <c r="B3" s="426" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339"/>
-      <c r="E3" s="339"/>
-      <c r="F3" s="339"/>
-      <c r="G3" s="339"/>
-      <c r="H3" s="339"/>
-      <c r="I3" s="339"/>
-      <c r="J3" s="339"/>
-      <c r="K3" s="339"/>
-      <c r="L3" s="339"/>
-      <c r="M3" s="340"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
+      <c r="L3" s="364"/>
+      <c r="M3" s="375"/>
       <c r="N3" s="202"/>
     </row>
     <row r="4" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18780,14 +18779,14 @@
       <c r="B4" s="465" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="342"/>
-      <c r="J4" s="343"/>
+      <c r="C4" s="368"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="368"/>
+      <c r="F4" s="368"/>
+      <c r="G4" s="368"/>
+      <c r="H4" s="368"/>
+      <c r="I4" s="368"/>
+      <c r="J4" s="356"/>
       <c r="K4" s="144" t="s">
         <v>3</v>
       </c>
@@ -18799,38 +18798,38 @@
     </row>
     <row r="5" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="350" t="s">
+      <c r="B5" s="459" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="337"/>
-      <c r="D5" s="428" t="str">
+      <c r="C5" s="372"/>
+      <c r="D5" s="421" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="337"/>
-      <c r="J5" s="338"/>
-      <c r="K5" s="349" t="s">
+      <c r="E5" s="372"/>
+      <c r="F5" s="372"/>
+      <c r="G5" s="372"/>
+      <c r="H5" s="372"/>
+      <c r="I5" s="372"/>
+      <c r="J5" s="373"/>
+      <c r="K5" s="415" t="s">
         <v>259</v>
       </c>
-      <c r="L5" s="337"/>
-      <c r="M5" s="338"/>
+      <c r="L5" s="372"/>
+      <c r="M5" s="373"/>
       <c r="N5" s="202"/>
     </row>
     <row r="6" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="339"/>
-      <c r="D6" s="339"/>
-      <c r="E6" s="339"/>
-      <c r="F6" s="339"/>
-      <c r="G6" s="339"/>
-      <c r="H6" s="339"/>
-      <c r="I6" s="339"/>
-      <c r="J6" s="340"/>
+      <c r="B6" s="374"/>
+      <c r="C6" s="364"/>
+      <c r="D6" s="364"/>
+      <c r="E6" s="364"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="364"/>
+      <c r="I6" s="364"/>
+      <c r="J6" s="375"/>
       <c r="K6" s="75" t="s">
         <v>6</v>
       </c>
@@ -18846,19 +18845,19 @@
       <c r="B7" s="465" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="342"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
-      <c r="F7" s="342"/>
-      <c r="G7" s="343"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
+      <c r="E7" s="368"/>
+      <c r="F7" s="368"/>
+      <c r="G7" s="356"/>
       <c r="H7" s="465" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="342"/>
-      <c r="J7" s="342"/>
-      <c r="K7" s="342"/>
-      <c r="L7" s="342"/>
-      <c r="M7" s="343"/>
+      <c r="I7" s="368"/>
+      <c r="J7" s="368"/>
+      <c r="K7" s="368"/>
+      <c r="L7" s="368"/>
+      <c r="M7" s="356"/>
       <c r="N7" s="202"/>
     </row>
     <row r="8" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18920,11 +18919,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="462" t="str">
+      <c r="J10" s="440" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="339"/>
+      <c r="K10" s="364"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -18934,18 +18933,18 @@
     <row r="11" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
       <c r="B11" s="167"/>
-      <c r="C11" s="453" t="s">
+      <c r="C11" s="445" t="s">
         <v>295</v>
       </c>
-      <c r="D11" s="342"/>
-      <c r="E11" s="342"/>
-      <c r="F11" s="342"/>
-      <c r="G11" s="343"/>
-      <c r="H11" s="453" t="s">
+      <c r="D11" s="368"/>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
+      <c r="G11" s="356"/>
+      <c r="H11" s="445" t="s">
         <v>321</v>
       </c>
-      <c r="I11" s="342"/>
-      <c r="J11" s="343"/>
+      <c r="I11" s="368"/>
+      <c r="J11" s="356"/>
       <c r="K11" s="167"/>
       <c r="L11" s="466" t="s">
         <v>164</v>
@@ -18957,54 +18956,54 @@
     </row>
     <row r="12" spans="1:14" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="249"/>
-      <c r="B12" s="452" t="s">
+      <c r="B12" s="439" t="s">
         <v>296</v>
       </c>
-      <c r="C12" s="452" t="s">
+      <c r="C12" s="439" t="s">
         <v>297</v>
       </c>
-      <c r="D12" s="452" t="s">
+      <c r="D12" s="439" t="s">
         <v>298</v>
       </c>
-      <c r="E12" s="452" t="s">
+      <c r="E12" s="439" t="s">
         <v>299</v>
       </c>
-      <c r="F12" s="452" t="s">
+      <c r="F12" s="439" t="s">
         <v>300</v>
       </c>
-      <c r="G12" s="452" t="s">
+      <c r="G12" s="439" t="s">
         <v>322</v>
       </c>
-      <c r="H12" s="452" t="s">
+      <c r="H12" s="439" t="s">
         <v>323</v>
       </c>
-      <c r="I12" s="452" t="s">
+      <c r="I12" s="439" t="s">
         <v>324</v>
       </c>
-      <c r="J12" s="452" t="s">
+      <c r="J12" s="439" t="s">
         <v>325</v>
       </c>
-      <c r="K12" s="452" t="s">
+      <c r="K12" s="439" t="s">
         <v>326</v>
       </c>
-      <c r="L12" s="427"/>
-      <c r="M12" s="427"/>
+      <c r="L12" s="419"/>
+      <c r="M12" s="419"/>
       <c r="N12" s="201"/>
     </row>
     <row r="13" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="249"/>
-      <c r="B13" s="353"/>
-      <c r="C13" s="353"/>
-      <c r="D13" s="353"/>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="G13" s="353"/>
-      <c r="H13" s="353"/>
-      <c r="I13" s="353"/>
-      <c r="J13" s="353"/>
-      <c r="K13" s="353"/>
-      <c r="L13" s="427"/>
-      <c r="M13" s="427"/>
+      <c r="B13" s="410"/>
+      <c r="C13" s="410"/>
+      <c r="D13" s="410"/>
+      <c r="E13" s="410"/>
+      <c r="F13" s="410"/>
+      <c r="G13" s="410"/>
+      <c r="H13" s="410"/>
+      <c r="I13" s="410"/>
+      <c r="J13" s="410"/>
+      <c r="K13" s="410"/>
+      <c r="L13" s="419"/>
+      <c r="M13" s="419"/>
       <c r="N13" s="201"/>
     </row>
     <row r="14" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19039,7 +19038,7 @@
       <c r="K14" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="L14" s="353"/>
+      <c r="L14" s="410"/>
       <c r="M14" s="167"/>
       <c r="N14" s="201"/>
     </row>
@@ -22000,13 +21999,6 @@
     <row r="81" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="D5:J6"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
     <mergeCell ref="L11:L14"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="H11:J11"/>
@@ -22023,6 +22015,13 @@
     <mergeCell ref="B3:M3"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="D5:J6"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
     <mergeCell ref="B12:B13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -22053,70 +22052,70 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="471"/>
-      <c r="C1" s="409"/>
-      <c r="D1" s="409"/>
-      <c r="E1" s="409"/>
-      <c r="F1" s="409"/>
-      <c r="G1" s="409"/>
-      <c r="H1" s="409"/>
-      <c r="I1" s="409"/>
-      <c r="J1" s="409"/>
-      <c r="K1" s="409"/>
-      <c r="L1" s="409"/>
+      <c r="B1" s="469"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+      <c r="E1" s="370"/>
+      <c r="F1" s="370"/>
+      <c r="G1" s="370"/>
+      <c r="H1" s="370"/>
+      <c r="I1" s="370"/>
+      <c r="J1" s="370"/>
+      <c r="K1" s="370"/>
+      <c r="L1" s="370"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="438" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="338"/>
+      <c r="B2" s="435" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="372"/>
+      <c r="D2" s="372"/>
+      <c r="E2" s="372"/>
+      <c r="F2" s="372"/>
+      <c r="G2" s="372"/>
+      <c r="H2" s="372"/>
+      <c r="I2" s="372"/>
+      <c r="J2" s="372"/>
+      <c r="K2" s="372"/>
+      <c r="L2" s="373"/>
       <c r="M2" s="202"/>
     </row>
     <row r="3" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="344" t="s">
+      <c r="B3" s="426" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339"/>
-      <c r="E3" s="339"/>
-      <c r="F3" s="339"/>
-      <c r="G3" s="339"/>
-      <c r="H3" s="339"/>
-      <c r="I3" s="339"/>
-      <c r="J3" s="339"/>
-      <c r="K3" s="339"/>
-      <c r="L3" s="340"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
+      <c r="L3" s="375"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="345" t="s">
+      <c r="B4" s="432" t="s">
         <v>333</v>
       </c>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="343"/>
-      <c r="J4" s="468" t="s">
+      <c r="C4" s="368"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="368"/>
+      <c r="F4" s="368"/>
+      <c r="G4" s="368"/>
+      <c r="H4" s="368"/>
+      <c r="I4" s="356"/>
+      <c r="J4" s="475" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="342"/>
-      <c r="L4" s="343"/>
+      <c r="K4" s="368"/>
+      <c r="L4" s="356"/>
       <c r="M4" s="202"/>
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -22124,16 +22123,16 @@
       <c r="B5" s="451" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="338"/>
-      <c r="D5" s="475" t="str">
+      <c r="C5" s="373"/>
+      <c r="D5" s="474" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="338"/>
+      <c r="E5" s="372"/>
+      <c r="F5" s="372"/>
+      <c r="G5" s="372"/>
+      <c r="H5" s="372"/>
+      <c r="I5" s="373"/>
       <c r="J5" s="49" t="s">
         <v>6</v>
       </c>
@@ -22145,14 +22144,14 @@
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="340"/>
-      <c r="D6" s="351"/>
-      <c r="E6" s="339"/>
-      <c r="F6" s="339"/>
-      <c r="G6" s="339"/>
-      <c r="H6" s="339"/>
-      <c r="I6" s="340"/>
+      <c r="B6" s="374"/>
+      <c r="C6" s="375"/>
+      <c r="D6" s="374"/>
+      <c r="E6" s="364"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="364"/>
+      <c r="I6" s="375"/>
       <c r="J6" s="31" t="s">
         <v>3</v>
       </c>
@@ -22164,21 +22163,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="345" t="s">
+      <c r="B7" s="432" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="342"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
-      <c r="F7" s="342"/>
-      <c r="G7" s="343"/>
-      <c r="H7" s="345" t="s">
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
+      <c r="E7" s="368"/>
+      <c r="F7" s="368"/>
+      <c r="G7" s="356"/>
+      <c r="H7" s="432" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="342"/>
-      <c r="J7" s="342"/>
-      <c r="K7" s="342"/>
-      <c r="L7" s="343"/>
+      <c r="I7" s="368"/>
+      <c r="J7" s="368"/>
+      <c r="K7" s="368"/>
+      <c r="L7" s="356"/>
       <c r="M7" s="202"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -22238,11 +22237,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="462" t="str">
+      <c r="J10" s="440" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="339"/>
+      <c r="K10" s="364"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -22370,42 +22369,42 @@
     </row>
     <row r="25" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="200"/>
-      <c r="B25" s="472" t="s">
+      <c r="B25" s="471" t="s">
         <v>340</v>
       </c>
-      <c r="C25" s="456"/>
-      <c r="D25" s="348"/>
-      <c r="E25" s="348"/>
-      <c r="F25" s="348"/>
-      <c r="G25" s="348"/>
-      <c r="H25" s="348"/>
-      <c r="I25" s="348"/>
-      <c r="J25" s="348"/>
-      <c r="K25" s="348"/>
-      <c r="L25" s="405"/>
+      <c r="C25" s="443"/>
+      <c r="D25" s="380"/>
+      <c r="E25" s="380"/>
+      <c r="F25" s="380"/>
+      <c r="G25" s="380"/>
+      <c r="H25" s="380"/>
+      <c r="I25" s="380"/>
+      <c r="J25" s="380"/>
+      <c r="K25" s="380"/>
+      <c r="L25" s="381"/>
       <c r="M25" s="202"/>
     </row>
     <row r="26" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="200"/>
-      <c r="B26" s="429"/>
-      <c r="C26" s="456"/>
-      <c r="D26" s="348"/>
-      <c r="E26" s="348"/>
-      <c r="F26" s="348"/>
-      <c r="G26" s="348"/>
-      <c r="H26" s="348"/>
-      <c r="I26" s="348"/>
-      <c r="J26" s="348"/>
-      <c r="K26" s="348"/>
-      <c r="L26" s="405"/>
+      <c r="B26" s="422"/>
+      <c r="C26" s="443"/>
+      <c r="D26" s="380"/>
+      <c r="E26" s="380"/>
+      <c r="F26" s="380"/>
+      <c r="G26" s="380"/>
+      <c r="H26" s="380"/>
+      <c r="I26" s="380"/>
+      <c r="J26" s="380"/>
+      <c r="K26" s="380"/>
+      <c r="L26" s="381"/>
       <c r="M26" s="202"/>
     </row>
     <row r="27" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="200"/>
-      <c r="B27" s="469" t="s">
+      <c r="B27" s="470" t="s">
         <v>341</v>
       </c>
-      <c r="C27" s="456"/>
+      <c r="C27" s="443"/>
       <c r="D27" s="324" t="e">
         <f>'QUADRO II'!F17</f>
         <v>#VALUE!</v>
@@ -22426,10 +22425,10 @@
     </row>
     <row r="28" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="200"/>
-      <c r="B28" s="469" t="s">
+      <c r="B28" s="470" t="s">
         <v>344</v>
       </c>
-      <c r="C28" s="456"/>
+      <c r="C28" s="443"/>
       <c r="D28" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22449,10 +22448,10 @@
     </row>
     <row r="29" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="200"/>
-      <c r="B29" s="469" t="s">
+      <c r="B29" s="470" t="s">
         <v>345</v>
       </c>
-      <c r="C29" s="456"/>
+      <c r="C29" s="443"/>
       <c r="D29" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22472,10 +22471,10 @@
     </row>
     <row r="30" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="200"/>
-      <c r="B30" s="469" t="s">
+      <c r="B30" s="470" t="s">
         <v>346</v>
       </c>
-      <c r="C30" s="456"/>
+      <c r="C30" s="443"/>
       <c r="D30" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22495,10 +22494,10 @@
     </row>
     <row r="31" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="200"/>
-      <c r="B31" s="469" t="s">
+      <c r="B31" s="470" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="456"/>
+      <c r="C31" s="443"/>
       <c r="D31" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22518,10 +22517,10 @@
     </row>
     <row r="32" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="200"/>
-      <c r="B32" s="469" t="s">
+      <c r="B32" s="470" t="s">
         <v>348</v>
       </c>
-      <c r="C32" s="456"/>
+      <c r="C32" s="443"/>
       <c r="D32" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22557,70 +22556,70 @@
     <row r="35" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="200"/>
       <c r="B35" s="271"/>
-      <c r="D35" s="474"/>
-      <c r="E35" s="348"/>
+      <c r="D35" s="473"/>
+      <c r="E35" s="380"/>
       <c r="L35" s="4"/>
       <c r="M35" s="202"/>
     </row>
     <row r="36" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="200"/>
-      <c r="B36" s="470" t="s">
+      <c r="B36" s="468" t="s">
         <v>350</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="338"/>
-      <c r="G36" s="473"/>
-      <c r="H36" s="337"/>
-      <c r="I36" s="337"/>
-      <c r="J36" s="337"/>
-      <c r="K36" s="338"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="373"/>
+      <c r="G36" s="472"/>
+      <c r="H36" s="372"/>
+      <c r="I36" s="372"/>
+      <c r="J36" s="372"/>
+      <c r="K36" s="373"/>
       <c r="L36" s="4"/>
       <c r="M36" s="202"/>
     </row>
     <row r="37" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="200"/>
-      <c r="B37" s="429"/>
-      <c r="C37" s="456"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="405"/>
-      <c r="G37" s="429"/>
-      <c r="H37" s="348"/>
-      <c r="I37" s="348"/>
-      <c r="J37" s="348"/>
-      <c r="K37" s="405"/>
+      <c r="B37" s="422"/>
+      <c r="C37" s="443"/>
+      <c r="D37" s="380"/>
+      <c r="E37" s="380"/>
+      <c r="F37" s="381"/>
+      <c r="G37" s="422"/>
+      <c r="H37" s="380"/>
+      <c r="I37" s="380"/>
+      <c r="J37" s="380"/>
+      <c r="K37" s="381"/>
       <c r="L37" s="4"/>
       <c r="M37" s="202"/>
     </row>
     <row r="38" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="200"/>
-      <c r="B38" s="429"/>
-      <c r="C38" s="456"/>
-      <c r="D38" s="348"/>
-      <c r="E38" s="348"/>
-      <c r="F38" s="405"/>
-      <c r="G38" s="429"/>
-      <c r="H38" s="348"/>
-      <c r="I38" s="348"/>
-      <c r="J38" s="348"/>
-      <c r="K38" s="405"/>
+      <c r="B38" s="422"/>
+      <c r="C38" s="443"/>
+      <c r="D38" s="380"/>
+      <c r="E38" s="380"/>
+      <c r="F38" s="381"/>
+      <c r="G38" s="422"/>
+      <c r="H38" s="380"/>
+      <c r="I38" s="380"/>
+      <c r="J38" s="380"/>
+      <c r="K38" s="381"/>
       <c r="L38" s="4"/>
       <c r="M38" s="202"/>
     </row>
     <row r="39" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="200"/>
-      <c r="B39" s="351"/>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="340"/>
-      <c r="G39" s="351"/>
-      <c r="H39" s="339"/>
-      <c r="I39" s="339"/>
-      <c r="J39" s="339"/>
-      <c r="K39" s="340"/>
+      <c r="B39" s="374"/>
+      <c r="C39" s="364"/>
+      <c r="D39" s="364"/>
+      <c r="E39" s="364"/>
+      <c r="F39" s="375"/>
+      <c r="G39" s="374"/>
+      <c r="H39" s="364"/>
+      <c r="I39" s="364"/>
+      <c r="J39" s="364"/>
+      <c r="K39" s="375"/>
       <c r="L39" s="4"/>
       <c r="M39" s="202"/>
     </row>
@@ -22664,6 +22663,10 @@
     <row r="43" spans="1:13" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="B2:L2"/>
     <mergeCell ref="B36:F39"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B29:C29"/>
@@ -22680,10 +22683,6 @@
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="B2:L2"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>

--- a/QUADROS ABNT.xlsx
+++ b/QUADROS ABNT.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D097D1A-7D02-492D-BF92-1C0D7326E169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="976" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA" sheetId="1" r:id="rId1"/>
@@ -3301,46 +3301,68 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3353,34 +3375,104 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3388,10 +3480,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3402,18 +3490,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3421,182 +3509,94 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="39" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="39" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="39" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="39" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3638,15 +3638,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3662,9 +3662,31 @@
     <xf numFmtId="39" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3674,61 +3696,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4057,15 +4057,15 @@
   <sheetData>
     <row r="1" spans="1:9" ht="40.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A1" s="168"/>
-      <c r="B1" s="345" t="s">
+      <c r="B1" s="359" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
-      <c r="H1" s="346"/>
+      <c r="C1" s="355"/>
+      <c r="D1" s="355"/>
+      <c r="E1" s="355"/>
+      <c r="F1" s="355"/>
+      <c r="G1" s="355"/>
+      <c r="H1" s="355"/>
       <c r="I1" s="169"/>
     </row>
     <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4082,15 +4082,15 @@
       <c r="B3" s="178" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="347" t="s">
+      <c r="C3" s="360" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="334"/>
-      <c r="E3" s="334"/>
-      <c r="F3" s="334"/>
-      <c r="G3" s="334"/>
-      <c r="H3" s="334"/>
-      <c r="I3" s="348"/>
+      <c r="D3" s="361"/>
+      <c r="E3" s="361"/>
+      <c r="F3" s="361"/>
+      <c r="G3" s="361"/>
+      <c r="H3" s="361"/>
+      <c r="I3" s="362"/>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="170"/>
@@ -4135,32 +4135,32 @@
     </row>
     <row r="7" spans="1:9" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="170"/>
-      <c r="B7" s="349" t="s">
+      <c r="B7" s="363" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="350"/>
-      <c r="D7" s="335" t="s">
+      <c r="C7" s="364"/>
+      <c r="D7" s="370" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="337" t="s">
+      <c r="E7" s="372" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="344" t="s">
+      <c r="F7" s="379" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="353" t="s">
+      <c r="G7" s="367" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="354"/>
+      <c r="H7" s="368"/>
       <c r="I7" s="171"/>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="170"/>
-      <c r="B8" s="351"/>
-      <c r="C8" s="352"/>
-      <c r="D8" s="336"/>
-      <c r="E8" s="336"/>
-      <c r="F8" s="336"/>
+      <c r="B8" s="365"/>
+      <c r="C8" s="366"/>
+      <c r="D8" s="371"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
       <c r="G8" s="177" t="s">
         <v>45</v>
       </c>
@@ -4226,17 +4226,17 @@
       <c r="I10" s="171"/>
     </row>
     <row r="11" spans="1:9" ht="38.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="341" t="s">
+      <c r="A11" s="376" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="342"/>
-      <c r="C11" s="342"/>
-      <c r="D11" s="342"/>
-      <c r="E11" s="342"/>
-      <c r="F11" s="342"/>
-      <c r="G11" s="342"/>
-      <c r="H11" s="342"/>
-      <c r="I11" s="343"/>
+      <c r="B11" s="377"/>
+      <c r="C11" s="377"/>
+      <c r="D11" s="377"/>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
+      <c r="G11" s="377"/>
+      <c r="H11" s="377"/>
+      <c r="I11" s="378"/>
     </row>
     <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="170"/>
@@ -4244,42 +4244,42 @@
     </row>
     <row r="13" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="170"/>
-      <c r="B13" s="333" t="s">
+      <c r="B13" s="369" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="334"/>
-      <c r="D13" s="334"/>
-      <c r="E13" s="334"/>
-      <c r="F13" s="334"/>
-      <c r="G13" s="334"/>
-      <c r="H13" s="334"/>
+      <c r="C13" s="361"/>
+      <c r="D13" s="361"/>
+      <c r="E13" s="361"/>
+      <c r="F13" s="361"/>
+      <c r="G13" s="361"/>
+      <c r="H13" s="361"/>
       <c r="I13" s="171"/>
     </row>
     <row r="14" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="338" t="s">
+      <c r="A14" s="373" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="339"/>
-      <c r="C14" s="339"/>
-      <c r="D14" s="339"/>
-      <c r="E14" s="339"/>
-      <c r="F14" s="339"/>
-      <c r="G14" s="339"/>
-      <c r="H14" s="339"/>
-      <c r="I14" s="340"/>
+      <c r="B14" s="374"/>
+      <c r="C14" s="374"/>
+      <c r="D14" s="374"/>
+      <c r="E14" s="374"/>
+      <c r="F14" s="374"/>
+      <c r="G14" s="374"/>
+      <c r="H14" s="374"/>
+      <c r="I14" s="375"/>
     </row>
     <row r="15" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="338" t="s">
+      <c r="A15" s="373" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="339"/>
-      <c r="C15" s="339"/>
-      <c r="D15" s="339"/>
-      <c r="E15" s="339"/>
-      <c r="F15" s="339"/>
-      <c r="G15" s="339"/>
-      <c r="H15" s="339"/>
-      <c r="I15" s="340"/>
+      <c r="B15" s="374"/>
+      <c r="C15" s="374"/>
+      <c r="D15" s="374"/>
+      <c r="E15" s="374"/>
+      <c r="F15" s="374"/>
+      <c r="G15" s="374"/>
+      <c r="H15" s="374"/>
+      <c r="I15" s="375"/>
     </row>
     <row r="16" spans="1:9" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="172"/>
@@ -4296,6 +4296,10 @@
     <row r="18" ht="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="B7:C8"/>
@@ -4303,10 +4307,6 @@
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="F7:F8"/>
   </mergeCells>
   <pageMargins left="1.181102362204725" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="52" orientation="portrait"/>
@@ -4334,65 +4334,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="369"/>
-      <c r="C1" s="370"/>
-      <c r="D1" s="370"/>
-      <c r="E1" s="370"/>
-      <c r="F1" s="370"/>
-      <c r="G1" s="370"/>
-      <c r="H1" s="370"/>
-      <c r="I1" s="370"/>
-      <c r="J1" s="370"/>
-      <c r="K1" s="370"/>
-      <c r="L1" s="370"/>
+      <c r="B1" s="409"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
+      <c r="K1" s="410"/>
+      <c r="L1" s="410"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="435" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="372"/>
-      <c r="D2" s="372"/>
-      <c r="E2" s="372"/>
-      <c r="F2" s="372"/>
-      <c r="G2" s="372"/>
-      <c r="H2" s="372"/>
-      <c r="I2" s="372"/>
-      <c r="J2" s="372"/>
-      <c r="K2" s="372"/>
-      <c r="L2" s="373"/>
+      <c r="B2" s="424" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
+      <c r="J2" s="342"/>
+      <c r="K2" s="342"/>
+      <c r="L2" s="343"/>
       <c r="M2" s="202"/>
     </row>
     <row r="3" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="426" t="s">
+      <c r="B3" s="436" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
-      <c r="L3" s="375"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
+      <c r="F3" s="344"/>
+      <c r="G3" s="344"/>
+      <c r="H3" s="344"/>
+      <c r="I3" s="344"/>
+      <c r="J3" s="344"/>
+      <c r="K3" s="344"/>
+      <c r="L3" s="345"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="432" t="s">
+      <c r="B4" s="431" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="368"/>
-      <c r="D4" s="368"/>
-      <c r="E4" s="368"/>
-      <c r="F4" s="368"/>
-      <c r="G4" s="368"/>
-      <c r="H4" s="368"/>
-      <c r="I4" s="356"/>
+      <c r="C4" s="337"/>
+      <c r="D4" s="337"/>
+      <c r="E4" s="337"/>
+      <c r="F4" s="337"/>
+      <c r="G4" s="337"/>
+      <c r="H4" s="337"/>
+      <c r="I4" s="334"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -4405,36 +4405,36 @@
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="487" t="s">
+      <c r="B5" s="476" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="373"/>
+      <c r="C5" s="343"/>
       <c r="D5" s="474" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="372"/>
-      <c r="F5" s="372"/>
-      <c r="G5" s="372"/>
-      <c r="H5" s="372"/>
-      <c r="I5" s="373"/>
-      <c r="J5" s="429" t="s">
+      <c r="E5" s="342"/>
+      <c r="F5" s="342"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="342"/>
+      <c r="I5" s="343"/>
+      <c r="J5" s="437" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="368"/>
-      <c r="L5" s="356"/>
+      <c r="K5" s="337"/>
+      <c r="L5" s="334"/>
       <c r="M5" s="202"/>
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="374"/>
-      <c r="C6" s="375"/>
-      <c r="D6" s="374"/>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
-      <c r="G6" s="364"/>
-      <c r="H6" s="364"/>
-      <c r="I6" s="375"/>
+      <c r="B6" s="348"/>
+      <c r="C6" s="345"/>
+      <c r="D6" s="348"/>
+      <c r="E6" s="344"/>
+      <c r="F6" s="344"/>
+      <c r="G6" s="344"/>
+      <c r="H6" s="344"/>
+      <c r="I6" s="345"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -4447,21 +4447,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="432" t="s">
+      <c r="B7" s="431" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
-      <c r="E7" s="368"/>
-      <c r="F7" s="368"/>
-      <c r="G7" s="356"/>
-      <c r="H7" s="432" t="s">
+      <c r="C7" s="337"/>
+      <c r="D7" s="337"/>
+      <c r="E7" s="337"/>
+      <c r="F7" s="337"/>
+      <c r="G7" s="334"/>
+      <c r="H7" s="431" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="368"/>
-      <c r="J7" s="368"/>
-      <c r="K7" s="368"/>
-      <c r="L7" s="356"/>
+      <c r="I7" s="337"/>
+      <c r="J7" s="337"/>
+      <c r="K7" s="337"/>
+      <c r="L7" s="334"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -4521,11 +4521,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="440" t="str">
+      <c r="J10" s="450" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="364"/>
+      <c r="K10" s="344"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -4540,230 +4540,231 @@
     </row>
     <row r="12" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="200"/>
-      <c r="B12" s="488" t="s">
+      <c r="B12" s="480" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="482"/>
-      <c r="D12" s="481" t="s">
+      <c r="C12" s="481"/>
+      <c r="D12" s="482" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="482"/>
-      <c r="F12" s="481" t="s">
+      <c r="E12" s="481"/>
+      <c r="F12" s="482" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="482"/>
-      <c r="H12" s="481" t="s">
+      <c r="G12" s="481"/>
+      <c r="H12" s="482" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="483"/>
-      <c r="J12" s="483"/>
-      <c r="K12" s="483"/>
-      <c r="L12" s="482"/>
+      <c r="I12" s="488"/>
+      <c r="J12" s="488"/>
+      <c r="K12" s="488"/>
+      <c r="L12" s="481"/>
       <c r="M12" s="202"/>
     </row>
     <row r="13" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="200"/>
-      <c r="B13" s="477" t="s">
+      <c r="B13" s="485" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="375"/>
-      <c r="D13" s="480" t="s">
+      <c r="C13" s="345"/>
+      <c r="D13" s="484" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="375"/>
-      <c r="F13" s="480" t="s">
+      <c r="E13" s="345"/>
+      <c r="F13" s="484" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="375"/>
-      <c r="H13" s="479" t="s">
+      <c r="G13" s="345"/>
+      <c r="H13" s="487" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="364"/>
-      <c r="J13" s="364"/>
-      <c r="K13" s="364"/>
-      <c r="L13" s="375"/>
+      <c r="I13" s="344"/>
+      <c r="J13" s="344"/>
+      <c r="K13" s="344"/>
+      <c r="L13" s="345"/>
       <c r="M13" s="202"/>
     </row>
     <row r="14" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="200"/>
-      <c r="B14" s="476" t="s">
+      <c r="B14" s="479" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="356"/>
-      <c r="D14" s="485" t="s">
+      <c r="C14" s="334"/>
+      <c r="D14" s="477" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="485" t="s">
+      <c r="E14" s="334"/>
+      <c r="F14" s="477" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="356"/>
-      <c r="H14" s="355"/>
-      <c r="I14" s="368"/>
-      <c r="J14" s="368"/>
-      <c r="K14" s="368"/>
-      <c r="L14" s="356"/>
+      <c r="G14" s="334"/>
+      <c r="H14" s="423"/>
+      <c r="I14" s="337"/>
+      <c r="J14" s="337"/>
+      <c r="K14" s="337"/>
+      <c r="L14" s="334"/>
       <c r="M14" s="202"/>
     </row>
     <row r="15" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="200"/>
-      <c r="B15" s="476" t="s">
+      <c r="B15" s="479" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="356"/>
-      <c r="D15" s="485" t="s">
+      <c r="C15" s="334"/>
+      <c r="D15" s="477" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="356"/>
-      <c r="F15" s="485" t="s">
+      <c r="E15" s="334"/>
+      <c r="F15" s="477" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="356"/>
-      <c r="H15" s="355"/>
-      <c r="I15" s="368"/>
-      <c r="J15" s="368"/>
-      <c r="K15" s="368"/>
-      <c r="L15" s="356"/>
+      <c r="G15" s="334"/>
+      <c r="H15" s="423"/>
+      <c r="I15" s="337"/>
+      <c r="J15" s="337"/>
+      <c r="K15" s="337"/>
+      <c r="L15" s="334"/>
       <c r="M15" s="202"/>
     </row>
     <row r="16" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="200"/>
-      <c r="B16" s="476" t="s">
+      <c r="B16" s="479" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="356"/>
-      <c r="D16" s="478" t="s">
+      <c r="C16" s="334"/>
+      <c r="D16" s="486" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="356"/>
-      <c r="F16" s="486" t="s">
+      <c r="E16" s="334"/>
+      <c r="F16" s="478" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="356"/>
-      <c r="H16" s="355"/>
-      <c r="I16" s="368"/>
-      <c r="J16" s="368"/>
-      <c r="K16" s="368"/>
-      <c r="L16" s="356"/>
+      <c r="G16" s="334"/>
+      <c r="H16" s="423"/>
+      <c r="I16" s="337"/>
+      <c r="J16" s="337"/>
+      <c r="K16" s="337"/>
+      <c r="L16" s="334"/>
       <c r="M16" s="202"/>
     </row>
     <row r="17" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="200"/>
-      <c r="B17" s="476" t="s">
+      <c r="B17" s="479" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="356"/>
-      <c r="D17" s="485" t="s">
+      <c r="C17" s="334"/>
+      <c r="D17" s="477" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="356"/>
-      <c r="F17" s="485" t="s">
+      <c r="E17" s="334"/>
+      <c r="F17" s="477" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="356"/>
-      <c r="H17" s="355"/>
-      <c r="I17" s="368"/>
-      <c r="J17" s="368"/>
-      <c r="K17" s="368"/>
-      <c r="L17" s="356"/>
+      <c r="G17" s="334"/>
+      <c r="H17" s="423"/>
+      <c r="I17" s="337"/>
+      <c r="J17" s="337"/>
+      <c r="K17" s="337"/>
+      <c r="L17" s="334"/>
       <c r="M17" s="202"/>
     </row>
     <row r="18" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="200"/>
-      <c r="B18" s="476" t="s">
+      <c r="B18" s="479" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="485" t="s">
+      <c r="C18" s="334"/>
+      <c r="D18" s="477" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="356"/>
-      <c r="F18" s="485" t="s">
+      <c r="E18" s="334"/>
+      <c r="F18" s="477" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="356"/>
-      <c r="H18" s="355"/>
-      <c r="I18" s="368"/>
-      <c r="J18" s="368"/>
-      <c r="K18" s="368"/>
-      <c r="L18" s="356"/>
+      <c r="G18" s="334"/>
+      <c r="H18" s="423"/>
+      <c r="I18" s="337"/>
+      <c r="J18" s="337"/>
+      <c r="K18" s="337"/>
+      <c r="L18" s="334"/>
       <c r="M18" s="202"/>
     </row>
     <row r="19" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="200"/>
-      <c r="B19" s="476" t="s">
+      <c r="B19" s="479" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="356"/>
-      <c r="D19" s="485" t="s">
+      <c r="C19" s="334"/>
+      <c r="D19" s="477" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="356"/>
-      <c r="F19" s="485" t="s">
+      <c r="E19" s="334"/>
+      <c r="F19" s="477" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="356"/>
-      <c r="H19" s="445"/>
-      <c r="I19" s="368"/>
-      <c r="J19" s="368"/>
-      <c r="K19" s="368"/>
-      <c r="L19" s="356"/>
+      <c r="G19" s="334"/>
+      <c r="H19" s="441"/>
+      <c r="I19" s="337"/>
+      <c r="J19" s="337"/>
+      <c r="K19" s="337"/>
+      <c r="L19" s="334"/>
       <c r="M19" s="202"/>
     </row>
     <row r="20" spans="1:13" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="476" t="s">
+      <c r="B20" s="479" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="356"/>
-      <c r="D20" s="486" t="s">
+      <c r="C20" s="334"/>
+      <c r="D20" s="478" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="356"/>
-      <c r="F20" s="486" t="s">
+      <c r="E20" s="334"/>
+      <c r="F20" s="478" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="356"/>
-      <c r="H20" s="445"/>
-      <c r="I20" s="368"/>
-      <c r="J20" s="368"/>
-      <c r="K20" s="368"/>
-      <c r="L20" s="356"/>
+      <c r="G20" s="334"/>
+      <c r="H20" s="441"/>
+      <c r="I20" s="337"/>
+      <c r="J20" s="337"/>
+      <c r="K20" s="337"/>
+      <c r="L20" s="334"/>
       <c r="M20" s="202"/>
     </row>
     <row r="21" spans="1:13" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="203"/>
-      <c r="B21" s="484"/>
-      <c r="C21" s="378"/>
-      <c r="D21" s="378"/>
-      <c r="E21" s="378"/>
-      <c r="F21" s="378"/>
-      <c r="G21" s="378"/>
-      <c r="H21" s="378"/>
-      <c r="I21" s="378"/>
-      <c r="J21" s="378"/>
-      <c r="K21" s="378"/>
-      <c r="L21" s="378"/>
+      <c r="B21" s="483"/>
+      <c r="C21" s="414"/>
+      <c r="D21" s="414"/>
+      <c r="E21" s="414"/>
+      <c r="F21" s="414"/>
+      <c r="G21" s="414"/>
+      <c r="H21" s="414"/>
+      <c r="I21" s="414"/>
+      <c r="J21" s="414"/>
+      <c r="K21" s="414"/>
+      <c r="L21" s="414"/>
       <c r="M21" s="204"/>
     </row>
     <row r="22" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="H17:L17"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="H12:L12"/>
     <mergeCell ref="B21:L21"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="D13:E13"/>
@@ -4780,22 +4781,21 @@
     <mergeCell ref="H18:L18"/>
     <mergeCell ref="H14:L14"/>
     <mergeCell ref="F14:G14"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="H17:L17"/>
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="D14:E14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -4818,65 +4818,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="369"/>
-      <c r="C1" s="370"/>
-      <c r="D1" s="370"/>
-      <c r="E1" s="370"/>
-      <c r="F1" s="370"/>
-      <c r="G1" s="370"/>
-      <c r="H1" s="370"/>
-      <c r="I1" s="370"/>
-      <c r="J1" s="370"/>
-      <c r="K1" s="370"/>
-      <c r="L1" s="370"/>
+      <c r="B1" s="409"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
+      <c r="K1" s="410"/>
+      <c r="L1" s="410"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="435" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="372"/>
-      <c r="D2" s="372"/>
-      <c r="E2" s="372"/>
-      <c r="F2" s="372"/>
-      <c r="G2" s="372"/>
-      <c r="H2" s="372"/>
-      <c r="I2" s="372"/>
-      <c r="J2" s="372"/>
-      <c r="K2" s="372"/>
-      <c r="L2" s="373"/>
+      <c r="B2" s="424" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
+      <c r="J2" s="342"/>
+      <c r="K2" s="342"/>
+      <c r="L2" s="343"/>
       <c r="M2" s="282"/>
     </row>
     <row r="3" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="426" t="s">
+      <c r="B3" s="436" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
-      <c r="L3" s="375"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
+      <c r="F3" s="344"/>
+      <c r="G3" s="344"/>
+      <c r="H3" s="344"/>
+      <c r="I3" s="344"/>
+      <c r="J3" s="344"/>
+      <c r="K3" s="344"/>
+      <c r="L3" s="345"/>
       <c r="M3" s="282"/>
     </row>
     <row r="4" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="432" t="s">
+      <c r="B4" s="431" t="s">
         <v>351</v>
       </c>
-      <c r="C4" s="368"/>
-      <c r="D4" s="368"/>
-      <c r="E4" s="368"/>
-      <c r="F4" s="368"/>
-      <c r="G4" s="368"/>
-      <c r="H4" s="368"/>
-      <c r="I4" s="356"/>
+      <c r="C4" s="337"/>
+      <c r="D4" s="337"/>
+      <c r="E4" s="337"/>
+      <c r="F4" s="337"/>
+      <c r="G4" s="337"/>
+      <c r="H4" s="337"/>
+      <c r="I4" s="334"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -4889,36 +4889,36 @@
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="487" t="s">
+      <c r="B5" s="476" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="373"/>
+      <c r="C5" s="343"/>
       <c r="D5" s="474" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="372"/>
-      <c r="F5" s="372"/>
-      <c r="G5" s="372"/>
-      <c r="H5" s="372"/>
-      <c r="I5" s="373"/>
-      <c r="J5" s="429" t="s">
+      <c r="E5" s="342"/>
+      <c r="F5" s="342"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="342"/>
+      <c r="I5" s="343"/>
+      <c r="J5" s="437" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="368"/>
-      <c r="L5" s="356"/>
+      <c r="K5" s="337"/>
+      <c r="L5" s="334"/>
       <c r="M5" s="213"/>
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="374"/>
-      <c r="C6" s="375"/>
-      <c r="D6" s="374"/>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
-      <c r="G6" s="364"/>
-      <c r="H6" s="364"/>
-      <c r="I6" s="375"/>
+      <c r="B6" s="348"/>
+      <c r="C6" s="345"/>
+      <c r="D6" s="348"/>
+      <c r="E6" s="344"/>
+      <c r="F6" s="344"/>
+      <c r="G6" s="344"/>
+      <c r="H6" s="344"/>
+      <c r="I6" s="345"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -4931,21 +4931,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="432" t="s">
+      <c r="B7" s="431" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
-      <c r="E7" s="368"/>
-      <c r="F7" s="368"/>
-      <c r="G7" s="356"/>
-      <c r="H7" s="432" t="s">
+      <c r="C7" s="337"/>
+      <c r="D7" s="337"/>
+      <c r="E7" s="337"/>
+      <c r="F7" s="337"/>
+      <c r="G7" s="334"/>
+      <c r="H7" s="431" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="368"/>
-      <c r="J7" s="368"/>
-      <c r="K7" s="368"/>
-      <c r="L7" s="356"/>
+      <c r="I7" s="337"/>
+      <c r="J7" s="337"/>
+      <c r="K7" s="337"/>
+      <c r="L7" s="334"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -5005,11 +5005,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="440" t="str">
+      <c r="J10" s="450" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="364"/>
+      <c r="K10" s="344"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -5024,24 +5024,24 @@
     </row>
     <row r="12" spans="1:13" s="25" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="285"/>
-      <c r="B12" s="488" t="s">
+      <c r="B12" s="480" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="482"/>
-      <c r="D12" s="481" t="s">
+      <c r="C12" s="481"/>
+      <c r="D12" s="482" t="s">
         <v>353</v>
       </c>
-      <c r="E12" s="483"/>
-      <c r="F12" s="482"/>
-      <c r="G12" s="481" t="s">
+      <c r="E12" s="488"/>
+      <c r="F12" s="481"/>
+      <c r="G12" s="482" t="s">
         <v>354</v>
       </c>
-      <c r="H12" s="483"/>
-      <c r="I12" s="482"/>
-      <c r="J12" s="481" t="s">
+      <c r="H12" s="488"/>
+      <c r="I12" s="481"/>
+      <c r="J12" s="482" t="s">
         <v>355</v>
       </c>
-      <c r="K12" s="482"/>
+      <c r="K12" s="481"/>
       <c r="L12" s="291" t="s">
         <v>356</v>
       </c>
@@ -5049,155 +5049,155 @@
     </row>
     <row r="13" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="285"/>
-      <c r="B13" s="494" t="s">
+      <c r="B13" s="495" t="s">
         <v>357</v>
       </c>
-      <c r="C13" s="495"/>
-      <c r="D13" s="496" t="s">
+      <c r="C13" s="494"/>
+      <c r="D13" s="492" t="s">
         <v>358</v>
       </c>
-      <c r="E13" s="497"/>
-      <c r="F13" s="495"/>
-      <c r="G13" s="496" t="s">
+      <c r="E13" s="493"/>
+      <c r="F13" s="494"/>
+      <c r="G13" s="492" t="s">
         <v>359</v>
       </c>
-      <c r="H13" s="497"/>
-      <c r="I13" s="495"/>
-      <c r="J13" s="496" t="s">
+      <c r="H13" s="493"/>
+      <c r="I13" s="494"/>
+      <c r="J13" s="492" t="s">
         <v>360</v>
       </c>
-      <c r="K13" s="495"/>
+      <c r="K13" s="494"/>
       <c r="L13" s="279"/>
       <c r="M13" s="286"/>
     </row>
     <row r="14" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="285"/>
-      <c r="B14" s="490" t="s">
+      <c r="B14" s="489" t="s">
         <v>197</v>
       </c>
-      <c r="C14" s="381"/>
-      <c r="D14" s="492" t="s">
+      <c r="C14" s="347"/>
+      <c r="D14" s="490" t="s">
         <v>358</v>
       </c>
-      <c r="E14" s="493"/>
-      <c r="F14" s="381"/>
-      <c r="G14" s="492" t="s">
+      <c r="E14" s="491"/>
+      <c r="F14" s="347"/>
+      <c r="G14" s="490" t="s">
         <v>359</v>
       </c>
-      <c r="H14" s="493"/>
-      <c r="I14" s="381"/>
-      <c r="J14" s="492" t="s">
+      <c r="H14" s="491"/>
+      <c r="I14" s="347"/>
+      <c r="J14" s="490" t="s">
         <v>360</v>
       </c>
-      <c r="K14" s="381"/>
+      <c r="K14" s="347"/>
       <c r="L14" s="280"/>
       <c r="M14" s="286"/>
     </row>
     <row r="15" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="285"/>
-      <c r="B15" s="490" t="s">
+      <c r="B15" s="489" t="s">
         <v>361</v>
       </c>
-      <c r="C15" s="381"/>
-      <c r="D15" s="492" t="s">
+      <c r="C15" s="347"/>
+      <c r="D15" s="490" t="s">
         <v>358</v>
       </c>
-      <c r="E15" s="493"/>
-      <c r="F15" s="381"/>
-      <c r="G15" s="492" t="s">
+      <c r="E15" s="491"/>
+      <c r="F15" s="347"/>
+      <c r="G15" s="490" t="s">
         <v>362</v>
       </c>
-      <c r="H15" s="493"/>
-      <c r="I15" s="381"/>
-      <c r="J15" s="492" t="s">
+      <c r="H15" s="491"/>
+      <c r="I15" s="347"/>
+      <c r="J15" s="490" t="s">
         <v>360</v>
       </c>
-      <c r="K15" s="381"/>
+      <c r="K15" s="347"/>
       <c r="L15" s="280"/>
       <c r="M15" s="286"/>
     </row>
     <row r="16" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="285"/>
-      <c r="B16" s="490" t="s">
+      <c r="B16" s="489" t="s">
         <v>363</v>
       </c>
-      <c r="C16" s="381"/>
-      <c r="D16" s="492" t="s">
+      <c r="C16" s="347"/>
+      <c r="D16" s="490" t="s">
         <v>358</v>
       </c>
-      <c r="E16" s="493"/>
-      <c r="F16" s="381"/>
-      <c r="G16" s="492" t="s">
+      <c r="E16" s="491"/>
+      <c r="F16" s="347"/>
+      <c r="G16" s="490" t="s">
         <v>362</v>
       </c>
-      <c r="H16" s="493"/>
-      <c r="I16" s="381"/>
-      <c r="J16" s="492" t="s">
+      <c r="H16" s="491"/>
+      <c r="I16" s="347"/>
+      <c r="J16" s="490" t="s">
         <v>360</v>
       </c>
-      <c r="K16" s="381"/>
+      <c r="K16" s="347"/>
       <c r="L16" s="280"/>
       <c r="M16" s="286"/>
     </row>
     <row r="17" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="285"/>
-      <c r="B17" s="490" t="s">
+      <c r="B17" s="489" t="s">
         <v>364</v>
       </c>
-      <c r="C17" s="381"/>
-      <c r="D17" s="492" t="s">
+      <c r="C17" s="347"/>
+      <c r="D17" s="490" t="s">
         <v>358</v>
       </c>
-      <c r="E17" s="493"/>
-      <c r="F17" s="381"/>
-      <c r="G17" s="492" t="s">
+      <c r="E17" s="491"/>
+      <c r="F17" s="347"/>
+      <c r="G17" s="490" t="s">
         <v>365</v>
       </c>
-      <c r="H17" s="493"/>
-      <c r="I17" s="381"/>
-      <c r="J17" s="492" t="s">
+      <c r="H17" s="491"/>
+      <c r="I17" s="347"/>
+      <c r="J17" s="490" t="s">
         <v>360</v>
       </c>
-      <c r="K17" s="381"/>
+      <c r="K17" s="347"/>
       <c r="L17" s="280"/>
       <c r="M17" s="286"/>
     </row>
     <row r="18" spans="1:13" s="25" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="285"/>
-      <c r="B18" s="477" t="s">
+      <c r="B18" s="485" t="s">
         <v>366</v>
       </c>
-      <c r="C18" s="375"/>
-      <c r="D18" s="492" t="s">
+      <c r="C18" s="345"/>
+      <c r="D18" s="490" t="s">
         <v>358</v>
       </c>
-      <c r="E18" s="493"/>
-      <c r="F18" s="381"/>
-      <c r="G18" s="491" t="s">
+      <c r="E18" s="491"/>
+      <c r="F18" s="347"/>
+      <c r="G18" s="497" t="s">
         <v>362</v>
       </c>
-      <c r="H18" s="364"/>
-      <c r="I18" s="375"/>
-      <c r="J18" s="491" t="s">
+      <c r="H18" s="344"/>
+      <c r="I18" s="345"/>
+      <c r="J18" s="497" t="s">
         <v>360</v>
       </c>
-      <c r="K18" s="375"/>
+      <c r="K18" s="345"/>
       <c r="L18" s="281"/>
       <c r="M18" s="286"/>
     </row>
     <row r="19" spans="1:13" s="25" customFormat="1" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="287"/>
-      <c r="B19" s="489"/>
-      <c r="C19" s="378"/>
-      <c r="D19" s="378"/>
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
-      <c r="G19" s="378"/>
-      <c r="H19" s="378"/>
-      <c r="I19" s="378"/>
-      <c r="J19" s="378"/>
-      <c r="K19" s="378"/>
-      <c r="L19" s="378"/>
+      <c r="B19" s="496"/>
+      <c r="C19" s="414"/>
+      <c r="D19" s="414"/>
+      <c r="E19" s="414"/>
+      <c r="F19" s="414"/>
+      <c r="G19" s="414"/>
+      <c r="H19" s="414"/>
+      <c r="I19" s="414"/>
+      <c r="J19" s="414"/>
+      <c r="K19" s="414"/>
+      <c r="L19" s="414"/>
       <c r="M19" s="288"/>
     </row>
     <row r="20" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -5492,29 +5492,6 @@
     <row r="309" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B19:L19"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="B7:G7"/>
@@ -5531,6 +5508,29 @@
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="B5:C6"/>
     <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D13:F13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -5557,65 +5557,65 @@
   <sheetData>
     <row r="1" spans="1:13" ht="13.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="369"/>
-      <c r="C1" s="370"/>
-      <c r="D1" s="370"/>
-      <c r="E1" s="370"/>
-      <c r="F1" s="370"/>
-      <c r="G1" s="370"/>
-      <c r="H1" s="370"/>
-      <c r="I1" s="370"/>
-      <c r="J1" s="370"/>
-      <c r="K1" s="370"/>
-      <c r="L1" s="370"/>
+      <c r="B1" s="409"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
+      <c r="K1" s="410"/>
+      <c r="L1" s="410"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="435" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="372"/>
-      <c r="D2" s="372"/>
-      <c r="E2" s="372"/>
-      <c r="F2" s="372"/>
-      <c r="G2" s="372"/>
-      <c r="H2" s="372"/>
-      <c r="I2" s="372"/>
-      <c r="J2" s="372"/>
-      <c r="K2" s="372"/>
-      <c r="L2" s="373"/>
+      <c r="B2" s="424" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
+      <c r="J2" s="342"/>
+      <c r="K2" s="342"/>
+      <c r="L2" s="343"/>
       <c r="M2" s="282"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="426" t="s">
+      <c r="B3" s="436" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
-      <c r="L3" s="375"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
+      <c r="F3" s="344"/>
+      <c r="G3" s="344"/>
+      <c r="H3" s="344"/>
+      <c r="I3" s="344"/>
+      <c r="J3" s="344"/>
+      <c r="K3" s="344"/>
+      <c r="L3" s="345"/>
       <c r="M3" s="282"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="432" t="s">
+      <c r="B4" s="431" t="s">
         <v>367</v>
       </c>
-      <c r="C4" s="368"/>
-      <c r="D4" s="368"/>
-      <c r="E4" s="368"/>
-      <c r="F4" s="368"/>
-      <c r="G4" s="368"/>
-      <c r="H4" s="368"/>
-      <c r="I4" s="356"/>
+      <c r="C4" s="337"/>
+      <c r="D4" s="337"/>
+      <c r="E4" s="337"/>
+      <c r="F4" s="337"/>
+      <c r="G4" s="337"/>
+      <c r="H4" s="337"/>
+      <c r="I4" s="334"/>
       <c r="J4" s="259" t="s">
         <v>3</v>
       </c>
@@ -5625,36 +5625,36 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="487" t="s">
+      <c r="B5" s="476" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="373"/>
+      <c r="C5" s="343"/>
       <c r="D5" s="474" t="str">
         <f>'QUADRO I'!D5:O6</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="372"/>
-      <c r="F5" s="372"/>
-      <c r="G5" s="372"/>
-      <c r="H5" s="372"/>
-      <c r="I5" s="373"/>
-      <c r="J5" s="429" t="s">
+      <c r="E5" s="342"/>
+      <c r="F5" s="342"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="342"/>
+      <c r="I5" s="343"/>
+      <c r="J5" s="437" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="368"/>
-      <c r="L5" s="356"/>
+      <c r="K5" s="337"/>
+      <c r="L5" s="334"/>
       <c r="M5" s="213"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="374"/>
-      <c r="C6" s="375"/>
-      <c r="D6" s="374"/>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
-      <c r="G6" s="364"/>
-      <c r="H6" s="364"/>
-      <c r="I6" s="375"/>
+      <c r="B6" s="348"/>
+      <c r="C6" s="345"/>
+      <c r="D6" s="348"/>
+      <c r="E6" s="344"/>
+      <c r="F6" s="344"/>
+      <c r="G6" s="344"/>
+      <c r="H6" s="344"/>
+      <c r="I6" s="345"/>
       <c r="J6" s="49" t="s">
         <v>6</v>
       </c>
@@ -5666,21 +5666,21 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="432" t="s">
+      <c r="B7" s="431" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
-      <c r="E7" s="368"/>
-      <c r="F7" s="368"/>
-      <c r="G7" s="356"/>
-      <c r="H7" s="432" t="s">
+      <c r="C7" s="337"/>
+      <c r="D7" s="337"/>
+      <c r="E7" s="337"/>
+      <c r="F7" s="337"/>
+      <c r="G7" s="334"/>
+      <c r="H7" s="431" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="368"/>
-      <c r="J7" s="368"/>
-      <c r="K7" s="368"/>
-      <c r="L7" s="356"/>
+      <c r="I7" s="337"/>
+      <c r="J7" s="337"/>
+      <c r="K7" s="337"/>
+      <c r="L7" s="334"/>
       <c r="M7" s="278"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -5688,14 +5688,14 @@
       <c r="B8" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="501" t="str">
+      <c r="C8" s="500" t="str">
         <f>'QUADRO VII'!C8</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="D8" s="372"/>
-      <c r="E8" s="372"/>
-      <c r="F8" s="372"/>
-      <c r="G8" s="373"/>
+      <c r="D8" s="342"/>
+      <c r="E8" s="342"/>
+      <c r="F8" s="342"/>
+      <c r="G8" s="343"/>
       <c r="H8" s="19" t="s">
         <v>9</v>
       </c>
@@ -5747,11 +5747,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="440" t="str">
+      <c r="J10" s="450" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="364"/>
+      <c r="K10" s="344"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -5760,24 +5760,24 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="445" t="s">
+      <c r="B11" s="441" t="s">
         <v>352</v>
       </c>
-      <c r="C11" s="356"/>
-      <c r="D11" s="445" t="s">
+      <c r="C11" s="334"/>
+      <c r="D11" s="441" t="s">
         <v>353</v>
       </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="356"/>
-      <c r="G11" s="445" t="s">
+      <c r="E11" s="337"/>
+      <c r="F11" s="334"/>
+      <c r="G11" s="441" t="s">
         <v>354</v>
       </c>
-      <c r="H11" s="368"/>
-      <c r="I11" s="356"/>
-      <c r="J11" s="445" t="s">
+      <c r="H11" s="337"/>
+      <c r="I11" s="334"/>
+      <c r="J11" s="441" t="s">
         <v>355</v>
       </c>
-      <c r="K11" s="356"/>
+      <c r="K11" s="334"/>
       <c r="L11" s="306" t="s">
         <v>356</v>
       </c>
@@ -5785,24 +5785,24 @@
     </row>
     <row r="12" spans="1:13" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="285"/>
-      <c r="B12" s="441" t="s">
+      <c r="B12" s="438" t="s">
         <v>368</v>
       </c>
-      <c r="C12" s="373"/>
-      <c r="D12" s="441" t="s">
+      <c r="C12" s="343"/>
+      <c r="D12" s="438" t="s">
         <v>369</v>
       </c>
-      <c r="E12" s="372"/>
-      <c r="F12" s="373"/>
-      <c r="G12" s="441" t="s">
+      <c r="E12" s="342"/>
+      <c r="F12" s="343"/>
+      <c r="G12" s="438" t="s">
         <v>370</v>
       </c>
-      <c r="H12" s="372"/>
-      <c r="I12" s="373"/>
-      <c r="J12" s="441" t="s">
+      <c r="H12" s="342"/>
+      <c r="I12" s="343"/>
+      <c r="J12" s="438" t="s">
         <v>371</v>
       </c>
-      <c r="K12" s="373"/>
+      <c r="K12" s="343"/>
       <c r="L12" s="307"/>
       <c r="M12" s="286"/>
     </row>
@@ -5811,21 +5811,21 @@
       <c r="B13" s="498" t="s">
         <v>372</v>
       </c>
-      <c r="C13" s="381"/>
+      <c r="C13" s="347"/>
       <c r="D13" s="498" t="s">
         <v>369</v>
       </c>
       <c r="E13" s="499"/>
-      <c r="F13" s="381"/>
+      <c r="F13" s="347"/>
       <c r="G13" s="498" t="s">
         <v>370</v>
       </c>
       <c r="H13" s="499"/>
-      <c r="I13" s="381"/>
+      <c r="I13" s="347"/>
       <c r="J13" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K13" s="381"/>
+      <c r="K13" s="347"/>
       <c r="L13" s="280"/>
       <c r="M13" s="286"/>
     </row>
@@ -5834,21 +5834,21 @@
       <c r="B14" s="498" t="s">
         <v>373</v>
       </c>
-      <c r="C14" s="381"/>
+      <c r="C14" s="347"/>
       <c r="D14" s="498" t="s">
         <v>369</v>
       </c>
       <c r="E14" s="499"/>
-      <c r="F14" s="381"/>
+      <c r="F14" s="347"/>
       <c r="G14" s="498" t="s">
         <v>369</v>
       </c>
       <c r="H14" s="499"/>
-      <c r="I14" s="381"/>
+      <c r="I14" s="347"/>
       <c r="J14" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K14" s="381"/>
+      <c r="K14" s="347"/>
       <c r="L14" s="280"/>
       <c r="M14" s="286"/>
     </row>
@@ -5857,21 +5857,21 @@
       <c r="B15" s="498" t="s">
         <v>374</v>
       </c>
-      <c r="C15" s="381"/>
+      <c r="C15" s="347"/>
       <c r="D15" s="498" t="s">
         <v>369</v>
       </c>
       <c r="E15" s="499"/>
-      <c r="F15" s="381"/>
+      <c r="F15" s="347"/>
       <c r="G15" s="498" t="s">
         <v>369</v>
       </c>
       <c r="H15" s="499"/>
-      <c r="I15" s="381"/>
+      <c r="I15" s="347"/>
       <c r="J15" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K15" s="381"/>
+      <c r="K15" s="347"/>
       <c r="L15" s="280"/>
       <c r="M15" s="286"/>
     </row>
@@ -5880,21 +5880,21 @@
       <c r="B16" s="498" t="s">
         <v>375</v>
       </c>
-      <c r="C16" s="381"/>
+      <c r="C16" s="347"/>
       <c r="D16" s="498" t="s">
         <v>369</v>
       </c>
       <c r="E16" s="499"/>
-      <c r="F16" s="381"/>
+      <c r="F16" s="347"/>
       <c r="G16" s="498" t="s">
         <v>370</v>
       </c>
       <c r="H16" s="499"/>
-      <c r="I16" s="381"/>
+      <c r="I16" s="347"/>
       <c r="J16" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K16" s="381"/>
+      <c r="K16" s="347"/>
       <c r="L16" s="280"/>
       <c r="M16" s="286"/>
     </row>
@@ -5903,21 +5903,21 @@
       <c r="B17" s="498" t="s">
         <v>376</v>
       </c>
-      <c r="C17" s="381"/>
+      <c r="C17" s="347"/>
       <c r="D17" s="498" t="s">
         <v>369</v>
       </c>
       <c r="E17" s="499"/>
-      <c r="F17" s="381"/>
+      <c r="F17" s="347"/>
       <c r="G17" s="498" t="s">
         <v>369</v>
       </c>
       <c r="H17" s="499"/>
-      <c r="I17" s="381"/>
+      <c r="I17" s="347"/>
       <c r="J17" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K17" s="381"/>
+      <c r="K17" s="347"/>
       <c r="L17" s="280"/>
       <c r="M17" s="286"/>
     </row>
@@ -5926,21 +5926,21 @@
       <c r="B18" s="498" t="s">
         <v>377</v>
       </c>
-      <c r="C18" s="381"/>
+      <c r="C18" s="347"/>
       <c r="D18" s="498" t="s">
         <v>378</v>
       </c>
       <c r="E18" s="499"/>
-      <c r="F18" s="381"/>
+      <c r="F18" s="347"/>
       <c r="G18" s="498" t="s">
         <v>369</v>
       </c>
       <c r="H18" s="499"/>
-      <c r="I18" s="381"/>
+      <c r="I18" s="347"/>
       <c r="J18" s="498" t="s">
         <v>371</v>
       </c>
-      <c r="K18" s="381"/>
+      <c r="K18" s="347"/>
       <c r="L18" s="280"/>
       <c r="M18" s="286"/>
     </row>
@@ -6096,22 +6096,22 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="285"/>
-      <c r="B29" s="500"/>
-      <c r="C29" s="372"/>
-      <c r="D29" s="372"/>
-      <c r="E29" s="372"/>
-      <c r="F29" s="372"/>
-      <c r="G29" s="372"/>
-      <c r="H29" s="372"/>
-      <c r="I29" s="372"/>
-      <c r="J29" s="372"/>
-      <c r="K29" s="372"/>
-      <c r="L29" s="373"/>
+      <c r="B29" s="501"/>
+      <c r="C29" s="342"/>
+      <c r="D29" s="342"/>
+      <c r="E29" s="342"/>
+      <c r="F29" s="342"/>
+      <c r="G29" s="342"/>
+      <c r="H29" s="342"/>
+      <c r="I29" s="342"/>
+      <c r="J29" s="342"/>
+      <c r="K29" s="342"/>
+      <c r="L29" s="343"/>
       <c r="M29" s="286"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="285"/>
-      <c r="B30" s="422"/>
+      <c r="B30" s="346"/>
       <c r="C30" s="499"/>
       <c r="D30" s="499"/>
       <c r="E30" s="499"/>
@@ -6121,12 +6121,12 @@
       <c r="I30" s="499"/>
       <c r="J30" s="499"/>
       <c r="K30" s="499"/>
-      <c r="L30" s="381"/>
+      <c r="L30" s="347"/>
       <c r="M30" s="286"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="285"/>
-      <c r="B31" s="422"/>
+      <c r="B31" s="346"/>
       <c r="C31" s="499"/>
       <c r="D31" s="499"/>
       <c r="E31" s="499"/>
@@ -6136,55 +6136,58 @@
       <c r="I31" s="499"/>
       <c r="J31" s="499"/>
       <c r="K31" s="499"/>
-      <c r="L31" s="381"/>
+      <c r="L31" s="347"/>
       <c r="M31" s="286"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="285"/>
-      <c r="B32" s="374"/>
-      <c r="C32" s="364"/>
-      <c r="D32" s="364"/>
-      <c r="E32" s="364"/>
-      <c r="F32" s="364"/>
-      <c r="G32" s="364"/>
-      <c r="H32" s="364"/>
-      <c r="I32" s="364"/>
-      <c r="J32" s="364"/>
-      <c r="K32" s="364"/>
-      <c r="L32" s="375"/>
+      <c r="B32" s="348"/>
+      <c r="C32" s="344"/>
+      <c r="D32" s="344"/>
+      <c r="E32" s="344"/>
+      <c r="F32" s="344"/>
+      <c r="G32" s="344"/>
+      <c r="H32" s="344"/>
+      <c r="I32" s="344"/>
+      <c r="J32" s="344"/>
+      <c r="K32" s="344"/>
+      <c r="L32" s="345"/>
       <c r="M32" s="286"/>
     </row>
     <row r="33" spans="1:13" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="287"/>
-      <c r="B33" s="489"/>
-      <c r="C33" s="378"/>
-      <c r="D33" s="378"/>
-      <c r="E33" s="378"/>
-      <c r="F33" s="378"/>
-      <c r="G33" s="378"/>
-      <c r="H33" s="378"/>
-      <c r="I33" s="378"/>
-      <c r="J33" s="378"/>
-      <c r="K33" s="378"/>
-      <c r="L33" s="378"/>
+      <c r="B33" s="496"/>
+      <c r="C33" s="414"/>
+      <c r="D33" s="414"/>
+      <c r="E33" s="414"/>
+      <c r="F33" s="414"/>
+      <c r="G33" s="414"/>
+      <c r="H33" s="414"/>
+      <c r="I33" s="414"/>
+      <c r="J33" s="414"/>
+      <c r="K33" s="414"/>
+      <c r="L33" s="414"/>
       <c r="M33" s="288"/>
     </row>
     <row r="34" spans="1:13" ht="13.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D5:I6"/>
-    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="B33:L33"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B29:L32"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="D18:F18"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="G16:I16"/>
@@ -6201,22 +6204,19 @@
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B33:L33"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B29:L32"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D5:I6"/>
+    <mergeCell ref="G13:I13"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -6245,32 +6245,32 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="369"/>
-      <c r="C1" s="370"/>
-      <c r="D1" s="370"/>
-      <c r="E1" s="370"/>
-      <c r="F1" s="370"/>
-      <c r="G1" s="370"/>
-      <c r="H1" s="370"/>
-      <c r="I1" s="370"/>
-      <c r="J1" s="370"/>
-      <c r="K1" s="370"/>
-      <c r="L1" s="370"/>
+      <c r="B1" s="409"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
+      <c r="K1" s="410"/>
+      <c r="L1" s="410"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="371" t="s">
+      <c r="B2" s="411" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="372"/>
-      <c r="D2" s="372"/>
-      <c r="E2" s="372"/>
-      <c r="F2" s="372"/>
-      <c r="G2" s="372"/>
-      <c r="H2" s="372"/>
-      <c r="I2" s="372"/>
-      <c r="J2" s="373"/>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
+      <c r="J2" s="343"/>
       <c r="K2" s="152" t="s">
         <v>58</v>
       </c>
@@ -6281,17 +6281,17 @@
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="374"/>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="375"/>
-      <c r="K3" s="355"/>
-      <c r="L3" s="356"/>
+      <c r="B3" s="348"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
+      <c r="F3" s="344"/>
+      <c r="G3" s="344"/>
+      <c r="H3" s="344"/>
+      <c r="I3" s="344"/>
+      <c r="J3" s="345"/>
+      <c r="K3" s="423"/>
+      <c r="L3" s="334"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6299,18 +6299,18 @@
       <c r="B4" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="367" t="s">
+      <c r="C4" s="395" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="368"/>
-      <c r="E4" s="368"/>
-      <c r="F4" s="368"/>
-      <c r="G4" s="368"/>
-      <c r="H4" s="368"/>
-      <c r="I4" s="368"/>
-      <c r="J4" s="368"/>
-      <c r="K4" s="368"/>
-      <c r="L4" s="356"/>
+      <c r="D4" s="337"/>
+      <c r="E4" s="337"/>
+      <c r="F4" s="337"/>
+      <c r="G4" s="337"/>
+      <c r="H4" s="337"/>
+      <c r="I4" s="337"/>
+      <c r="J4" s="337"/>
+      <c r="K4" s="337"/>
+      <c r="L4" s="334"/>
       <c r="M4" s="202"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6319,19 +6319,19 @@
       <c r="C5" s="140" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="362" t="s">
+      <c r="D5" s="408" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="358"/>
-      <c r="F5" s="357" t="s">
+      <c r="E5" s="402"/>
+      <c r="F5" s="419" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="358"/>
-      <c r="H5" s="358"/>
-      <c r="I5" s="358"/>
-      <c r="J5" s="358"/>
-      <c r="K5" s="358"/>
-      <c r="L5" s="359"/>
+      <c r="G5" s="402"/>
+      <c r="H5" s="402"/>
+      <c r="I5" s="402"/>
+      <c r="J5" s="402"/>
+      <c r="K5" s="402"/>
+      <c r="L5" s="403"/>
       <c r="M5" s="202"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6340,19 +6340,19 @@
       <c r="C6" s="141" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="389" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="361"/>
-      <c r="F6" s="376" t="s">
+      <c r="E6" s="382"/>
+      <c r="F6" s="412" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="361"/>
-      <c r="H6" s="361"/>
-      <c r="I6" s="361"/>
-      <c r="J6" s="361"/>
-      <c r="K6" s="361"/>
-      <c r="L6" s="366"/>
+      <c r="G6" s="382"/>
+      <c r="H6" s="382"/>
+      <c r="I6" s="382"/>
+      <c r="J6" s="382"/>
+      <c r="K6" s="382"/>
+      <c r="L6" s="383"/>
       <c r="M6" s="202"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6361,17 +6361,17 @@
       <c r="C7" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="383" t="s">
+      <c r="D7" s="417" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="384"/>
-      <c r="F7" s="398"/>
-      <c r="G7" s="384"/>
-      <c r="H7" s="384"/>
-      <c r="I7" s="384"/>
-      <c r="J7" s="384"/>
-      <c r="K7" s="384"/>
-      <c r="L7" s="399"/>
+      <c r="E7" s="385"/>
+      <c r="F7" s="384"/>
+      <c r="G7" s="385"/>
+      <c r="H7" s="385"/>
+      <c r="I7" s="385"/>
+      <c r="J7" s="385"/>
+      <c r="K7" s="385"/>
+      <c r="L7" s="386"/>
       <c r="M7" s="202"/>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6380,13 +6380,13 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="364"/>
-      <c r="G8" s="364"/>
-      <c r="H8" s="364"/>
-      <c r="I8" s="364"/>
-      <c r="J8" s="364"/>
-      <c r="K8" s="364"/>
-      <c r="L8" s="375"/>
+      <c r="F8" s="344"/>
+      <c r="G8" s="344"/>
+      <c r="H8" s="344"/>
+      <c r="I8" s="344"/>
+      <c r="J8" s="344"/>
+      <c r="K8" s="344"/>
+      <c r="L8" s="345"/>
       <c r="M8" s="202"/>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6394,18 +6394,18 @@
       <c r="B9" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="367" t="s">
+      <c r="C9" s="395" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="368"/>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
-      <c r="G9" s="368"/>
-      <c r="H9" s="368"/>
-      <c r="I9" s="368"/>
-      <c r="J9" s="368"/>
-      <c r="K9" s="368"/>
-      <c r="L9" s="356"/>
+      <c r="D9" s="337"/>
+      <c r="E9" s="337"/>
+      <c r="F9" s="337"/>
+      <c r="G9" s="337"/>
+      <c r="H9" s="337"/>
+      <c r="I9" s="337"/>
+      <c r="J9" s="337"/>
+      <c r="K9" s="337"/>
+      <c r="L9" s="334"/>
       <c r="M9" s="202"/>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6414,20 +6414,20 @@
       <c r="C10" s="140" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="362" t="s">
+      <c r="D10" s="408" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
-      <c r="G10" s="390" t="str">
+      <c r="E10" s="402"/>
+      <c r="F10" s="402"/>
+      <c r="G10" s="401" t="str">
         <f>CAPA!A14</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="H10" s="358"/>
-      <c r="I10" s="358"/>
-      <c r="J10" s="358"/>
-      <c r="K10" s="358"/>
-      <c r="L10" s="359"/>
+      <c r="H10" s="402"/>
+      <c r="I10" s="402"/>
+      <c r="J10" s="402"/>
+      <c r="K10" s="402"/>
+      <c r="L10" s="403"/>
       <c r="M10" s="202"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6436,20 +6436,20 @@
       <c r="C11" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="360" t="s">
+      <c r="D11" s="389" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="361"/>
-      <c r="F11" s="361"/>
-      <c r="G11" s="365" t="str">
+      <c r="E11" s="382"/>
+      <c r="F11" s="382"/>
+      <c r="G11" s="391" t="str">
         <f>CAPA!A15</f>
         <v>{CREA}</v>
       </c>
-      <c r="H11" s="361"/>
-      <c r="I11" s="361"/>
-      <c r="J11" s="361"/>
-      <c r="K11" s="361"/>
-      <c r="L11" s="366"/>
+      <c r="H11" s="382"/>
+      <c r="I11" s="382"/>
+      <c r="J11" s="382"/>
+      <c r="K11" s="382"/>
+      <c r="L11" s="383"/>
       <c r="M11" s="202"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6458,30 +6458,30 @@
       <c r="C12" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="360" t="s">
+      <c r="D12" s="389" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="361"/>
-      <c r="F12" s="361"/>
-      <c r="G12" s="365"/>
-      <c r="H12" s="361"/>
-      <c r="I12" s="361"/>
-      <c r="J12" s="361"/>
-      <c r="K12" s="361"/>
-      <c r="L12" s="366"/>
+      <c r="E12" s="382"/>
+      <c r="F12" s="382"/>
+      <c r="G12" s="391"/>
+      <c r="H12" s="382"/>
+      <c r="I12" s="382"/>
+      <c r="J12" s="382"/>
+      <c r="K12" s="382"/>
+      <c r="L12" s="383"/>
       <c r="M12" s="202"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="200"/>
-      <c r="B13" s="402"/>
-      <c r="C13" s="363" t="s">
+      <c r="B13" s="392"/>
+      <c r="C13" s="416" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="363" t="s">
+      <c r="D13" s="416" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="384"/>
-      <c r="F13" s="384"/>
+      <c r="E13" s="385"/>
+      <c r="F13" s="385"/>
       <c r="G13" s="187"/>
       <c r="H13" s="187"/>
       <c r="I13" s="187"/>
@@ -6492,11 +6492,11 @@
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="200"/>
-      <c r="B14" s="374"/>
-      <c r="C14" s="364"/>
-      <c r="D14" s="364"/>
-      <c r="E14" s="364"/>
-      <c r="F14" s="364"/>
+      <c r="B14" s="348"/>
+      <c r="C14" s="344"/>
+      <c r="D14" s="344"/>
+      <c r="E14" s="344"/>
+      <c r="F14" s="344"/>
       <c r="G14" s="188"/>
       <c r="H14" s="188"/>
       <c r="I14" s="188"/>
@@ -6510,18 +6510,18 @@
       <c r="B15" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="367" t="s">
+      <c r="C15" s="395" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="368"/>
-      <c r="E15" s="368"/>
-      <c r="F15" s="368"/>
-      <c r="G15" s="368"/>
-      <c r="H15" s="368"/>
-      <c r="I15" s="368"/>
-      <c r="J15" s="368"/>
-      <c r="K15" s="368"/>
-      <c r="L15" s="356"/>
+      <c r="D15" s="337"/>
+      <c r="E15" s="337"/>
+      <c r="F15" s="337"/>
+      <c r="G15" s="337"/>
+      <c r="H15" s="337"/>
+      <c r="I15" s="337"/>
+      <c r="J15" s="337"/>
+      <c r="K15" s="337"/>
+      <c r="L15" s="334"/>
       <c r="M15" s="202"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6530,19 +6530,19 @@
       <c r="C16" s="140" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="362" t="s">
+      <c r="D16" s="408" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="358"/>
-      <c r="F16" s="358"/>
-      <c r="G16" s="385" t="s">
+      <c r="E16" s="402"/>
+      <c r="F16" s="402"/>
+      <c r="G16" s="418" t="s">
         <v>80</v>
       </c>
-      <c r="H16" s="372"/>
-      <c r="I16" s="372"/>
-      <c r="J16" s="372"/>
-      <c r="K16" s="372"/>
-      <c r="L16" s="373"/>
+      <c r="H16" s="342"/>
+      <c r="I16" s="342"/>
+      <c r="J16" s="342"/>
+      <c r="K16" s="342"/>
+      <c r="L16" s="343"/>
       <c r="M16" s="202"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6551,20 +6551,20 @@
       <c r="C17" s="141" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="360" t="s">
+      <c r="D17" s="389" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="361"/>
-      <c r="F17" s="361"/>
-      <c r="G17" s="404" t="str">
+      <c r="E17" s="382"/>
+      <c r="F17" s="382"/>
+      <c r="G17" s="396" t="str">
         <f>CAPA!C3</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="H17" s="380"/>
-      <c r="I17" s="380"/>
-      <c r="J17" s="380"/>
-      <c r="K17" s="380"/>
-      <c r="L17" s="381"/>
+      <c r="H17" s="397"/>
+      <c r="I17" s="397"/>
+      <c r="J17" s="397"/>
+      <c r="K17" s="397"/>
+      <c r="L17" s="347"/>
       <c r="M17" s="202"/>
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6574,12 +6574,12 @@
       <c r="D18" s="310"/>
       <c r="E18" s="310"/>
       <c r="F18" s="310"/>
-      <c r="G18" s="391"/>
-      <c r="H18" s="391"/>
-      <c r="I18" s="391"/>
-      <c r="J18" s="391"/>
-      <c r="K18" s="391"/>
-      <c r="L18" s="405"/>
+      <c r="G18" s="388"/>
+      <c r="H18" s="388"/>
+      <c r="I18" s="388"/>
+      <c r="J18" s="388"/>
+      <c r="K18" s="388"/>
+      <c r="L18" s="398"/>
       <c r="M18" s="202"/>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6588,18 +6588,18 @@
       <c r="C19" s="141" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="360" t="s">
+      <c r="D19" s="389" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="361"/>
-      <c r="F19" s="361"/>
-      <c r="G19" s="403" t="s">
+      <c r="E19" s="382"/>
+      <c r="F19" s="382"/>
+      <c r="G19" s="393" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="382"/>
-      <c r="I19" s="382"/>
-      <c r="J19" s="382"/>
-      <c r="K19" s="382"/>
+      <c r="H19" s="394"/>
+      <c r="I19" s="394"/>
+      <c r="J19" s="394"/>
+      <c r="K19" s="394"/>
       <c r="L19" s="207" t="s">
         <v>86</v>
       </c>
@@ -6607,15 +6607,15 @@
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="387"/>
-      <c r="C20" s="360" t="s">
+      <c r="B20" s="421"/>
+      <c r="C20" s="389" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="400" t="s">
+      <c r="D20" s="387" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="384"/>
-      <c r="F20" s="384"/>
+      <c r="E20" s="385"/>
+      <c r="F20" s="385"/>
       <c r="G20" s="72" t="s">
         <v>89</v>
       </c>
@@ -6634,11 +6634,11 @@
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="200"/>
-      <c r="B21" s="388"/>
-      <c r="C21" s="391"/>
-      <c r="D21" s="391"/>
-      <c r="E21" s="391"/>
-      <c r="F21" s="391"/>
+      <c r="B21" s="422"/>
+      <c r="C21" s="388"/>
+      <c r="D21" s="388"/>
+      <c r="E21" s="388"/>
+      <c r="F21" s="388"/>
       <c r="G21" s="72" t="s">
         <v>93</v>
       </c>
@@ -6659,19 +6659,19 @@
       <c r="C22" s="141" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="360" t="s">
+      <c r="D22" s="389" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="361"/>
-      <c r="F22" s="361"/>
-      <c r="G22" s="357" t="s">
+      <c r="E22" s="382"/>
+      <c r="F22" s="382"/>
+      <c r="G22" s="419" t="s">
         <v>98</v>
       </c>
-      <c r="H22" s="358"/>
-      <c r="I22" s="358"/>
-      <c r="J22" s="358"/>
-      <c r="K22" s="358"/>
-      <c r="L22" s="359"/>
+      <c r="H22" s="402"/>
+      <c r="I22" s="402"/>
+      <c r="J22" s="402"/>
+      <c r="K22" s="402"/>
+      <c r="L22" s="403"/>
       <c r="M22" s="202"/>
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6680,19 +6680,19 @@
       <c r="C23" s="141" t="s">
         <v>99</v>
       </c>
-      <c r="D23" s="360" t="s">
+      <c r="D23" s="389" t="s">
         <v>100</v>
       </c>
-      <c r="E23" s="361"/>
-      <c r="F23" s="361"/>
-      <c r="G23" s="365" t="s">
+      <c r="E23" s="382"/>
+      <c r="F23" s="382"/>
+      <c r="G23" s="391" t="s">
         <v>101</v>
       </c>
-      <c r="H23" s="361"/>
-      <c r="I23" s="361"/>
-      <c r="J23" s="361"/>
-      <c r="K23" s="361"/>
-      <c r="L23" s="366"/>
+      <c r="H23" s="382"/>
+      <c r="I23" s="382"/>
+      <c r="J23" s="382"/>
+      <c r="K23" s="382"/>
+      <c r="L23" s="383"/>
       <c r="M23" s="202"/>
     </row>
     <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6701,19 +6701,19 @@
       <c r="C24" s="141" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="360" t="s">
+      <c r="D24" s="389" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="361"/>
-      <c r="F24" s="361"/>
-      <c r="G24" s="365" t="s">
+      <c r="E24" s="382"/>
+      <c r="F24" s="382"/>
+      <c r="G24" s="391" t="s">
         <v>104</v>
       </c>
-      <c r="H24" s="361"/>
-      <c r="I24" s="361"/>
-      <c r="J24" s="361"/>
-      <c r="K24" s="361"/>
-      <c r="L24" s="366"/>
+      <c r="H24" s="382"/>
+      <c r="I24" s="382"/>
+      <c r="J24" s="382"/>
+      <c r="K24" s="382"/>
+      <c r="L24" s="383"/>
       <c r="M24" s="202"/>
     </row>
     <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6722,17 +6722,17 @@
       <c r="C25" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="D25" s="406" t="s">
+      <c r="D25" s="399" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="361"/>
-      <c r="F25" s="361"/>
-      <c r="G25" s="361"/>
-      <c r="H25" s="361"/>
-      <c r="I25" s="361"/>
-      <c r="J25" s="361"/>
-      <c r="K25" s="361"/>
-      <c r="L25" s="366"/>
+      <c r="E25" s="382"/>
+      <c r="F25" s="382"/>
+      <c r="G25" s="382"/>
+      <c r="H25" s="382"/>
+      <c r="I25" s="382"/>
+      <c r="J25" s="382"/>
+      <c r="K25" s="382"/>
+      <c r="L25" s="383"/>
       <c r="M25" s="202"/>
     </row>
     <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6742,18 +6742,18 @@
       <c r="D26" s="141" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="360" t="s">
+      <c r="E26" s="389" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="361"/>
-      <c r="G26" s="361"/>
-      <c r="H26" s="361"/>
-      <c r="I26" s="365" t="s">
+      <c r="F26" s="382"/>
+      <c r="G26" s="382"/>
+      <c r="H26" s="382"/>
+      <c r="I26" s="391" t="s">
         <v>109</v>
       </c>
-      <c r="J26" s="361"/>
-      <c r="K26" s="361"/>
-      <c r="L26" s="366"/>
+      <c r="J26" s="382"/>
+      <c r="K26" s="382"/>
+      <c r="L26" s="383"/>
       <c r="M26" s="202"/>
     </row>
     <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6763,16 +6763,16 @@
       <c r="D27" s="141" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="360" t="s">
+      <c r="E27" s="389" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="361"/>
-      <c r="G27" s="361"/>
-      <c r="H27" s="361"/>
-      <c r="I27" s="397"/>
-      <c r="J27" s="361"/>
-      <c r="K27" s="361"/>
-      <c r="L27" s="366"/>
+      <c r="F27" s="382"/>
+      <c r="G27" s="382"/>
+      <c r="H27" s="382"/>
+      <c r="I27" s="381"/>
+      <c r="J27" s="382"/>
+      <c r="K27" s="382"/>
+      <c r="L27" s="383"/>
       <c r="M27" s="202"/>
     </row>
     <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6782,12 +6782,12 @@
       <c r="D28" s="141" t="s">
         <v>112</v>
       </c>
-      <c r="E28" s="360" t="s">
+      <c r="E28" s="389" t="s">
         <v>113</v>
       </c>
-      <c r="F28" s="361"/>
-      <c r="G28" s="361"/>
-      <c r="H28" s="361"/>
+      <c r="F28" s="382"/>
+      <c r="G28" s="382"/>
+      <c r="H28" s="382"/>
       <c r="I28" s="186"/>
       <c r="J28" s="141"/>
       <c r="K28" s="141"/>
@@ -6800,17 +6800,17 @@
       <c r="C29" s="141" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="360" t="s">
+      <c r="D29" s="389" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="361"/>
-      <c r="F29" s="361"/>
-      <c r="G29" s="361"/>
-      <c r="H29" s="392">
+      <c r="E29" s="382"/>
+      <c r="F29" s="382"/>
+      <c r="G29" s="382"/>
+      <c r="H29" s="404">
         <f>CAPA!D4</f>
         <v>0</v>
       </c>
-      <c r="I29" s="361"/>
+      <c r="I29" s="382"/>
       <c r="J29" s="308" t="s">
         <v>40</v>
       </c>
@@ -6824,17 +6824,17 @@
       <c r="C30" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="360" t="s">
+      <c r="D30" s="389" t="s">
         <v>117</v>
       </c>
-      <c r="E30" s="361"/>
-      <c r="F30" s="361"/>
-      <c r="G30" s="361"/>
-      <c r="H30" s="397"/>
-      <c r="I30" s="361"/>
-      <c r="J30" s="361"/>
-      <c r="K30" s="361"/>
-      <c r="L30" s="366"/>
+      <c r="E30" s="382"/>
+      <c r="F30" s="382"/>
+      <c r="G30" s="382"/>
+      <c r="H30" s="381"/>
+      <c r="I30" s="382"/>
+      <c r="J30" s="382"/>
+      <c r="K30" s="382"/>
+      <c r="L30" s="383"/>
       <c r="M30" s="202"/>
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6843,17 +6843,17 @@
       <c r="C31" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="363" t="s">
+      <c r="D31" s="416" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="382"/>
-      <c r="F31" s="382"/>
-      <c r="G31" s="382"/>
-      <c r="H31" s="394"/>
-      <c r="I31" s="382"/>
-      <c r="J31" s="382"/>
-      <c r="K31" s="382"/>
-      <c r="L31" s="395"/>
+      <c r="E31" s="394"/>
+      <c r="F31" s="394"/>
+      <c r="G31" s="394"/>
+      <c r="H31" s="406"/>
+      <c r="I31" s="394"/>
+      <c r="J31" s="394"/>
+      <c r="K31" s="394"/>
+      <c r="L31" s="407"/>
       <c r="M31" s="202"/>
     </row>
     <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6861,73 +6861,73 @@
       <c r="B32" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="C32" s="367" t="s">
+      <c r="C32" s="395" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="368"/>
-      <c r="E32" s="368"/>
-      <c r="F32" s="368"/>
-      <c r="G32" s="368"/>
-      <c r="H32" s="368"/>
-      <c r="I32" s="368"/>
-      <c r="J32" s="368"/>
-      <c r="K32" s="368"/>
-      <c r="L32" s="356"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
+      <c r="G32" s="337"/>
+      <c r="H32" s="337"/>
+      <c r="I32" s="337"/>
+      <c r="J32" s="337"/>
+      <c r="K32" s="337"/>
+      <c r="L32" s="334"/>
       <c r="M32" s="202"/>
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
-      <c r="B33" s="393" t="s">
+      <c r="B33" s="405" t="s">
         <v>122</v>
       </c>
-      <c r="C33" s="372"/>
-      <c r="D33" s="372"/>
-      <c r="E33" s="372"/>
+      <c r="C33" s="342"/>
+      <c r="D33" s="342"/>
+      <c r="E33" s="342"/>
       <c r="F33" s="72">
         <v>10</v>
       </c>
-      <c r="G33" s="401" t="s">
+      <c r="G33" s="390" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="372"/>
-      <c r="I33" s="372"/>
-      <c r="J33" s="372"/>
-      <c r="K33" s="372"/>
-      <c r="L33" s="373"/>
+      <c r="H33" s="342"/>
+      <c r="I33" s="342"/>
+      <c r="J33" s="342"/>
+      <c r="K33" s="342"/>
+      <c r="L33" s="343"/>
       <c r="M33" s="202"/>
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="200"/>
-      <c r="B34" s="386" t="s">
+      <c r="B34" s="420" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="380"/>
-      <c r="D34" s="380"/>
-      <c r="E34" s="380"/>
-      <c r="F34" s="380"/>
-      <c r="G34" s="380"/>
-      <c r="H34" s="380"/>
-      <c r="I34" s="380"/>
-      <c r="J34" s="380"/>
-      <c r="K34" s="380"/>
-      <c r="L34" s="381"/>
+      <c r="C34" s="397"/>
+      <c r="D34" s="397"/>
+      <c r="E34" s="397"/>
+      <c r="F34" s="397"/>
+      <c r="G34" s="397"/>
+      <c r="H34" s="397"/>
+      <c r="I34" s="397"/>
+      <c r="J34" s="397"/>
+      <c r="K34" s="397"/>
+      <c r="L34" s="347"/>
       <c r="M34" s="202"/>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="200"/>
-      <c r="B35" s="396" t="s">
+      <c r="B35" s="380" t="s">
         <v>125</v>
       </c>
-      <c r="C35" s="364"/>
-      <c r="D35" s="364"/>
-      <c r="E35" s="364"/>
-      <c r="F35" s="364"/>
-      <c r="G35" s="364"/>
-      <c r="H35" s="364"/>
-      <c r="I35" s="364"/>
-      <c r="J35" s="364"/>
-      <c r="K35" s="364"/>
-      <c r="L35" s="375"/>
+      <c r="C35" s="344"/>
+      <c r="D35" s="344"/>
+      <c r="E35" s="344"/>
+      <c r="F35" s="344"/>
+      <c r="G35" s="344"/>
+      <c r="H35" s="344"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="345"/>
       <c r="M35" s="202"/>
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6935,18 +6935,18 @@
       <c r="B36" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="C36" s="367" t="s">
+      <c r="C36" s="395" t="s">
         <v>127</v>
       </c>
-      <c r="D36" s="368"/>
-      <c r="E36" s="368"/>
-      <c r="F36" s="368"/>
-      <c r="G36" s="368"/>
-      <c r="H36" s="368"/>
-      <c r="I36" s="368"/>
-      <c r="J36" s="368"/>
-      <c r="K36" s="368"/>
-      <c r="L36" s="356"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
+      <c r="G36" s="337"/>
+      <c r="H36" s="337"/>
+      <c r="I36" s="337"/>
+      <c r="J36" s="337"/>
+      <c r="K36" s="337"/>
+      <c r="L36" s="334"/>
       <c r="M36" s="202"/>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6990,27 +6990,27 @@
       <c r="B41" s="209" t="s">
         <v>128</v>
       </c>
-      <c r="G41" s="389" t="s">
+      <c r="G41" s="400" t="s">
         <v>54</v>
       </c>
-      <c r="H41" s="380"/>
-      <c r="I41" s="380"/>
-      <c r="J41" s="380"/>
-      <c r="K41" s="380"/>
+      <c r="H41" s="397"/>
+      <c r="I41" s="397"/>
+      <c r="J41" s="397"/>
+      <c r="K41" s="397"/>
       <c r="L41" s="4"/>
       <c r="M41" s="202"/>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="200"/>
       <c r="B42" s="12"/>
-      <c r="G42" s="342" t="str">
+      <c r="G42" s="377" t="str">
         <f>F5</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="H42" s="380"/>
-      <c r="I42" s="380"/>
-      <c r="J42" s="380"/>
-      <c r="K42" s="380"/>
+      <c r="H42" s="397"/>
+      <c r="I42" s="397"/>
+      <c r="J42" s="397"/>
+      <c r="K42" s="397"/>
       <c r="L42" s="4"/>
       <c r="M42" s="202"/>
     </row>
@@ -7043,26 +7043,26 @@
       <c r="B47" s="209" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="389" t="s">
+      <c r="G47" s="400" t="s">
         <v>54</v>
       </c>
-      <c r="H47" s="380"/>
-      <c r="I47" s="380"/>
-      <c r="J47" s="380"/>
-      <c r="K47" s="380"/>
+      <c r="H47" s="397"/>
+      <c r="I47" s="397"/>
+      <c r="J47" s="397"/>
+      <c r="K47" s="397"/>
       <c r="L47" s="4"/>
       <c r="M47" s="202"/>
     </row>
     <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="200"/>
       <c r="B48" s="12"/>
-      <c r="G48" s="342" t="s">
+      <c r="G48" s="377" t="s">
         <v>55</v>
       </c>
-      <c r="H48" s="380"/>
-      <c r="I48" s="380"/>
-      <c r="J48" s="380"/>
-      <c r="K48" s="380"/>
+      <c r="H48" s="397"/>
+      <c r="I48" s="397"/>
+      <c r="J48" s="397"/>
+      <c r="K48" s="397"/>
       <c r="L48" s="4"/>
       <c r="M48" s="202"/>
     </row>
@@ -7080,67 +7080,112 @@
     </row>
     <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="200"/>
-      <c r="B51" s="379" t="s">
+      <c r="B51" s="415" t="s">
         <v>130</v>
       </c>
-      <c r="C51" s="380"/>
-      <c r="D51" s="380"/>
-      <c r="E51" s="380"/>
-      <c r="F51" s="380"/>
-      <c r="G51" s="380"/>
-      <c r="H51" s="380"/>
-      <c r="I51" s="380"/>
-      <c r="J51" s="380"/>
-      <c r="K51" s="380"/>
-      <c r="L51" s="381"/>
+      <c r="C51" s="397"/>
+      <c r="D51" s="397"/>
+      <c r="E51" s="397"/>
+      <c r="F51" s="397"/>
+      <c r="G51" s="397"/>
+      <c r="H51" s="397"/>
+      <c r="I51" s="397"/>
+      <c r="J51" s="397"/>
+      <c r="K51" s="397"/>
+      <c r="L51" s="347"/>
       <c r="M51" s="202"/>
     </row>
     <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="200"/>
-      <c r="B52" s="374"/>
-      <c r="C52" s="364"/>
-      <c r="D52" s="364"/>
-      <c r="E52" s="364"/>
-      <c r="F52" s="364"/>
-      <c r="G52" s="364"/>
-      <c r="H52" s="364"/>
-      <c r="I52" s="364"/>
-      <c r="J52" s="364"/>
-      <c r="K52" s="364"/>
-      <c r="L52" s="375"/>
+      <c r="B52" s="348"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+      <c r="G52" s="344"/>
+      <c r="H52" s="344"/>
+      <c r="I52" s="344"/>
+      <c r="J52" s="344"/>
+      <c r="K52" s="344"/>
+      <c r="L52" s="345"/>
       <c r="M52" s="202"/>
     </row>
     <row r="53" spans="1:13" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="203"/>
-      <c r="B53" s="377"/>
-      <c r="C53" s="378"/>
-      <c r="D53" s="378"/>
-      <c r="E53" s="378"/>
-      <c r="F53" s="378"/>
-      <c r="G53" s="378"/>
-      <c r="H53" s="378"/>
-      <c r="I53" s="378"/>
-      <c r="J53" s="378"/>
-      <c r="K53" s="378"/>
-      <c r="L53" s="378"/>
+      <c r="B53" s="413"/>
+      <c r="C53" s="414"/>
+      <c r="D53" s="414"/>
+      <c r="E53" s="414"/>
+      <c r="F53" s="414"/>
+      <c r="G53" s="414"/>
+      <c r="H53" s="414"/>
+      <c r="I53" s="414"/>
+      <c r="J53" s="414"/>
+      <c r="K53" s="414"/>
+      <c r="L53" s="414"/>
       <c r="M53" s="204"/>
     </row>
     <row r="54" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
-      <c r="B54" s="389"/>
-      <c r="C54" s="380"/>
-      <c r="D54" s="380"/>
-      <c r="E54" s="380"/>
-      <c r="F54" s="380"/>
-      <c r="G54" s="380"/>
-      <c r="H54" s="380"/>
-      <c r="I54" s="380"/>
-      <c r="J54" s="380"/>
-      <c r="K54" s="380"/>
-      <c r="L54" s="380"/>
+      <c r="B54" s="400"/>
+      <c r="C54" s="397"/>
+      <c r="D54" s="397"/>
+      <c r="E54" s="397"/>
+      <c r="F54" s="397"/>
+      <c r="G54" s="397"/>
+      <c r="H54" s="397"/>
+      <c r="I54" s="397"/>
+      <c r="J54" s="397"/>
+      <c r="K54" s="397"/>
+      <c r="L54" s="397"/>
     </row>
   </sheetData>
   <mergeCells count="61">
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B2:J3"/>
+    <mergeCell ref="F6:L6"/>
+    <mergeCell ref="B53:L53"/>
+    <mergeCell ref="B51:L52"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G16:L16"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="H31:L31"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="G47:K47"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="C36:L36"/>
     <mergeCell ref="B35:L35"/>
     <mergeCell ref="H30:L30"/>
     <mergeCell ref="F7:L8"/>
@@ -7157,51 +7202,6 @@
     <mergeCell ref="D25:L25"/>
     <mergeCell ref="I27:L27"/>
     <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B54:L54"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="G42:K42"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="H31:L31"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G48:K48"/>
-    <mergeCell ref="G47:K47"/>
-    <mergeCell ref="G41:K41"/>
-    <mergeCell ref="C36:L36"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B2:J3"/>
-    <mergeCell ref="F6:L6"/>
-    <mergeCell ref="B53:L53"/>
-    <mergeCell ref="B51:L52"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="C9:L9"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -7225,95 +7225,95 @@
   <sheetData>
     <row r="1" spans="1:30" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="210"/>
-      <c r="B1" s="413"/>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
-      <c r="H1" s="346"/>
-      <c r="I1" s="346"/>
-      <c r="J1" s="346"/>
-      <c r="K1" s="346"/>
-      <c r="L1" s="346"/>
-      <c r="M1" s="346"/>
-      <c r="N1" s="346"/>
-      <c r="O1" s="346"/>
-      <c r="P1" s="346"/>
-      <c r="Q1" s="346"/>
-      <c r="R1" s="346"/>
-      <c r="S1" s="346"/>
-      <c r="T1" s="346"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="355"/>
+      <c r="D1" s="355"/>
+      <c r="E1" s="355"/>
+      <c r="F1" s="355"/>
+      <c r="G1" s="355"/>
+      <c r="H1" s="355"/>
+      <c r="I1" s="355"/>
+      <c r="J1" s="355"/>
+      <c r="K1" s="355"/>
+      <c r="L1" s="355"/>
+      <c r="M1" s="355"/>
+      <c r="N1" s="355"/>
+      <c r="O1" s="355"/>
+      <c r="P1" s="355"/>
+      <c r="Q1" s="355"/>
+      <c r="R1" s="355"/>
+      <c r="S1" s="355"/>
+      <c r="T1" s="355"/>
       <c r="U1" s="211"/>
     </row>
     <row r="2" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="212"/>
-      <c r="B2" s="407" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="408"/>
-      <c r="D2" s="408"/>
-      <c r="E2" s="408"/>
-      <c r="F2" s="408"/>
-      <c r="G2" s="408"/>
-      <c r="H2" s="408"/>
-      <c r="I2" s="408"/>
-      <c r="J2" s="408"/>
-      <c r="K2" s="408"/>
-      <c r="L2" s="408"/>
-      <c r="M2" s="408"/>
-      <c r="N2" s="408"/>
-      <c r="O2" s="408"/>
-      <c r="P2" s="408"/>
-      <c r="Q2" s="408"/>
-      <c r="R2" s="408"/>
-      <c r="S2" s="408"/>
-      <c r="T2" s="408"/>
+      <c r="B2" s="351" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="352"/>
+      <c r="D2" s="352"/>
+      <c r="E2" s="352"/>
+      <c r="F2" s="352"/>
+      <c r="G2" s="352"/>
+      <c r="H2" s="352"/>
+      <c r="I2" s="352"/>
+      <c r="J2" s="352"/>
+      <c r="K2" s="352"/>
+      <c r="L2" s="352"/>
+      <c r="M2" s="352"/>
+      <c r="N2" s="352"/>
+      <c r="O2" s="352"/>
+      <c r="P2" s="352"/>
+      <c r="Q2" s="352"/>
+      <c r="R2" s="352"/>
+      <c r="S2" s="352"/>
+      <c r="T2" s="352"/>
       <c r="U2" s="213"/>
     </row>
     <row r="3" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="212"/>
-      <c r="B3" s="417" t="s">
+      <c r="B3" s="358" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
-      <c r="L3" s="364"/>
-      <c r="M3" s="364"/>
-      <c r="N3" s="364"/>
-      <c r="O3" s="364"/>
-      <c r="P3" s="364"/>
-      <c r="Q3" s="364"/>
-      <c r="R3" s="364"/>
-      <c r="S3" s="364"/>
-      <c r="T3" s="364"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
+      <c r="F3" s="344"/>
+      <c r="G3" s="344"/>
+      <c r="H3" s="344"/>
+      <c r="I3" s="344"/>
+      <c r="J3" s="344"/>
+      <c r="K3" s="344"/>
+      <c r="L3" s="344"/>
+      <c r="M3" s="344"/>
+      <c r="N3" s="344"/>
+      <c r="O3" s="344"/>
+      <c r="P3" s="344"/>
+      <c r="Q3" s="344"/>
+      <c r="R3" s="344"/>
+      <c r="S3" s="344"/>
+      <c r="T3" s="344"/>
       <c r="U3" s="213"/>
     </row>
     <row r="4" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="212"/>
-      <c r="B4" s="418" t="s">
+      <c r="B4" s="336" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="368"/>
-      <c r="D4" s="368"/>
-      <c r="E4" s="368"/>
-      <c r="F4" s="368"/>
-      <c r="G4" s="368"/>
-      <c r="H4" s="368"/>
-      <c r="I4" s="368"/>
-      <c r="J4" s="368"/>
-      <c r="K4" s="368"/>
-      <c r="L4" s="368"/>
-      <c r="M4" s="368"/>
-      <c r="N4" s="368"/>
-      <c r="O4" s="356"/>
+      <c r="C4" s="337"/>
+      <c r="D4" s="337"/>
+      <c r="E4" s="337"/>
+      <c r="F4" s="337"/>
+      <c r="G4" s="337"/>
+      <c r="H4" s="337"/>
+      <c r="I4" s="337"/>
+      <c r="J4" s="337"/>
+      <c r="K4" s="337"/>
+      <c r="L4" s="337"/>
+      <c r="M4" s="337"/>
+      <c r="N4" s="337"/>
+      <c r="O4" s="334"/>
       <c r="P4" s="259" t="s">
         <v>58</v>
       </c>
@@ -7328,50 +7328,50 @@
     </row>
     <row r="5" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="212"/>
-      <c r="B5" s="423" t="s">
+      <c r="B5" s="350" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="372"/>
-      <c r="D5" s="421" t="str">
+      <c r="C5" s="342"/>
+      <c r="D5" s="341" t="str">
         <f>CAPA!C3</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="372"/>
-      <c r="F5" s="372"/>
-      <c r="G5" s="372"/>
-      <c r="H5" s="372"/>
-      <c r="I5" s="372"/>
-      <c r="J5" s="372"/>
-      <c r="K5" s="372"/>
-      <c r="L5" s="372"/>
-      <c r="M5" s="372"/>
-      <c r="N5" s="372"/>
-      <c r="O5" s="373"/>
-      <c r="P5" s="415" t="s">
+      <c r="E5" s="342"/>
+      <c r="F5" s="342"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="342"/>
+      <c r="I5" s="342"/>
+      <c r="J5" s="342"/>
+      <c r="K5" s="342"/>
+      <c r="L5" s="342"/>
+      <c r="M5" s="342"/>
+      <c r="N5" s="342"/>
+      <c r="O5" s="343"/>
+      <c r="P5" s="356" t="s">
         <v>5</v>
       </c>
-      <c r="Q5" s="372"/>
-      <c r="R5" s="372"/>
-      <c r="S5" s="372"/>
-      <c r="T5" s="373"/>
+      <c r="Q5" s="342"/>
+      <c r="R5" s="342"/>
+      <c r="S5" s="342"/>
+      <c r="T5" s="343"/>
       <c r="U5" s="213"/>
     </row>
     <row r="6" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="212"/>
-      <c r="B6" s="374"/>
-      <c r="C6" s="364"/>
-      <c r="D6" s="364"/>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
-      <c r="G6" s="364"/>
-      <c r="H6" s="364"/>
-      <c r="I6" s="364"/>
-      <c r="J6" s="364"/>
-      <c r="K6" s="364"/>
-      <c r="L6" s="364"/>
-      <c r="M6" s="364"/>
-      <c r="N6" s="364"/>
-      <c r="O6" s="375"/>
+      <c r="B6" s="348"/>
+      <c r="C6" s="344"/>
+      <c r="D6" s="344"/>
+      <c r="E6" s="344"/>
+      <c r="F6" s="344"/>
+      <c r="G6" s="344"/>
+      <c r="H6" s="344"/>
+      <c r="I6" s="344"/>
+      <c r="J6" s="344"/>
+      <c r="K6" s="344"/>
+      <c r="L6" s="344"/>
+      <c r="M6" s="344"/>
+      <c r="N6" s="344"/>
+      <c r="O6" s="345"/>
       <c r="P6" s="75" t="s">
         <v>6</v>
       </c>
@@ -7385,29 +7385,29 @@
     </row>
     <row r="7" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="212"/>
-      <c r="B7" s="411" t="s">
+      <c r="B7" s="353" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
-      <c r="E7" s="368"/>
-      <c r="F7" s="368"/>
-      <c r="G7" s="368"/>
-      <c r="H7" s="368"/>
-      <c r="I7" s="368"/>
-      <c r="J7" s="368"/>
+      <c r="C7" s="337"/>
+      <c r="D7" s="337"/>
+      <c r="E7" s="337"/>
+      <c r="F7" s="337"/>
+      <c r="G7" s="337"/>
+      <c r="H7" s="337"/>
+      <c r="I7" s="337"/>
+      <c r="J7" s="337"/>
       <c r="K7" s="267"/>
       <c r="L7" s="268"/>
-      <c r="M7" s="418" t="s">
+      <c r="M7" s="336" t="s">
         <v>8</v>
       </c>
-      <c r="N7" s="368"/>
-      <c r="O7" s="368"/>
-      <c r="P7" s="368"/>
-      <c r="Q7" s="368"/>
-      <c r="R7" s="368"/>
-      <c r="S7" s="368"/>
-      <c r="T7" s="356"/>
+      <c r="N7" s="337"/>
+      <c r="O7" s="337"/>
+      <c r="P7" s="337"/>
+      <c r="Q7" s="337"/>
+      <c r="R7" s="337"/>
+      <c r="S7" s="337"/>
+      <c r="T7" s="334"/>
       <c r="U7" s="213"/>
     </row>
     <row r="8" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7496,110 +7496,110 @@
     <row r="11" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="214"/>
       <c r="B11" s="159"/>
-      <c r="C11" s="416" t="s">
+      <c r="C11" s="357" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="368"/>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
-      <c r="G11" s="368"/>
-      <c r="H11" s="368"/>
-      <c r="I11" s="368"/>
-      <c r="J11" s="368"/>
-      <c r="K11" s="368"/>
-      <c r="L11" s="356"/>
-      <c r="M11" s="412" t="s">
+      <c r="D11" s="337"/>
+      <c r="E11" s="337"/>
+      <c r="F11" s="337"/>
+      <c r="G11" s="337"/>
+      <c r="H11" s="337"/>
+      <c r="I11" s="337"/>
+      <c r="J11" s="337"/>
+      <c r="K11" s="337"/>
+      <c r="L11" s="334"/>
+      <c r="M11" s="349" t="s">
         <v>136</v>
       </c>
-      <c r="N11" s="368"/>
-      <c r="O11" s="368"/>
-      <c r="P11" s="368"/>
-      <c r="Q11" s="356"/>
-      <c r="R11" s="409" t="s">
+      <c r="N11" s="337"/>
+      <c r="O11" s="337"/>
+      <c r="P11" s="337"/>
+      <c r="Q11" s="334"/>
+      <c r="R11" s="335" t="s">
         <v>137</v>
       </c>
-      <c r="S11" s="373"/>
-      <c r="T11" s="420" t="s">
+      <c r="S11" s="343"/>
+      <c r="T11" s="338" t="s">
         <v>138</v>
       </c>
       <c r="U11" s="215"/>
     </row>
     <row r="12" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="214"/>
-      <c r="B12" s="409" t="s">
+      <c r="B12" s="335" t="s">
         <v>139</v>
       </c>
-      <c r="C12" s="416" t="s">
+      <c r="C12" s="357" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="368"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
-      <c r="G12" s="356"/>
-      <c r="H12" s="412" t="s">
+      <c r="D12" s="337"/>
+      <c r="E12" s="337"/>
+      <c r="F12" s="337"/>
+      <c r="G12" s="334"/>
+      <c r="H12" s="349" t="s">
         <v>141</v>
       </c>
-      <c r="I12" s="368"/>
-      <c r="J12" s="368"/>
-      <c r="K12" s="368"/>
-      <c r="L12" s="356"/>
-      <c r="M12" s="412" t="s">
+      <c r="I12" s="337"/>
+      <c r="J12" s="337"/>
+      <c r="K12" s="337"/>
+      <c r="L12" s="334"/>
+      <c r="M12" s="349" t="s">
         <v>142</v>
       </c>
-      <c r="N12" s="368"/>
-      <c r="O12" s="368"/>
-      <c r="P12" s="368"/>
-      <c r="Q12" s="356"/>
-      <c r="R12" s="422"/>
-      <c r="S12" s="381"/>
-      <c r="T12" s="419"/>
+      <c r="N12" s="337"/>
+      <c r="O12" s="337"/>
+      <c r="P12" s="337"/>
+      <c r="Q12" s="334"/>
+      <c r="R12" s="346"/>
+      <c r="S12" s="347"/>
+      <c r="T12" s="339"/>
       <c r="U12" s="215"/>
     </row>
     <row r="13" spans="1:30" s="53" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="216"/>
-      <c r="B13" s="419"/>
-      <c r="C13" s="409" t="s">
+      <c r="B13" s="339"/>
+      <c r="C13" s="335" t="s">
         <v>143</v>
       </c>
-      <c r="D13" s="409" t="s">
+      <c r="D13" s="335" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="414" t="s">
+      <c r="E13" s="334"/>
+      <c r="F13" s="333" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="356"/>
-      <c r="H13" s="409" t="s">
+      <c r="G13" s="334"/>
+      <c r="H13" s="335" t="s">
         <v>143</v>
       </c>
-      <c r="I13" s="409" t="s">
+      <c r="I13" s="335" t="s">
         <v>144</v>
       </c>
-      <c r="J13" s="356"/>
-      <c r="K13" s="414" t="s">
+      <c r="J13" s="334"/>
+      <c r="K13" s="333" t="s">
         <v>145</v>
       </c>
-      <c r="L13" s="356"/>
-      <c r="M13" s="409" t="s">
+      <c r="L13" s="334"/>
+      <c r="M13" s="335" t="s">
         <v>143</v>
       </c>
-      <c r="N13" s="409" t="s">
+      <c r="N13" s="335" t="s">
         <v>144</v>
       </c>
-      <c r="O13" s="356"/>
-      <c r="P13" s="414" t="s">
+      <c r="O13" s="334"/>
+      <c r="P13" s="333" t="s">
         <v>145</v>
       </c>
-      <c r="Q13" s="356"/>
-      <c r="R13" s="374"/>
-      <c r="S13" s="375"/>
-      <c r="T13" s="419"/>
+      <c r="Q13" s="334"/>
+      <c r="R13" s="348"/>
+      <c r="S13" s="345"/>
+      <c r="T13" s="339"/>
       <c r="U13" s="217"/>
     </row>
     <row r="14" spans="1:30" s="53" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="216"/>
-      <c r="B14" s="410"/>
-      <c r="C14" s="410"/>
+      <c r="B14" s="340"/>
+      <c r="C14" s="340"/>
       <c r="D14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7612,7 +7612,7 @@
       <c r="G14" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="H14" s="410"/>
+      <c r="H14" s="340"/>
       <c r="I14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7625,7 +7625,7 @@
       <c r="L14" s="151" t="s">
         <v>151</v>
       </c>
-      <c r="M14" s="410"/>
+      <c r="M14" s="340"/>
       <c r="N14" s="78" t="s">
         <v>146</v>
       </c>
@@ -7644,7 +7644,7 @@
       <c r="S14" s="151" t="s">
         <v>155</v>
       </c>
-      <c r="T14" s="419"/>
+      <c r="T14" s="339"/>
       <c r="U14" s="217"/>
     </row>
     <row r="15" spans="1:30" s="16" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7703,7 +7703,7 @@
       <c r="S15" s="15">
         <v>18</v>
       </c>
-      <c r="T15" s="410"/>
+      <c r="T15" s="340"/>
       <c r="U15" s="201"/>
       <c r="V15" s="10"/>
       <c r="W15" s="10"/>
@@ -8914,16 +8914,6 @@
     <row r="42" spans="1:21" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="T11:T15"/>
-    <mergeCell ref="D5:O6"/>
-    <mergeCell ref="R11:S13"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="M11:Q11"/>
-    <mergeCell ref="B5:C6"/>
     <mergeCell ref="B2:T2"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="B7:J7"/>
@@ -8940,6 +8930,16 @@
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="T11:T15"/>
+    <mergeCell ref="D5:O6"/>
+    <mergeCell ref="R11:S13"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="B5:C6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -8980,103 +8980,103 @@
   <sheetData>
     <row r="1" spans="1:23" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="223"/>
-      <c r="B1" s="430"/>
-      <c r="C1" s="370"/>
-      <c r="D1" s="370"/>
-      <c r="E1" s="370"/>
-      <c r="F1" s="370"/>
-      <c r="G1" s="370"/>
-      <c r="H1" s="370"/>
-      <c r="I1" s="370"/>
-      <c r="J1" s="370"/>
-      <c r="K1" s="370"/>
-      <c r="L1" s="370"/>
-      <c r="M1" s="370"/>
-      <c r="N1" s="370"/>
-      <c r="O1" s="370"/>
-      <c r="P1" s="370"/>
-      <c r="Q1" s="370"/>
-      <c r="R1" s="370"/>
-      <c r="S1" s="370"/>
-      <c r="T1" s="370"/>
-      <c r="U1" s="370"/>
-      <c r="V1" s="370"/>
+      <c r="B1" s="429"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
+      <c r="K1" s="410"/>
+      <c r="L1" s="410"/>
+      <c r="M1" s="410"/>
+      <c r="N1" s="410"/>
+      <c r="O1" s="410"/>
+      <c r="P1" s="410"/>
+      <c r="Q1" s="410"/>
+      <c r="R1" s="410"/>
+      <c r="S1" s="410"/>
+      <c r="T1" s="410"/>
+      <c r="U1" s="410"/>
+      <c r="V1" s="410"/>
       <c r="W1" s="224"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="435" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="372"/>
-      <c r="D2" s="372"/>
-      <c r="E2" s="372"/>
-      <c r="F2" s="372"/>
-      <c r="G2" s="372"/>
-      <c r="H2" s="372"/>
-      <c r="I2" s="372"/>
-      <c r="J2" s="372"/>
-      <c r="K2" s="372"/>
-      <c r="L2" s="372"/>
-      <c r="M2" s="372"/>
-      <c r="N2" s="372"/>
-      <c r="O2" s="372"/>
-      <c r="P2" s="372"/>
-      <c r="Q2" s="372"/>
-      <c r="R2" s="372"/>
-      <c r="S2" s="372"/>
-      <c r="T2" s="372"/>
-      <c r="U2" s="372"/>
-      <c r="V2" s="373"/>
+      <c r="B2" s="424" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
+      <c r="J2" s="342"/>
+      <c r="K2" s="342"/>
+      <c r="L2" s="342"/>
+      <c r="M2" s="342"/>
+      <c r="N2" s="342"/>
+      <c r="O2" s="342"/>
+      <c r="P2" s="342"/>
+      <c r="Q2" s="342"/>
+      <c r="R2" s="342"/>
+      <c r="S2" s="342"/>
+      <c r="T2" s="342"/>
+      <c r="U2" s="342"/>
+      <c r="V2" s="343"/>
       <c r="W2" s="202"/>
     </row>
     <row r="3" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="426" t="s">
+      <c r="B3" s="436" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
-      <c r="L3" s="364"/>
-      <c r="M3" s="364"/>
-      <c r="N3" s="364"/>
-      <c r="O3" s="364"/>
-      <c r="P3" s="364"/>
-      <c r="Q3" s="364"/>
-      <c r="R3" s="364"/>
-      <c r="S3" s="364"/>
-      <c r="T3" s="364"/>
-      <c r="U3" s="364"/>
-      <c r="V3" s="375"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
+      <c r="F3" s="344"/>
+      <c r="G3" s="344"/>
+      <c r="H3" s="344"/>
+      <c r="I3" s="344"/>
+      <c r="J3" s="344"/>
+      <c r="K3" s="344"/>
+      <c r="L3" s="344"/>
+      <c r="M3" s="344"/>
+      <c r="N3" s="344"/>
+      <c r="O3" s="344"/>
+      <c r="P3" s="344"/>
+      <c r="Q3" s="344"/>
+      <c r="R3" s="344"/>
+      <c r="S3" s="344"/>
+      <c r="T3" s="344"/>
+      <c r="U3" s="344"/>
+      <c r="V3" s="345"/>
       <c r="W3" s="202"/>
     </row>
     <row r="4" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="432" t="s">
+      <c r="B4" s="431" t="s">
         <v>160</v>
       </c>
-      <c r="C4" s="368"/>
-      <c r="D4" s="368"/>
-      <c r="E4" s="368"/>
-      <c r="F4" s="368"/>
-      <c r="G4" s="368"/>
-      <c r="H4" s="368"/>
-      <c r="I4" s="368"/>
-      <c r="J4" s="368"/>
-      <c r="K4" s="368"/>
-      <c r="L4" s="368"/>
-      <c r="M4" s="368"/>
-      <c r="N4" s="368"/>
-      <c r="O4" s="368"/>
-      <c r="P4" s="368"/>
-      <c r="Q4" s="356"/>
+      <c r="C4" s="337"/>
+      <c r="D4" s="337"/>
+      <c r="E4" s="337"/>
+      <c r="F4" s="337"/>
+      <c r="G4" s="337"/>
+      <c r="H4" s="337"/>
+      <c r="I4" s="337"/>
+      <c r="J4" s="337"/>
+      <c r="K4" s="337"/>
+      <c r="L4" s="337"/>
+      <c r="M4" s="337"/>
+      <c r="N4" s="337"/>
+      <c r="O4" s="337"/>
+      <c r="P4" s="337"/>
+      <c r="Q4" s="334"/>
       <c r="R4" s="259" t="s">
         <v>58</v>
       </c>
@@ -9091,54 +9091,54 @@
     </row>
     <row r="5" spans="1:23" s="1" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="431" t="s">
+      <c r="B5" s="430" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="372"/>
-      <c r="D5" s="421" t="str">
+      <c r="C5" s="342"/>
+      <c r="D5" s="341" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="372"/>
-      <c r="F5" s="372"/>
-      <c r="G5" s="372"/>
-      <c r="H5" s="372"/>
-      <c r="I5" s="372"/>
-      <c r="J5" s="372"/>
-      <c r="K5" s="372"/>
-      <c r="L5" s="372"/>
-      <c r="M5" s="372"/>
-      <c r="N5" s="372"/>
-      <c r="O5" s="372"/>
-      <c r="P5" s="372"/>
-      <c r="Q5" s="373"/>
-      <c r="R5" s="429" t="s">
+      <c r="E5" s="342"/>
+      <c r="F5" s="342"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="342"/>
+      <c r="I5" s="342"/>
+      <c r="J5" s="342"/>
+      <c r="K5" s="342"/>
+      <c r="L5" s="342"/>
+      <c r="M5" s="342"/>
+      <c r="N5" s="342"/>
+      <c r="O5" s="342"/>
+      <c r="P5" s="342"/>
+      <c r="Q5" s="343"/>
+      <c r="R5" s="437" t="s">
         <v>5</v>
       </c>
-      <c r="S5" s="368"/>
-      <c r="T5" s="368"/>
-      <c r="U5" s="368"/>
-      <c r="V5" s="356"/>
+      <c r="S5" s="337"/>
+      <c r="T5" s="337"/>
+      <c r="U5" s="337"/>
+      <c r="V5" s="334"/>
       <c r="W5" s="202"/>
     </row>
     <row r="6" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="225"/>
-      <c r="B6" s="374"/>
-      <c r="C6" s="364"/>
-      <c r="D6" s="364"/>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
-      <c r="G6" s="364"/>
-      <c r="H6" s="364"/>
-      <c r="I6" s="364"/>
-      <c r="J6" s="364"/>
-      <c r="K6" s="364"/>
-      <c r="L6" s="364"/>
-      <c r="M6" s="364"/>
-      <c r="N6" s="364"/>
-      <c r="O6" s="364"/>
-      <c r="P6" s="364"/>
-      <c r="Q6" s="375"/>
+      <c r="B6" s="348"/>
+      <c r="C6" s="344"/>
+      <c r="D6" s="344"/>
+      <c r="E6" s="344"/>
+      <c r="F6" s="344"/>
+      <c r="G6" s="344"/>
+      <c r="H6" s="344"/>
+      <c r="I6" s="344"/>
+      <c r="J6" s="344"/>
+      <c r="K6" s="344"/>
+      <c r="L6" s="344"/>
+      <c r="M6" s="344"/>
+      <c r="N6" s="344"/>
+      <c r="O6" s="344"/>
+      <c r="P6" s="344"/>
+      <c r="Q6" s="345"/>
       <c r="R6" s="49" t="s">
         <v>6</v>
       </c>
@@ -9153,31 +9153,31 @@
     </row>
     <row r="7" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="225"/>
-      <c r="B7" s="437" t="s">
+      <c r="B7" s="428" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
-      <c r="E7" s="368"/>
-      <c r="F7" s="368"/>
-      <c r="G7" s="368"/>
-      <c r="H7" s="368"/>
-      <c r="I7" s="368"/>
-      <c r="J7" s="368"/>
-      <c r="K7" s="368"/>
-      <c r="L7" s="368"/>
-      <c r="M7" s="356"/>
-      <c r="N7" s="437" t="s">
+      <c r="C7" s="337"/>
+      <c r="D7" s="337"/>
+      <c r="E7" s="337"/>
+      <c r="F7" s="337"/>
+      <c r="G7" s="337"/>
+      <c r="H7" s="337"/>
+      <c r="I7" s="337"/>
+      <c r="J7" s="337"/>
+      <c r="K7" s="337"/>
+      <c r="L7" s="337"/>
+      <c r="M7" s="334"/>
+      <c r="N7" s="428" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="368"/>
-      <c r="P7" s="368"/>
-      <c r="Q7" s="368"/>
-      <c r="R7" s="368"/>
-      <c r="S7" s="368"/>
-      <c r="T7" s="368"/>
-      <c r="U7" s="368"/>
-      <c r="V7" s="356"/>
+      <c r="O7" s="337"/>
+      <c r="P7" s="337"/>
+      <c r="Q7" s="337"/>
+      <c r="R7" s="337"/>
+      <c r="S7" s="337"/>
+      <c r="T7" s="337"/>
+      <c r="U7" s="337"/>
+      <c r="V7" s="334"/>
       <c r="W7" s="226"/>
     </row>
     <row r="8" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9274,33 +9274,33 @@
       <c r="B11" s="425" t="s">
         <v>161</v>
       </c>
-      <c r="C11" s="433" t="s">
+      <c r="C11" s="432" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="368"/>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
-      <c r="G11" s="368"/>
-      <c r="H11" s="368"/>
-      <c r="I11" s="368"/>
-      <c r="J11" s="368"/>
-      <c r="K11" s="368"/>
-      <c r="L11" s="368"/>
-      <c r="M11" s="356"/>
-      <c r="N11" s="427" t="s">
+      <c r="D11" s="337"/>
+      <c r="E11" s="337"/>
+      <c r="F11" s="337"/>
+      <c r="G11" s="337"/>
+      <c r="H11" s="337"/>
+      <c r="I11" s="337"/>
+      <c r="J11" s="337"/>
+      <c r="K11" s="337"/>
+      <c r="L11" s="337"/>
+      <c r="M11" s="334"/>
+      <c r="N11" s="433" t="s">
         <v>162</v>
       </c>
-      <c r="O11" s="424" t="s">
+      <c r="O11" s="426" t="s">
         <v>136</v>
       </c>
-      <c r="P11" s="368"/>
-      <c r="Q11" s="368"/>
-      <c r="R11" s="368"/>
-      <c r="S11" s="356"/>
-      <c r="T11" s="436" t="s">
+      <c r="P11" s="337"/>
+      <c r="Q11" s="337"/>
+      <c r="R11" s="337"/>
+      <c r="S11" s="334"/>
+      <c r="T11" s="427" t="s">
         <v>163</v>
       </c>
-      <c r="U11" s="373"/>
+      <c r="U11" s="343"/>
       <c r="V11" s="434" t="s">
         <v>164</v>
       </c>
@@ -9308,147 +9308,147 @@
     </row>
     <row r="12" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="296"/>
-      <c r="B12" s="419"/>
-      <c r="C12" s="433" t="s">
+      <c r="B12" s="339"/>
+      <c r="C12" s="432" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="368"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
-      <c r="G12" s="356"/>
-      <c r="H12" s="424" t="s">
+      <c r="D12" s="337"/>
+      <c r="E12" s="337"/>
+      <c r="F12" s="337"/>
+      <c r="G12" s="334"/>
+      <c r="H12" s="426" t="s">
         <v>141</v>
       </c>
-      <c r="I12" s="368"/>
-      <c r="J12" s="368"/>
-      <c r="K12" s="368"/>
-      <c r="L12" s="356"/>
-      <c r="M12" s="427" t="s">
+      <c r="I12" s="337"/>
+      <c r="J12" s="337"/>
+      <c r="K12" s="337"/>
+      <c r="L12" s="334"/>
+      <c r="M12" s="433" t="s">
         <v>165</v>
       </c>
-      <c r="N12" s="419"/>
-      <c r="O12" s="424" t="s">
+      <c r="N12" s="339"/>
+      <c r="O12" s="426" t="s">
         <v>142</v>
       </c>
-      <c r="P12" s="368"/>
-      <c r="Q12" s="368"/>
-      <c r="R12" s="368"/>
-      <c r="S12" s="356"/>
-      <c r="T12" s="422"/>
-      <c r="U12" s="381"/>
-      <c r="V12" s="419"/>
+      <c r="P12" s="337"/>
+      <c r="Q12" s="337"/>
+      <c r="R12" s="337"/>
+      <c r="S12" s="334"/>
+      <c r="T12" s="346"/>
+      <c r="U12" s="347"/>
+      <c r="V12" s="339"/>
       <c r="W12" s="227"/>
     </row>
     <row r="13" spans="1:23" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="296"/>
-      <c r="B13" s="419"/>
-      <c r="C13" s="409" t="s">
+      <c r="B13" s="339"/>
+      <c r="C13" s="335" t="s">
         <v>166</v>
       </c>
-      <c r="D13" s="409" t="s">
+      <c r="D13" s="335" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="428" t="s">
+      <c r="E13" s="334"/>
+      <c r="F13" s="435" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="373"/>
-      <c r="H13" s="409" t="s">
+      <c r="G13" s="343"/>
+      <c r="H13" s="335" t="s">
         <v>166</v>
       </c>
-      <c r="I13" s="409" t="s">
+      <c r="I13" s="335" t="s">
         <v>144</v>
       </c>
-      <c r="J13" s="356"/>
-      <c r="K13" s="428" t="s">
+      <c r="J13" s="334"/>
+      <c r="K13" s="435" t="s">
         <v>145</v>
       </c>
-      <c r="L13" s="373"/>
-      <c r="M13" s="419"/>
-      <c r="N13" s="419"/>
-      <c r="O13" s="409" t="s">
+      <c r="L13" s="343"/>
+      <c r="M13" s="339"/>
+      <c r="N13" s="339"/>
+      <c r="O13" s="335" t="s">
         <v>167</v>
       </c>
-      <c r="P13" s="409" t="s">
+      <c r="P13" s="335" t="s">
         <v>144</v>
       </c>
-      <c r="Q13" s="356"/>
+      <c r="Q13" s="334"/>
       <c r="R13" s="425" t="s">
         <v>145</v>
       </c>
-      <c r="S13" s="356"/>
-      <c r="T13" s="374"/>
-      <c r="U13" s="375"/>
-      <c r="V13" s="419"/>
+      <c r="S13" s="334"/>
+      <c r="T13" s="348"/>
+      <c r="U13" s="345"/>
+      <c r="V13" s="339"/>
       <c r="W13" s="227"/>
     </row>
     <row r="14" spans="1:23" s="36" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="296"/>
-      <c r="B14" s="419"/>
-      <c r="C14" s="419"/>
+      <c r="B14" s="339"/>
+      <c r="C14" s="339"/>
       <c r="D14" s="425" t="s">
         <v>146</v>
       </c>
-      <c r="E14" s="409" t="s">
+      <c r="E14" s="335" t="s">
         <v>168</v>
       </c>
-      <c r="F14" s="409" t="s">
+      <c r="F14" s="335" t="s">
         <v>169</v>
       </c>
-      <c r="G14" s="409" t="s">
+      <c r="G14" s="335" t="s">
         <v>170</v>
       </c>
-      <c r="H14" s="419"/>
+      <c r="H14" s="339"/>
       <c r="I14" s="425" t="s">
         <v>146</v>
       </c>
-      <c r="J14" s="409" t="s">
+      <c r="J14" s="335" t="s">
         <v>168</v>
       </c>
-      <c r="K14" s="409" t="s">
+      <c r="K14" s="335" t="s">
         <v>171</v>
       </c>
-      <c r="L14" s="409" t="s">
+      <c r="L14" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="M14" s="419"/>
-      <c r="N14" s="410"/>
-      <c r="O14" s="410"/>
+      <c r="M14" s="339"/>
+      <c r="N14" s="340"/>
+      <c r="O14" s="340"/>
       <c r="P14" s="159" t="s">
         <v>173</v>
       </c>
       <c r="Q14" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="R14" s="409" t="s">
+      <c r="R14" s="335" t="s">
         <v>174</v>
       </c>
-      <c r="S14" s="409" t="s">
+      <c r="S14" s="335" t="s">
         <v>175</v>
       </c>
-      <c r="T14" s="409" t="s">
+      <c r="T14" s="335" t="s">
         <v>176</v>
       </c>
-      <c r="U14" s="409" t="s">
+      <c r="U14" s="335" t="s">
         <v>177</v>
       </c>
-      <c r="V14" s="419"/>
+      <c r="V14" s="339"/>
       <c r="W14" s="227"/>
     </row>
     <row r="15" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="296"/>
-      <c r="B15" s="410"/>
-      <c r="C15" s="410"/>
-      <c r="D15" s="410"/>
-      <c r="E15" s="410"/>
-      <c r="F15" s="410"/>
-      <c r="G15" s="410"/>
-      <c r="H15" s="410"/>
-      <c r="I15" s="410"/>
-      <c r="J15" s="410"/>
-      <c r="K15" s="410"/>
-      <c r="L15" s="410"/>
-      <c r="M15" s="410"/>
+      <c r="B15" s="340"/>
+      <c r="C15" s="340"/>
+      <c r="D15" s="340"/>
+      <c r="E15" s="340"/>
+      <c r="F15" s="340"/>
+      <c r="G15" s="340"/>
+      <c r="H15" s="340"/>
+      <c r="I15" s="340"/>
+      <c r="J15" s="340"/>
+      <c r="K15" s="340"/>
+      <c r="L15" s="340"/>
+      <c r="M15" s="340"/>
       <c r="N15" s="150" t="s">
         <v>178</v>
       </c>
@@ -9461,11 +9461,11 @@
       <c r="Q15" s="151" t="s">
         <v>181</v>
       </c>
-      <c r="R15" s="410"/>
-      <c r="S15" s="410"/>
-      <c r="T15" s="410"/>
-      <c r="U15" s="410"/>
-      <c r="V15" s="419"/>
+      <c r="R15" s="340"/>
+      <c r="S15" s="340"/>
+      <c r="T15" s="340"/>
+      <c r="U15" s="340"/>
+      <c r="V15" s="339"/>
       <c r="W15" s="227"/>
     </row>
     <row r="16" spans="1:23" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9530,7 +9530,7 @@
       <c r="U16" s="38">
         <v>38</v>
       </c>
-      <c r="V16" s="410"/>
+      <c r="V16" s="340"/>
       <c r="W16" s="227"/>
     </row>
     <row r="17" spans="1:98" s="36" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -9859,6 +9859,30 @@
     <row r="22" spans="1:98" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="B3:V3"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="N11:N14"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B1:V1"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="D5:Q6"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="M12:M15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="C11:M11"/>
+    <mergeCell ref="V11:V16"/>
+    <mergeCell ref="F13:G13"/>
     <mergeCell ref="B2:V2"/>
     <mergeCell ref="S14:S15"/>
     <mergeCell ref="T14:T15"/>
@@ -9875,30 +9899,6 @@
     <mergeCell ref="H12:L12"/>
     <mergeCell ref="R14:R15"/>
     <mergeCell ref="O13:O14"/>
-    <mergeCell ref="B1:V1"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="D5:Q6"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="M12:M15"/>
-    <mergeCell ref="U14:U15"/>
-    <mergeCell ref="C11:M11"/>
-    <mergeCell ref="V11:V16"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="B3:V3"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="N11:N14"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -9933,90 +9933,90 @@
   <sheetData>
     <row r="1" spans="1:14" ht="5.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="369"/>
-      <c r="C1" s="370"/>
-      <c r="D1" s="370"/>
-      <c r="E1" s="370"/>
-      <c r="F1" s="370"/>
-      <c r="G1" s="370"/>
-      <c r="H1" s="370"/>
-      <c r="I1" s="370"/>
-      <c r="J1" s="370"/>
-      <c r="K1" s="370"/>
-      <c r="L1" s="370"/>
-      <c r="M1" s="370"/>
+      <c r="B1" s="409"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
+      <c r="K1" s="410"/>
+      <c r="L1" s="410"/>
+      <c r="M1" s="410"/>
       <c r="N1" s="199"/>
     </row>
     <row r="2" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="249"/>
-      <c r="B2" s="435" t="s">
+      <c r="B2" s="424" t="s">
         <v>185</v>
       </c>
-      <c r="C2" s="372"/>
-      <c r="D2" s="372"/>
-      <c r="E2" s="372"/>
-      <c r="F2" s="372"/>
-      <c r="G2" s="372"/>
-      <c r="H2" s="372"/>
-      <c r="I2" s="372"/>
-      <c r="J2" s="372"/>
-      <c r="K2" s="372"/>
-      <c r="L2" s="372"/>
-      <c r="M2" s="373"/>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
+      <c r="J2" s="342"/>
+      <c r="K2" s="342"/>
+      <c r="L2" s="342"/>
+      <c r="M2" s="343"/>
       <c r="N2" s="201"/>
     </row>
     <row r="3" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="249"/>
-      <c r="B3" s="426" t="s">
+      <c r="B3" s="436" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
-      <c r="L3" s="364"/>
-      <c r="M3" s="375"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
+      <c r="F3" s="344"/>
+      <c r="G3" s="344"/>
+      <c r="H3" s="344"/>
+      <c r="I3" s="344"/>
+      <c r="J3" s="344"/>
+      <c r="K3" s="344"/>
+      <c r="L3" s="344"/>
+      <c r="M3" s="345"/>
       <c r="N3" s="201"/>
     </row>
     <row r="4" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="249"/>
-      <c r="B4" s="432" t="s">
+      <c r="B4" s="431" t="s">
         <v>186</v>
       </c>
-      <c r="C4" s="368"/>
-      <c r="D4" s="368"/>
-      <c r="E4" s="368"/>
-      <c r="F4" s="368"/>
-      <c r="G4" s="368"/>
-      <c r="H4" s="356"/>
-      <c r="I4" s="449" t="s">
+      <c r="C4" s="337"/>
+      <c r="D4" s="337"/>
+      <c r="E4" s="337"/>
+      <c r="F4" s="337"/>
+      <c r="G4" s="337"/>
+      <c r="H4" s="334"/>
+      <c r="I4" s="447" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="368"/>
-      <c r="K4" s="368"/>
-      <c r="L4" s="368"/>
-      <c r="M4" s="356"/>
+      <c r="J4" s="337"/>
+      <c r="K4" s="337"/>
+      <c r="L4" s="337"/>
+      <c r="M4" s="334"/>
       <c r="N4" s="201"/>
     </row>
     <row r="5" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="249"/>
-      <c r="B5" s="431" t="s">
+      <c r="B5" s="430" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="372"/>
-      <c r="D5" s="421" t="str">
+      <c r="C5" s="342"/>
+      <c r="D5" s="341" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="372"/>
-      <c r="F5" s="372"/>
-      <c r="G5" s="372"/>
-      <c r="H5" s="373"/>
+      <c r="E5" s="342"/>
+      <c r="F5" s="342"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="343"/>
       <c r="I5" s="136" t="s">
         <v>6</v>
       </c>
@@ -10031,17 +10031,17 @@
     </row>
     <row r="6" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="249"/>
-      <c r="B6" s="374"/>
-      <c r="C6" s="364"/>
-      <c r="D6" s="364"/>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
-      <c r="G6" s="364"/>
-      <c r="H6" s="375"/>
-      <c r="I6" s="451" t="s">
+      <c r="B6" s="348"/>
+      <c r="C6" s="344"/>
+      <c r="D6" s="344"/>
+      <c r="E6" s="344"/>
+      <c r="F6" s="344"/>
+      <c r="G6" s="344"/>
+      <c r="H6" s="345"/>
+      <c r="I6" s="439" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="356"/>
+      <c r="J6" s="334"/>
       <c r="K6" s="156"/>
       <c r="L6" s="148">
         <f>('QUADRO II'!T4)+1</f>
@@ -10053,21 +10053,21 @@
     <row r="7" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="249"/>
       <c r="B7" s="259"/>
-      <c r="C7" s="452" t="s">
+      <c r="C7" s="442" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="368"/>
-      <c r="E7" s="368"/>
-      <c r="F7" s="368"/>
-      <c r="G7" s="432" t="s">
+      <c r="D7" s="337"/>
+      <c r="E7" s="337"/>
+      <c r="F7" s="337"/>
+      <c r="G7" s="431" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="368"/>
-      <c r="I7" s="368"/>
-      <c r="J7" s="368"/>
-      <c r="K7" s="368"/>
-      <c r="L7" s="368"/>
-      <c r="M7" s="356"/>
+      <c r="H7" s="337"/>
+      <c r="I7" s="337"/>
+      <c r="J7" s="337"/>
+      <c r="K7" s="337"/>
+      <c r="L7" s="337"/>
+      <c r="M7" s="334"/>
       <c r="N7" s="201"/>
     </row>
     <row r="8" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10076,24 +10076,24 @@
         <v>9</v>
       </c>
       <c r="C8" s="76"/>
-      <c r="D8" s="447" t="str">
+      <c r="D8" s="445" t="str">
         <f>('QUADRO I'!$C$8)</f>
         <v>{IMCORPORADOR}</v>
       </c>
-      <c r="E8" s="372"/>
-      <c r="F8" s="373"/>
+      <c r="E8" s="342"/>
+      <c r="F8" s="343"/>
       <c r="G8" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="448" t="str">
+      <c r="H8" s="446" t="str">
         <f>('QUADRO I'!$N$8)</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="I8" s="372"/>
-      <c r="J8" s="372"/>
-      <c r="K8" s="372"/>
-      <c r="L8" s="372"/>
-      <c r="M8" s="373"/>
+      <c r="I8" s="342"/>
+      <c r="J8" s="342"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="343"/>
       <c r="N8" s="201"/>
     </row>
     <row r="9" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10102,18 +10102,18 @@
         <v>10</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="446"/>
-      <c r="E9" s="443"/>
-      <c r="F9" s="381"/>
+      <c r="D9" s="443"/>
+      <c r="E9" s="444"/>
+      <c r="F9" s="347"/>
       <c r="G9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="450"/>
-      <c r="I9" s="443"/>
-      <c r="J9" s="443"/>
-      <c r="K9" s="443"/>
-      <c r="L9" s="443"/>
-      <c r="M9" s="381"/>
+      <c r="H9" s="448"/>
+      <c r="I9" s="444"/>
+      <c r="J9" s="444"/>
+      <c r="K9" s="444"/>
+      <c r="L9" s="444"/>
+      <c r="M9" s="347"/>
       <c r="N9" s="201"/>
     </row>
     <row r="10" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -10122,12 +10122,12 @@
         <v>11</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="442" t="str">
+      <c r="D10" s="451" t="str">
         <f>('QUADRO I'!$C$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="E10" s="364"/>
-      <c r="F10" s="375"/>
+      <c r="E10" s="344"/>
+      <c r="F10" s="345"/>
       <c r="G10" s="5" t="s">
         <v>11</v>
       </c>
@@ -10135,12 +10135,12 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="I10" s="440" t="str">
+      <c r="I10" s="450" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="J10" s="364"/>
-      <c r="K10" s="364"/>
+      <c r="J10" s="344"/>
+      <c r="K10" s="344"/>
       <c r="L10" s="67" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -10150,7 +10150,7 @@
     </row>
     <row r="11" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="438" t="s">
+      <c r="B11" s="449" t="s">
         <v>188</v>
       </c>
       <c r="C11" s="163" t="s">
@@ -10170,132 +10170,132 @@
     </row>
     <row r="12" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="249"/>
-      <c r="B12" s="419"/>
-      <c r="C12" s="444" t="s">
+      <c r="B12" s="339"/>
+      <c r="C12" s="452" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="368"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
-      <c r="G12" s="445" t="s">
+      <c r="D12" s="337"/>
+      <c r="E12" s="337"/>
+      <c r="F12" s="337"/>
+      <c r="G12" s="441" t="s">
         <v>191</v>
       </c>
-      <c r="H12" s="368"/>
-      <c r="I12" s="368"/>
-      <c r="J12" s="368"/>
-      <c r="K12" s="368"/>
-      <c r="L12" s="368"/>
-      <c r="M12" s="356"/>
+      <c r="H12" s="337"/>
+      <c r="I12" s="337"/>
+      <c r="J12" s="337"/>
+      <c r="K12" s="337"/>
+      <c r="L12" s="337"/>
+      <c r="M12" s="334"/>
       <c r="N12" s="201"/>
     </row>
     <row r="13" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="249"/>
-      <c r="B13" s="419"/>
-      <c r="C13" s="439" t="s">
+      <c r="B13" s="339"/>
+      <c r="C13" s="440" t="s">
         <v>192</v>
       </c>
-      <c r="D13" s="439" t="s">
+      <c r="D13" s="440" t="s">
         <v>193</v>
       </c>
-      <c r="E13" s="439" t="s">
+      <c r="E13" s="440" t="s">
         <v>194</v>
       </c>
-      <c r="F13" s="439" t="s">
+      <c r="F13" s="440" t="s">
         <v>195</v>
       </c>
-      <c r="G13" s="445" t="s">
+      <c r="G13" s="441" t="s">
         <v>196</v>
       </c>
-      <c r="H13" s="372"/>
-      <c r="I13" s="372"/>
-      <c r="J13" s="372"/>
-      <c r="K13" s="372"/>
-      <c r="L13" s="372"/>
-      <c r="M13" s="373"/>
+      <c r="H13" s="342"/>
+      <c r="I13" s="342"/>
+      <c r="J13" s="342"/>
+      <c r="K13" s="342"/>
+      <c r="L13" s="342"/>
+      <c r="M13" s="343"/>
       <c r="N13" s="201"/>
     </row>
     <row r="14" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="249"/>
-      <c r="B14" s="419"/>
-      <c r="C14" s="419"/>
-      <c r="D14" s="419"/>
-      <c r="E14" s="419"/>
-      <c r="F14" s="419"/>
-      <c r="G14" s="374"/>
-      <c r="H14" s="364"/>
-      <c r="I14" s="364"/>
-      <c r="J14" s="364"/>
-      <c r="K14" s="364"/>
-      <c r="L14" s="364"/>
-      <c r="M14" s="375"/>
+      <c r="B14" s="339"/>
+      <c r="C14" s="339"/>
+      <c r="D14" s="339"/>
+      <c r="E14" s="339"/>
+      <c r="F14" s="339"/>
+      <c r="G14" s="348"/>
+      <c r="H14" s="344"/>
+      <c r="I14" s="344"/>
+      <c r="J14" s="344"/>
+      <c r="K14" s="344"/>
+      <c r="L14" s="344"/>
+      <c r="M14" s="345"/>
       <c r="N14" s="201"/>
     </row>
     <row r="15" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="249"/>
-      <c r="B15" s="419"/>
-      <c r="C15" s="419"/>
-      <c r="D15" s="419"/>
-      <c r="E15" s="419"/>
-      <c r="F15" s="419"/>
-      <c r="G15" s="445" t="s">
+      <c r="B15" s="339"/>
+      <c r="C15" s="339"/>
+      <c r="D15" s="339"/>
+      <c r="E15" s="339"/>
+      <c r="F15" s="339"/>
+      <c r="G15" s="441" t="s">
         <v>197</v>
       </c>
-      <c r="H15" s="445" t="s">
+      <c r="H15" s="441" t="s">
         <v>198</v>
       </c>
-      <c r="I15" s="439" t="s">
+      <c r="I15" s="440" t="s">
         <v>199</v>
       </c>
-      <c r="J15" s="373"/>
-      <c r="K15" s="439" t="s">
+      <c r="J15" s="343"/>
+      <c r="K15" s="440" t="s">
         <v>200</v>
       </c>
-      <c r="L15" s="372"/>
-      <c r="M15" s="373"/>
+      <c r="L15" s="342"/>
+      <c r="M15" s="343"/>
       <c r="N15" s="201"/>
     </row>
     <row r="16" spans="1:14" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="249"/>
-      <c r="B16" s="419"/>
-      <c r="C16" s="419"/>
-      <c r="D16" s="419"/>
-      <c r="E16" s="419"/>
-      <c r="F16" s="419"/>
-      <c r="G16" s="419"/>
-      <c r="H16" s="419"/>
-      <c r="I16" s="422"/>
-      <c r="J16" s="381"/>
-      <c r="K16" s="422"/>
-      <c r="L16" s="443"/>
-      <c r="M16" s="381"/>
+      <c r="B16" s="339"/>
+      <c r="C16" s="339"/>
+      <c r="D16" s="339"/>
+      <c r="E16" s="339"/>
+      <c r="F16" s="339"/>
+      <c r="G16" s="339"/>
+      <c r="H16" s="339"/>
+      <c r="I16" s="346"/>
+      <c r="J16" s="347"/>
+      <c r="K16" s="346"/>
+      <c r="L16" s="444"/>
+      <c r="M16" s="347"/>
       <c r="N16" s="201"/>
     </row>
     <row r="17" spans="1:14" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="249"/>
-      <c r="B17" s="419"/>
-      <c r="C17" s="410"/>
-      <c r="D17" s="410"/>
-      <c r="E17" s="410"/>
-      <c r="F17" s="410"/>
-      <c r="G17" s="410"/>
-      <c r="H17" s="410"/>
-      <c r="I17" s="374"/>
-      <c r="J17" s="375"/>
-      <c r="K17" s="374"/>
-      <c r="L17" s="364"/>
-      <c r="M17" s="375"/>
+      <c r="B17" s="339"/>
+      <c r="C17" s="340"/>
+      <c r="D17" s="340"/>
+      <c r="E17" s="340"/>
+      <c r="F17" s="340"/>
+      <c r="G17" s="340"/>
+      <c r="H17" s="340"/>
+      <c r="I17" s="348"/>
+      <c r="J17" s="345"/>
+      <c r="K17" s="348"/>
+      <c r="L17" s="344"/>
+      <c r="M17" s="345"/>
       <c r="N17" s="201"/>
     </row>
     <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="200"/>
-      <c r="B18" s="419"/>
-      <c r="C18" s="441" t="s">
+      <c r="B18" s="339"/>
+      <c r="C18" s="438" t="s">
         <v>201</v>
       </c>
-      <c r="D18" s="441" t="s">
+      <c r="D18" s="438" t="s">
         <v>202</v>
       </c>
-      <c r="E18" s="441">
+      <c r="E18" s="438">
         <v>1</v>
       </c>
       <c r="F18" s="234" t="str">
@@ -10308,68 +10308,68 @@
       <c r="H18" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="I18" s="439" t="s">
+      <c r="I18" s="440" t="s">
         <v>203</v>
       </c>
-      <c r="J18" s="356"/>
-      <c r="K18" s="439" t="s">
+      <c r="J18" s="334"/>
+      <c r="K18" s="440" t="s">
         <v>203</v>
       </c>
-      <c r="L18" s="368"/>
-      <c r="M18" s="356"/>
+      <c r="L18" s="337"/>
+      <c r="M18" s="334"/>
       <c r="N18" s="202"/>
     </row>
     <row r="19" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="200"/>
-      <c r="B19" s="419"/>
-      <c r="C19" s="419"/>
-      <c r="D19" s="419"/>
-      <c r="E19" s="419"/>
+      <c r="B19" s="339"/>
+      <c r="C19" s="339"/>
+      <c r="D19" s="339"/>
+      <c r="E19" s="339"/>
       <c r="F19" s="234"/>
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
-      <c r="I19" s="439"/>
-      <c r="J19" s="356"/>
-      <c r="K19" s="439"/>
-      <c r="L19" s="368"/>
-      <c r="M19" s="356"/>
+      <c r="I19" s="440"/>
+      <c r="J19" s="334"/>
+      <c r="K19" s="440"/>
+      <c r="L19" s="337"/>
+      <c r="M19" s="334"/>
       <c r="N19" s="202"/>
     </row>
     <row r="20" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="200"/>
-      <c r="B20" s="419"/>
-      <c r="C20" s="419"/>
-      <c r="D20" s="419"/>
-      <c r="E20" s="419"/>
+      <c r="B20" s="339"/>
+      <c r="C20" s="339"/>
+      <c r="D20" s="339"/>
+      <c r="E20" s="339"/>
       <c r="F20" s="234"/>
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
-      <c r="I20" s="439"/>
-      <c r="J20" s="356"/>
-      <c r="K20" s="439"/>
-      <c r="L20" s="368"/>
-      <c r="M20" s="356"/>
+      <c r="I20" s="440"/>
+      <c r="J20" s="334"/>
+      <c r="K20" s="440"/>
+      <c r="L20" s="337"/>
+      <c r="M20" s="334"/>
       <c r="N20" s="202"/>
     </row>
     <row r="21" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="200"/>
-      <c r="B21" s="419"/>
-      <c r="C21" s="419"/>
-      <c r="D21" s="419"/>
-      <c r="E21" s="419"/>
+      <c r="B21" s="339"/>
+      <c r="C21" s="339"/>
+      <c r="D21" s="339"/>
+      <c r="E21" s="339"/>
       <c r="F21" s="234"/>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="439"/>
-      <c r="J21" s="356"/>
-      <c r="K21" s="439"/>
-      <c r="L21" s="368"/>
-      <c r="M21" s="356"/>
+      <c r="I21" s="440"/>
+      <c r="J21" s="334"/>
+      <c r="K21" s="440"/>
+      <c r="L21" s="337"/>
+      <c r="M21" s="334"/>
       <c r="N21" s="202"/>
     </row>
     <row r="22" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="200"/>
-      <c r="B22" s="419"/>
+      <c r="B22" s="339"/>
       <c r="C22" s="56" t="s">
         <v>204</v>
       </c>
@@ -10389,7 +10389,7 @@
     </row>
     <row r="23" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="200"/>
-      <c r="B23" s="419"/>
+      <c r="B23" s="339"/>
       <c r="C23" s="56" t="s">
         <v>206</v>
       </c>
@@ -10415,7 +10415,7 @@
     </row>
     <row r="24" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="200"/>
-      <c r="B24" s="419"/>
+      <c r="B24" s="339"/>
       <c r="C24" s="45" t="s">
         <v>209</v>
       </c>
@@ -10433,7 +10433,7 @@
     </row>
     <row r="25" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="200"/>
-      <c r="B25" s="419"/>
+      <c r="B25" s="339"/>
       <c r="C25" s="239"/>
       <c r="D25" s="25" t="s">
         <v>210</v>
@@ -10459,7 +10459,7 @@
     </row>
     <row r="26" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="200"/>
-      <c r="B26" s="419"/>
+      <c r="B26" s="339"/>
       <c r="C26" s="239"/>
       <c r="D26" s="25" t="s">
         <v>213</v>
@@ -10485,7 +10485,7 @@
     </row>
     <row r="27" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="200"/>
-      <c r="B27" s="419"/>
+      <c r="B27" s="339"/>
       <c r="C27" s="239"/>
       <c r="D27" s="25" t="s">
         <v>214</v>
@@ -10510,7 +10510,7 @@
     </row>
     <row r="28" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="200"/>
-      <c r="B28" s="419"/>
+      <c r="B28" s="339"/>
       <c r="C28" s="239"/>
       <c r="D28" s="25" t="s">
         <v>215</v>
@@ -10536,7 +10536,7 @@
     </row>
     <row r="29" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="200"/>
-      <c r="B29" s="419"/>
+      <c r="B29" s="339"/>
       <c r="C29" s="239"/>
       <c r="D29" s="25" t="s">
         <v>216</v>
@@ -10562,7 +10562,7 @@
     </row>
     <row r="30" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="200"/>
-      <c r="B30" s="419"/>
+      <c r="B30" s="339"/>
       <c r="C30" s="239"/>
       <c r="D30" s="25" t="s">
         <v>217</v>
@@ -10587,7 +10587,7 @@
     </row>
     <row r="31" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="200"/>
-      <c r="B31" s="410"/>
+      <c r="B31" s="340"/>
       <c r="C31" s="30"/>
       <c r="D31" s="154" t="s">
         <v>218</v>
@@ -10605,7 +10605,7 @@
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="200"/>
-      <c r="B32" s="438" t="s">
+      <c r="B32" s="449" t="s">
         <v>219</v>
       </c>
       <c r="C32" s="56" t="s">
@@ -10630,7 +10630,7 @@
     </row>
     <row r="33" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
-      <c r="B33" s="419"/>
+      <c r="B33" s="339"/>
       <c r="C33" s="45"/>
       <c r="D33" s="27" t="s">
         <v>222</v>
@@ -10648,7 +10648,7 @@
     </row>
     <row r="34" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="200"/>
-      <c r="B34" s="419"/>
+      <c r="B34" s="339"/>
       <c r="C34" s="239"/>
       <c r="E34" s="1" t="s">
         <v>223</v>
@@ -10676,7 +10676,7 @@
     </row>
     <row r="35" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="200"/>
-      <c r="B35" s="419"/>
+      <c r="B35" s="339"/>
       <c r="C35" s="30"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2" t="s">
@@ -10708,7 +10708,7 @@
     </row>
     <row r="36" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="200"/>
-      <c r="B36" s="419"/>
+      <c r="B36" s="339"/>
       <c r="C36" s="56" t="s">
         <v>225</v>
       </c>
@@ -10726,7 +10726,7 @@
     </row>
     <row r="37" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="200"/>
-      <c r="B37" s="419"/>
+      <c r="B37" s="339"/>
       <c r="C37" s="45"/>
       <c r="D37" s="246" t="s">
         <v>226</v>
@@ -10746,7 +10746,7 @@
     </row>
     <row r="38" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="200"/>
-      <c r="B38" s="419"/>
+      <c r="B38" s="339"/>
       <c r="C38" s="239"/>
       <c r="D38" s="1" t="s">
         <v>227</v>
@@ -10762,7 +10762,7 @@
     </row>
     <row r="39" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="200"/>
-      <c r="B39" s="419"/>
+      <c r="B39" s="339"/>
       <c r="C39" s="239"/>
       <c r="D39" s="1" t="s">
         <v>228</v>
@@ -10776,7 +10776,7 @@
     </row>
     <row r="40" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="200"/>
-      <c r="B40" s="419"/>
+      <c r="B40" s="339"/>
       <c r="C40" s="239"/>
       <c r="E40" s="1" t="s">
         <v>229</v>
@@ -10792,7 +10792,7 @@
     </row>
     <row r="41" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="200"/>
-      <c r="B41" s="419"/>
+      <c r="B41" s="339"/>
       <c r="C41" s="239"/>
       <c r="E41" s="1" t="s">
         <v>230</v>
@@ -10808,7 +10808,7 @@
     </row>
     <row r="42" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="200"/>
-      <c r="B42" s="419"/>
+      <c r="B42" s="339"/>
       <c r="C42" s="239"/>
       <c r="E42" s="1" t="s">
         <v>231</v>
@@ -10824,7 +10824,7 @@
     </row>
     <row r="43" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="200"/>
-      <c r="B43" s="419"/>
+      <c r="B43" s="339"/>
       <c r="C43" s="239"/>
       <c r="E43" s="1" t="s">
         <v>232</v>
@@ -10840,7 +10840,7 @@
     </row>
     <row r="44" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="200"/>
-      <c r="B44" s="419"/>
+      <c r="B44" s="339"/>
       <c r="C44" s="239"/>
       <c r="E44" s="1" t="s">
         <v>233</v>
@@ -10856,7 +10856,7 @@
     </row>
     <row r="45" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="200"/>
-      <c r="B45" s="419"/>
+      <c r="B45" s="339"/>
       <c r="C45" s="239"/>
       <c r="E45" s="1" t="s">
         <v>234</v>
@@ -10872,7 +10872,7 @@
     </row>
     <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="200"/>
-      <c r="B46" s="419"/>
+      <c r="B46" s="339"/>
       <c r="C46" s="239"/>
       <c r="E46" s="1" t="s">
         <v>235</v>
@@ -10888,7 +10888,7 @@
     </row>
     <row r="47" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="200"/>
-      <c r="B47" s="419"/>
+      <c r="B47" s="339"/>
       <c r="C47" s="239"/>
       <c r="E47" s="1" t="s">
         <v>236</v>
@@ -10904,7 +10904,7 @@
     </row>
     <row r="48" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="200"/>
-      <c r="B48" s="419"/>
+      <c r="B48" s="339"/>
       <c r="C48" s="239"/>
       <c r="D48" s="1" t="s">
         <v>237</v>
@@ -10920,7 +10920,7 @@
     </row>
     <row r="49" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="200"/>
-      <c r="B49" s="419"/>
+      <c r="B49" s="339"/>
       <c r="C49" s="248"/>
       <c r="D49" s="1" t="s">
         <v>238</v>
@@ -10934,7 +10934,7 @@
     </row>
     <row r="50" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="200"/>
-      <c r="B50" s="419"/>
+      <c r="B50" s="339"/>
       <c r="C50" s="239"/>
       <c r="E50" s="1" t="s">
         <v>239</v>
@@ -10950,7 +10950,7 @@
     </row>
     <row r="51" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="200"/>
-      <c r="B51" s="419"/>
+      <c r="B51" s="339"/>
       <c r="C51" s="239"/>
       <c r="E51" s="1" t="s">
         <v>240</v>
@@ -10966,7 +10966,7 @@
     </row>
     <row r="52" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="200"/>
-      <c r="B52" s="419"/>
+      <c r="B52" s="339"/>
       <c r="C52" s="239"/>
       <c r="E52" s="1" t="s">
         <v>241</v>
@@ -10982,7 +10982,7 @@
     </row>
     <row r="53" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="200"/>
-      <c r="B53" s="419"/>
+      <c r="B53" s="339"/>
       <c r="C53" s="239"/>
       <c r="E53" s="1" t="s">
         <v>242</v>
@@ -10998,7 +10998,7 @@
     </row>
     <row r="54" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="200"/>
-      <c r="B54" s="419"/>
+      <c r="B54" s="339"/>
       <c r="C54" s="239"/>
       <c r="E54" s="1" t="s">
         <v>243</v>
@@ -11014,7 +11014,7 @@
     </row>
     <row r="55" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="200"/>
-      <c r="B55" s="419"/>
+      <c r="B55" s="339"/>
       <c r="C55" s="30"/>
       <c r="D55" s="2" t="s">
         <v>244</v>
@@ -11034,7 +11034,7 @@
     </row>
     <row r="56" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="200"/>
-      <c r="B56" s="419"/>
+      <c r="B56" s="339"/>
       <c r="C56" s="56" t="s">
         <v>245</v>
       </c>
@@ -11057,7 +11057,7 @@
     </row>
     <row r="57" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="200"/>
-      <c r="B57" s="419"/>
+      <c r="B57" s="339"/>
       <c r="C57" s="45" t="s">
         <v>246</v>
       </c>
@@ -11077,7 +11077,7 @@
     </row>
     <row r="58" spans="1:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="200"/>
-      <c r="B58" s="419"/>
+      <c r="B58" s="339"/>
       <c r="C58" s="239" t="s">
         <v>247</v>
       </c>
@@ -11090,7 +11090,7 @@
     </row>
     <row r="59" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="200"/>
-      <c r="B59" s="419"/>
+      <c r="B59" s="339"/>
       <c r="C59" s="239"/>
       <c r="E59" s="1" t="s">
         <v>248</v>
@@ -11106,7 +11106,7 @@
     </row>
     <row r="60" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="200"/>
-      <c r="B60" s="419"/>
+      <c r="B60" s="339"/>
       <c r="C60" s="239"/>
       <c r="E60" s="1" t="s">
         <v>249</v>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="61" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="200"/>
-      <c r="B61" s="419"/>
+      <c r="B61" s="339"/>
       <c r="C61" s="239"/>
       <c r="E61" s="1" t="s">
         <v>250</v>
@@ -11138,7 +11138,7 @@
     </row>
     <row r="62" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="200"/>
-      <c r="B62" s="419"/>
+      <c r="B62" s="339"/>
       <c r="C62" s="239"/>
       <c r="E62" s="1" t="s">
         <v>251</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="63" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="200"/>
-      <c r="B63" s="419"/>
+      <c r="B63" s="339"/>
       <c r="C63" s="56" t="s">
         <v>252</v>
       </c>
@@ -11177,7 +11177,7 @@
     </row>
     <row r="64" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="200"/>
-      <c r="B64" s="419"/>
+      <c r="B64" s="339"/>
       <c r="C64" s="45" t="s">
         <v>253</v>
       </c>
@@ -11201,7 +11201,7 @@
     </row>
     <row r="65" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="200"/>
-      <c r="B65" s="419"/>
+      <c r="B65" s="339"/>
       <c r="C65" s="30" t="s">
         <v>254</v>
       </c>
@@ -11225,7 +11225,7 @@
     </row>
     <row r="66" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="200"/>
-      <c r="B66" s="419"/>
+      <c r="B66" s="339"/>
       <c r="C66" s="56" t="s">
         <v>255</v>
       </c>
@@ -11248,7 +11248,7 @@
     </row>
     <row r="67" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="200"/>
-      <c r="B67" s="410"/>
+      <c r="B67" s="340"/>
       <c r="C67" s="56" t="s">
         <v>256</v>
       </c>
@@ -11290,30 +11290,6 @@
     <row r="69" spans="1:16" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="D13:D17"/>
-    <mergeCell ref="I15:J17"/>
-    <mergeCell ref="G13:M14"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="F13:F17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="G12:M12"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G7:M7"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="H9:M9"/>
     <mergeCell ref="B32:B67"/>
     <mergeCell ref="B11:B31"/>
     <mergeCell ref="I18:J18"/>
@@ -11330,6 +11306,30 @@
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="K21:M21"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="F13:F17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="G12:M12"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G7:M7"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="I15:J17"/>
+    <mergeCell ref="G13:M14"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="C18:C21"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -11360,39 +11360,39 @@
       <c r="B1" s="453" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
-      <c r="H1" s="346"/>
-      <c r="I1" s="346"/>
-      <c r="J1" s="346"/>
-      <c r="K1" s="346"/>
-      <c r="L1" s="346"/>
-      <c r="M1" s="346"/>
-      <c r="N1" s="346"/>
+      <c r="C1" s="355"/>
+      <c r="D1" s="355"/>
+      <c r="E1" s="355"/>
+      <c r="F1" s="355"/>
+      <c r="G1" s="355"/>
+      <c r="H1" s="355"/>
+      <c r="I1" s="355"/>
+      <c r="J1" s="355"/>
+      <c r="K1" s="355"/>
+      <c r="L1" s="355"/>
+      <c r="M1" s="355"/>
+      <c r="N1" s="355"/>
       <c r="O1" s="454"/>
       <c r="P1" s="199"/>
     </row>
     <row r="2" spans="1:56" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="426" t="s">
+      <c r="B2" s="436" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="364"/>
-      <c r="D2" s="364"/>
-      <c r="E2" s="364"/>
-      <c r="F2" s="364"/>
-      <c r="G2" s="364"/>
-      <c r="H2" s="364"/>
-      <c r="I2" s="364"/>
-      <c r="J2" s="364"/>
-      <c r="K2" s="364"/>
-      <c r="L2" s="364"/>
-      <c r="M2" s="364"/>
-      <c r="N2" s="364"/>
-      <c r="O2" s="375"/>
+      <c r="C2" s="344"/>
+      <c r="D2" s="344"/>
+      <c r="E2" s="344"/>
+      <c r="F2" s="344"/>
+      <c r="G2" s="344"/>
+      <c r="H2" s="344"/>
+      <c r="I2" s="344"/>
+      <c r="J2" s="344"/>
+      <c r="K2" s="344"/>
+      <c r="L2" s="344"/>
+      <c r="M2" s="344"/>
+      <c r="N2" s="344"/>
+      <c r="O2" s="345"/>
       <c r="P2" s="202"/>
     </row>
     <row r="3" spans="1:56" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -11400,16 +11400,16 @@
       <c r="B3" s="457" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="372"/>
-      <c r="D3" s="372"/>
-      <c r="E3" s="372"/>
-      <c r="F3" s="372"/>
-      <c r="G3" s="372"/>
-      <c r="H3" s="372"/>
-      <c r="I3" s="372"/>
-      <c r="J3" s="372"/>
-      <c r="K3" s="372"/>
-      <c r="L3" s="373"/>
+      <c r="C3" s="342"/>
+      <c r="D3" s="342"/>
+      <c r="E3" s="342"/>
+      <c r="F3" s="342"/>
+      <c r="G3" s="342"/>
+      <c r="H3" s="342"/>
+      <c r="I3" s="342"/>
+      <c r="J3" s="342"/>
+      <c r="K3" s="342"/>
+      <c r="L3" s="343"/>
       <c r="M3" s="259" t="s">
         <v>3</v>
       </c>
@@ -11425,39 +11425,39 @@
       <c r="B4" s="459" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="372"/>
+      <c r="C4" s="342"/>
       <c r="D4" s="455" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E4" s="372"/>
-      <c r="F4" s="372"/>
-      <c r="G4" s="372"/>
-      <c r="H4" s="372"/>
-      <c r="I4" s="372"/>
-      <c r="J4" s="372"/>
-      <c r="K4" s="372"/>
-      <c r="L4" s="373"/>
-      <c r="M4" s="415" t="s">
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="342"/>
+      <c r="J4" s="342"/>
+      <c r="K4" s="342"/>
+      <c r="L4" s="343"/>
+      <c r="M4" s="356" t="s">
         <v>259</v>
       </c>
-      <c r="N4" s="372"/>
-      <c r="O4" s="373"/>
+      <c r="N4" s="342"/>
+      <c r="O4" s="343"/>
       <c r="P4" s="202"/>
     </row>
     <row r="5" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="374"/>
-      <c r="C5" s="364"/>
-      <c r="D5" s="364"/>
-      <c r="E5" s="364"/>
-      <c r="F5" s="364"/>
-      <c r="G5" s="364"/>
-      <c r="H5" s="364"/>
-      <c r="I5" s="364"/>
-      <c r="J5" s="364"/>
-      <c r="K5" s="364"/>
-      <c r="L5" s="375"/>
+      <c r="B5" s="348"/>
+      <c r="C5" s="344"/>
+      <c r="D5" s="344"/>
+      <c r="E5" s="344"/>
+      <c r="F5" s="344"/>
+      <c r="G5" s="344"/>
+      <c r="H5" s="344"/>
+      <c r="I5" s="344"/>
+      <c r="J5" s="344"/>
+      <c r="K5" s="344"/>
+      <c r="L5" s="345"/>
       <c r="M5" s="75" t="s">
         <v>6</v>
       </c>
@@ -11470,24 +11470,24 @@
     </row>
     <row r="6" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="432" t="s">
+      <c r="B6" s="431" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="368"/>
-      <c r="D6" s="368"/>
-      <c r="E6" s="368"/>
-      <c r="F6" s="368"/>
-      <c r="G6" s="356"/>
-      <c r="H6" s="432" t="s">
+      <c r="C6" s="337"/>
+      <c r="D6" s="337"/>
+      <c r="E6" s="337"/>
+      <c r="F6" s="337"/>
+      <c r="G6" s="334"/>
+      <c r="H6" s="431" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="368"/>
-      <c r="J6" s="368"/>
-      <c r="K6" s="368"/>
-      <c r="L6" s="368"/>
-      <c r="M6" s="368"/>
-      <c r="N6" s="368"/>
-      <c r="O6" s="356"/>
+      <c r="I6" s="337"/>
+      <c r="J6" s="337"/>
+      <c r="K6" s="337"/>
+      <c r="L6" s="337"/>
+      <c r="M6" s="337"/>
+      <c r="N6" s="337"/>
+      <c r="O6" s="334"/>
       <c r="P6" s="202"/>
     </row>
     <row r="7" spans="1:56" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -11553,7 +11553,7 @@
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="L9" s="380"/>
+      <c r="L9" s="397"/>
       <c r="M9" s="67" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -11570,8 +11570,8 @@
       <c r="C10" s="464" t="s">
         <v>261</v>
       </c>
-      <c r="D10" s="372"/>
-      <c r="E10" s="372"/>
+      <c r="D10" s="342"/>
+      <c r="E10" s="342"/>
       <c r="F10" s="461" t="s">
         <v>262</v>
       </c>
@@ -11584,13 +11584,13 @@
       <c r="M10" s="456" t="s">
         <v>263</v>
       </c>
-      <c r="N10" s="368"/>
-      <c r="O10" s="356"/>
+      <c r="N10" s="337"/>
+      <c r="O10" s="334"/>
       <c r="P10" s="201"/>
     </row>
     <row r="11" spans="1:56" s="10" customFormat="1" ht="105" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
-      <c r="B11" s="410"/>
+      <c r="B11" s="340"/>
       <c r="C11" s="166" t="s">
         <v>264</v>
       </c>
@@ -16004,45 +16004,45 @@
   <sheetData>
     <row r="1" spans="1:11" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="369"/>
-      <c r="C1" s="370"/>
-      <c r="D1" s="370"/>
-      <c r="E1" s="370"/>
-      <c r="F1" s="370"/>
-      <c r="G1" s="370"/>
-      <c r="H1" s="370"/>
-      <c r="I1" s="370"/>
-      <c r="J1" s="370"/>
+      <c r="B1" s="409"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
       <c r="K1" s="199"/>
     </row>
     <row r="2" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="435" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="372"/>
-      <c r="D2" s="372"/>
-      <c r="E2" s="372"/>
-      <c r="F2" s="372"/>
-      <c r="G2" s="372"/>
-      <c r="H2" s="372"/>
-      <c r="I2" s="372"/>
-      <c r="J2" s="373"/>
+      <c r="B2" s="424" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
+      <c r="J2" s="343"/>
       <c r="K2" s="202"/>
     </row>
     <row r="3" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="426" t="s">
+      <c r="B3" s="436" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="375"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
+      <c r="F3" s="344"/>
+      <c r="G3" s="344"/>
+      <c r="H3" s="344"/>
+      <c r="I3" s="344"/>
+      <c r="J3" s="345"/>
       <c r="K3" s="202"/>
     </row>
     <row r="4" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -16050,12 +16050,12 @@
       <c r="B4" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C4" s="368"/>
-      <c r="D4" s="368"/>
-      <c r="E4" s="368"/>
-      <c r="F4" s="368"/>
-      <c r="G4" s="368"/>
-      <c r="H4" s="356"/>
+      <c r="C4" s="337"/>
+      <c r="D4" s="337"/>
+      <c r="E4" s="337"/>
+      <c r="F4" s="337"/>
+      <c r="G4" s="337"/>
+      <c r="H4" s="334"/>
       <c r="I4" s="144" t="s">
         <v>3</v>
       </c>
@@ -16074,26 +16074,26 @@
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="D5" s="372"/>
-      <c r="E5" s="372"/>
-      <c r="F5" s="372"/>
-      <c r="G5" s="372"/>
-      <c r="H5" s="373"/>
-      <c r="I5" s="415" t="s">
+      <c r="D5" s="342"/>
+      <c r="E5" s="342"/>
+      <c r="F5" s="342"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="343"/>
+      <c r="I5" s="356" t="s">
         <v>259</v>
       </c>
-      <c r="J5" s="373"/>
+      <c r="J5" s="343"/>
       <c r="K5" s="202"/>
     </row>
     <row r="6" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="374"/>
-      <c r="C6" s="364"/>
-      <c r="D6" s="364"/>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
-      <c r="G6" s="364"/>
-      <c r="H6" s="375"/>
+      <c r="B6" s="348"/>
+      <c r="C6" s="344"/>
+      <c r="D6" s="344"/>
+      <c r="E6" s="344"/>
+      <c r="F6" s="344"/>
+      <c r="G6" s="344"/>
+      <c r="H6" s="345"/>
       <c r="I6" s="75" t="s">
         <v>6</v>
       </c>
@@ -16108,16 +16108,16 @@
       <c r="B7" s="465" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
-      <c r="E7" s="368"/>
-      <c r="F7" s="356"/>
+      <c r="C7" s="337"/>
+      <c r="D7" s="337"/>
+      <c r="E7" s="337"/>
+      <c r="F7" s="334"/>
       <c r="G7" s="465" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="368"/>
-      <c r="I7" s="368"/>
-      <c r="J7" s="356"/>
+      <c r="H7" s="337"/>
+      <c r="I7" s="337"/>
+      <c r="J7" s="334"/>
       <c r="K7" s="202"/>
     </row>
     <row r="8" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -16187,18 +16187,18 @@
     <row r="11" spans="1:11" s="10" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
       <c r="B11" s="164"/>
-      <c r="C11" s="445" t="s">
+      <c r="C11" s="441" t="s">
         <v>295</v>
       </c>
-      <c r="D11" s="368"/>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
-      <c r="G11" s="356"/>
+      <c r="D11" s="337"/>
+      <c r="E11" s="337"/>
+      <c r="F11" s="337"/>
+      <c r="G11" s="334"/>
       <c r="H11" s="164"/>
       <c r="I11" s="466" t="s">
         <v>164</v>
       </c>
-      <c r="J11" s="439" t="s">
+      <c r="J11" s="440" t="s">
         <v>159</v>
       </c>
       <c r="K11" s="201"/>
@@ -16226,8 +16226,8 @@
       <c r="H12" s="164" t="s">
         <v>302</v>
       </c>
-      <c r="I12" s="419"/>
-      <c r="J12" s="410"/>
+      <c r="I12" s="339"/>
+      <c r="J12" s="340"/>
       <c r="K12" s="201"/>
     </row>
     <row r="13" spans="1:11" s="10" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -16253,7 +16253,7 @@
       <c r="H13" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="I13" s="410"/>
+      <c r="I13" s="340"/>
       <c r="J13" s="167"/>
       <c r="K13" s="201"/>
     </row>
@@ -18724,54 +18724,54 @@
   <sheetData>
     <row r="1" spans="1:14" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="369"/>
-      <c r="C1" s="370"/>
-      <c r="D1" s="370"/>
-      <c r="E1" s="370"/>
-      <c r="F1" s="370"/>
-      <c r="G1" s="370"/>
-      <c r="H1" s="370"/>
-      <c r="I1" s="370"/>
-      <c r="J1" s="370"/>
-      <c r="K1" s="370"/>
-      <c r="L1" s="370"/>
-      <c r="M1" s="370"/>
+      <c r="B1" s="409"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
+      <c r="K1" s="410"/>
+      <c r="L1" s="410"/>
+      <c r="M1" s="410"/>
       <c r="N1" s="199"/>
     </row>
     <row r="2" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="435" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="372"/>
-      <c r="D2" s="372"/>
-      <c r="E2" s="372"/>
-      <c r="F2" s="372"/>
-      <c r="G2" s="372"/>
-      <c r="H2" s="372"/>
-      <c r="I2" s="372"/>
-      <c r="J2" s="372"/>
-      <c r="K2" s="372"/>
-      <c r="L2" s="372"/>
-      <c r="M2" s="373"/>
+      <c r="B2" s="424" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
+      <c r="J2" s="342"/>
+      <c r="K2" s="342"/>
+      <c r="L2" s="342"/>
+      <c r="M2" s="343"/>
       <c r="N2" s="202"/>
     </row>
     <row r="3" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="426" t="s">
+      <c r="B3" s="436" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
-      <c r="L3" s="364"/>
-      <c r="M3" s="375"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
+      <c r="F3" s="344"/>
+      <c r="G3" s="344"/>
+      <c r="H3" s="344"/>
+      <c r="I3" s="344"/>
+      <c r="J3" s="344"/>
+      <c r="K3" s="344"/>
+      <c r="L3" s="344"/>
+      <c r="M3" s="345"/>
       <c r="N3" s="202"/>
     </row>
     <row r="4" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18779,14 +18779,14 @@
       <c r="B4" s="465" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="368"/>
-      <c r="D4" s="368"/>
-      <c r="E4" s="368"/>
-      <c r="F4" s="368"/>
-      <c r="G4" s="368"/>
-      <c r="H4" s="368"/>
-      <c r="I4" s="368"/>
-      <c r="J4" s="356"/>
+      <c r="C4" s="337"/>
+      <c r="D4" s="337"/>
+      <c r="E4" s="337"/>
+      <c r="F4" s="337"/>
+      <c r="G4" s="337"/>
+      <c r="H4" s="337"/>
+      <c r="I4" s="337"/>
+      <c r="J4" s="334"/>
       <c r="K4" s="144" t="s">
         <v>3</v>
       </c>
@@ -18801,35 +18801,35 @@
       <c r="B5" s="459" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="372"/>
-      <c r="D5" s="421" t="str">
+      <c r="C5" s="342"/>
+      <c r="D5" s="341" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="372"/>
-      <c r="F5" s="372"/>
-      <c r="G5" s="372"/>
-      <c r="H5" s="372"/>
-      <c r="I5" s="372"/>
-      <c r="J5" s="373"/>
-      <c r="K5" s="415" t="s">
+      <c r="E5" s="342"/>
+      <c r="F5" s="342"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="342"/>
+      <c r="I5" s="342"/>
+      <c r="J5" s="343"/>
+      <c r="K5" s="356" t="s">
         <v>259</v>
       </c>
-      <c r="L5" s="372"/>
-      <c r="M5" s="373"/>
+      <c r="L5" s="342"/>
+      <c r="M5" s="343"/>
       <c r="N5" s="202"/>
     </row>
     <row r="6" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="374"/>
-      <c r="C6" s="364"/>
-      <c r="D6" s="364"/>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
-      <c r="G6" s="364"/>
-      <c r="H6" s="364"/>
-      <c r="I6" s="364"/>
-      <c r="J6" s="375"/>
+      <c r="B6" s="348"/>
+      <c r="C6" s="344"/>
+      <c r="D6" s="344"/>
+      <c r="E6" s="344"/>
+      <c r="F6" s="344"/>
+      <c r="G6" s="344"/>
+      <c r="H6" s="344"/>
+      <c r="I6" s="344"/>
+      <c r="J6" s="345"/>
       <c r="K6" s="75" t="s">
         <v>6</v>
       </c>
@@ -18845,19 +18845,19 @@
       <c r="B7" s="465" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
-      <c r="E7" s="368"/>
-      <c r="F7" s="368"/>
-      <c r="G7" s="356"/>
+      <c r="C7" s="337"/>
+      <c r="D7" s="337"/>
+      <c r="E7" s="337"/>
+      <c r="F7" s="337"/>
+      <c r="G7" s="334"/>
       <c r="H7" s="465" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="368"/>
-      <c r="J7" s="368"/>
-      <c r="K7" s="368"/>
-      <c r="L7" s="368"/>
-      <c r="M7" s="356"/>
+      <c r="I7" s="337"/>
+      <c r="J7" s="337"/>
+      <c r="K7" s="337"/>
+      <c r="L7" s="337"/>
+      <c r="M7" s="334"/>
       <c r="N7" s="202"/>
     </row>
     <row r="8" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18919,11 +18919,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="440" t="str">
+      <c r="J10" s="450" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="364"/>
+      <c r="K10" s="344"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -18933,18 +18933,18 @@
     <row r="11" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="249"/>
       <c r="B11" s="167"/>
-      <c r="C11" s="445" t="s">
+      <c r="C11" s="441" t="s">
         <v>295</v>
       </c>
-      <c r="D11" s="368"/>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
-      <c r="G11" s="356"/>
-      <c r="H11" s="445" t="s">
+      <c r="D11" s="337"/>
+      <c r="E11" s="337"/>
+      <c r="F11" s="337"/>
+      <c r="G11" s="334"/>
+      <c r="H11" s="441" t="s">
         <v>321</v>
       </c>
-      <c r="I11" s="368"/>
-      <c r="J11" s="356"/>
+      <c r="I11" s="337"/>
+      <c r="J11" s="334"/>
       <c r="K11" s="167"/>
       <c r="L11" s="466" t="s">
         <v>164</v>
@@ -18956,54 +18956,54 @@
     </row>
     <row r="12" spans="1:14" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="249"/>
-      <c r="B12" s="439" t="s">
+      <c r="B12" s="440" t="s">
         <v>296</v>
       </c>
-      <c r="C12" s="439" t="s">
+      <c r="C12" s="440" t="s">
         <v>297</v>
       </c>
-      <c r="D12" s="439" t="s">
+      <c r="D12" s="440" t="s">
         <v>298</v>
       </c>
-      <c r="E12" s="439" t="s">
+      <c r="E12" s="440" t="s">
         <v>299</v>
       </c>
-      <c r="F12" s="439" t="s">
+      <c r="F12" s="440" t="s">
         <v>300</v>
       </c>
-      <c r="G12" s="439" t="s">
+      <c r="G12" s="440" t="s">
         <v>322</v>
       </c>
-      <c r="H12" s="439" t="s">
+      <c r="H12" s="440" t="s">
         <v>323</v>
       </c>
-      <c r="I12" s="439" t="s">
+      <c r="I12" s="440" t="s">
         <v>324</v>
       </c>
-      <c r="J12" s="439" t="s">
+      <c r="J12" s="440" t="s">
         <v>325</v>
       </c>
-      <c r="K12" s="439" t="s">
+      <c r="K12" s="440" t="s">
         <v>326</v>
       </c>
-      <c r="L12" s="419"/>
-      <c r="M12" s="419"/>
+      <c r="L12" s="339"/>
+      <c r="M12" s="339"/>
       <c r="N12" s="201"/>
     </row>
     <row r="13" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="249"/>
-      <c r="B13" s="410"/>
-      <c r="C13" s="410"/>
-      <c r="D13" s="410"/>
-      <c r="E13" s="410"/>
-      <c r="F13" s="410"/>
-      <c r="G13" s="410"/>
-      <c r="H13" s="410"/>
-      <c r="I13" s="410"/>
-      <c r="J13" s="410"/>
-      <c r="K13" s="410"/>
-      <c r="L13" s="419"/>
-      <c r="M13" s="419"/>
+      <c r="B13" s="340"/>
+      <c r="C13" s="340"/>
+      <c r="D13" s="340"/>
+      <c r="E13" s="340"/>
+      <c r="F13" s="340"/>
+      <c r="G13" s="340"/>
+      <c r="H13" s="340"/>
+      <c r="I13" s="340"/>
+      <c r="J13" s="340"/>
+      <c r="K13" s="340"/>
+      <c r="L13" s="339"/>
+      <c r="M13" s="339"/>
       <c r="N13" s="201"/>
     </row>
     <row r="14" spans="1:14" s="10" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -19038,7 +19038,7 @@
       <c r="K14" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="L14" s="410"/>
+      <c r="L14" s="340"/>
       <c r="M14" s="167"/>
       <c r="N14" s="201"/>
     </row>
@@ -21999,6 +21999,14 @@
     <row r="81" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="D5:J6"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="L11:L14"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="H11:J11"/>
@@ -22015,14 +22023,6 @@
     <mergeCell ref="B3:M3"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="D5:J6"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
@@ -22052,87 +22052,87 @@
   <sheetData>
     <row r="1" spans="1:13" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="198"/>
-      <c r="B1" s="469"/>
-      <c r="C1" s="370"/>
-      <c r="D1" s="370"/>
-      <c r="E1" s="370"/>
-      <c r="F1" s="370"/>
-      <c r="G1" s="370"/>
-      <c r="H1" s="370"/>
-      <c r="I1" s="370"/>
-      <c r="J1" s="370"/>
-      <c r="K1" s="370"/>
-      <c r="L1" s="370"/>
+      <c r="B1" s="470"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
+      <c r="K1" s="410"/>
+      <c r="L1" s="410"/>
       <c r="M1" s="199"/>
     </row>
     <row r="2" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="200"/>
-      <c r="B2" s="435" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="372"/>
-      <c r="D2" s="372"/>
-      <c r="E2" s="372"/>
-      <c r="F2" s="372"/>
-      <c r="G2" s="372"/>
-      <c r="H2" s="372"/>
-      <c r="I2" s="372"/>
-      <c r="J2" s="372"/>
-      <c r="K2" s="372"/>
-      <c r="L2" s="373"/>
+      <c r="B2" s="424" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
+      <c r="J2" s="342"/>
+      <c r="K2" s="342"/>
+      <c r="L2" s="343"/>
       <c r="M2" s="202"/>
     </row>
     <row r="3" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="200"/>
-      <c r="B3" s="426" t="s">
+      <c r="B3" s="436" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
-      <c r="L3" s="375"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
+      <c r="F3" s="344"/>
+      <c r="G3" s="344"/>
+      <c r="H3" s="344"/>
+      <c r="I3" s="344"/>
+      <c r="J3" s="344"/>
+      <c r="K3" s="344"/>
+      <c r="L3" s="345"/>
       <c r="M3" s="202"/>
     </row>
     <row r="4" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="200"/>
-      <c r="B4" s="432" t="s">
+      <c r="B4" s="431" t="s">
         <v>333</v>
       </c>
-      <c r="C4" s="368"/>
-      <c r="D4" s="368"/>
-      <c r="E4" s="368"/>
-      <c r="F4" s="368"/>
-      <c r="G4" s="368"/>
-      <c r="H4" s="368"/>
-      <c r="I4" s="356"/>
+      <c r="C4" s="337"/>
+      <c r="D4" s="337"/>
+      <c r="E4" s="337"/>
+      <c r="F4" s="337"/>
+      <c r="G4" s="337"/>
+      <c r="H4" s="337"/>
+      <c r="I4" s="334"/>
       <c r="J4" s="475" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="368"/>
-      <c r="L4" s="356"/>
+      <c r="K4" s="337"/>
+      <c r="L4" s="334"/>
       <c r="M4" s="202"/>
     </row>
     <row r="5" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="200"/>
-      <c r="B5" s="451" t="s">
+      <c r="B5" s="439" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="373"/>
+      <c r="C5" s="343"/>
       <c r="D5" s="474" t="str">
         <f>('QUADRO I'!$D$5)</f>
         <v>{RUA}, {COMPLEMENTO}; {SETOR} - {CIDADE}</v>
       </c>
-      <c r="E5" s="372"/>
-      <c r="F5" s="372"/>
-      <c r="G5" s="372"/>
-      <c r="H5" s="372"/>
-      <c r="I5" s="373"/>
+      <c r="E5" s="342"/>
+      <c r="F5" s="342"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="342"/>
+      <c r="I5" s="343"/>
       <c r="J5" s="49" t="s">
         <v>6</v>
       </c>
@@ -22144,14 +22144,14 @@
     </row>
     <row r="6" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="200"/>
-      <c r="B6" s="374"/>
-      <c r="C6" s="375"/>
-      <c r="D6" s="374"/>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
-      <c r="G6" s="364"/>
-      <c r="H6" s="364"/>
-      <c r="I6" s="375"/>
+      <c r="B6" s="348"/>
+      <c r="C6" s="345"/>
+      <c r="D6" s="348"/>
+      <c r="E6" s="344"/>
+      <c r="F6" s="344"/>
+      <c r="G6" s="344"/>
+      <c r="H6" s="344"/>
+      <c r="I6" s="345"/>
       <c r="J6" s="31" t="s">
         <v>3</v>
       </c>
@@ -22163,21 +22163,21 @@
     </row>
     <row r="7" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="200"/>
-      <c r="B7" s="432" t="s">
+      <c r="B7" s="431" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
-      <c r="E7" s="368"/>
-      <c r="F7" s="368"/>
-      <c r="G7" s="356"/>
-      <c r="H7" s="432" t="s">
+      <c r="C7" s="337"/>
+      <c r="D7" s="337"/>
+      <c r="E7" s="337"/>
+      <c r="F7" s="337"/>
+      <c r="G7" s="334"/>
+      <c r="H7" s="431" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="368"/>
-      <c r="J7" s="368"/>
-      <c r="K7" s="368"/>
-      <c r="L7" s="356"/>
+      <c r="I7" s="337"/>
+      <c r="J7" s="337"/>
+      <c r="K7" s="337"/>
+      <c r="L7" s="334"/>
       <c r="M7" s="202"/>
     </row>
     <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -22237,11 +22237,11 @@
         <f>('QUADRO I'!$N$10)</f>
         <v>{DATA HOJE}</v>
       </c>
-      <c r="J10" s="440" t="str">
+      <c r="J10" s="450" t="str">
         <f>('QUADRO I'!$Q$10)</f>
         <v>Registro no CREA:</v>
       </c>
-      <c r="K10" s="364"/>
+      <c r="K10" s="344"/>
       <c r="L10" s="114" t="str">
         <f>('QUADRO I'!$S$10)</f>
         <v>{CREA}</v>
@@ -22372,39 +22372,39 @@
       <c r="B25" s="471" t="s">
         <v>340</v>
       </c>
-      <c r="C25" s="443"/>
-      <c r="D25" s="380"/>
-      <c r="E25" s="380"/>
-      <c r="F25" s="380"/>
-      <c r="G25" s="380"/>
-      <c r="H25" s="380"/>
-      <c r="I25" s="380"/>
-      <c r="J25" s="380"/>
-      <c r="K25" s="380"/>
-      <c r="L25" s="381"/>
+      <c r="C25" s="444"/>
+      <c r="D25" s="397"/>
+      <c r="E25" s="397"/>
+      <c r="F25" s="397"/>
+      <c r="G25" s="397"/>
+      <c r="H25" s="397"/>
+      <c r="I25" s="397"/>
+      <c r="J25" s="397"/>
+      <c r="K25" s="397"/>
+      <c r="L25" s="347"/>
       <c r="M25" s="202"/>
     </row>
     <row r="26" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="200"/>
-      <c r="B26" s="422"/>
-      <c r="C26" s="443"/>
-      <c r="D26" s="380"/>
-      <c r="E26" s="380"/>
-      <c r="F26" s="380"/>
-      <c r="G26" s="380"/>
-      <c r="H26" s="380"/>
-      <c r="I26" s="380"/>
-      <c r="J26" s="380"/>
-      <c r="K26" s="380"/>
-      <c r="L26" s="381"/>
+      <c r="B26" s="346"/>
+      <c r="C26" s="444"/>
+      <c r="D26" s="397"/>
+      <c r="E26" s="397"/>
+      <c r="F26" s="397"/>
+      <c r="G26" s="397"/>
+      <c r="H26" s="397"/>
+      <c r="I26" s="397"/>
+      <c r="J26" s="397"/>
+      <c r="K26" s="397"/>
+      <c r="L26" s="347"/>
       <c r="M26" s="202"/>
     </row>
     <row r="27" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="200"/>
-      <c r="B27" s="470" t="s">
+      <c r="B27" s="468" t="s">
         <v>341</v>
       </c>
-      <c r="C27" s="443"/>
+      <c r="C27" s="444"/>
       <c r="D27" s="324" t="e">
         <f>'QUADRO II'!F17</f>
         <v>#VALUE!</v>
@@ -22425,10 +22425,10 @@
     </row>
     <row r="28" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="200"/>
-      <c r="B28" s="470" t="s">
+      <c r="B28" s="468" t="s">
         <v>344</v>
       </c>
-      <c r="C28" s="443"/>
+      <c r="C28" s="444"/>
       <c r="D28" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22448,10 +22448,10 @@
     </row>
     <row r="29" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="200"/>
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="468" t="s">
         <v>345</v>
       </c>
-      <c r="C29" s="443"/>
+      <c r="C29" s="444"/>
       <c r="D29" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22471,10 +22471,10 @@
     </row>
     <row r="30" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="200"/>
-      <c r="B30" s="470" t="s">
+      <c r="B30" s="468" t="s">
         <v>346</v>
       </c>
-      <c r="C30" s="443"/>
+      <c r="C30" s="444"/>
       <c r="D30" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22494,10 +22494,10 @@
     </row>
     <row r="31" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="200"/>
-      <c r="B31" s="470" t="s">
+      <c r="B31" s="468" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="443"/>
+      <c r="C31" s="444"/>
       <c r="D31" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22517,10 +22517,10 @@
     </row>
     <row r="32" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="200"/>
-      <c r="B32" s="470" t="s">
+      <c r="B32" s="468" t="s">
         <v>348</v>
       </c>
-      <c r="C32" s="443"/>
+      <c r="C32" s="444"/>
       <c r="D32" s="324" t="e">
         <f>'QUADRO II'!#REF!</f>
         <v>#REF!</v>
@@ -22557,69 +22557,69 @@
       <c r="A35" s="200"/>
       <c r="B35" s="271"/>
       <c r="D35" s="473"/>
-      <c r="E35" s="380"/>
+      <c r="E35" s="397"/>
       <c r="L35" s="4"/>
       <c r="M35" s="202"/>
     </row>
     <row r="36" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="200"/>
-      <c r="B36" s="468" t="s">
+      <c r="B36" s="469" t="s">
         <v>350</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="373"/>
+      <c r="C36" s="342"/>
+      <c r="D36" s="342"/>
+      <c r="E36" s="342"/>
+      <c r="F36" s="343"/>
       <c r="G36" s="472"/>
-      <c r="H36" s="372"/>
-      <c r="I36" s="372"/>
-      <c r="J36" s="372"/>
-      <c r="K36" s="373"/>
+      <c r="H36" s="342"/>
+      <c r="I36" s="342"/>
+      <c r="J36" s="342"/>
+      <c r="K36" s="343"/>
       <c r="L36" s="4"/>
       <c r="M36" s="202"/>
     </row>
     <row r="37" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="200"/>
-      <c r="B37" s="422"/>
-      <c r="C37" s="443"/>
-      <c r="D37" s="380"/>
-      <c r="E37" s="380"/>
-      <c r="F37" s="381"/>
-      <c r="G37" s="422"/>
-      <c r="H37" s="380"/>
-      <c r="I37" s="380"/>
-      <c r="J37" s="380"/>
-      <c r="K37" s="381"/>
+      <c r="B37" s="346"/>
+      <c r="C37" s="444"/>
+      <c r="D37" s="397"/>
+      <c r="E37" s="397"/>
+      <c r="F37" s="347"/>
+      <c r="G37" s="346"/>
+      <c r="H37" s="397"/>
+      <c r="I37" s="397"/>
+      <c r="J37" s="397"/>
+      <c r="K37" s="347"/>
       <c r="L37" s="4"/>
       <c r="M37" s="202"/>
     </row>
     <row r="38" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="200"/>
-      <c r="B38" s="422"/>
-      <c r="C38" s="443"/>
-      <c r="D38" s="380"/>
-      <c r="E38" s="380"/>
-      <c r="F38" s="381"/>
-      <c r="G38" s="422"/>
-      <c r="H38" s="380"/>
-      <c r="I38" s="380"/>
-      <c r="J38" s="380"/>
-      <c r="K38" s="381"/>
+      <c r="B38" s="346"/>
+      <c r="C38" s="444"/>
+      <c r="D38" s="397"/>
+      <c r="E38" s="397"/>
+      <c r="F38" s="347"/>
+      <c r="G38" s="346"/>
+      <c r="H38" s="397"/>
+      <c r="I38" s="397"/>
+      <c r="J38" s="397"/>
+      <c r="K38" s="347"/>
       <c r="L38" s="4"/>
       <c r="M38" s="202"/>
     </row>
     <row r="39" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="200"/>
-      <c r="B39" s="374"/>
-      <c r="C39" s="364"/>
-      <c r="D39" s="364"/>
-      <c r="E39" s="364"/>
-      <c r="F39" s="375"/>
-      <c r="G39" s="374"/>
-      <c r="H39" s="364"/>
-      <c r="I39" s="364"/>
-      <c r="J39" s="364"/>
-      <c r="K39" s="375"/>
+      <c r="B39" s="348"/>
+      <c r="C39" s="344"/>
+      <c r="D39" s="344"/>
+      <c r="E39" s="344"/>
+      <c r="F39" s="345"/>
+      <c r="G39" s="348"/>
+      <c r="H39" s="344"/>
+      <c r="I39" s="344"/>
+      <c r="J39" s="344"/>
+      <c r="K39" s="345"/>
       <c r="L39" s="4"/>
       <c r="M39" s="202"/>
     </row>
@@ -22663,26 +22663,26 @@
     <row r="43" spans="1:13" ht="10.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B36:F39"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="H7:L7"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B25:L26"/>
     <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="G36:K39"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B4:I4"/>
-    <mergeCell ref="D35:E35"/>
     <mergeCell ref="D5:I6"/>
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B36:F39"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="G36:K39"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D35:E35"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
